--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB5246F-3655-426C-932D-120CEBDCE6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EE2656-A98F-4747-8846-90E9097A3B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="421" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="64">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -226,6 +226,9 @@
   </si>
   <si>
     <t>1.21.6 / 1.21.7</t>
+  </si>
+  <si>
+    <t>Added golden dandelion texture</t>
   </si>
 </sst>
 </file>
@@ -404,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -440,23 +443,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -474,6 +461,21 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -749,13 +751,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
       <c r="G1" s="7" t="s">
         <v>20</v>
       </c>
@@ -765,11 +767,11 @@
       <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
@@ -785,15 +787,15 @@
       <c r="K2" s="8"/>
     </row>
     <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="str">
+      <c r="A3" s="27" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5340</v>
-      </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
+        <v>v10.0.11_1-build-5343</v>
+      </c>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
       <c r="D3" s="9">
-        <f>SUM(2601,637,2026,27,49)</f>
-        <v>5340</v>
+        <f>SUM(2601,637,2026,27,52)</f>
+        <v>5343</v>
       </c>
       <c r="E3" s="17">
         <f>K4</f>
@@ -822,11 +824,11 @@
       <c r="B4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="28"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="22"/>
       <c r="G4" s="9" t="s">
         <v>13</v>
       </c>
@@ -838,22 +840,22 @@
       </c>
       <c r="J4" s="9">
         <f>D3</f>
-        <v>5340</v>
+        <v>5343</v>
       </c>
       <c r="K4" s="9">
         <v>26.1</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="29" t="s">
+      <c r="B5" s="8"/>
+      <c r="C5" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="31"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="25"/>
       <c r="G5" s="4" t="s">
         <v>8</v>
       </c>
@@ -866,10 +868,10 @@
       <c r="K5" s="14"/>
     </row>
     <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="25"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -886,7 +888,9 @@
       <c r="K6" s="14"/>
     </row>
     <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
+      <c r="A7" s="8" t="s">
+        <v>63</v>
+      </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -897,7 +901,7 @@
       </c>
       <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5340</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5343</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13"/>
@@ -954,7 +958,7 @@
       </c>
       <c r="I10" s="9">
         <f>J4</f>
-        <v>5340</v>
+        <v>5343</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>10</v>
@@ -1009,7 +1013,7 @@
       </c>
       <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5340</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5343</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="8"/>
@@ -1051,7 +1055,7 @@
       </c>
       <c r="I15" s="9">
         <f>I10</f>
-        <v>5340</v>
+        <v>5343</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>11</v>
@@ -1106,7 +1110,7 @@
       </c>
       <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5340</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5343</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="8"/>
@@ -1148,7 +1152,7 @@
       </c>
       <c r="I20" s="9">
         <f>I15</f>
-        <v>5340</v>
+        <v>5343</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>62</v>
@@ -1203,7 +1207,7 @@
       </c>
       <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5340</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5343</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="8"/>
@@ -1245,7 +1249,7 @@
       </c>
       <c r="I25" s="9">
         <f>I20</f>
-        <v>5340</v>
+        <v>5343</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>12</v>
@@ -1300,7 +1304,7 @@
       </c>
       <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5340</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5343</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="8"/>
@@ -1357,7 +1361,7 @@
       </c>
       <c r="I31" s="9">
         <f>I25</f>
-        <v>5340</v>
+        <v>5343</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>14</v>
@@ -1412,7 +1416,7 @@
       </c>
       <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5340</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5343</v>
       </c>
       <c r="I34" s="16"/>
       <c r="J34" s="8"/>
@@ -1469,7 +1473,7 @@
       </c>
       <c r="I37" s="9">
         <f>I31</f>
-        <v>5340</v>
+        <v>5343</v>
       </c>
       <c r="J37" s="9" t="s">
         <v>17</v>
@@ -1523,7 +1527,7 @@
       </c>
       <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5340</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5343</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="8"/>
@@ -1580,7 +1584,7 @@
       </c>
       <c r="I43" s="9">
         <f>I37</f>
-        <v>5340</v>
+        <v>5343</v>
       </c>
       <c r="J43" s="9" t="s">
         <v>18</v>
@@ -1634,7 +1638,7 @@
       </c>
       <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5340</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5343</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="8"/>
@@ -1706,7 +1710,7 @@
       </c>
       <c r="I50" s="9">
         <f>I43</f>
-        <v>5340</v>
+        <v>5343</v>
       </c>
       <c r="J50" s="9" t="s">
         <v>30</v>
@@ -1760,7 +1764,7 @@
       </c>
       <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5340</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5343</v>
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="8"/>
@@ -1817,7 +1821,7 @@
       </c>
       <c r="I56" s="9">
         <f>I50</f>
-        <v>5340</v>
+        <v>5343</v>
       </c>
       <c r="J56" s="9" t="s">
         <v>31</v>
@@ -1871,7 +1875,7 @@
       </c>
       <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5340</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5343</v>
       </c>
       <c r="I59" s="16"/>
       <c r="J59" s="8"/>
@@ -1928,7 +1932,7 @@
       </c>
       <c r="I62" s="9">
         <f>I56</f>
-        <v>5340</v>
+        <v>5343</v>
       </c>
       <c r="J62" s="9" t="s">
         <v>61</v>
@@ -1982,7 +1986,7 @@
       </c>
       <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5340</v>
+        <v>v7.11.3-Better_Default_7-build-5343</v>
       </c>
       <c r="I65" s="16"/>
       <c r="J65" s="8"/>
@@ -2009,12 +2013,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -2053,21 +2057,21 @@
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="22"/>
+      <c r="C5" s="29"/>
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="21" t="str">
+      <c r="B6" s="28" t="str">
         <f>A4 &amp; "." &amp; B4 &amp; "." &amp; C4 &amp; "-" &amp; B5</f>
         <v>v6.0.7-Better_Default_6</v>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="29"/>
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2107,21 +2111,21 @@
       <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="22"/>
+      <c r="C10" s="29"/>
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="21" t="str">
+      <c r="B11" s="28" t="str">
         <f>A9 &amp; "." &amp; B9 &amp; "." &amp; C9 &amp; "-" &amp; B10</f>
         <v>v1.4.0-Better_Default_5</v>
       </c>
-      <c r="C11" s="22"/>
+      <c r="C11" s="29"/>
       <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2161,21 +2165,21 @@
       <c r="A15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="29"/>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="21" t="str">
+      <c r="B16" s="28" t="str">
         <f>A14 &amp; "." &amp; B14 &amp; "." &amp; C14 &amp; "-" &amp; B15</f>
         <v>v1.3.0-Better_Default_4</v>
       </c>
-      <c r="C16" s="22"/>
+      <c r="C16" s="29"/>
       <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2215,21 +2219,21 @@
       <c r="A20" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="22"/>
+      <c r="C20" s="29"/>
       <c r="D20" s="1"/>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="21" t="str">
+      <c r="B21" s="28" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
         <v>v1.2.2-Better_Default_3</v>
       </c>
-      <c r="C21" s="22"/>
+      <c r="C21" s="29"/>
       <c r="D21" s="1"/>
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2269,21 +2273,21 @@
       <c r="A25" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="22"/>
+      <c r="C25" s="29"/>
       <c r="D25" s="1"/>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="21" t="str">
+      <c r="B26" s="28" t="str">
         <f>A24 &amp; "." &amp; B24 &amp; "." &amp; C24 &amp; "-" &amp; B25</f>
         <v>v1.2.1-Better_Default_3</v>
       </c>
-      <c r="C26" s="22"/>
+      <c r="C26" s="29"/>
       <c r="D26" s="1"/>
     </row>
     <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2323,21 +2327,21 @@
       <c r="A30" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="22"/>
+      <c r="C30" s="29"/>
       <c r="D30" s="1"/>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="21" t="str">
+      <c r="B31" s="28" t="str">
         <f>A29 &amp; "." &amp; B29 &amp; "." &amp; C29 &amp; "-" &amp; B30</f>
         <v>v1.2.0-Better_Default_2</v>
       </c>
-      <c r="C31" s="22"/>
+      <c r="C31" s="29"/>
       <c r="D31" s="1"/>
     </row>
     <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2377,21 +2381,21 @@
       <c r="A35" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="22"/>
+      <c r="C35" s="29"/>
       <c r="D35" s="1"/>
     </row>
     <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B36" s="21" t="str">
+      <c r="B36" s="28" t="str">
         <f>A34 &amp; "." &amp; B34 &amp; "." &amp; C34 &amp; "-" &amp; B35</f>
         <v>v1.1.1-Better_Default</v>
       </c>
-      <c r="C36" s="22"/>
+      <c r="C36" s="29"/>
       <c r="D36" s="1"/>
     </row>
     <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2431,21 +2435,21 @@
       <c r="A40" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="22"/>
+      <c r="C40" s="29"/>
       <c r="D40" s="1"/>
     </row>
     <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="21" t="str">
+      <c r="B41" s="28" t="str">
         <f>A39 &amp; "." &amp; B39 &amp; "." &amp; C39 &amp; "-" &amp; B40</f>
         <v>v1.1.0-Better_Default</v>
       </c>
-      <c r="C41" s="22"/>
+      <c r="C41" s="29"/>
       <c r="D41" s="1"/>
     </row>
   </sheetData>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EE2656-A98F-4747-8846-90E9097A3B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B215DA1B-C05F-4AA7-97AC-FA423FB2A3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="421" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="67">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -229,6 +229,15 @@
   </si>
   <si>
     <t>Added golden dandelion texture</t>
+  </si>
+  <si>
+    <t>Better_Default_3.1</t>
+  </si>
+  <si>
+    <t>Re-added classic cat sound</t>
+  </si>
+  <si>
+    <t>Crackers0106 (golden dandelion texture)</t>
   </si>
 </sst>
 </file>
@@ -747,7 +756,7 @@
   <dimension ref="A1:K65"/>
   <sheetFormatPr defaultColWidth="27.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="54.85546875" customWidth="1"/>
+    <col min="1" max="2" width="54.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
@@ -789,13 +798,13 @@
     <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5343</v>
+        <v>v10.0.11_1-build-5349-rt3</v>
       </c>
       <c r="B3" s="27"/>
       <c r="C3" s="27"/>
-      <c r="D3" s="9">
-        <f>SUM(2601,637,2026,27,52)</f>
-        <v>5343</v>
+      <c r="D3" s="9" t="str">
+        <f>SUM(2601,637,2026,27,58) &amp; "-rt3"</f>
+        <v>5349-rt3</v>
       </c>
       <c r="E3" s="17">
         <f>K4</f>
@@ -838,9 +847,9 @@
       <c r="I4" s="9">
         <v>1</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="9" t="str">
         <f>D3</f>
-        <v>5343</v>
+        <v>5349-rt3</v>
       </c>
       <c r="K4" s="9">
         <v>26.1</v>
@@ -850,7 +859,9 @@
       <c r="A5" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="8"/>
+      <c r="B5" s="8" t="s">
+        <v>66</v>
+      </c>
       <c r="C5" s="23" t="s">
         <v>3</v>
       </c>
@@ -901,14 +912,16 @@
       </c>
       <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5343</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5349-rt3</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13"/>
       <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
+      <c r="A8" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -956,9 +969,9 @@
       <c r="H10" s="9">
         <v>10</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="9" t="str">
         <f>J4</f>
-        <v>5343</v>
+        <v>5349-rt3</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>10</v>
@@ -1013,7 +1026,7 @@
       </c>
       <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5343</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5349-rt3</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="8"/>
@@ -1053,9 +1066,9 @@
       <c r="H15" s="9">
         <v>9</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="9" t="str">
         <f>I10</f>
-        <v>5343</v>
+        <v>5349-rt3</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>11</v>
@@ -1110,7 +1123,7 @@
       </c>
       <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5343</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5349-rt3</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="8"/>
@@ -1150,9 +1163,9 @@
       <c r="H20" s="9">
         <v>7</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="9" t="str">
         <f>I15</f>
-        <v>5343</v>
+        <v>5349-rt3</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>62</v>
@@ -1207,7 +1220,7 @@
       </c>
       <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5343</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5349-rt3</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="8"/>
@@ -1247,9 +1260,9 @@
       <c r="H25" s="9">
         <v>4</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="9" t="str">
         <f>I20</f>
-        <v>5343</v>
+        <v>5349-rt3</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>12</v>
@@ -1304,7 +1317,7 @@
       </c>
       <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5343</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5349-rt3</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="8"/>
@@ -1359,9 +1372,9 @@
       <c r="H31" s="9">
         <v>3</v>
       </c>
-      <c r="I31" s="9">
+      <c r="I31" s="9" t="str">
         <f>I25</f>
-        <v>5343</v>
+        <v>5349-rt3</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>14</v>
@@ -1416,7 +1429,7 @@
       </c>
       <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5343</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5349-rt3</v>
       </c>
       <c r="I34" s="16"/>
       <c r="J34" s="8"/>
@@ -1471,9 +1484,9 @@
       <c r="H37" s="9">
         <v>2</v>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="9" t="str">
         <f>I31</f>
-        <v>5343</v>
+        <v>5349-rt3</v>
       </c>
       <c r="J37" s="9" t="s">
         <v>17</v>
@@ -1527,7 +1540,7 @@
       </c>
       <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5343</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5349-rt3</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="8"/>
@@ -1582,9 +1595,9 @@
       <c r="H43" s="9">
         <v>1</v>
       </c>
-      <c r="I43" s="9">
+      <c r="I43" s="9" t="str">
         <f>I37</f>
-        <v>5343</v>
+        <v>5349-rt3</v>
       </c>
       <c r="J43" s="9" t="s">
         <v>18</v>
@@ -1638,7 +1651,7 @@
       </c>
       <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5343</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5349-rt3</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="8"/>
@@ -1708,9 +1721,9 @@
       <c r="H50" s="9">
         <v>32</v>
       </c>
-      <c r="I50" s="9">
+      <c r="I50" s="9" t="str">
         <f>I43</f>
-        <v>5343</v>
+        <v>5349-rt3</v>
       </c>
       <c r="J50" s="9" t="s">
         <v>30</v>
@@ -1764,7 +1777,7 @@
       </c>
       <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5343</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5349-rt3</v>
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="8"/>
@@ -1819,9 +1832,9 @@
       <c r="H56" s="9">
         <v>31</v>
       </c>
-      <c r="I56" s="9">
+      <c r="I56" s="9" t="str">
         <f>I50</f>
-        <v>5343</v>
+        <v>5349-rt3</v>
       </c>
       <c r="J56" s="9" t="s">
         <v>31</v>
@@ -1875,7 +1888,7 @@
       </c>
       <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5343</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5349-rt3</v>
       </c>
       <c r="I59" s="16"/>
       <c r="J59" s="8"/>
@@ -1930,9 +1943,9 @@
       <c r="H62" s="9">
         <v>3</v>
       </c>
-      <c r="I62" s="9">
+      <c r="I62" s="9" t="str">
         <f>I56</f>
-        <v>5343</v>
+        <v>5349-rt3</v>
       </c>
       <c r="J62" s="9" t="s">
         <v>61</v>
@@ -1986,7 +1999,7 @@
       </c>
       <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5343</v>
+        <v>v7.11.3-Better_Default_7-build-5349-rt3</v>
       </c>
       <c r="I65" s="16"/>
       <c r="J65" s="8"/>
@@ -2220,7 +2233,7 @@
         <v>8</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C20" s="29"/>
       <c r="D20" s="1"/>
@@ -2231,7 +2244,7 @@
       </c>
       <c r="B21" s="28" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
-        <v>v1.2.2-Better_Default_3</v>
+        <v>v1.2.2-Better_Default_3.1</v>
       </c>
       <c r="C21" s="29"/>
       <c r="D21" s="1"/>
@@ -2454,11 +2467,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2471,6 +2479,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B215DA1B-C05F-4AA7-97AC-FA423FB2A3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C444AE81-E89D-403E-ACFE-2D476726762C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="421" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="68">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>Crackers0106 (golden dandelion texture)</t>
+  </si>
+  <si>
+    <t>Fixed entity lighting</t>
   </si>
 </sst>
 </file>
@@ -936,7 +939,9 @@
       <c r="K8" s="8"/>
     </row>
     <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
+      <c r="A9" s="8" t="s">
+        <v>67</v>
+      </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -2467,6 +2472,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2479,11 +2489,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C444AE81-E89D-403E-ACFE-2D476726762C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0E22BF-734E-446C-8171-FD53E67EB43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="421" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="70">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -241,6 +241,12 @@
   </si>
   <si>
     <t>Fixed entity lighting</t>
+  </si>
+  <si>
+    <t>Fixed invisible items</t>
+  </si>
+  <si>
+    <t>Added biome modifiers</t>
   </si>
 </sst>
 </file>
@@ -962,7 +968,9 @@
       <c r="K9" s="8"/>
     </row>
     <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
+      <c r="A10" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -984,7 +992,9 @@
       <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
+      <c r="A11" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -2472,11 +2482,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2489,6 +2494,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0E22BF-734E-446C-8171-FD53E67EB43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976A356A-6D3F-48BB-81C9-D06BAF966FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="421" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -807,13 +807,13 @@
     <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5349-rt3</v>
+        <v>v10.0.11_1-build-5367-rt3</v>
       </c>
       <c r="B3" s="27"/>
       <c r="C3" s="27"/>
       <c r="D3" s="9" t="str">
-        <f>SUM(2601,637,2026,27,58) &amp; "-rt3"</f>
-        <v>5349-rt3</v>
+        <f>SUM(2601,637,2026,27,76) &amp; "-rt3"</f>
+        <v>5367-rt3</v>
       </c>
       <c r="E3" s="17">
         <f>K4</f>
@@ -858,7 +858,7 @@
       </c>
       <c r="J4" s="9" t="str">
         <f>D3</f>
-        <v>5349-rt3</v>
+        <v>5367-rt3</v>
       </c>
       <c r="K4" s="9">
         <v>26.1</v>
@@ -921,7 +921,7 @@
       </c>
       <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5349-rt3</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5367-rt3</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13"/>
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" s="9" t="str">
         <f>J4</f>
-        <v>5349-rt3</v>
+        <v>5367-rt3</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>10</v>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5349-rt3</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5367-rt3</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="8"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="I15" s="9" t="str">
         <f>I10</f>
-        <v>5349-rt3</v>
+        <v>5367-rt3</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>11</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5349-rt3</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5367-rt3</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="8"/>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="I20" s="9" t="str">
         <f>I15</f>
-        <v>5349-rt3</v>
+        <v>5367-rt3</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>62</v>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5349-rt3</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5367-rt3</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="8"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I25" s="9" t="str">
         <f>I20</f>
-        <v>5349-rt3</v>
+        <v>5367-rt3</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>12</v>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5349-rt3</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5367-rt3</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="8"/>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="I31" s="9" t="str">
         <f>I25</f>
-        <v>5349-rt3</v>
+        <v>5367-rt3</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>14</v>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5349-rt3</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5367-rt3</v>
       </c>
       <c r="I34" s="16"/>
       <c r="J34" s="8"/>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="I37" s="9" t="str">
         <f>I31</f>
-        <v>5349-rt3</v>
+        <v>5367-rt3</v>
       </c>
       <c r="J37" s="9" t="s">
         <v>17</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5349-rt3</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5367-rt3</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="8"/>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="I43" s="9" t="str">
         <f>I37</f>
-        <v>5349-rt3</v>
+        <v>5367-rt3</v>
       </c>
       <c r="J43" s="9" t="s">
         <v>18</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5349-rt3</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5367-rt3</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="8"/>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="I50" s="9" t="str">
         <f>I43</f>
-        <v>5349-rt3</v>
+        <v>5367-rt3</v>
       </c>
       <c r="J50" s="9" t="s">
         <v>30</v>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5349-rt3</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5367-rt3</v>
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="8"/>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="I56" s="9" t="str">
         <f>I50</f>
-        <v>5349-rt3</v>
+        <v>5367-rt3</v>
       </c>
       <c r="J56" s="9" t="s">
         <v>31</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5349-rt3</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5367-rt3</v>
       </c>
       <c r="I59" s="16"/>
       <c r="J59" s="8"/>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="I62" s="9" t="str">
         <f>I56</f>
-        <v>5349-rt3</v>
+        <v>5367-rt3</v>
       </c>
       <c r="J62" s="9" t="s">
         <v>61</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5349-rt3</v>
+        <v>v7.11.3-Better_Default_7-build-5367-rt3</v>
       </c>
       <c r="I65" s="16"/>
       <c r="J65" s="8"/>
@@ -2482,6 +2482,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2494,11 +2499,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976A356A-6D3F-48BB-81C9-D06BAF966FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E827B5-BA2A-42A2-BDFC-342BFDBD6ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="421" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="71">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>Added biome modifiers</t>
+  </si>
+  <si>
+    <t>Clamped cloud distance rendering between cloud render distance and terrain render distance</t>
   </si>
 </sst>
 </file>
@@ -765,7 +768,8 @@
   <dimension ref="A1:K65"/>
   <sheetFormatPr defaultColWidth="27.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="54.85546875" customWidth="1"/>
+    <col min="1" max="1" width="91.42578125" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
@@ -807,13 +811,13 @@
     <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5367-rt3</v>
+        <v>v10.0.11_1-build-5368-rt3</v>
       </c>
       <c r="B3" s="27"/>
       <c r="C3" s="27"/>
       <c r="D3" s="9" t="str">
-        <f>SUM(2601,637,2026,27,76) &amp; "-rt3"</f>
-        <v>5367-rt3</v>
+        <f>SUM(2601,637,2026,27,77) &amp; "-rt3"</f>
+        <v>5368-rt3</v>
       </c>
       <c r="E3" s="17">
         <f>K4</f>
@@ -858,7 +862,7 @@
       </c>
       <c r="J4" s="9" t="str">
         <f>D3</f>
-        <v>5367-rt3</v>
+        <v>5368-rt3</v>
       </c>
       <c r="K4" s="9">
         <v>26.1</v>
@@ -921,7 +925,7 @@
       </c>
       <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5367-rt3</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5368-rt3</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13"/>
@@ -984,7 +988,7 @@
       </c>
       <c r="I10" s="9" t="str">
         <f>J4</f>
-        <v>5367-rt3</v>
+        <v>5368-rt3</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>10</v>
@@ -1012,7 +1016,9 @@
       <c r="K11" s="8"/>
     </row>
     <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
+      <c r="A12" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -1041,7 +1047,7 @@
       </c>
       <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5367-rt3</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5368-rt3</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="8"/>
@@ -1083,7 +1089,7 @@
       </c>
       <c r="I15" s="9" t="str">
         <f>I10</f>
-        <v>5367-rt3</v>
+        <v>5368-rt3</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>11</v>
@@ -1138,7 +1144,7 @@
       </c>
       <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5367-rt3</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5368-rt3</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="8"/>
@@ -1180,7 +1186,7 @@
       </c>
       <c r="I20" s="9" t="str">
         <f>I15</f>
-        <v>5367-rt3</v>
+        <v>5368-rt3</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>62</v>
@@ -1235,7 +1241,7 @@
       </c>
       <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5367-rt3</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5368-rt3</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="8"/>
@@ -1277,7 +1283,7 @@
       </c>
       <c r="I25" s="9" t="str">
         <f>I20</f>
-        <v>5367-rt3</v>
+        <v>5368-rt3</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>12</v>
@@ -1332,7 +1338,7 @@
       </c>
       <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5367-rt3</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5368-rt3</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="8"/>
@@ -1389,7 +1395,7 @@
       </c>
       <c r="I31" s="9" t="str">
         <f>I25</f>
-        <v>5367-rt3</v>
+        <v>5368-rt3</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>14</v>
@@ -1444,7 +1450,7 @@
       </c>
       <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5367-rt3</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5368-rt3</v>
       </c>
       <c r="I34" s="16"/>
       <c r="J34" s="8"/>
@@ -1501,7 +1507,7 @@
       </c>
       <c r="I37" s="9" t="str">
         <f>I31</f>
-        <v>5367-rt3</v>
+        <v>5368-rt3</v>
       </c>
       <c r="J37" s="9" t="s">
         <v>17</v>
@@ -1555,7 +1561,7 @@
       </c>
       <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5367-rt3</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5368-rt3</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="8"/>
@@ -1612,7 +1618,7 @@
       </c>
       <c r="I43" s="9" t="str">
         <f>I37</f>
-        <v>5367-rt3</v>
+        <v>5368-rt3</v>
       </c>
       <c r="J43" s="9" t="s">
         <v>18</v>
@@ -1666,7 +1672,7 @@
       </c>
       <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5367-rt3</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5368-rt3</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="8"/>
@@ -1738,7 +1744,7 @@
       </c>
       <c r="I50" s="9" t="str">
         <f>I43</f>
-        <v>5367-rt3</v>
+        <v>5368-rt3</v>
       </c>
       <c r="J50" s="9" t="s">
         <v>30</v>
@@ -1792,7 +1798,7 @@
       </c>
       <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5367-rt3</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5368-rt3</v>
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="8"/>
@@ -1849,7 +1855,7 @@
       </c>
       <c r="I56" s="9" t="str">
         <f>I50</f>
-        <v>5367-rt3</v>
+        <v>5368-rt3</v>
       </c>
       <c r="J56" s="9" t="s">
         <v>31</v>
@@ -1903,7 +1909,7 @@
       </c>
       <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5367-rt3</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5368-rt3</v>
       </c>
       <c r="I59" s="16"/>
       <c r="J59" s="8"/>
@@ -1960,7 +1966,7 @@
       </c>
       <c r="I62" s="9" t="str">
         <f>I56</f>
-        <v>5367-rt3</v>
+        <v>5368-rt3</v>
       </c>
       <c r="J62" s="9" t="s">
         <v>61</v>
@@ -2014,7 +2020,7 @@
       </c>
       <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5367-rt3</v>
+        <v>v7.11.3-Better_Default_7-build-5368-rt3</v>
       </c>
       <c r="I65" s="16"/>
       <c r="J65" s="8"/>
@@ -2482,11 +2488,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2499,6 +2500,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E827B5-BA2A-42A2-BDFC-342BFDBD6ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4853A2-BAEC-4D73-A10E-E11B4E9A6163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="421" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="64">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -216,40 +216,19 @@
     <t>Current version in development</t>
   </si>
   <si>
-    <t>Renamed resource pack folders</t>
-  </si>
-  <si>
-    <t>Fixed environmental fog for 1.21.6 and above</t>
-  </si>
-  <si>
     <t>1.20.0</t>
   </si>
   <si>
     <t>1.21.6 / 1.21.7</t>
   </si>
   <si>
-    <t>Added golden dandelion texture</t>
-  </si>
-  <si>
     <t>Better_Default_3.1</t>
   </si>
   <si>
-    <t>Re-added classic cat sound</t>
-  </si>
-  <si>
-    <t>Crackers0106 (golden dandelion texture)</t>
-  </si>
-  <si>
-    <t>Fixed entity lighting</t>
-  </si>
-  <si>
-    <t>Fixed invisible items</t>
-  </si>
-  <si>
-    <t>Added biome modifiers</t>
-  </si>
-  <si>
-    <t>Clamped cloud distance rendering between cloud render distance and terrain render distance</t>
+    <t>Reverted classic sun and moon</t>
+  </si>
+  <si>
+    <t>Raised GLSL version for 1.20.2 and 1.21</t>
   </si>
 </sst>
 </file>
@@ -811,13 +790,13 @@
     <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5368-rt3</v>
+        <v>v10.0.11_1-build-5369-rt3</v>
       </c>
       <c r="B3" s="27"/>
       <c r="C3" s="27"/>
       <c r="D3" s="9" t="str">
-        <f>SUM(2601,637,2026,27,77) &amp; "-rt3"</f>
-        <v>5368-rt3</v>
+        <f>SUM(2601,637,2026,27,78) &amp; "-rt3"</f>
+        <v>5369-rt3</v>
       </c>
       <c r="E3" s="17">
         <f>K4</f>
@@ -862,7 +841,7 @@
       </c>
       <c r="J4" s="9" t="str">
         <f>D3</f>
-        <v>5368-rt3</v>
+        <v>5369-rt3</v>
       </c>
       <c r="K4" s="9">
         <v>26.1</v>
@@ -870,11 +849,9 @@
     </row>
     <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>66</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B5" s="8"/>
       <c r="C5" s="23" t="s">
         <v>3</v>
       </c>
@@ -893,7 +870,7 @@
     </row>
     <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -912,9 +889,7 @@
       <c r="K6" s="14"/>
     </row>
     <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>63</v>
-      </c>
+      <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -925,16 +900,14 @@
       </c>
       <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5368-rt3</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5369-rt3</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13"/>
       <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>65</v>
-      </c>
+      <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -949,9 +922,7 @@
       <c r="K8" s="8"/>
     </row>
     <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>67</v>
-      </c>
+      <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -972,9 +943,7 @@
       <c r="K9" s="8"/>
     </row>
     <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>68</v>
-      </c>
+      <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -988,7 +957,7 @@
       </c>
       <c r="I10" s="9" t="str">
         <f>J4</f>
-        <v>5368-rt3</v>
+        <v>5369-rt3</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>10</v>
@@ -996,9 +965,7 @@
       <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>69</v>
-      </c>
+      <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -1016,9 +983,7 @@
       <c r="K11" s="8"/>
     </row>
     <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
-        <v>70</v>
-      </c>
+      <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -1047,7 +1012,7 @@
       </c>
       <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5368-rt3</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5369-rt3</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="8"/>
@@ -1089,7 +1054,7 @@
       </c>
       <c r="I15" s="9" t="str">
         <f>I10</f>
-        <v>5368-rt3</v>
+        <v>5369-rt3</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>11</v>
@@ -1144,7 +1109,7 @@
       </c>
       <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5368-rt3</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5369-rt3</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="8"/>
@@ -1186,10 +1151,10 @@
       </c>
       <c r="I20" s="9" t="str">
         <f>I15</f>
-        <v>5368-rt3</v>
+        <v>5369-rt3</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K20" s="8"/>
     </row>
@@ -1241,7 +1206,7 @@
       </c>
       <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5368-rt3</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5369-rt3</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="8"/>
@@ -1283,7 +1248,7 @@
       </c>
       <c r="I25" s="9" t="str">
         <f>I20</f>
-        <v>5368-rt3</v>
+        <v>5369-rt3</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>12</v>
@@ -1338,7 +1303,7 @@
       </c>
       <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5368-rt3</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5369-rt3</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="8"/>
@@ -1395,7 +1360,7 @@
       </c>
       <c r="I31" s="9" t="str">
         <f>I25</f>
-        <v>5368-rt3</v>
+        <v>5369-rt3</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>14</v>
@@ -1450,7 +1415,7 @@
       </c>
       <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5368-rt3</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5369-rt3</v>
       </c>
       <c r="I34" s="16"/>
       <c r="J34" s="8"/>
@@ -1507,7 +1472,7 @@
       </c>
       <c r="I37" s="9" t="str">
         <f>I31</f>
-        <v>5368-rt3</v>
+        <v>5369-rt3</v>
       </c>
       <c r="J37" s="9" t="s">
         <v>17</v>
@@ -1561,7 +1526,7 @@
       </c>
       <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5368-rt3</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5369-rt3</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="8"/>
@@ -1618,7 +1583,7 @@
       </c>
       <c r="I43" s="9" t="str">
         <f>I37</f>
-        <v>5368-rt3</v>
+        <v>5369-rt3</v>
       </c>
       <c r="J43" s="9" t="s">
         <v>18</v>
@@ -1672,7 +1637,7 @@
       </c>
       <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5368-rt3</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5369-rt3</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="8"/>
@@ -1744,7 +1709,7 @@
       </c>
       <c r="I50" s="9" t="str">
         <f>I43</f>
-        <v>5368-rt3</v>
+        <v>5369-rt3</v>
       </c>
       <c r="J50" s="9" t="s">
         <v>30</v>
@@ -1798,7 +1763,7 @@
       </c>
       <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5368-rt3</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5369-rt3</v>
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="8"/>
@@ -1855,7 +1820,7 @@
       </c>
       <c r="I56" s="9" t="str">
         <f>I50</f>
-        <v>5368-rt3</v>
+        <v>5369-rt3</v>
       </c>
       <c r="J56" s="9" t="s">
         <v>31</v>
@@ -1909,7 +1874,7 @@
       </c>
       <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5368-rt3</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5369-rt3</v>
       </c>
       <c r="I59" s="16"/>
       <c r="J59" s="8"/>
@@ -1966,10 +1931,10 @@
       </c>
       <c r="I62" s="9" t="str">
         <f>I56</f>
-        <v>5368-rt3</v>
+        <v>5369-rt3</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K62" s="8"/>
     </row>
@@ -2020,7 +1985,7 @@
       </c>
       <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5368-rt3</v>
+        <v>v7.11.3-Better_Default_7-build-5369-rt3</v>
       </c>
       <c r="I65" s="16"/>
       <c r="J65" s="8"/>
@@ -2254,7 +2219,7 @@
         <v>8</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C20" s="29"/>
       <c r="D20" s="1"/>
@@ -2488,6 +2453,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2500,11 +2470,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4853A2-BAEC-4D73-A10E-E11B4E9A6163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE029E73-A8C0-45F5-9198-042E78DCA9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="421" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="65">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>Raised GLSL version for 1.20.2 and 1.21</t>
+  </si>
+  <si>
+    <t>Reimproved environmental fog</t>
   </si>
 </sst>
 </file>
@@ -790,13 +793,13 @@
     <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5369-rt3</v>
+        <v>v10.0.11_1-build-5372-rt3</v>
       </c>
       <c r="B3" s="27"/>
       <c r="C3" s="27"/>
       <c r="D3" s="9" t="str">
-        <f>SUM(2601,637,2026,27,78) &amp; "-rt3"</f>
-        <v>5369-rt3</v>
+        <f>SUM(2601,637,2026,27,81) &amp; "-rt3"</f>
+        <v>5372-rt3</v>
       </c>
       <c r="E3" s="17">
         <f>K4</f>
@@ -841,7 +844,7 @@
       </c>
       <c r="J4" s="9" t="str">
         <f>D3</f>
-        <v>5369-rt3</v>
+        <v>5372-rt3</v>
       </c>
       <c r="K4" s="9">
         <v>26.1</v>
@@ -889,7 +892,9 @@
       <c r="K6" s="14"/>
     </row>
     <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
+      <c r="A7" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -900,7 +905,7 @@
       </c>
       <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5369-rt3</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5372-rt3</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13"/>
@@ -957,7 +962,7 @@
       </c>
       <c r="I10" s="9" t="str">
         <f>J4</f>
-        <v>5369-rt3</v>
+        <v>5372-rt3</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>10</v>
@@ -1012,7 +1017,7 @@
       </c>
       <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5369-rt3</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5372-rt3</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="8"/>
@@ -1054,7 +1059,7 @@
       </c>
       <c r="I15" s="9" t="str">
         <f>I10</f>
-        <v>5369-rt3</v>
+        <v>5372-rt3</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>11</v>
@@ -1109,7 +1114,7 @@
       </c>
       <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5369-rt3</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5372-rt3</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="8"/>
@@ -1151,7 +1156,7 @@
       </c>
       <c r="I20" s="9" t="str">
         <f>I15</f>
-        <v>5369-rt3</v>
+        <v>5372-rt3</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>60</v>
@@ -1206,7 +1211,7 @@
       </c>
       <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5369-rt3</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5372-rt3</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="8"/>
@@ -1248,7 +1253,7 @@
       </c>
       <c r="I25" s="9" t="str">
         <f>I20</f>
-        <v>5369-rt3</v>
+        <v>5372-rt3</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>12</v>
@@ -1303,7 +1308,7 @@
       </c>
       <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5369-rt3</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5372-rt3</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="8"/>
@@ -1360,7 +1365,7 @@
       </c>
       <c r="I31" s="9" t="str">
         <f>I25</f>
-        <v>5369-rt3</v>
+        <v>5372-rt3</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>14</v>
@@ -1415,7 +1420,7 @@
       </c>
       <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5369-rt3</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5372-rt3</v>
       </c>
       <c r="I34" s="16"/>
       <c r="J34" s="8"/>
@@ -1472,7 +1477,7 @@
       </c>
       <c r="I37" s="9" t="str">
         <f>I31</f>
-        <v>5369-rt3</v>
+        <v>5372-rt3</v>
       </c>
       <c r="J37" s="9" t="s">
         <v>17</v>
@@ -1526,7 +1531,7 @@
       </c>
       <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5369-rt3</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5372-rt3</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="8"/>
@@ -1583,7 +1588,7 @@
       </c>
       <c r="I43" s="9" t="str">
         <f>I37</f>
-        <v>5369-rt3</v>
+        <v>5372-rt3</v>
       </c>
       <c r="J43" s="9" t="s">
         <v>18</v>
@@ -1637,7 +1642,7 @@
       </c>
       <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5369-rt3</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5372-rt3</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="8"/>
@@ -1709,7 +1714,7 @@
       </c>
       <c r="I50" s="9" t="str">
         <f>I43</f>
-        <v>5369-rt3</v>
+        <v>5372-rt3</v>
       </c>
       <c r="J50" s="9" t="s">
         <v>30</v>
@@ -1763,7 +1768,7 @@
       </c>
       <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5369-rt3</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5372-rt3</v>
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="8"/>
@@ -1820,7 +1825,7 @@
       </c>
       <c r="I56" s="9" t="str">
         <f>I50</f>
-        <v>5369-rt3</v>
+        <v>5372-rt3</v>
       </c>
       <c r="J56" s="9" t="s">
         <v>31</v>
@@ -1874,7 +1879,7 @@
       </c>
       <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5369-rt3</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5372-rt3</v>
       </c>
       <c r="I59" s="16"/>
       <c r="J59" s="8"/>
@@ -1931,7 +1936,7 @@
       </c>
       <c r="I62" s="9" t="str">
         <f>I56</f>
-        <v>5369-rt3</v>
+        <v>5372-rt3</v>
       </c>
       <c r="J62" s="9" t="s">
         <v>59</v>
@@ -1985,7 +1990,7 @@
       </c>
       <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5369-rt3</v>
+        <v>v7.11.3-Better_Default_7-build-5372-rt3</v>
       </c>
       <c r="I65" s="16"/>
       <c r="J65" s="8"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE029E73-A8C0-45F5-9198-042E78DCA9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E65C3CD-2664-4FAA-8DBB-8D6D7F850CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="421" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="66">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -232,6 +232,9 @@
   </si>
   <si>
     <t>Reimproved environmental fog</t>
+  </si>
+  <si>
+    <t>Fixed nether fog (1.21.6+)</t>
   </si>
 </sst>
 </file>
@@ -912,7 +915,9 @@
       <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
+      <c r="A8" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -2458,11 +2463,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2475,6 +2475,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E65C3CD-2664-4FAA-8DBB-8D6D7F850CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99D8632-118D-4398-8BE6-B36D7D2E5EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="421" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="67">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t>Fixed nether fog (1.21.6+)</t>
+  </si>
+  <si>
+    <t>Updated pack format versions for better compatibility</t>
   </si>
 </sst>
 </file>
@@ -796,13 +799,13 @@
     <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5372-rt3</v>
+        <v>v10.0.11_1-build-5381-rt3</v>
       </c>
       <c r="B3" s="27"/>
       <c r="C3" s="27"/>
       <c r="D3" s="9" t="str">
-        <f>SUM(2601,637,2026,27,81) &amp; "-rt3"</f>
-        <v>5372-rt3</v>
+        <f>SUM(2601,664,2026,90) &amp; "-rt3"</f>
+        <v>5381-rt3</v>
       </c>
       <c r="E3" s="17">
         <f>K4</f>
@@ -847,7 +850,7 @@
       </c>
       <c r="J4" s="9" t="str">
         <f>D3</f>
-        <v>5372-rt3</v>
+        <v>5381-rt3</v>
       </c>
       <c r="K4" s="9">
         <v>26.1</v>
@@ -908,7 +911,7 @@
       </c>
       <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5372-rt3</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5381-rt3</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13"/>
@@ -932,7 +935,9 @@
       <c r="K8" s="8"/>
     </row>
     <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
+      <c r="A9" s="8" t="s">
+        <v>66</v>
+      </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -967,7 +972,7 @@
       </c>
       <c r="I10" s="9" t="str">
         <f>J4</f>
-        <v>5372-rt3</v>
+        <v>5381-rt3</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>10</v>
@@ -1022,7 +1027,7 @@
       </c>
       <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5372-rt3</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5381-rt3</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="8"/>
@@ -1064,7 +1069,7 @@
       </c>
       <c r="I15" s="9" t="str">
         <f>I10</f>
-        <v>5372-rt3</v>
+        <v>5381-rt3</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>11</v>
@@ -1119,7 +1124,7 @@
       </c>
       <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5372-rt3</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5381-rt3</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="8"/>
@@ -1161,7 +1166,7 @@
       </c>
       <c r="I20" s="9" t="str">
         <f>I15</f>
-        <v>5372-rt3</v>
+        <v>5381-rt3</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>60</v>
@@ -1216,7 +1221,7 @@
       </c>
       <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5372-rt3</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5381-rt3</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="8"/>
@@ -1258,7 +1263,7 @@
       </c>
       <c r="I25" s="9" t="str">
         <f>I20</f>
-        <v>5372-rt3</v>
+        <v>5381-rt3</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>12</v>
@@ -1313,7 +1318,7 @@
       </c>
       <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5372-rt3</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5381-rt3</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="8"/>
@@ -1370,7 +1375,7 @@
       </c>
       <c r="I31" s="9" t="str">
         <f>I25</f>
-        <v>5372-rt3</v>
+        <v>5381-rt3</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>14</v>
@@ -1425,7 +1430,7 @@
       </c>
       <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5372-rt3</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5381-rt3</v>
       </c>
       <c r="I34" s="16"/>
       <c r="J34" s="8"/>
@@ -1482,7 +1487,7 @@
       </c>
       <c r="I37" s="9" t="str">
         <f>I31</f>
-        <v>5372-rt3</v>
+        <v>5381-rt3</v>
       </c>
       <c r="J37" s="9" t="s">
         <v>17</v>
@@ -1536,7 +1541,7 @@
       </c>
       <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5372-rt3</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5381-rt3</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="8"/>
@@ -1593,7 +1598,7 @@
       </c>
       <c r="I43" s="9" t="str">
         <f>I37</f>
-        <v>5372-rt3</v>
+        <v>5381-rt3</v>
       </c>
       <c r="J43" s="9" t="s">
         <v>18</v>
@@ -1647,7 +1652,7 @@
       </c>
       <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5372-rt3</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5381-rt3</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="8"/>
@@ -1719,7 +1724,7 @@
       </c>
       <c r="I50" s="9" t="str">
         <f>I43</f>
-        <v>5372-rt3</v>
+        <v>5381-rt3</v>
       </c>
       <c r="J50" s="9" t="s">
         <v>30</v>
@@ -1773,7 +1778,7 @@
       </c>
       <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5372-rt3</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5381-rt3</v>
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="8"/>
@@ -1830,7 +1835,7 @@
       </c>
       <c r="I56" s="9" t="str">
         <f>I50</f>
-        <v>5372-rt3</v>
+        <v>5381-rt3</v>
       </c>
       <c r="J56" s="9" t="s">
         <v>31</v>
@@ -1884,7 +1889,7 @@
       </c>
       <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5372-rt3</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5381-rt3</v>
       </c>
       <c r="I59" s="16"/>
       <c r="J59" s="8"/>
@@ -1941,7 +1946,7 @@
       </c>
       <c r="I62" s="9" t="str">
         <f>I56</f>
-        <v>5372-rt3</v>
+        <v>5381-rt3</v>
       </c>
       <c r="J62" s="9" t="s">
         <v>59</v>
@@ -1995,7 +2000,7 @@
       </c>
       <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5372-rt3</v>
+        <v>v7.11.3-Better_Default_7-build-5381-rt3</v>
       </c>
       <c r="I65" s="16"/>
       <c r="J65" s="8"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -1,46 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0DAFB9-E0FE-4144-8376-FF1F802D2B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Active releases and Changelog" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Deprecated releases" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Active releases and Changelog" sheetId="1" r:id="rId1"/>
+    <sheet name="Deprecated releases" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
-  <si>
-    <t xml:space="preserve">Current version in development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Classic Reimagined 10 version history</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource Pack Version</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="69">
+  <si>
+    <t>Current version in development</t>
+  </si>
+  <si>
+    <t>Classic Reimagined 10 version history</t>
+  </si>
+  <si>
+    <t>Resource Pack Version</t>
   </si>
   <si>
     <t>Build</t>
   </si>
   <si>
-    <t xml:space="preserve">Minecraft Version</t>
+    <t>Minecraft Version</t>
   </si>
   <si>
     <t>_SE_2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Minor version</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seasonal Drop</t>
+    <t>Minor version</t>
+  </si>
+  <si>
+    <t>Seasonal Drop</t>
   </si>
   <si>
     <t>Changelog</t>
@@ -49,46 +66,46 @@
     <t>Contributions</t>
   </si>
   <si>
-    <t xml:space="preserve">Known issues (Compatibility)</t>
+    <t>Known issues (Compatibility)</t>
   </si>
   <si>
     <t>v10.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Reverted classic sun and moon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VulkanMod compatibility (WIP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raised GLSL version for 1.20.2 and 1.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource Pack Release</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reimproved environmental fog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource Pack Build</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed nether fog (1.21.6+)</t>
+    <t>Reverted classic sun and moon</t>
+  </si>
+  <si>
+    <t>VulkanMod compatibility (WIP)</t>
+  </si>
+  <si>
+    <t>Resource Name</t>
+  </si>
+  <si>
+    <t>Raised GLSL version for 1.20.2 and 1.21</t>
+  </si>
+  <si>
+    <t>Resource Pack Release</t>
+  </si>
+  <si>
+    <t>Reimproved environmental fog</t>
+  </si>
+  <si>
+    <t>Resource Pack Build</t>
+  </si>
+  <si>
+    <t>Fixed nether fog (1.21.6+)</t>
   </si>
   <si>
     <t>_SE_2</t>
   </si>
   <si>
-    <t xml:space="preserve">Updated pack format versions for better compatibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core version</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Updated item and entity shaders for 26.1-s6</t>
+    <t>Updated pack format versions for better compatibility</t>
+  </si>
+  <si>
+    <t>Core version</t>
+  </si>
+  <si>
+    <t>Updated item and entity shaders for 26.1-s6</t>
   </si>
   <si>
     <t>1.21.11</t>
@@ -97,7 +114,7 @@
     <t>1.21.9</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21.6 / 1.21.7</t>
+    <t>1.21.6 / 1.21.7</t>
   </si>
   <si>
     <t>1.21.5</t>
@@ -118,19 +135,19 @@
     <t>Classic_Reimagined_10s</t>
   </si>
   <si>
-    <t xml:space="preserve">First Release</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20.5 / 1.21</t>
+    <t>First Release</t>
+  </si>
+  <si>
+    <t>1.20.5 / 1.21</t>
   </si>
   <si>
     <t>Classic_Reimagined_10</t>
   </si>
   <si>
-    <t xml:space="preserve">Classic Reimagined 8 version history</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Second Release</t>
+    <t>Classic Reimagined 8 version history</t>
+  </si>
+  <si>
+    <t>Second Release</t>
   </si>
   <si>
     <t>v8.10</t>
@@ -145,7 +162,7 @@
     <t>1.20.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Better Default 7 version history</t>
+    <t>Better Default 7 version history</t>
   </si>
   <si>
     <t>v7.11</t>
@@ -157,10 +174,10 @@
     <t>Better_Default_7</t>
   </si>
   <si>
-    <t xml:space="preserve">Better Default Legacy version history</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Better Default 6</t>
+    <t>Better Default Legacy version history</t>
+  </si>
+  <si>
+    <t>Better Default 6</t>
   </si>
   <si>
     <t>Patch</t>
@@ -175,7 +192,7 @@
     <t>Better_Default_6</t>
   </si>
   <si>
-    <t xml:space="preserve">Better Default 5</t>
+    <t>Better Default 5</t>
   </si>
   <si>
     <t>v1</t>
@@ -187,7 +204,7 @@
     <t>Better_Default_5</t>
   </si>
   <si>
-    <t xml:space="preserve">Better Default 4</t>
+    <t>Better Default 4</t>
   </si>
   <si>
     <t>1.17.x</t>
@@ -196,7 +213,7 @@
     <t>Better_Default_4</t>
   </si>
   <si>
-    <t xml:space="preserve">Better Default 3</t>
+    <t>Better Default 3</t>
   </si>
   <si>
     <t>1.16.2</t>
@@ -208,50 +225,53 @@
     <t>Better_Default_3</t>
   </si>
   <si>
-    <t xml:space="preserve">Better Default 2</t>
+    <t>Better Default 2</t>
   </si>
   <si>
     <t>Better_Default_2</t>
   </si>
   <si>
-    <t xml:space="preserve">Better Default 1.1a</t>
+    <t>Better Default 1.1a</t>
   </si>
   <si>
     <t>Better_Default</t>
   </si>
   <si>
-    <t xml:space="preserve">Better Default 1.1</t>
+    <t>Better Default 1.1</t>
+  </si>
+  <si>
+    <t>Removed fog banding</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="Segoe UI"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Segoe UI"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color indexed="64"/>
       <name val="Segoe UI"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color indexed="65"/>
       <name val="Segoe UI"/>
     </font>
@@ -306,11 +326,11 @@
   </fills>
   <borders count="6">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -325,34 +345,34 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="none"/>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -362,71 +382,83 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="1" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="29">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="4" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="3" fillId="7" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="7" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="7" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf fontId="1" fillId="8" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="2" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="2" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="1" fillId="3" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="3" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -446,291 +478,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -782,7 +531,7 @@
         <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -896,18 +645,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultColWidth="27.28515625" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K65"/>
+  <sheetFormatPr defaultColWidth="27.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="91.42578125"/>
-    <col customWidth="1" min="2" max="2" width="54.85546875"/>
+    <col min="1" max="1" width="91.42578125" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5">
+    <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -923,12 +674,12 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" ht="16.5">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
@@ -943,20 +694,20 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" ht="16.5">
-      <c r="A3" s="7" t="str">
+    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5381-rt3</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
+        <v>v10.0.11_1-build-5398-rt3</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
       <c r="D3" s="8" t="str">
-        <f>SUM(2601,664,2026,90) &amp; "-rt3"</f>
-        <v>5381-rt3</v>
+        <f>SUM(2601,664,2026,107) &amp; "-rt3"</f>
+        <v>5398-rt3</v>
       </c>
       <c r="E3" s="7">
         <f>K4</f>
-        <v>26.100000000000001</v>
+        <v>26.1</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>2</v>
@@ -974,18 +725,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="16.5">
+    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="22"/>
       <c r="G4" s="8" t="s">
         <v>11</v>
       </c>
@@ -997,34 +748,34 @@
       </c>
       <c r="J4" s="8" t="str">
         <f>D3</f>
-        <v>5381-rt3</v>
+        <v>5398-rt3</v>
       </c>
       <c r="K4" s="8">
-        <v>26.100000000000001</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="6"/>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="15"/>
-      <c r="G5" s="16" t="s">
+      <c r="D5" s="24"/>
+      <c r="E5" s="25"/>
+      <c r="G5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="17" t="str">
+      <c r="H5" s="11" t="str">
         <f>"Classic_Reimagined_10" &amp; G2</f>
         <v>Classic_Reimagined_10_SE_2.1</v>
       </c>
-      <c r="I5" s="18"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="20"/>
-    </row>
-    <row r="6" ht="16.5">
+      <c r="I5" s="12"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="14"/>
+    </row>
+    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>15</v>
       </c>
@@ -1033,18 +784,18 @@
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="17" t="str">
+      <c r="H6" s="11" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-" &amp; H5</f>
         <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1</v>
       </c>
-      <c r="I6" s="18"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="20"/>
-    </row>
-    <row r="7" ht="16.5">
+      <c r="I6" s="12"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="14"/>
+    </row>
+    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>17</v>
       </c>
@@ -1053,18 +804,18 @@
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="17" t="str">
+      <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5381-rt3</v>
-      </c>
-      <c r="I7" s="18"/>
-      <c r="J7" s="19"/>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5398-rt3</v>
+      </c>
+      <c r="I7" s="12"/>
+      <c r="J7" s="13"/>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" ht="16.5">
+    <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
@@ -1081,7 +832,7 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" ht="16.5">
+    <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>21</v>
       </c>
@@ -1104,7 +855,7 @@
       </c>
       <c r="K9" s="6"/>
     </row>
-    <row r="10" ht="16.5">
+    <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>23</v>
       </c>
@@ -1121,68 +872,70 @@
       </c>
       <c r="I10" s="8" t="str">
         <f>J4</f>
-        <v>5381-rt3</v>
+        <v>5398-rt3</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>24</v>
       </c>
       <c r="K10" s="6"/>
     </row>
-    <row r="11" ht="16.5">
-      <c r="A11" s="6"/>
+    <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="21" t="str">
+      <c r="H11" s="15" t="str">
         <f>"Classic_Reimagined_10" &amp; G8</f>
         <v>Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I11" s="22"/>
-      <c r="J11" s="20"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="14"/>
       <c r="K11" s="6"/>
     </row>
-    <row r="12" ht="16.5">
+    <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="21" t="str">
+      <c r="H12" s="15" t="str">
         <f>G10 &amp; "." &amp; H10 &amp; "-" &amp; H11</f>
         <v>v10.0.10-Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I12" s="22"/>
-      <c r="J12" s="20"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="14"/>
       <c r="K12" s="6"/>
     </row>
-    <row r="13" ht="16.5">
+    <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="21" t="str">
+      <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5381-rt3</v>
-      </c>
-      <c r="I13" s="22"/>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5398-rt3</v>
+      </c>
+      <c r="I13" s="16"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
     </row>
-    <row r="14" ht="16.5">
+    <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -1203,7 +956,7 @@
       </c>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" ht="16.5">
+    <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -1218,68 +971,68 @@
       </c>
       <c r="I15" s="8" t="str">
         <f>I10</f>
-        <v>5381-rt3</v>
+        <v>5398-rt3</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>25</v>
       </c>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" ht="16.5">
+    <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="21" t="str">
+      <c r="H16" s="15" t="str">
         <f>H11</f>
         <v>Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I16" s="22"/>
-      <c r="J16" s="20"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="14"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" ht="16.5">
+    <row r="17" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
-      <c r="G17" s="16" t="s">
+      <c r="G17" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="21" t="str">
+      <c r="H17" s="15" t="str">
         <f>G15 &amp; "." &amp; H15 &amp; "-" &amp; H16</f>
         <v>v10.0.9-Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I17" s="22"/>
-      <c r="J17" s="20"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="14"/>
       <c r="K17" s="6"/>
     </row>
-    <row r="18" ht="16.5">
+    <row r="18" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="21" t="str">
+      <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5381-rt3</v>
-      </c>
-      <c r="I18" s="22"/>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5398-rt3</v>
+      </c>
+      <c r="I18" s="16"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
     </row>
-    <row r="19" ht="16.5">
+    <row r="19" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -1300,7 +1053,7 @@
       </c>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" ht="16.5">
+    <row r="20" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -1315,68 +1068,68 @@
       </c>
       <c r="I20" s="8" t="str">
         <f>I15</f>
-        <v>5381-rt3</v>
+        <v>5398-rt3</v>
       </c>
       <c r="J20" s="8" t="s">
         <v>26</v>
       </c>
       <c r="K20" s="6"/>
     </row>
-    <row r="21" ht="16.5">
+    <row r="21" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
-      <c r="G21" s="16" t="s">
+      <c r="G21" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H21" s="21" t="str">
+      <c r="H21" s="15" t="str">
         <f>H16</f>
         <v>Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I21" s="22"/>
-      <c r="J21" s="20"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="14"/>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" ht="16.5">
+    <row r="22" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H22" s="21" t="str">
+      <c r="H22" s="15" t="str">
         <f>G20 &amp; "." &amp; H20 &amp; "-" &amp; H21</f>
         <v>v10.0.7-Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I22" s="22"/>
-      <c r="J22" s="20"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="14"/>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" ht="16.5">
+    <row r="23" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
-      <c r="G23" s="16" t="s">
+      <c r="G23" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H23" s="21" t="str">
+      <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5381-rt3</v>
-      </c>
-      <c r="I23" s="22"/>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5398-rt3</v>
+      </c>
+      <c r="I23" s="16"/>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
     </row>
-    <row r="24" ht="16.5">
+    <row r="24" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -1397,7 +1150,7 @@
       </c>
       <c r="K24" s="6"/>
     </row>
-    <row r="25" ht="16.5">
+    <row r="25" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -1412,68 +1165,68 @@
       </c>
       <c r="I25" s="8" t="str">
         <f>I20</f>
-        <v>5381-rt3</v>
+        <v>5398-rt3</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>27</v>
       </c>
       <c r="K25" s="6"/>
     </row>
-    <row r="26" ht="16.5">
+    <row r="26" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H26" s="21" t="str">
+      <c r="H26" s="15" t="str">
         <f>H21</f>
         <v>Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I26" s="22"/>
-      <c r="J26" s="20"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="14"/>
       <c r="K26" s="6"/>
     </row>
-    <row r="27" ht="16.5">
+    <row r="27" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
-      <c r="G27" s="16" t="s">
+      <c r="G27" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H27" s="21" t="str">
+      <c r="H27" s="15" t="str">
         <f>G25 &amp; "." &amp; H25 &amp; "-" &amp; H26</f>
         <v>v10.0.4-Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I27" s="22"/>
-      <c r="J27" s="20"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="14"/>
       <c r="K27" s="6"/>
     </row>
-    <row r="28" ht="16.5">
+    <row r="28" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
-      <c r="G28" s="16" t="s">
+      <c r="G28" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H28" s="21" t="str">
+      <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5381-rt3</v>
-      </c>
-      <c r="I28" s="22"/>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5398-rt3</v>
+      </c>
+      <c r="I28" s="16"/>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
     </row>
-    <row r="29" ht="16.5">
+    <row r="29" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -1488,7 +1241,7 @@
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
     </row>
-    <row r="30" ht="16.5">
+    <row r="30" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -1509,7 +1262,7 @@
       </c>
       <c r="K30" s="6"/>
     </row>
-    <row r="31" ht="16.5">
+    <row r="31" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -1524,68 +1277,68 @@
       </c>
       <c r="I31" s="8" t="str">
         <f>I25</f>
-        <v>5381-rt3</v>
+        <v>5398-rt3</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K31" s="6"/>
     </row>
-    <row r="32" ht="16.5">
+    <row r="32" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
-      <c r="G32" s="16" t="s">
+      <c r="G32" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H32" s="21" t="str">
+      <c r="H32" s="15" t="str">
         <f>"Classic_Reimagined_10" &amp; G29</f>
         <v>Classic_Reimagined_10_SE</v>
       </c>
-      <c r="I32" s="22"/>
-      <c r="J32" s="20"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="14"/>
       <c r="K32" s="6"/>
     </row>
-    <row r="33" ht="16.5">
+    <row r="33" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
-      <c r="G33" s="16" t="s">
+      <c r="G33" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H33" s="21" t="str">
+      <c r="H33" s="15" t="str">
         <f>G31 &amp; "." &amp; H31 &amp; "-" &amp; H32</f>
         <v>v10.0.3-Classic_Reimagined_10_SE</v>
       </c>
-      <c r="I33" s="22"/>
-      <c r="J33" s="20"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="14"/>
       <c r="K33" s="6"/>
     </row>
-    <row r="34" ht="16.5">
+    <row r="34" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
-      <c r="G34" s="16" t="s">
+      <c r="G34" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H34" s="21" t="str">
+      <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5381-rt3</v>
-      </c>
-      <c r="I34" s="22"/>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5398-rt3</v>
+      </c>
+      <c r="I34" s="16"/>
       <c r="J34" s="6"/>
       <c r="K34" s="6"/>
     </row>
-    <row r="35" ht="16.5">
+    <row r="35" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -1600,7 +1353,7 @@
       <c r="J35" s="6"/>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" ht="16.5">
+    <row r="36" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -1621,7 +1374,7 @@
       </c>
       <c r="K36" s="6"/>
     </row>
-    <row r="37" ht="16.5">
+    <row r="37" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -1636,67 +1389,67 @@
       </c>
       <c r="I37" s="8" t="str">
         <f>I31</f>
-        <v>5381-rt3</v>
+        <v>5398-rt3</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>31</v>
       </c>
       <c r="K37" s="6"/>
     </row>
-    <row r="38" ht="16.5">
+    <row r="38" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
-      <c r="G38" s="16" t="s">
+      <c r="G38" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H38" s="21" t="s">
+      <c r="H38" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="I38" s="22"/>
-      <c r="J38" s="20"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="14"/>
       <c r="K38" s="6"/>
     </row>
-    <row r="39" ht="16.5">
+    <row r="39" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
-      <c r="G39" s="16" t="s">
+      <c r="G39" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H39" s="21" t="str">
+      <c r="H39" s="15" t="str">
         <f>G37 &amp; "." &amp; H37 &amp; "-" &amp; H38</f>
         <v>v10.0.2-Classic_Reimagined_10s</v>
       </c>
-      <c r="I39" s="22"/>
-      <c r="J39" s="20"/>
+      <c r="I39" s="16"/>
+      <c r="J39" s="14"/>
       <c r="K39" s="6"/>
     </row>
-    <row r="40" ht="16.5">
+    <row r="40" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
-      <c r="G40" s="16" t="s">
+      <c r="G40" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H40" s="21" t="str">
+      <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5381-rt3</v>
-      </c>
-      <c r="I40" s="22"/>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5398-rt3</v>
+      </c>
+      <c r="I40" s="16"/>
       <c r="J40" s="6"/>
       <c r="K40" s="6"/>
     </row>
-    <row r="41" ht="16.5">
+    <row r="41" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1711,7 +1464,7 @@
       <c r="J41" s="6"/>
       <c r="K41" s="6"/>
     </row>
-    <row r="42" ht="16.5">
+    <row r="42" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -1732,7 +1485,7 @@
       </c>
       <c r="K42" s="6"/>
     </row>
-    <row r="43" ht="16.5">
+    <row r="43" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -1747,67 +1500,67 @@
       </c>
       <c r="I43" s="8" t="str">
         <f>I37</f>
-        <v>5381-rt3</v>
+        <v>5398-rt3</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>34</v>
       </c>
       <c r="K43" s="6"/>
     </row>
-    <row r="44" ht="16.5">
+    <row r="44" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
-      <c r="G44" s="16" t="s">
+      <c r="G44" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H44" s="21" t="s">
+      <c r="H44" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="I44" s="22"/>
-      <c r="J44" s="20"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="14"/>
       <c r="K44" s="6"/>
     </row>
-    <row r="45" ht="16.5">
+    <row r="45" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
-      <c r="G45" s="16" t="s">
+      <c r="G45" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H45" s="21" t="str">
+      <c r="H45" s="15" t="str">
         <f>G43 &amp; "." &amp; H43 &amp; "-" &amp; H44</f>
         <v>v10.0.1-Classic_Reimagined_10</v>
       </c>
-      <c r="I45" s="22"/>
-      <c r="J45" s="20"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="14"/>
       <c r="K45" s="6"/>
     </row>
-    <row r="46" ht="16.5">
+    <row r="46" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
-      <c r="G46" s="16" t="s">
+      <c r="G46" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H46" s="21" t="str">
+      <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5381-rt3</v>
-      </c>
-      <c r="I46" s="22"/>
+        <v>v10.0.1-Classic_Reimagined_10-build-5398-rt3</v>
+      </c>
+      <c r="I46" s="16"/>
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
     </row>
-    <row r="47" ht="16.5">
+    <row r="47" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -1822,7 +1575,7 @@
       <c r="J47" s="2"/>
       <c r="K47" s="6"/>
     </row>
-    <row r="48" ht="16.5">
+    <row r="48" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -1837,7 +1590,7 @@
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
     </row>
-    <row r="49" ht="16.5">
+    <row r="49" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -1858,7 +1611,7 @@
       </c>
       <c r="K49" s="6"/>
     </row>
-    <row r="50" ht="16.5">
+    <row r="50" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -1873,67 +1626,67 @@
       </c>
       <c r="I50" s="8" t="str">
         <f>I43</f>
-        <v>5381-rt3</v>
+        <v>5398-rt3</v>
       </c>
       <c r="J50" s="8" t="s">
         <v>39</v>
       </c>
       <c r="K50" s="6"/>
     </row>
-    <row r="51" ht="16.5">
+    <row r="51" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
-      <c r="G51" s="16" t="s">
+      <c r="G51" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="21" t="s">
+      <c r="H51" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="I51" s="22"/>
-      <c r="J51" s="20"/>
+      <c r="I51" s="16"/>
+      <c r="J51" s="14"/>
       <c r="K51" s="6"/>
     </row>
-    <row r="52" ht="16.5">
+    <row r="52" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
-      <c r="G52" s="16" t="s">
+      <c r="G52" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H52" s="21" t="str">
+      <c r="H52" s="15" t="str">
         <f>G50 &amp; "." &amp; H50 &amp; "-" &amp; H51</f>
         <v>v8.10.32-Classic_Reimagined_8</v>
       </c>
-      <c r="I52" s="22"/>
-      <c r="J52" s="20"/>
+      <c r="I52" s="16"/>
+      <c r="J52" s="14"/>
       <c r="K52" s="6"/>
     </row>
-    <row r="53" ht="16.5">
+    <row r="53" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
       <c r="F53" s="6"/>
-      <c r="G53" s="16" t="s">
+      <c r="G53" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H53" s="21" t="str">
+      <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5381-rt3</v>
-      </c>
-      <c r="I53" s="22"/>
+        <v>v8.10.32-Classic_Reimagined_8-build-5398-rt3</v>
+      </c>
+      <c r="I53" s="16"/>
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
     </row>
-    <row r="54" ht="16.5">
+    <row r="54" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -1948,7 +1701,7 @@
       <c r="J54" s="6"/>
       <c r="K54" s="6"/>
     </row>
-    <row r="55" ht="16.5">
+    <row r="55" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -1969,7 +1722,7 @@
       </c>
       <c r="K55" s="6"/>
     </row>
-    <row r="56" ht="16.5">
+    <row r="56" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -1984,82 +1737,82 @@
       </c>
       <c r="I56" s="8" t="str">
         <f>I50</f>
-        <v>5381-rt3</v>
+        <v>5398-rt3</v>
       </c>
       <c r="J56" s="8" t="s">
         <v>41</v>
       </c>
       <c r="K56" s="6"/>
     </row>
-    <row r="57" ht="16.5">
+    <row r="57" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
-      <c r="G57" s="16" t="s">
+      <c r="G57" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H57" s="21" t="s">
+      <c r="H57" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="I57" s="22"/>
-      <c r="J57" s="20"/>
+      <c r="I57" s="16"/>
+      <c r="J57" s="14"/>
       <c r="K57" s="6"/>
     </row>
-    <row r="58" ht="16.5">
+    <row r="58" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
-      <c r="G58" s="16" t="s">
+      <c r="G58" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H58" s="21" t="str">
+      <c r="H58" s="15" t="str">
         <f>G56 &amp; "." &amp; H56 &amp; "-" &amp; H57</f>
         <v>v8.10.31-Classic_Reimagined_8</v>
       </c>
-      <c r="I58" s="22"/>
-      <c r="J58" s="20"/>
+      <c r="I58" s="16"/>
+      <c r="J58" s="14"/>
       <c r="K58" s="6"/>
     </row>
-    <row r="59" ht="16.5">
+    <row r="59" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
-      <c r="G59" s="16" t="s">
+      <c r="G59" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H59" s="21" t="str">
+      <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5381-rt3</v>
-      </c>
-      <c r="I59" s="22"/>
+        <v>v8.10.31-Classic_Reimagined_8-build-5398-rt3</v>
+      </c>
+      <c r="I59" s="16"/>
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
     </row>
-    <row r="60" ht="16.5">
+    <row r="60" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
-      <c r="G60" s="23" t="s">
+      <c r="G60" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="H60" s="23"/>
-      <c r="I60" s="23"/>
-      <c r="J60" s="23"/>
+      <c r="H60" s="17"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="17"/>
       <c r="K60" s="6"/>
     </row>
-    <row r="61" ht="16.5">
+    <row r="61" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -2080,7 +1833,7 @@
       </c>
       <c r="K61" s="6"/>
     </row>
-    <row r="62" ht="16.5">
+    <row r="62" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -2095,63 +1848,63 @@
       </c>
       <c r="I62" s="8" t="str">
         <f>I56</f>
-        <v>5381-rt3</v>
+        <v>5398-rt3</v>
       </c>
       <c r="J62" s="8" t="s">
         <v>44</v>
       </c>
       <c r="K62" s="6"/>
     </row>
-    <row r="63" ht="16.5">
+    <row r="63" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
-      <c r="G63" s="16" t="s">
+      <c r="G63" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H63" s="21" t="s">
+      <c r="H63" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="I63" s="22"/>
-      <c r="J63" s="20"/>
+      <c r="I63" s="16"/>
+      <c r="J63" s="14"/>
       <c r="K63" s="6"/>
     </row>
-    <row r="64" ht="16.5">
+    <row r="64" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
-      <c r="G64" s="16" t="s">
+      <c r="G64" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H64" s="21" t="str">
+      <c r="H64" s="15" t="str">
         <f>G62 &amp; "." &amp; H62 &amp; "-" &amp; H63</f>
         <v>v7.11.3-Better_Default_7</v>
       </c>
-      <c r="I64" s="22"/>
-      <c r="J64" s="20"/>
+      <c r="I64" s="16"/>
+      <c r="J64" s="14"/>
       <c r="K64" s="6"/>
     </row>
-    <row r="65" ht="16.5">
+    <row r="65" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
-      <c r="G65" s="16" t="s">
+      <c r="G65" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H65" s="21" t="str">
+      <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5381-rt3</v>
-      </c>
-      <c r="I65" s="22"/>
+        <v>v7.11.3-Better_Default_7-build-5398-rt3</v>
+      </c>
+      <c r="I65" s="16"/>
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
     </row>
@@ -2162,34 +1915,33 @@
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="C5:E5"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="27.42578125"/>
+    <col min="1" max="4" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-    </row>
-    <row r="2" ht="16.5">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+    </row>
+    <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" ht="16.5">
+    <row r="3" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>22</v>
       </c>
@@ -2203,7 +1955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="16.5">
+    <row r="4" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>49</v>
       </c>
@@ -2217,33 +1969,33 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" ht="16.5">
-      <c r="A5" s="16" t="s">
+    <row r="5" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="20"/>
-    </row>
-    <row r="6" ht="16.5">
-      <c r="A6" s="16" t="s">
+      <c r="C5" s="27"/>
+      <c r="D5" s="14"/>
+    </row>
+    <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="21" t="str">
+      <c r="B6" s="26" t="str">
         <f>A4 &amp; "." &amp; B4 &amp; "." &amp; C4 &amp; "-" &amp; B5</f>
         <v>v6.0.7-Better_Default_6</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="20"/>
-    </row>
-    <row r="7" ht="16.5">
+      <c r="C6" s="27"/>
+      <c r="D6" s="14"/>
+    </row>
+    <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="8" ht="16.5">
+    <row r="8" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
@@ -2257,7 +2009,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" ht="16.5">
+    <row r="9" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>53</v>
       </c>
@@ -2271,33 +2023,33 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" ht="16.5">
-      <c r="A10" s="16" t="s">
+    <row r="10" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="20"/>
-    </row>
-    <row r="11" ht="16.5">
-      <c r="A11" s="16" t="s">
+      <c r="C10" s="27"/>
+      <c r="D10" s="14"/>
+    </row>
+    <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="21" t="str">
+      <c r="B11" s="26" t="str">
         <f>A9 &amp; "." &amp; B9 &amp; "." &amp; C9 &amp; "-" &amp; B10</f>
         <v>v1.4.0-Better_Default_5</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="20"/>
-    </row>
-    <row r="12" ht="16.5">
+      <c r="C11" s="27"/>
+      <c r="D11" s="14"/>
+    </row>
+    <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="13" ht="16.5">
+    <row r="13" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>22</v>
       </c>
@@ -2311,7 +2063,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" ht="16.5">
+    <row r="14" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>53</v>
       </c>
@@ -2325,33 +2077,33 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" ht="16.5">
-      <c r="A15" s="16" t="s">
+    <row r="15" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="20"/>
-    </row>
-    <row r="16" ht="16.5">
-      <c r="A16" s="16" t="s">
+      <c r="C15" s="27"/>
+      <c r="D15" s="14"/>
+    </row>
+    <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="21" t="str">
+      <c r="B16" s="26" t="str">
         <f>A14 &amp; "." &amp; B14 &amp; "." &amp; C14 &amp; "-" &amp; B15</f>
         <v>v1.3.0-Better_Default_4</v>
       </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="20"/>
-    </row>
-    <row r="17" ht="16.5">
+      <c r="C16" s="27"/>
+      <c r="D16" s="14"/>
+    </row>
+    <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="18" ht="16.5">
+    <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>22</v>
       </c>
@@ -2365,7 +2117,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" ht="16.5">
+    <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>53</v>
       </c>
@@ -2379,33 +2131,33 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" ht="16.5">
-      <c r="A20" s="16" t="s">
+    <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="20"/>
-    </row>
-    <row r="21" ht="16.5">
-      <c r="A21" s="16" t="s">
+      <c r="C20" s="27"/>
+      <c r="D20" s="14"/>
+    </row>
+    <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="21" t="str">
+      <c r="B21" s="26" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
         <v>v1.2.2-Better_Default_3.1</v>
       </c>
-      <c r="C21" s="22"/>
-      <c r="D21" s="20"/>
-    </row>
-    <row r="22" ht="16.5">
+      <c r="C21" s="27"/>
+      <c r="D21" s="14"/>
+    </row>
+    <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="23" ht="16.5">
+    <row r="23" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
@@ -2419,7 +2171,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" ht="16.5">
+    <row r="24" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>53</v>
       </c>
@@ -2433,33 +2185,33 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="25" ht="16.5">
-      <c r="A25" s="16" t="s">
+    <row r="25" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="20"/>
-    </row>
-    <row r="26" ht="16.5">
-      <c r="A26" s="16" t="s">
+      <c r="C25" s="27"/>
+      <c r="D25" s="14"/>
+    </row>
+    <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A26" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="21" t="str">
+      <c r="B26" s="26" t="str">
         <f>A24 &amp; "." &amp; B24 &amp; "." &amp; C24 &amp; "-" &amp; B25</f>
         <v>v1.2.1-Better_Default_3</v>
       </c>
-      <c r="C26" s="22"/>
-      <c r="D26" s="20"/>
-    </row>
-    <row r="27" ht="16.5">
+      <c r="C26" s="27"/>
+      <c r="D26" s="14"/>
+    </row>
+    <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="28" ht="16.5">
+    <row r="28" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>22</v>
       </c>
@@ -2473,7 +2225,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" ht="16.5">
+    <row r="29" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>53</v>
       </c>
@@ -2487,33 +2239,33 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="30" ht="16.5">
-      <c r="A30" s="16" t="s">
+    <row r="30" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A30" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="20"/>
-    </row>
-    <row r="31" ht="16.5">
-      <c r="A31" s="16" t="s">
+      <c r="C30" s="27"/>
+      <c r="D30" s="14"/>
+    </row>
+    <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A31" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="21" t="str">
+      <c r="B31" s="26" t="str">
         <f>A29 &amp; "." &amp; B29 &amp; "." &amp; C29 &amp; "-" &amp; B30</f>
         <v>v1.2.0-Better_Default_2</v>
       </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="20"/>
-    </row>
-    <row r="32" ht="16.5">
+      <c r="C31" s="27"/>
+      <c r="D31" s="14"/>
+    </row>
+    <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="33" ht="16.5">
+    <row r="33" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>22</v>
       </c>
@@ -2527,7 +2279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" ht="16.5">
+    <row r="34" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>53</v>
       </c>
@@ -2541,33 +2293,33 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="35" ht="16.5">
-      <c r="A35" s="16" t="s">
+    <row r="35" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A35" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="22"/>
-      <c r="D35" s="20"/>
-    </row>
-    <row r="36" ht="16.5">
-      <c r="A36" s="16" t="s">
+      <c r="C35" s="27"/>
+      <c r="D35" s="14"/>
+    </row>
+    <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A36" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B36" s="21" t="str">
+      <c r="B36" s="26" t="str">
         <f>A34 &amp; "." &amp; B34 &amp; "." &amp; C34 &amp; "-" &amp; B35</f>
         <v>v1.1.1-Better_Default</v>
       </c>
-      <c r="C36" s="22"/>
-      <c r="D36" s="20"/>
-    </row>
-    <row r="37" ht="16.5">
+      <c r="C36" s="27"/>
+      <c r="D36" s="14"/>
+    </row>
+    <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="38" ht="16.5">
+    <row r="38" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>22</v>
       </c>
@@ -2581,7 +2333,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" ht="16.5">
+    <row r="39" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>53</v>
       </c>
@@ -2595,29 +2347,34 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="40" ht="16.5">
-      <c r="A40" s="16" t="s">
+    <row r="40" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A40" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="C40" s="22"/>
-      <c r="D40" s="20"/>
-    </row>
-    <row r="41" ht="16.5">
-      <c r="A41" s="16" t="s">
+      <c r="C40" s="27"/>
+      <c r="D40" s="14"/>
+    </row>
+    <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A41" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B41" s="21" t="str">
+      <c r="B41" s="26" t="str">
         <f>A39 &amp; "." &amp; B39 &amp; "." &amp; C39 &amp; "-" &amp; B40</f>
         <v>v1.1.0-Better_Default</v>
       </c>
-      <c r="C41" s="22"/>
-      <c r="D41" s="20"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2630,15 +2387,8 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0DAFB9-E0FE-4144-8376-FF1F802D2B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D52E8A7-4575-491A-A210-79B3A6771B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="70">
   <si>
     <t>Current version in development</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>Removed fog banding</t>
+  </si>
+  <si>
+    <t>Updated porkchop texture</t>
   </si>
 </sst>
 </file>
@@ -697,13 +700,13 @@
     <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5398-rt3</v>
+        <v>v10.0.11_1-build-5406-rt3</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
       <c r="D3" s="8" t="str">
-        <f>SUM(2601,664,2026,107) &amp; "-rt3"</f>
-        <v>5398-rt3</v>
+        <f>SUM(2601,664,2026,115) &amp; "-rt3"</f>
+        <v>5406-rt3</v>
       </c>
       <c r="E3" s="7">
         <f>K4</f>
@@ -748,7 +751,7 @@
       </c>
       <c r="J4" s="8" t="str">
         <f>D3</f>
-        <v>5398-rt3</v>
+        <v>5406-rt3</v>
       </c>
       <c r="K4" s="8">
         <v>26.1</v>
@@ -809,7 +812,7 @@
       </c>
       <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5398-rt3</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5406-rt3</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13"/>
@@ -872,7 +875,7 @@
       </c>
       <c r="I10" s="8" t="str">
         <f>J4</f>
-        <v>5398-rt3</v>
+        <v>5406-rt3</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>24</v>
@@ -900,7 +903,9 @@
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
+      <c r="A12" s="6" t="s">
+        <v>69</v>
+      </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -929,7 +934,7 @@
       </c>
       <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5398-rt3</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5406-rt3</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="6"/>
@@ -971,7 +976,7 @@
       </c>
       <c r="I15" s="8" t="str">
         <f>I10</f>
-        <v>5398-rt3</v>
+        <v>5406-rt3</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>25</v>
@@ -1026,7 +1031,7 @@
       </c>
       <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5398-rt3</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5406-rt3</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="6"/>
@@ -1068,7 +1073,7 @@
       </c>
       <c r="I20" s="8" t="str">
         <f>I15</f>
-        <v>5398-rt3</v>
+        <v>5406-rt3</v>
       </c>
       <c r="J20" s="8" t="s">
         <v>26</v>
@@ -1123,7 +1128,7 @@
       </c>
       <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5398-rt3</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5406-rt3</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="6"/>
@@ -1165,7 +1170,7 @@
       </c>
       <c r="I25" s="8" t="str">
         <f>I20</f>
-        <v>5398-rt3</v>
+        <v>5406-rt3</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>27</v>
@@ -1220,7 +1225,7 @@
       </c>
       <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5398-rt3</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5406-rt3</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="6"/>
@@ -1277,7 +1282,7 @@
       </c>
       <c r="I31" s="8" t="str">
         <f>I25</f>
-        <v>5398-rt3</v>
+        <v>5406-rt3</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>29</v>
@@ -1332,7 +1337,7 @@
       </c>
       <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5398-rt3</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5406-rt3</v>
       </c>
       <c r="I34" s="16"/>
       <c r="J34" s="6"/>
@@ -1389,7 +1394,7 @@
       </c>
       <c r="I37" s="8" t="str">
         <f>I31</f>
-        <v>5398-rt3</v>
+        <v>5406-rt3</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>31</v>
@@ -1443,7 +1448,7 @@
       </c>
       <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5398-rt3</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5406-rt3</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="6"/>
@@ -1500,7 +1505,7 @@
       </c>
       <c r="I43" s="8" t="str">
         <f>I37</f>
-        <v>5398-rt3</v>
+        <v>5406-rt3</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>34</v>
@@ -1554,7 +1559,7 @@
       </c>
       <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5398-rt3</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5406-rt3</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="6"/>
@@ -1626,7 +1631,7 @@
       </c>
       <c r="I50" s="8" t="str">
         <f>I43</f>
-        <v>5398-rt3</v>
+        <v>5406-rt3</v>
       </c>
       <c r="J50" s="8" t="s">
         <v>39</v>
@@ -1680,7 +1685,7 @@
       </c>
       <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5398-rt3</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5406-rt3</v>
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="6"/>
@@ -1737,7 +1742,7 @@
       </c>
       <c r="I56" s="8" t="str">
         <f>I50</f>
-        <v>5398-rt3</v>
+        <v>5406-rt3</v>
       </c>
       <c r="J56" s="8" t="s">
         <v>41</v>
@@ -1791,7 +1796,7 @@
       </c>
       <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5398-rt3</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5406-rt3</v>
       </c>
       <c r="I59" s="16"/>
       <c r="J59" s="6"/>
@@ -1848,7 +1853,7 @@
       </c>
       <c r="I62" s="8" t="str">
         <f>I56</f>
-        <v>5398-rt3</v>
+        <v>5406-rt3</v>
       </c>
       <c r="J62" s="8" t="s">
         <v>44</v>
@@ -1902,7 +1907,7 @@
       </c>
       <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5398-rt3</v>
+        <v>v7.11.3-Better_Default_7-build-5406-rt3</v>
       </c>
       <c r="I65" s="16"/>
       <c r="J65" s="6"/>
@@ -2370,11 +2375,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2387,6 +2387,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D52E8A7-4575-491A-A210-79B3A6771B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8DE1B4-D41C-44D0-8E9B-8F10A57F91D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="71">
   <si>
     <t>Current version in development</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>Updated porkchop texture</t>
+  </si>
+  <si>
+    <t>Updated GUI textures</t>
   </si>
 </sst>
 </file>
@@ -700,13 +703,13 @@
     <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5406-rt3</v>
+        <v>v10.0.11_1-build-5407-rt3</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
       <c r="D3" s="8" t="str">
-        <f>SUM(2601,664,2026,115) &amp; "-rt3"</f>
-        <v>5406-rt3</v>
+        <f>SUM(2601,664,2026,116) &amp; "-rt3"</f>
+        <v>5407-rt3</v>
       </c>
       <c r="E3" s="7">
         <f>K4</f>
@@ -751,7 +754,7 @@
       </c>
       <c r="J4" s="8" t="str">
         <f>D3</f>
-        <v>5406-rt3</v>
+        <v>5407-rt3</v>
       </c>
       <c r="K4" s="8">
         <v>26.1</v>
@@ -812,7 +815,7 @@
       </c>
       <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5406-rt3</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5407-rt3</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13"/>
@@ -875,7 +878,7 @@
       </c>
       <c r="I10" s="8" t="str">
         <f>J4</f>
-        <v>5406-rt3</v>
+        <v>5407-rt3</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>24</v>
@@ -923,7 +926,9 @@
       <c r="K12" s="6"/>
     </row>
     <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
+      <c r="A13" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -934,7 +939,7 @@
       </c>
       <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5406-rt3</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5407-rt3</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="6"/>
@@ -976,7 +981,7 @@
       </c>
       <c r="I15" s="8" t="str">
         <f>I10</f>
-        <v>5406-rt3</v>
+        <v>5407-rt3</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>25</v>
@@ -1031,7 +1036,7 @@
       </c>
       <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5406-rt3</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5407-rt3</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="6"/>
@@ -1073,7 +1078,7 @@
       </c>
       <c r="I20" s="8" t="str">
         <f>I15</f>
-        <v>5406-rt3</v>
+        <v>5407-rt3</v>
       </c>
       <c r="J20" s="8" t="s">
         <v>26</v>
@@ -1128,7 +1133,7 @@
       </c>
       <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5406-rt3</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5407-rt3</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="6"/>
@@ -1170,7 +1175,7 @@
       </c>
       <c r="I25" s="8" t="str">
         <f>I20</f>
-        <v>5406-rt3</v>
+        <v>5407-rt3</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>27</v>
@@ -1225,7 +1230,7 @@
       </c>
       <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5406-rt3</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5407-rt3</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="6"/>
@@ -1282,7 +1287,7 @@
       </c>
       <c r="I31" s="8" t="str">
         <f>I25</f>
-        <v>5406-rt3</v>
+        <v>5407-rt3</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>29</v>
@@ -1337,7 +1342,7 @@
       </c>
       <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5406-rt3</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5407-rt3</v>
       </c>
       <c r="I34" s="16"/>
       <c r="J34" s="6"/>
@@ -1394,7 +1399,7 @@
       </c>
       <c r="I37" s="8" t="str">
         <f>I31</f>
-        <v>5406-rt3</v>
+        <v>5407-rt3</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>31</v>
@@ -1448,7 +1453,7 @@
       </c>
       <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5406-rt3</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5407-rt3</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="6"/>
@@ -1505,7 +1510,7 @@
       </c>
       <c r="I43" s="8" t="str">
         <f>I37</f>
-        <v>5406-rt3</v>
+        <v>5407-rt3</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>34</v>
@@ -1559,7 +1564,7 @@
       </c>
       <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5406-rt3</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5407-rt3</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="6"/>
@@ -1631,7 +1636,7 @@
       </c>
       <c r="I50" s="8" t="str">
         <f>I43</f>
-        <v>5406-rt3</v>
+        <v>5407-rt3</v>
       </c>
       <c r="J50" s="8" t="s">
         <v>39</v>
@@ -1685,7 +1690,7 @@
       </c>
       <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5406-rt3</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5407-rt3</v>
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="6"/>
@@ -1742,7 +1747,7 @@
       </c>
       <c r="I56" s="8" t="str">
         <f>I50</f>
-        <v>5406-rt3</v>
+        <v>5407-rt3</v>
       </c>
       <c r="J56" s="8" t="s">
         <v>41</v>
@@ -1796,7 +1801,7 @@
       </c>
       <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5406-rt3</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5407-rt3</v>
       </c>
       <c r="I59" s="16"/>
       <c r="J59" s="6"/>
@@ -1853,7 +1858,7 @@
       </c>
       <c r="I62" s="8" t="str">
         <f>I56</f>
-        <v>5406-rt3</v>
+        <v>5407-rt3</v>
       </c>
       <c r="J62" s="8" t="s">
         <v>44</v>
@@ -1907,7 +1912,7 @@
       </c>
       <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5406-rt3</v>
+        <v>v7.11.3-Better_Default_7-build-5407-rt3</v>
       </c>
       <c r="I65" s="16"/>
       <c r="J65" s="6"/>
@@ -2375,6 +2380,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2387,11 +2397,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8DE1B4-D41C-44D0-8E9B-8F10A57F91D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C305EB-6D67-4668-80E1-7B6AEC9C7698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="72">
   <si>
     <t>Current version in development</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>Updated GUI textures</t>
+  </si>
+  <si>
+    <t>Undone 26.1 shader fix</t>
   </si>
 </sst>
 </file>
@@ -703,13 +706,13 @@
     <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5407-rt3</v>
+        <v>v10.0.11_1-build-5410-rt3</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
       <c r="D3" s="8" t="str">
-        <f>SUM(2601,664,2026,116) &amp; "-rt3"</f>
-        <v>5407-rt3</v>
+        <f>SUM(2601,664,2026,119) &amp; "-rt3"</f>
+        <v>5410-rt3</v>
       </c>
       <c r="E3" s="7">
         <f>K4</f>
@@ -754,7 +757,7 @@
       </c>
       <c r="J4" s="8" t="str">
         <f>D3</f>
-        <v>5407-rt3</v>
+        <v>5410-rt3</v>
       </c>
       <c r="K4" s="8">
         <v>26.1</v>
@@ -815,7 +818,7 @@
       </c>
       <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5407-rt3</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5410-rt3</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13"/>
@@ -878,7 +881,7 @@
       </c>
       <c r="I10" s="8" t="str">
         <f>J4</f>
-        <v>5407-rt3</v>
+        <v>5410-rt3</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>24</v>
@@ -939,14 +942,16 @@
       </c>
       <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5407-rt3</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5410-rt3</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
     </row>
     <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
+      <c r="A14" s="6" t="s">
+        <v>71</v>
+      </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -981,7 +986,7 @@
       </c>
       <c r="I15" s="8" t="str">
         <f>I10</f>
-        <v>5407-rt3</v>
+        <v>5410-rt3</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>25</v>
@@ -1036,7 +1041,7 @@
       </c>
       <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5407-rt3</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5410-rt3</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="6"/>
@@ -1078,7 +1083,7 @@
       </c>
       <c r="I20" s="8" t="str">
         <f>I15</f>
-        <v>5407-rt3</v>
+        <v>5410-rt3</v>
       </c>
       <c r="J20" s="8" t="s">
         <v>26</v>
@@ -1133,7 +1138,7 @@
       </c>
       <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5407-rt3</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5410-rt3</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="6"/>
@@ -1175,7 +1180,7 @@
       </c>
       <c r="I25" s="8" t="str">
         <f>I20</f>
-        <v>5407-rt3</v>
+        <v>5410-rt3</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>27</v>
@@ -1230,7 +1235,7 @@
       </c>
       <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5407-rt3</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5410-rt3</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="6"/>
@@ -1287,7 +1292,7 @@
       </c>
       <c r="I31" s="8" t="str">
         <f>I25</f>
-        <v>5407-rt3</v>
+        <v>5410-rt3</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>29</v>
@@ -1342,7 +1347,7 @@
       </c>
       <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5407-rt3</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5410-rt3</v>
       </c>
       <c r="I34" s="16"/>
       <c r="J34" s="6"/>
@@ -1399,7 +1404,7 @@
       </c>
       <c r="I37" s="8" t="str">
         <f>I31</f>
-        <v>5407-rt3</v>
+        <v>5410-rt3</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>31</v>
@@ -1453,7 +1458,7 @@
       </c>
       <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5407-rt3</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5410-rt3</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="6"/>
@@ -1510,7 +1515,7 @@
       </c>
       <c r="I43" s="8" t="str">
         <f>I37</f>
-        <v>5407-rt3</v>
+        <v>5410-rt3</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>34</v>
@@ -1564,7 +1569,7 @@
       </c>
       <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5407-rt3</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5410-rt3</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="6"/>
@@ -1636,7 +1641,7 @@
       </c>
       <c r="I50" s="8" t="str">
         <f>I43</f>
-        <v>5407-rt3</v>
+        <v>5410-rt3</v>
       </c>
       <c r="J50" s="8" t="s">
         <v>39</v>
@@ -1690,7 +1695,7 @@
       </c>
       <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5407-rt3</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5410-rt3</v>
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="6"/>
@@ -1747,7 +1752,7 @@
       </c>
       <c r="I56" s="8" t="str">
         <f>I50</f>
-        <v>5407-rt3</v>
+        <v>5410-rt3</v>
       </c>
       <c r="J56" s="8" t="s">
         <v>41</v>
@@ -1801,7 +1806,7 @@
       </c>
       <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5407-rt3</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5410-rt3</v>
       </c>
       <c r="I59" s="16"/>
       <c r="J59" s="6"/>
@@ -1858,7 +1863,7 @@
       </c>
       <c r="I62" s="8" t="str">
         <f>I56</f>
-        <v>5407-rt3</v>
+        <v>5410-rt3</v>
       </c>
       <c r="J62" s="8" t="s">
         <v>44</v>
@@ -1912,7 +1917,7 @@
       </c>
       <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5407-rt3</v>
+        <v>v7.11.3-Better_Default_7-build-5410-rt3</v>
       </c>
       <c r="I65" s="16"/>
       <c r="J65" s="6"/>
@@ -2380,11 +2385,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2397,6 +2397,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C305EB-6D67-4668-80E1-7B6AEC9C7698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E03C683-591C-43F5-98C2-393D406ABDE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="73">
   <si>
     <t>Current version in development</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>Undone 26.1 shader fix</t>
+  </si>
+  <si>
+    <t>Improved cloud fog</t>
   </si>
 </sst>
 </file>
@@ -972,7 +975,9 @@
       <c r="K14" s="6"/>
     </row>
     <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
+      <c r="A15" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -2385,6 +2390,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2397,11 +2407,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E03C683-591C-43F5-98C2-393D406ABDE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3F5905-D098-4802-8407-E2AEF7B21A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="74">
   <si>
     <t>Current version in development</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>Improved cloud fog</t>
+  </si>
+  <si>
+    <t>Restored adult horse markings blackdots</t>
   </si>
 </sst>
 </file>
@@ -709,13 +712,13 @@
     <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5410-rt3</v>
+        <v>v10.0.11_1-build-5417-rt3</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
       <c r="D3" s="8" t="str">
-        <f>SUM(2601,664,2026,119) &amp; "-rt3"</f>
-        <v>5410-rt3</v>
+        <f>SUM(2601,664,2026,126) &amp; "-rt3"</f>
+        <v>5417-rt3</v>
       </c>
       <c r="E3" s="7">
         <f>K4</f>
@@ -760,7 +763,7 @@
       </c>
       <c r="J4" s="8" t="str">
         <f>D3</f>
-        <v>5410-rt3</v>
+        <v>5417-rt3</v>
       </c>
       <c r="K4" s="8">
         <v>26.1</v>
@@ -821,7 +824,7 @@
       </c>
       <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5410-rt3</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5417-rt3</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13"/>
@@ -884,7 +887,7 @@
       </c>
       <c r="I10" s="8" t="str">
         <f>J4</f>
-        <v>5410-rt3</v>
+        <v>5417-rt3</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>24</v>
@@ -945,7 +948,7 @@
       </c>
       <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5410-rt3</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5417-rt3</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="6"/>
@@ -991,7 +994,7 @@
       </c>
       <c r="I15" s="8" t="str">
         <f>I10</f>
-        <v>5410-rt3</v>
+        <v>5417-rt3</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>25</v>
@@ -999,7 +1002,9 @@
       <c r="K15" s="6"/>
     </row>
     <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
+      <c r="A16" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -1046,7 +1051,7 @@
       </c>
       <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5410-rt3</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5417-rt3</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="6"/>
@@ -1088,7 +1093,7 @@
       </c>
       <c r="I20" s="8" t="str">
         <f>I15</f>
-        <v>5410-rt3</v>
+        <v>5417-rt3</v>
       </c>
       <c r="J20" s="8" t="s">
         <v>26</v>
@@ -1143,7 +1148,7 @@
       </c>
       <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5410-rt3</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5417-rt3</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="6"/>
@@ -1185,7 +1190,7 @@
       </c>
       <c r="I25" s="8" t="str">
         <f>I20</f>
-        <v>5410-rt3</v>
+        <v>5417-rt3</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>27</v>
@@ -1240,7 +1245,7 @@
       </c>
       <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5410-rt3</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5417-rt3</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="6"/>
@@ -1297,7 +1302,7 @@
       </c>
       <c r="I31" s="8" t="str">
         <f>I25</f>
-        <v>5410-rt3</v>
+        <v>5417-rt3</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>29</v>
@@ -1352,7 +1357,7 @@
       </c>
       <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5410-rt3</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5417-rt3</v>
       </c>
       <c r="I34" s="16"/>
       <c r="J34" s="6"/>
@@ -1409,7 +1414,7 @@
       </c>
       <c r="I37" s="8" t="str">
         <f>I31</f>
-        <v>5410-rt3</v>
+        <v>5417-rt3</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>31</v>
@@ -1463,7 +1468,7 @@
       </c>
       <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5410-rt3</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5417-rt3</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="6"/>
@@ -1520,7 +1525,7 @@
       </c>
       <c r="I43" s="8" t="str">
         <f>I37</f>
-        <v>5410-rt3</v>
+        <v>5417-rt3</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>34</v>
@@ -1574,7 +1579,7 @@
       </c>
       <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5410-rt3</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5417-rt3</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="6"/>
@@ -1646,7 +1651,7 @@
       </c>
       <c r="I50" s="8" t="str">
         <f>I43</f>
-        <v>5410-rt3</v>
+        <v>5417-rt3</v>
       </c>
       <c r="J50" s="8" t="s">
         <v>39</v>
@@ -1700,7 +1705,7 @@
       </c>
       <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5410-rt3</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5417-rt3</v>
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="6"/>
@@ -1757,7 +1762,7 @@
       </c>
       <c r="I56" s="8" t="str">
         <f>I50</f>
-        <v>5410-rt3</v>
+        <v>5417-rt3</v>
       </c>
       <c r="J56" s="8" t="s">
         <v>41</v>
@@ -1811,7 +1816,7 @@
       </c>
       <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5410-rt3</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5417-rt3</v>
       </c>
       <c r="I59" s="16"/>
       <c r="J59" s="6"/>
@@ -1868,7 +1873,7 @@
       </c>
       <c r="I62" s="8" t="str">
         <f>I56</f>
-        <v>5410-rt3</v>
+        <v>5417-rt3</v>
       </c>
       <c r="J62" s="8" t="s">
         <v>44</v>
@@ -1922,7 +1927,7 @@
       </c>
       <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5410-rt3</v>
+        <v>v7.11.3-Better_Default_7-build-5417-rt3</v>
       </c>
       <c r="I65" s="16"/>
       <c r="J65" s="6"/>
@@ -2390,11 +2395,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2407,6 +2407,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3F5905-D098-4802-8407-E2AEF7B21A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F02373-835C-4B98-B4B3-9D419BF84A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="62">
   <si>
     <t>Current version in development</t>
   </si>
@@ -72,42 +72,24 @@
     <t>v10.0</t>
   </si>
   <si>
-    <t>Reverted classic sun and moon</t>
-  </si>
-  <si>
     <t>VulkanMod compatibility (WIP)</t>
   </si>
   <si>
     <t>Resource Name</t>
   </si>
   <si>
-    <t>Raised GLSL version for 1.20.2 and 1.21</t>
-  </si>
-  <si>
     <t>Resource Pack Release</t>
   </si>
   <si>
-    <t>Reimproved environmental fog</t>
-  </si>
-  <si>
     <t>Resource Pack Build</t>
   </si>
   <si>
-    <t>Fixed nether fog (1.21.6+)</t>
-  </si>
-  <si>
     <t>_SE_2</t>
   </si>
   <si>
-    <t>Updated pack format versions for better compatibility</t>
-  </si>
-  <si>
     <t>Core version</t>
   </si>
   <si>
-    <t>Updated item and entity shaders for 26.1-s6</t>
-  </si>
-  <si>
     <t>1.21.11</t>
   </si>
   <si>
@@ -238,24 +220,6 @@
   </si>
   <si>
     <t>Better Default 1.1</t>
-  </si>
-  <si>
-    <t>Removed fog banding</t>
-  </si>
-  <si>
-    <t>Updated porkchop texture</t>
-  </si>
-  <si>
-    <t>Updated GUI textures</t>
-  </si>
-  <si>
-    <t>Undone 26.1 shader fix</t>
-  </si>
-  <si>
-    <t>Improved cloud fog</t>
-  </si>
-  <si>
-    <t>Restored adult horse markings blackdots</t>
   </si>
 </sst>
 </file>
@@ -712,13 +676,13 @@
     <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5417-rt3</v>
+        <v>v10.0.11_1-build-5418-rt3</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
       <c r="D3" s="8" t="str">
-        <f>SUM(2601,664,2026,126) &amp; "-rt3"</f>
-        <v>5417-rt3</v>
+        <f>SUM(2601,664,2026,127) &amp; "-rt3"</f>
+        <v>5418-rt3</v>
       </c>
       <c r="E3" s="7">
         <f>K4</f>
@@ -763,24 +727,22 @@
       </c>
       <c r="J4" s="8" t="str">
         <f>D3</f>
-        <v>5417-rt3</v>
+        <v>5418-rt3</v>
       </c>
       <c r="K4" s="8">
         <v>26.1</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>12</v>
-      </c>
+      <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" s="24"/>
       <c r="E5" s="25"/>
       <c r="G5" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" s="11" t="str">
         <f>"Classic_Reimagined_10" &amp; G2</f>
@@ -791,16 +753,14 @@
       <c r="K5" s="14"/>
     </row>
     <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H6" s="11" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-" &amp; H5</f>
@@ -811,36 +771,32 @@
       <c r="K6" s="14"/>
     </row>
     <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5417-rt3</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5418-rt3</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13"/>
       <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -848,16 +804,14 @@
       <c r="K8" s="6"/>
     </row>
     <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>6</v>
@@ -871,9 +825,7 @@
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -887,24 +839,22 @@
       </c>
       <c r="I10" s="8" t="str">
         <f>J4</f>
-        <v>5417-rt3</v>
+        <v>5418-rt3</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K10" s="6"/>
     </row>
     <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>68</v>
-      </c>
+      <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H11" s="15" t="str">
         <f>"Classic_Reimagined_10" &amp; G8</f>
@@ -915,16 +865,14 @@
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>69</v>
-      </c>
+      <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H12" s="15" t="str">
         <f>G10 &amp; "." &amp; H10 &amp; "-" &amp; H11</f>
@@ -935,36 +883,32 @@
       <c r="K12" s="6"/>
     </row>
     <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>70</v>
-      </c>
+      <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5417-rt3</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5418-rt3</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
     </row>
     <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>71</v>
-      </c>
+      <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>6</v>
@@ -978,9 +922,7 @@
       <c r="K14" s="6"/>
     </row>
     <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>72</v>
-      </c>
+      <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -994,24 +936,22 @@
       </c>
       <c r="I15" s="8" t="str">
         <f>I10</f>
-        <v>5417-rt3</v>
+        <v>5418-rt3</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K15" s="6"/>
     </row>
     <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>73</v>
-      </c>
+      <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H16" s="15" t="str">
         <f>H11</f>
@@ -1029,7 +969,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H17" s="15" t="str">
         <f>G15 &amp; "." &amp; H15 &amp; "-" &amp; H16</f>
@@ -1047,11 +987,11 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5417-rt3</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5418-rt3</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="6"/>
@@ -1065,7 +1005,7 @@
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>6</v>
@@ -1093,10 +1033,10 @@
       </c>
       <c r="I20" s="8" t="str">
         <f>I15</f>
-        <v>5417-rt3</v>
+        <v>5418-rt3</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K20" s="6"/>
     </row>
@@ -1108,7 +1048,7 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H21" s="15" t="str">
         <f>H16</f>
@@ -1126,7 +1066,7 @@
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H22" s="15" t="str">
         <f>G20 &amp; "." &amp; H20 &amp; "-" &amp; H21</f>
@@ -1144,11 +1084,11 @@
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5417-rt3</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5418-rt3</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="6"/>
@@ -1162,7 +1102,7 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>6</v>
@@ -1190,10 +1130,10 @@
       </c>
       <c r="I25" s="8" t="str">
         <f>I20</f>
-        <v>5417-rt3</v>
+        <v>5418-rt3</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K25" s="6"/>
     </row>
@@ -1205,7 +1145,7 @@
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H26" s="15" t="str">
         <f>H21</f>
@@ -1223,7 +1163,7 @@
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H27" s="15" t="str">
         <f>G25 &amp; "." &amp; H25 &amp; "-" &amp; H26</f>
@@ -1241,11 +1181,11 @@
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5417-rt3</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5418-rt3</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="6"/>
@@ -1259,7 +1199,7 @@
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
@@ -1274,7 +1214,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>6</v>
@@ -1302,10 +1242,10 @@
       </c>
       <c r="I31" s="8" t="str">
         <f>I25</f>
-        <v>5417-rt3</v>
+        <v>5418-rt3</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K31" s="6"/>
     </row>
@@ -1317,7 +1257,7 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H32" s="15" t="str">
         <f>"Classic_Reimagined_10" &amp; G29</f>
@@ -1335,7 +1275,7 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H33" s="15" t="str">
         <f>G31 &amp; "." &amp; H31 &amp; "-" &amp; H32</f>
@@ -1353,11 +1293,11 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5417-rt3</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5418-rt3</v>
       </c>
       <c r="I34" s="16"/>
       <c r="J34" s="6"/>
@@ -1371,7 +1311,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
@@ -1386,7 +1326,7 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>6</v>
@@ -1414,10 +1354,10 @@
       </c>
       <c r="I37" s="8" t="str">
         <f>I31</f>
-        <v>5417-rt3</v>
+        <v>5418-rt3</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K37" s="6"/>
     </row>
@@ -1429,10 +1369,10 @@
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H38" s="15" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I38" s="16"/>
       <c r="J38" s="14"/>
@@ -1446,7 +1386,7 @@
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H39" s="15" t="str">
         <f>G37 &amp; "." &amp; H37 &amp; "-" &amp; H38</f>
@@ -1464,11 +1404,11 @@
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
       <c r="G40" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5417-rt3</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5418-rt3</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="6"/>
@@ -1482,7 +1422,7 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
       <c r="G41" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
@@ -1497,7 +1437,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
       <c r="G42" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>6</v>
@@ -1525,10 +1465,10 @@
       </c>
       <c r="I43" s="8" t="str">
         <f>I37</f>
-        <v>5417-rt3</v>
+        <v>5418-rt3</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K43" s="6"/>
     </row>
@@ -1540,10 +1480,10 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
       <c r="G44" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H44" s="15" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I44" s="16"/>
       <c r="J44" s="14"/>
@@ -1557,7 +1497,7 @@
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
       <c r="G45" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H45" s="15" t="str">
         <f>G43 &amp; "." &amp; H43 &amp; "-" &amp; H44</f>
@@ -1575,11 +1515,11 @@
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
       <c r="G46" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5417-rt3</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5418-rt3</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="6"/>
@@ -1593,7 +1533,7 @@
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
       <c r="G47" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
@@ -1608,7 +1548,7 @@
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
       <c r="G48" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H48" s="6"/>
       <c r="I48" s="6"/>
@@ -1623,7 +1563,7 @@
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
       <c r="G49" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H49" s="4" t="s">
         <v>6</v>
@@ -1644,17 +1584,17 @@
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
       <c r="G50" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H50" s="8">
         <v>32</v>
       </c>
       <c r="I50" s="8" t="str">
         <f>I43</f>
-        <v>5417-rt3</v>
+        <v>5418-rt3</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="K50" s="6"/>
     </row>
@@ -1666,10 +1606,10 @@
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
       <c r="G51" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H51" s="15" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="I51" s="16"/>
       <c r="J51" s="14"/>
@@ -1683,7 +1623,7 @@
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
       <c r="G52" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H52" s="15" t="str">
         <f>G50 &amp; "." &amp; H50 &amp; "-" &amp; H51</f>
@@ -1701,11 +1641,11 @@
       <c r="E53" s="6"/>
       <c r="F53" s="6"/>
       <c r="G53" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5417-rt3</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5418-rt3</v>
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="6"/>
@@ -1719,7 +1659,7 @@
       <c r="E54" s="6"/>
       <c r="F54" s="6"/>
       <c r="G54" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
@@ -1734,7 +1674,7 @@
       <c r="E55" s="6"/>
       <c r="F55" s="6"/>
       <c r="G55" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>6</v>
@@ -1755,17 +1695,17 @@
       <c r="E56" s="6"/>
       <c r="F56" s="6"/>
       <c r="G56" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H56" s="8">
         <v>31</v>
       </c>
       <c r="I56" s="8" t="str">
         <f>I50</f>
-        <v>5417-rt3</v>
+        <v>5418-rt3</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="K56" s="6"/>
     </row>
@@ -1777,10 +1717,10 @@
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
       <c r="G57" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H57" s="15" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="I57" s="16"/>
       <c r="J57" s="14"/>
@@ -1794,7 +1734,7 @@
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
       <c r="G58" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H58" s="15" t="str">
         <f>G56 &amp; "." &amp; H56 &amp; "-" &amp; H57</f>
@@ -1812,11 +1752,11 @@
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
       <c r="G59" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5417-rt3</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5418-rt3</v>
       </c>
       <c r="I59" s="16"/>
       <c r="J59" s="6"/>
@@ -1830,7 +1770,7 @@
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
       <c r="G60" s="17" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H60" s="17"/>
       <c r="I60" s="17"/>
@@ -1845,7 +1785,7 @@
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
       <c r="G61" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>6</v>
@@ -1866,17 +1806,17 @@
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
       <c r="G62" s="8" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H62" s="8">
         <v>3</v>
       </c>
       <c r="I62" s="8" t="str">
         <f>I56</f>
-        <v>5417-rt3</v>
+        <v>5418-rt3</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="K62" s="6"/>
     </row>
@@ -1888,10 +1828,10 @@
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
       <c r="G63" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H63" s="15" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I63" s="16"/>
       <c r="J63" s="14"/>
@@ -1905,7 +1845,7 @@
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
       <c r="G64" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H64" s="15" t="str">
         <f>G62 &amp; "." &amp; H62 &amp; "-" &amp; H63</f>
@@ -1923,11 +1863,11 @@
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
       <c r="G65" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5417-rt3</v>
+        <v>v7.11.3-Better_Default_7-build-5418-rt3</v>
       </c>
       <c r="I65" s="16"/>
       <c r="J65" s="6"/>
@@ -1955,7 +1895,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -1963,18 +1903,18 @@
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>4</v>
@@ -1982,7 +1922,7 @@
     </row>
     <row r="4" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B4" s="8">
         <v>0</v>
@@ -1991,22 +1931,22 @@
         <v>7</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C5" s="27"/>
       <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B6" s="26" t="str">
         <f>A4 &amp; "." &amp; B4 &amp; "." &amp; C4 &amp; "-" &amp; B5</f>
@@ -2017,18 +1957,18 @@
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>4</v>
@@ -2036,7 +1976,7 @@
     </row>
     <row r="9" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B9" s="8">
         <v>4</v>
@@ -2045,22 +1985,22 @@
         <v>0</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C10" s="27"/>
       <c r="D10" s="14"/>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B11" s="26" t="str">
         <f>A9 &amp; "." &amp; B9 &amp; "." &amp; C9 &amp; "-" &amp; B10</f>
@@ -2071,18 +2011,18 @@
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>4</v>
@@ -2090,7 +2030,7 @@
     </row>
     <row r="14" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B14" s="8">
         <v>3</v>
@@ -2099,22 +2039,22 @@
         <v>0</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C15" s="27"/>
       <c r="D15" s="14"/>
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B16" s="26" t="str">
         <f>A14 &amp; "." &amp; B14 &amp; "." &amp; C14 &amp; "-" &amp; B15</f>
@@ -2125,18 +2065,18 @@
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>4</v>
@@ -2144,7 +2084,7 @@
     </row>
     <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B19" s="8">
         <v>2</v>
@@ -2153,22 +2093,22 @@
         <v>2</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C20" s="27"/>
       <c r="D20" s="14"/>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B21" s="26" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
@@ -2179,12 +2119,12 @@
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>6</v>
@@ -2198,7 +2138,7 @@
     </row>
     <row r="24" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B24" s="8">
         <v>2</v>
@@ -2212,17 +2152,17 @@
     </row>
     <row r="25" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C25" s="27"/>
       <c r="D25" s="14"/>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B26" s="26" t="str">
         <f>A24 &amp; "." &amp; B24 &amp; "." &amp; C24 &amp; "-" &amp; B25</f>
@@ -2233,12 +2173,12 @@
     </row>
     <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>6</v>
@@ -2252,7 +2192,7 @@
     </row>
     <row r="29" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B29" s="8">
         <v>2</v>
@@ -2266,17 +2206,17 @@
     </row>
     <row r="30" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C30" s="27"/>
       <c r="D30" s="14"/>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B31" s="26" t="str">
         <f>A29 &amp; "." &amp; B29 &amp; "." &amp; C29 &amp; "-" &amp; B30</f>
@@ -2287,18 +2227,18 @@
     </row>
     <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>4</v>
@@ -2306,7 +2246,7 @@
     </row>
     <row r="34" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B34" s="8">
         <v>1</v>
@@ -2320,17 +2260,17 @@
     </row>
     <row r="35" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C35" s="27"/>
       <c r="D35" s="14"/>
     </row>
     <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B36" s="26" t="str">
         <f>A34 &amp; "." &amp; B34 &amp; "." &amp; C34 &amp; "-" &amp; B35</f>
@@ -2341,18 +2281,18 @@
     </row>
     <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>4</v>
@@ -2360,7 +2300,7 @@
     </row>
     <row r="39" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B39" s="8">
         <v>1</v>
@@ -2374,17 +2314,17 @@
     </row>
     <row r="40" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C40" s="27"/>
       <c r="D40" s="14"/>
     </row>
     <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B41" s="26" t="str">
         <f>A39 &amp; "." &amp; B39 &amp; "." &amp; C39 &amp; "-" &amp; B40</f>
@@ -2395,6 +2335,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2407,11 +2352,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F02373-835C-4B98-B4B3-9D419BF84A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C381E3-9D83-4830-8B3D-525450BC188E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="66">
   <si>
     <t>Current version in development</t>
   </si>
@@ -220,6 +220,18 @@
   </si>
   <si>
     <t>Better Default 1.1</t>
+  </si>
+  <si>
+    <t>Classic Reimagined Lite version history</t>
+  </si>
+  <si>
+    <t>v1.2</t>
+  </si>
+  <si>
+    <t>v1.1</t>
+  </si>
+  <si>
+    <t>1.21.6</t>
   </si>
 </sst>
 </file>
@@ -376,7 +388,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -439,6 +451,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -630,14 +645,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:Q65"/>
   <sheetFormatPr defaultColWidth="27.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="91.42578125" customWidth="1"/>
     <col min="2" max="2" width="54.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -652,8 +667,15 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-    </row>
-    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M1" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+    </row>
+    <row r="2" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
         <v>2</v>
       </c>
@@ -672,17 +694,32 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
-    </row>
-    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5418-rt3</v>
+        <v>v10.0.11_1-build-5418-rt4</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
       <c r="D3" s="8" t="str">
-        <f>SUM(2601,664,2026,127) &amp; "-rt3"</f>
-        <v>5418-rt3</v>
+        <f>SUM(2601,664,2026,127) &amp; "-rt4"</f>
+        <v>5418-rt4</v>
       </c>
       <c r="E3" s="7">
         <f>K4</f>
@@ -703,8 +740,24 @@
       <c r="K3" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M3" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N3" s="8">
+        <v>7</v>
+      </c>
+      <c r="O3" s="8">
+        <v>1</v>
+      </c>
+      <c r="P3" s="8" t="str">
+        <f>J4</f>
+        <v>5418-rt4</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
@@ -727,13 +780,23 @@
       </c>
       <c r="J4" s="8" t="str">
         <f>D3</f>
-        <v>5418-rt3</v>
+        <v>5418-rt4</v>
       </c>
       <c r="K4" s="8">
         <v>26.1</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" s="11" t="str">
+        <f>"Classic_Reimagined_Lite"</f>
+        <v>Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O4" s="12"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="14"/>
+    </row>
+    <row r="5" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="23" t="s">
@@ -751,8 +814,18 @@
       <c r="I5" s="12"/>
       <c r="J5" s="13"/>
       <c r="K5" s="14"/>
-    </row>
-    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M5" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="N5" s="11" t="str">
+        <f>M3 &amp; "." &amp; N3 &amp; "_" &amp; O3 &amp; "-" &amp; N4</f>
+        <v>v1.2.7_1-Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O5" s="12"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="14"/>
+    </row>
+    <row r="6" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -769,8 +842,18 @@
       <c r="I6" s="12"/>
       <c r="J6" s="13"/>
       <c r="K6" s="14"/>
-    </row>
-    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N6" s="11" t="str">
+        <f>N5 &amp; "-build-" &amp; P3</f>
+        <v>v1.2.7_1-Classic_Reimagined_Lite-build-5418-rt4</v>
+      </c>
+      <c r="O6" s="12"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -782,13 +865,25 @@
       </c>
       <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5418-rt3</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5418-rt4</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13"/>
       <c r="K7" s="6"/>
-    </row>
-    <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -802,8 +897,21 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
-    </row>
-    <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M8" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N8" s="8">
+        <v>6</v>
+      </c>
+      <c r="O8" s="8" t="str">
+        <f>P3</f>
+        <v>5418-rt4</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -823,8 +931,17 @@
         <v>4</v>
       </c>
       <c r="K9" s="6"/>
-    </row>
-    <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M9" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="N9" s="15" t="str">
+        <f>N4</f>
+        <v>Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O9" s="16"/>
+      <c r="P9" s="14"/>
+    </row>
+    <row r="10" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -839,14 +956,23 @@
       </c>
       <c r="I10" s="8" t="str">
         <f>J4</f>
-        <v>5418-rt3</v>
+        <v>5418-rt4</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>18</v>
       </c>
       <c r="K10" s="6"/>
-    </row>
-    <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="N10" s="15" t="str">
+        <f>M8 &amp; "." &amp; N8 &amp; "-" &amp; N9</f>
+        <v>v1.2.6-Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O10" s="16"/>
+      <c r="P10" s="14"/>
+    </row>
+    <row r="11" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -863,8 +989,17 @@
       <c r="I11" s="16"/>
       <c r="J11" s="14"/>
       <c r="K11" s="6"/>
-    </row>
-    <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M11" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N11" s="15" t="str">
+        <f>N10 &amp; "-build-" &amp; O8</f>
+        <v>v1.2.6-Classic_Reimagined_Lite-build-5418-rt4</v>
+      </c>
+      <c r="O11" s="16"/>
+      <c r="P11" s="6"/>
+    </row>
+    <row r="12" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -881,8 +1016,20 @@
       <c r="I12" s="16"/>
       <c r="J12" s="14"/>
       <c r="K12" s="6"/>
-    </row>
-    <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -894,13 +1041,26 @@
       </c>
       <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5418-rt3</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5418-rt4</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
-    </row>
-    <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M13" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N13" s="8">
+        <v>5</v>
+      </c>
+      <c r="O13" s="8" t="str">
+        <f>P3</f>
+        <v>5418-rt4</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -920,8 +1080,17 @@
         <v>4</v>
       </c>
       <c r="K14" s="6"/>
-    </row>
-    <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M14" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="N14" s="15" t="str">
+        <f>N4</f>
+        <v>Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O14" s="16"/>
+      <c r="P14" s="14"/>
+    </row>
+    <row r="15" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -936,14 +1105,23 @@
       </c>
       <c r="I15" s="8" t="str">
         <f>I10</f>
-        <v>5418-rt3</v>
+        <v>5418-rt4</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>19</v>
       </c>
       <c r="K15" s="6"/>
-    </row>
-    <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M15" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="N15" s="15" t="str">
+        <f>M13 &amp; "." &amp; N13 &amp; "-" &amp; N14</f>
+        <v>v1.2.5-Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O15" s="16"/>
+      <c r="P15" s="14"/>
+    </row>
+    <row r="16" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -960,8 +1138,17 @@
       <c r="I16" s="16"/>
       <c r="J16" s="14"/>
       <c r="K16" s="6"/>
-    </row>
-    <row r="17" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M16" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N16" s="15" t="str">
+        <f>N15 &amp; "-build-" &amp; O13</f>
+        <v>v1.2.5-Classic_Reimagined_Lite-build-5418-rt4</v>
+      </c>
+      <c r="O16" s="16"/>
+      <c r="P16" s="6"/>
+    </row>
+    <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -978,8 +1165,20 @@
       <c r="I17" s="16"/>
       <c r="J17" s="14"/>
       <c r="K17" s="6"/>
-    </row>
-    <row r="18" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -991,13 +1190,26 @@
       </c>
       <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5418-rt3</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5418-rt4</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
-    </row>
-    <row r="19" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M18" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N18" s="8">
+        <v>4</v>
+      </c>
+      <c r="O18" s="8" t="str">
+        <f>P3</f>
+        <v>5418-rt4</v>
+      </c>
+      <c r="P18" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -1017,8 +1229,17 @@
         <v>4</v>
       </c>
       <c r="K19" s="6"/>
-    </row>
-    <row r="20" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M19" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="N19" s="15" t="str">
+        <f>N4</f>
+        <v>Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O19" s="16"/>
+      <c r="P19" s="14"/>
+    </row>
+    <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -1033,14 +1254,23 @@
       </c>
       <c r="I20" s="8" t="str">
         <f>I15</f>
-        <v>5418-rt3</v>
+        <v>5418-rt4</v>
       </c>
       <c r="J20" s="8" t="s">
         <v>20</v>
       </c>
       <c r="K20" s="6"/>
-    </row>
-    <row r="21" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M20" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="N20" s="15" t="str">
+        <f>M18 &amp; "." &amp; N18 &amp; "-" &amp; N19</f>
+        <v>v1.2.4-Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O20" s="16"/>
+      <c r="P20" s="14"/>
+    </row>
+    <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -1057,8 +1287,17 @@
       <c r="I21" s="16"/>
       <c r="J21" s="14"/>
       <c r="K21" s="6"/>
-    </row>
-    <row r="22" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M21" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N21" s="15" t="str">
+        <f>N20 &amp; "-build-" &amp; O18</f>
+        <v>v1.2.4-Classic_Reimagined_Lite-build-5418-rt4</v>
+      </c>
+      <c r="O21" s="16"/>
+      <c r="P21" s="6"/>
+    </row>
+    <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -1075,8 +1314,20 @@
       <c r="I22" s="16"/>
       <c r="J22" s="14"/>
       <c r="K22" s="6"/>
-    </row>
-    <row r="23" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M22" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -1088,13 +1339,26 @@
       </c>
       <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5418-rt3</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5418-rt4</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
-    </row>
-    <row r="24" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M23" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N23" s="8">
+        <v>3</v>
+      </c>
+      <c r="O23" s="8" t="str">
+        <f>P3</f>
+        <v>5418-rt4</v>
+      </c>
+      <c r="P23" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -1114,8 +1378,17 @@
         <v>4</v>
       </c>
       <c r="K24" s="6"/>
-    </row>
-    <row r="25" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M24" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="N24" s="15" t="str">
+        <f>N4</f>
+        <v>Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O24" s="16"/>
+      <c r="P24" s="14"/>
+    </row>
+    <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -1130,14 +1403,23 @@
       </c>
       <c r="I25" s="8" t="str">
         <f>I20</f>
-        <v>5418-rt3</v>
+        <v>5418-rt4</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>21</v>
       </c>
       <c r="K25" s="6"/>
-    </row>
-    <row r="26" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M25" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="N25" s="15" t="str">
+        <f>M23 &amp; "." &amp; N23 &amp; "-" &amp; N24</f>
+        <v>v1.2.3-Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O25" s="16"/>
+      <c r="P25" s="14"/>
+    </row>
+    <row r="26" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -1154,8 +1436,17 @@
       <c r="I26" s="16"/>
       <c r="J26" s="14"/>
       <c r="K26" s="6"/>
-    </row>
-    <row r="27" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M26" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N26" s="15" t="str">
+        <f>N25 &amp; "-build-" &amp; O23</f>
+        <v>v1.2.3-Classic_Reimagined_Lite-build-5418-rt4</v>
+      </c>
+      <c r="O26" s="16"/>
+      <c r="P26" s="6"/>
+    </row>
+    <row r="27" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -1172,8 +1463,20 @@
       <c r="I27" s="16"/>
       <c r="J27" s="14"/>
       <c r="K27" s="6"/>
-    </row>
-    <row r="28" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M27" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O27" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -1185,13 +1488,26 @@
       </c>
       <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5418-rt3</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5418-rt4</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
-    </row>
-    <row r="29" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M28" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N28" s="8">
+        <v>2</v>
+      </c>
+      <c r="O28" s="8" t="str">
+        <f>O23</f>
+        <v>5418-rt4</v>
+      </c>
+      <c r="P28" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -1205,8 +1521,17 @@
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
-    </row>
-    <row r="30" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M29" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="N29" s="15" t="str">
+        <f>N24</f>
+        <v>Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O29" s="16"/>
+      <c r="P29" s="14"/>
+    </row>
+    <row r="30" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -1226,8 +1551,17 @@
         <v>4</v>
       </c>
       <c r="K30" s="6"/>
-    </row>
-    <row r="31" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M30" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="N30" s="15" t="str">
+        <f>M28 &amp; "." &amp; N28 &amp; "-" &amp; N29</f>
+        <v>v1.2.2-Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O30" s="16"/>
+      <c r="P30" s="14"/>
+    </row>
+    <row r="31" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -1242,14 +1576,23 @@
       </c>
       <c r="I31" s="8" t="str">
         <f>I25</f>
-        <v>5418-rt3</v>
+        <v>5418-rt4</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>23</v>
       </c>
       <c r="K31" s="6"/>
-    </row>
-    <row r="32" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M31" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N31" s="15" t="str">
+        <f>N30 &amp; "-build-" &amp; O28</f>
+        <v>v1.2.2-Classic_Reimagined_Lite-build-5418-rt4</v>
+      </c>
+      <c r="O31" s="16"/>
+      <c r="P31" s="6"/>
+    </row>
+    <row r="32" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -1266,8 +1609,20 @@
       <c r="I32" s="16"/>
       <c r="J32" s="14"/>
       <c r="K32" s="6"/>
-    </row>
-    <row r="33" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O32" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -1284,8 +1639,21 @@
       <c r="I33" s="16"/>
       <c r="J33" s="14"/>
       <c r="K33" s="6"/>
-    </row>
-    <row r="34" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M33" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N33" s="8">
+        <v>1</v>
+      </c>
+      <c r="O33" s="8" t="str">
+        <f>O28</f>
+        <v>5418-rt4</v>
+      </c>
+      <c r="P33" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -1297,13 +1665,22 @@
       </c>
       <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5418-rt3</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5418-rt4</v>
       </c>
       <c r="I34" s="16"/>
       <c r="J34" s="6"/>
       <c r="K34" s="6"/>
-    </row>
-    <row r="35" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M34" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="N34" s="15" t="str">
+        <f>N29</f>
+        <v>Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O34" s="16"/>
+      <c r="P34" s="14"/>
+    </row>
+    <row r="35" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -1317,8 +1694,17 @@
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
       <c r="K35" s="6"/>
-    </row>
-    <row r="36" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M35" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="N35" s="15" t="str">
+        <f>M33 &amp; "." &amp; N33 &amp; "-" &amp; N34</f>
+        <v>v1.2.1-Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O35" s="16"/>
+      <c r="P35" s="14"/>
+    </row>
+    <row r="36" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -1338,8 +1724,17 @@
         <v>4</v>
       </c>
       <c r="K36" s="6"/>
-    </row>
-    <row r="37" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M36" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N36" s="15" t="str">
+        <f>N35 &amp; "-build-" &amp; O33</f>
+        <v>v1.2.1-Classic_Reimagined_Lite-build-5418-rt4</v>
+      </c>
+      <c r="O36" s="16"/>
+      <c r="P36" s="6"/>
+    </row>
+    <row r="37" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -1354,14 +1749,26 @@
       </c>
       <c r="I37" s="8" t="str">
         <f>I31</f>
-        <v>5418-rt3</v>
+        <v>5418-rt4</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>25</v>
       </c>
       <c r="K37" s="6"/>
-    </row>
-    <row r="38" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M37" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O37" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="P37" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -1377,8 +1784,21 @@
       <c r="I38" s="16"/>
       <c r="J38" s="14"/>
       <c r="K38" s="6"/>
-    </row>
-    <row r="39" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M38" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N38" s="8">
+        <v>0</v>
+      </c>
+      <c r="O38" s="8" t="str">
+        <f>O33</f>
+        <v>5418-rt4</v>
+      </c>
+      <c r="P38" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1395,8 +1815,17 @@
       <c r="I39" s="16"/>
       <c r="J39" s="14"/>
       <c r="K39" s="6"/>
-    </row>
-    <row r="40" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M39" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="N39" s="15" t="str">
+        <f>N34</f>
+        <v>Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O39" s="16"/>
+      <c r="P39" s="14"/>
+    </row>
+    <row r="40" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1408,13 +1837,22 @@
       </c>
       <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5418-rt3</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5418-rt4</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="6"/>
       <c r="K40" s="6"/>
-    </row>
-    <row r="41" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M40" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="N40" s="15" t="str">
+        <f>M38 &amp; "." &amp; N38 &amp; "-" &amp; N39</f>
+        <v>v1.2.0-Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O40" s="16"/>
+      <c r="P40" s="14"/>
+    </row>
+    <row r="41" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1428,8 +1866,17 @@
       <c r="I41" s="6"/>
       <c r="J41" s="6"/>
       <c r="K41" s="6"/>
-    </row>
-    <row r="42" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M41" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N41" s="15" t="str">
+        <f>N40 &amp; "-build-" &amp; O38</f>
+        <v>v1.2.0-Classic_Reimagined_Lite-build-5418-rt4</v>
+      </c>
+      <c r="O41" s="16"/>
+      <c r="P41" s="6"/>
+    </row>
+    <row r="42" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -1449,8 +1896,20 @@
         <v>4</v>
       </c>
       <c r="K42" s="6"/>
-    </row>
-    <row r="43" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M42" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N42" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O42" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -1465,14 +1924,27 @@
       </c>
       <c r="I43" s="8" t="str">
         <f>I37</f>
-        <v>5418-rt3</v>
+        <v>5418-rt4</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>28</v>
       </c>
       <c r="K43" s="6"/>
-    </row>
-    <row r="44" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M43" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="N43" s="8">
+        <v>1</v>
+      </c>
+      <c r="O43" s="8" t="str">
+        <f>O38</f>
+        <v>5418-rt4</v>
+      </c>
+      <c r="P43" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -1488,8 +1960,17 @@
       <c r="I44" s="16"/>
       <c r="J44" s="14"/>
       <c r="K44" s="6"/>
-    </row>
-    <row r="45" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M44" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="N44" s="15" t="str">
+        <f>N39</f>
+        <v>Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O44" s="16"/>
+      <c r="P44" s="14"/>
+    </row>
+    <row r="45" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -1506,8 +1987,17 @@
       <c r="I45" s="16"/>
       <c r="J45" s="14"/>
       <c r="K45" s="6"/>
-    </row>
-    <row r="46" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M45" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="N45" s="15" t="str">
+        <f>M43 &amp; "." &amp; N43 &amp; "-" &amp; N44</f>
+        <v>v1.1.1-Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O45" s="16"/>
+      <c r="P45" s="14"/>
+    </row>
+    <row r="46" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -1519,13 +2009,22 @@
       </c>
       <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5418-rt3</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5418-rt4</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
-    </row>
-    <row r="47" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M46" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N46" s="15" t="str">
+        <f>N45 &amp; "-build-" &amp; O43</f>
+        <v>v1.1.1-Classic_Reimagined_Lite-build-5418-rt4</v>
+      </c>
+      <c r="O46" s="16"/>
+      <c r="P46" s="6"/>
+    </row>
+    <row r="47" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -1539,8 +2038,20 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="6"/>
-    </row>
-    <row r="48" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M47" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -1554,8 +2065,21 @@
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
-    </row>
-    <row r="49" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M48" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="N48" s="8">
+        <v>0</v>
+      </c>
+      <c r="O48" s="8" t="str">
+        <f>O43</f>
+        <v>5418-rt4</v>
+      </c>
+      <c r="P48" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -1575,8 +2099,17 @@
         <v>4</v>
       </c>
       <c r="K49" s="6"/>
-    </row>
-    <row r="50" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M49" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="N49" s="15" t="str">
+        <f>N44</f>
+        <v>Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O49" s="16"/>
+      <c r="P49" s="14"/>
+    </row>
+    <row r="50" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -1591,14 +2124,23 @@
       </c>
       <c r="I50" s="8" t="str">
         <f>I43</f>
-        <v>5418-rt3</v>
+        <v>5418-rt4</v>
       </c>
       <c r="J50" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K50" s="6"/>
-    </row>
-    <row r="51" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M50" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="N50" s="15" t="str">
+        <f>M48 &amp; "." &amp; N48 &amp; "-" &amp; N49</f>
+        <v>v1.1.0-Classic_Reimagined_Lite</v>
+      </c>
+      <c r="O50" s="16"/>
+      <c r="P50" s="14"/>
+    </row>
+    <row r="51" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -1614,8 +2156,17 @@
       <c r="I51" s="16"/>
       <c r="J51" s="14"/>
       <c r="K51" s="6"/>
-    </row>
-    <row r="52" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M51" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N51" s="15" t="str">
+        <f>N50 &amp; "-build-" &amp; O48</f>
+        <v>v1.1.0-Classic_Reimagined_Lite-build-5418-rt4</v>
+      </c>
+      <c r="O51" s="16"/>
+      <c r="P51" s="6"/>
+    </row>
+    <row r="52" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -1633,7 +2184,7 @@
       <c r="J52" s="14"/>
       <c r="K52" s="6"/>
     </row>
-    <row r="53" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -1645,13 +2196,13 @@
       </c>
       <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5418-rt3</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5418-rt4</v>
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
     </row>
-    <row r="54" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -1666,7 +2217,7 @@
       <c r="J54" s="6"/>
       <c r="K54" s="6"/>
     </row>
-    <row r="55" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -1687,7 +2238,7 @@
       </c>
       <c r="K55" s="6"/>
     </row>
-    <row r="56" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -1702,14 +2253,14 @@
       </c>
       <c r="I56" s="8" t="str">
         <f>I50</f>
-        <v>5418-rt3</v>
+        <v>5418-rt4</v>
       </c>
       <c r="J56" s="8" t="s">
         <v>35</v>
       </c>
       <c r="K56" s="6"/>
     </row>
-    <row r="57" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -1726,7 +2277,7 @@
       <c r="J57" s="14"/>
       <c r="K57" s="6"/>
     </row>
-    <row r="58" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -1744,7 +2295,7 @@
       <c r="J58" s="14"/>
       <c r="K58" s="6"/>
     </row>
-    <row r="59" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -1756,13 +2307,13 @@
       </c>
       <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5418-rt3</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5418-rt4</v>
       </c>
       <c r="I59" s="16"/>
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
     </row>
-    <row r="60" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -1777,7 +2328,7 @@
       <c r="J60" s="17"/>
       <c r="K60" s="6"/>
     </row>
-    <row r="61" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -1798,7 +2349,7 @@
       </c>
       <c r="K61" s="6"/>
     </row>
-    <row r="62" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -1813,14 +2364,14 @@
       </c>
       <c r="I62" s="8" t="str">
         <f>I56</f>
-        <v>5418-rt3</v>
+        <v>5418-rt4</v>
       </c>
       <c r="J62" s="8" t="s">
         <v>38</v>
       </c>
       <c r="K62" s="6"/>
     </row>
-    <row r="63" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -1837,7 +2388,7 @@
       <c r="J63" s="14"/>
       <c r="K63" s="6"/>
     </row>
-    <row r="64" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -1867,18 +2418,19 @@
       </c>
       <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5418-rt3</v>
+        <v>v7.11.3-Better_Default_7-build-5418-rt4</v>
       </c>
       <c r="I65" s="16"/>
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="C5:E5"/>
+    <mergeCell ref="M1:Q1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2335,11 +2887,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2352,6 +2899,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C381E3-9D83-4830-8B3D-525450BC188E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439D96C4-95AA-456B-8109-D2786F3E5B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="68">
   <si>
     <t>Current version in development</t>
   </si>
@@ -232,6 +232,12 @@
   </si>
   <si>
     <t>1.21.6</t>
+  </si>
+  <si>
+    <t>Created Classic Reimagined Lite</t>
+  </si>
+  <si>
+    <t>Lite version</t>
   </si>
 </sst>
 </file>
@@ -388,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -419,12 +425,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -443,6 +443,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -452,8 +455,19 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -667,20 +681,22 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="M1" s="29" t="s">
+      <c r="M1" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
     </row>
     <row r="2" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
+      <c r="B2" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="31"/>
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
@@ -711,15 +727,18 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="str">
+      <c r="A3" s="29" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5418-rt4</v>
-      </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
+        <v>v10.0.11_1-build-5423-rt4</v>
+      </c>
+      <c r="B3" s="32" t="str">
+        <f>"v1.2.7_1-build-" &amp; D3 &amp; "-" &amp; E3</f>
+        <v>v1.2.7_1-build-5423-rt4-26.1</v>
+      </c>
+      <c r="C3" s="33"/>
       <c r="D3" s="8" t="str">
-        <f>SUM(2601,664,2026,127) &amp; "-rt4"</f>
-        <v>5418-rt4</v>
+        <f>SUM(2601,664,2026,132) &amp; "-rt4"</f>
+        <v>5423-rt4</v>
       </c>
       <c r="E3" s="7">
         <f>K4</f>
@@ -751,7 +770,7 @@
       </c>
       <c r="P3" s="8" t="str">
         <f>J4</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="Q3" s="8">
         <v>26.1</v>
@@ -764,11 +783,11 @@
       <c r="B4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="22"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="20"/>
       <c r="G4" s="8" t="s">
         <v>11</v>
       </c>
@@ -780,7 +799,7 @@
       </c>
       <c r="J4" s="8" t="str">
         <f>D3</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="K4" s="8">
         <v>26.1</v>
@@ -797,13 +816,15 @@
       <c r="Q4" s="14"/>
     </row>
     <row r="5" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
+      <c r="A5" s="6" t="s">
+        <v>66</v>
+      </c>
       <c r="B5" s="6"/>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="24"/>
-      <c r="E5" s="25"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="23"/>
       <c r="G5" s="10" t="s">
         <v>13</v>
       </c>
@@ -847,7 +868,7 @@
       </c>
       <c r="N6" s="11" t="str">
         <f>N5 &amp; "-build-" &amp; P3</f>
-        <v>v1.2.7_1-Classic_Reimagined_Lite-build-5418-rt4</v>
+        <v>v1.2.7_1-Classic_Reimagined_Lite-build-5423-rt4</v>
       </c>
       <c r="O6" s="12"/>
       <c r="P6" s="13"/>
@@ -865,7 +886,7 @@
       </c>
       <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5418-rt4</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5423-rt4</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13"/>
@@ -905,7 +926,7 @@
       </c>
       <c r="O8" s="8" t="str">
         <f>P3</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="P8" s="8" t="s">
         <v>18</v>
@@ -956,7 +977,7 @@
       </c>
       <c r="I10" s="8" t="str">
         <f>J4</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>18</v>
@@ -994,7 +1015,7 @@
       </c>
       <c r="N11" s="15" t="str">
         <f>N10 &amp; "-build-" &amp; O8</f>
-        <v>v1.2.6-Classic_Reimagined_Lite-build-5418-rt4</v>
+        <v>v1.2.6-Classic_Reimagined_Lite-build-5423-rt4</v>
       </c>
       <c r="O11" s="16"/>
       <c r="P11" s="6"/>
@@ -1041,7 +1062,7 @@
       </c>
       <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5418-rt4</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5423-rt4</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="6"/>
@@ -1054,7 +1075,7 @@
       </c>
       <c r="O13" s="8" t="str">
         <f>P3</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="P13" s="8" t="s">
         <v>19</v>
@@ -1105,7 +1126,7 @@
       </c>
       <c r="I15" s="8" t="str">
         <f>I10</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>19</v>
@@ -1143,7 +1164,7 @@
       </c>
       <c r="N16" s="15" t="str">
         <f>N15 &amp; "-build-" &amp; O13</f>
-        <v>v1.2.5-Classic_Reimagined_Lite-build-5418-rt4</v>
+        <v>v1.2.5-Classic_Reimagined_Lite-build-5423-rt4</v>
       </c>
       <c r="O16" s="16"/>
       <c r="P16" s="6"/>
@@ -1190,7 +1211,7 @@
       </c>
       <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5418-rt4</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5423-rt4</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="6"/>
@@ -1203,7 +1224,7 @@
       </c>
       <c r="O18" s="8" t="str">
         <f>P3</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="P18" s="8" t="s">
         <v>65</v>
@@ -1254,7 +1275,7 @@
       </c>
       <c r="I20" s="8" t="str">
         <f>I15</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="J20" s="8" t="s">
         <v>20</v>
@@ -1292,7 +1313,7 @@
       </c>
       <c r="N21" s="15" t="str">
         <f>N20 &amp; "-build-" &amp; O18</f>
-        <v>v1.2.4-Classic_Reimagined_Lite-build-5418-rt4</v>
+        <v>v1.2.4-Classic_Reimagined_Lite-build-5423-rt4</v>
       </c>
       <c r="O21" s="16"/>
       <c r="P21" s="6"/>
@@ -1339,7 +1360,7 @@
       </c>
       <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5418-rt4</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5423-rt4</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="6"/>
@@ -1352,7 +1373,7 @@
       </c>
       <c r="O23" s="8" t="str">
         <f>P3</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="P23" s="8" t="s">
         <v>21</v>
@@ -1403,7 +1424,7 @@
       </c>
       <c r="I25" s="8" t="str">
         <f>I20</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>21</v>
@@ -1441,7 +1462,7 @@
       </c>
       <c r="N26" s="15" t="str">
         <f>N25 &amp; "-build-" &amp; O23</f>
-        <v>v1.2.3-Classic_Reimagined_Lite-build-5418-rt4</v>
+        <v>v1.2.3-Classic_Reimagined_Lite-build-5423-rt4</v>
       </c>
       <c r="O26" s="16"/>
       <c r="P26" s="6"/>
@@ -1488,7 +1509,7 @@
       </c>
       <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5418-rt4</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5423-rt4</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="6"/>
@@ -1501,7 +1522,7 @@
       </c>
       <c r="O28" s="8" t="str">
         <f>O23</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="P28" s="8" t="s">
         <v>23</v>
@@ -1576,7 +1597,7 @@
       </c>
       <c r="I31" s="8" t="str">
         <f>I25</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>23</v>
@@ -1587,7 +1608,7 @@
       </c>
       <c r="N31" s="15" t="str">
         <f>N30 &amp; "-build-" &amp; O28</f>
-        <v>v1.2.2-Classic_Reimagined_Lite-build-5418-rt4</v>
+        <v>v1.2.2-Classic_Reimagined_Lite-build-5423-rt4</v>
       </c>
       <c r="O31" s="16"/>
       <c r="P31" s="6"/>
@@ -1647,7 +1668,7 @@
       </c>
       <c r="O33" s="8" t="str">
         <f>O28</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="P33" s="8" t="s">
         <v>25</v>
@@ -1665,7 +1686,7 @@
       </c>
       <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5418-rt4</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5423-rt4</v>
       </c>
       <c r="I34" s="16"/>
       <c r="J34" s="6"/>
@@ -1729,7 +1750,7 @@
       </c>
       <c r="N36" s="15" t="str">
         <f>N35 &amp; "-build-" &amp; O33</f>
-        <v>v1.2.1-Classic_Reimagined_Lite-build-5418-rt4</v>
+        <v>v1.2.1-Classic_Reimagined_Lite-build-5423-rt4</v>
       </c>
       <c r="O36" s="16"/>
       <c r="P36" s="6"/>
@@ -1749,7 +1770,7 @@
       </c>
       <c r="I37" s="8" t="str">
         <f>I31</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>25</v>
@@ -1792,7 +1813,7 @@
       </c>
       <c r="O38" s="8" t="str">
         <f>O33</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="P38" s="8" t="s">
         <v>28</v>
@@ -1837,7 +1858,7 @@
       </c>
       <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5418-rt4</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5423-rt4</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="6"/>
@@ -1871,7 +1892,7 @@
       </c>
       <c r="N41" s="15" t="str">
         <f>N40 &amp; "-build-" &amp; O38</f>
-        <v>v1.2.0-Classic_Reimagined_Lite-build-5418-rt4</v>
+        <v>v1.2.0-Classic_Reimagined_Lite-build-5423-rt4</v>
       </c>
       <c r="O41" s="16"/>
       <c r="P41" s="6"/>
@@ -1924,7 +1945,7 @@
       </c>
       <c r="I43" s="8" t="str">
         <f>I37</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>28</v>
@@ -1938,7 +1959,7 @@
       </c>
       <c r="O43" s="8" t="str">
         <f>O38</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="P43" s="8" t="s">
         <v>33</v>
@@ -2009,7 +2030,7 @@
       </c>
       <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5418-rt4</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5423-rt4</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="6"/>
@@ -2019,7 +2040,7 @@
       </c>
       <c r="N46" s="15" t="str">
         <f>N45 &amp; "-build-" &amp; O43</f>
-        <v>v1.1.1-Classic_Reimagined_Lite-build-5418-rt4</v>
+        <v>v1.1.1-Classic_Reimagined_Lite-build-5423-rt4</v>
       </c>
       <c r="O46" s="16"/>
       <c r="P46" s="6"/>
@@ -2073,7 +2094,7 @@
       </c>
       <c r="O48" s="8" t="str">
         <f>O43</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="P48" s="8" t="s">
         <v>35</v>
@@ -2124,7 +2145,7 @@
       </c>
       <c r="I50" s="8" t="str">
         <f>I43</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="J50" s="8" t="s">
         <v>33</v>
@@ -2161,7 +2182,7 @@
       </c>
       <c r="N51" s="15" t="str">
         <f>N50 &amp; "-build-" &amp; O48</f>
-        <v>v1.1.0-Classic_Reimagined_Lite-build-5418-rt4</v>
+        <v>v1.1.0-Classic_Reimagined_Lite-build-5423-rt4</v>
       </c>
       <c r="O51" s="16"/>
       <c r="P51" s="6"/>
@@ -2196,7 +2217,7 @@
       </c>
       <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5418-rt4</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5423-rt4</v>
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="6"/>
@@ -2253,7 +2274,7 @@
       </c>
       <c r="I56" s="8" t="str">
         <f>I50</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="J56" s="8" t="s">
         <v>35</v>
@@ -2307,7 +2328,7 @@
       </c>
       <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5418-rt4</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5423-rt4</v>
       </c>
       <c r="I59" s="16"/>
       <c r="J59" s="6"/>
@@ -2364,7 +2385,7 @@
       </c>
       <c r="I62" s="8" t="str">
         <f>I56</f>
-        <v>5418-rt4</v>
+        <v>5423-rt4</v>
       </c>
       <c r="J62" s="8" t="s">
         <v>38</v>
@@ -2418,7 +2439,7 @@
       </c>
       <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5418-rt4</v>
+        <v>v7.11.3-Better_Default_7-build-5423-rt4</v>
       </c>
       <c r="I65" s="16"/>
       <c r="J65" s="6"/>
@@ -2426,11 +2447,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2446,12 +2467,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -2490,21 +2511,21 @@
       <c r="A5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="27"/>
+      <c r="C5" s="26"/>
       <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="26" t="str">
+      <c r="B6" s="25" t="str">
         <f>A4 &amp; "." &amp; B4 &amp; "." &amp; C4 &amp; "-" &amp; B5</f>
         <v>v6.0.7-Better_Default_6</v>
       </c>
-      <c r="C6" s="27"/>
+      <c r="C6" s="26"/>
       <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2544,21 +2565,21 @@
       <c r="A10" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="27"/>
+      <c r="C10" s="26"/>
       <c r="D10" s="14"/>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="26" t="str">
+      <c r="B11" s="25" t="str">
         <f>A9 &amp; "." &amp; B9 &amp; "." &amp; C9 &amp; "-" &amp; B10</f>
         <v>v1.4.0-Better_Default_5</v>
       </c>
-      <c r="C11" s="27"/>
+      <c r="C11" s="26"/>
       <c r="D11" s="14"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2598,21 +2619,21 @@
       <c r="A15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="27"/>
+      <c r="C15" s="26"/>
       <c r="D15" s="14"/>
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="26" t="str">
+      <c r="B16" s="25" t="str">
         <f>A14 &amp; "." &amp; B14 &amp; "." &amp; C14 &amp; "-" &amp; B15</f>
         <v>v1.3.0-Better_Default_4</v>
       </c>
-      <c r="C16" s="27"/>
+      <c r="C16" s="26"/>
       <c r="D16" s="14"/>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2652,21 +2673,21 @@
       <c r="A20" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="27"/>
+      <c r="C20" s="26"/>
       <c r="D20" s="14"/>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="26" t="str">
+      <c r="B21" s="25" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
         <v>v1.2.2-Better_Default_3.1</v>
       </c>
-      <c r="C21" s="27"/>
+      <c r="C21" s="26"/>
       <c r="D21" s="14"/>
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2706,21 +2727,21 @@
       <c r="A25" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="26" t="s">
+      <c r="B25" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="27"/>
+      <c r="C25" s="26"/>
       <c r="D25" s="14"/>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="26" t="str">
+      <c r="B26" s="25" t="str">
         <f>A24 &amp; "." &amp; B24 &amp; "." &amp; C24 &amp; "-" &amp; B25</f>
         <v>v1.2.1-Better_Default_3</v>
       </c>
-      <c r="C26" s="27"/>
+      <c r="C26" s="26"/>
       <c r="D26" s="14"/>
     </row>
     <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2760,21 +2781,21 @@
       <c r="A30" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="26" t="s">
+      <c r="B30" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="27"/>
+      <c r="C30" s="26"/>
       <c r="D30" s="14"/>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="26" t="str">
+      <c r="B31" s="25" t="str">
         <f>A29 &amp; "." &amp; B29 &amp; "." &amp; C29 &amp; "-" &amp; B30</f>
         <v>v1.2.0-Better_Default_2</v>
       </c>
-      <c r="C31" s="27"/>
+      <c r="C31" s="26"/>
       <c r="D31" s="14"/>
     </row>
     <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2814,21 +2835,21 @@
       <c r="A35" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="26" t="s">
+      <c r="B35" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="27"/>
+      <c r="C35" s="26"/>
       <c r="D35" s="14"/>
     </row>
     <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="26" t="str">
+      <c r="B36" s="25" t="str">
         <f>A34 &amp; "." &amp; B34 &amp; "." &amp; C34 &amp; "-" &amp; B35</f>
         <v>v1.1.1-Better_Default</v>
       </c>
-      <c r="C36" s="27"/>
+      <c r="C36" s="26"/>
       <c r="D36" s="14"/>
     </row>
     <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2868,25 +2889,30 @@
       <c r="A40" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="26" t="s">
+      <c r="B40" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="27"/>
+      <c r="C40" s="26"/>
       <c r="D40" s="14"/>
     </row>
     <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="26" t="str">
+      <c r="B41" s="25" t="str">
         <f>A39 &amp; "." &amp; B39 &amp; "." &amp; C39 &amp; "-" &amp; B40</f>
         <v>v1.1.0-Better_Default</v>
       </c>
-      <c r="C41" s="27"/>
+      <c r="C41" s="26"/>
       <c r="D41" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2899,11 +2925,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439D96C4-95AA-456B-8109-D2786F3E5B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2E3A0F-1E4D-4BF0-99FF-E669000A48E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="69">
   <si>
     <t>Current version in development</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>Lite version</t>
+  </si>
+  <si>
+    <t>Update fog/discard behavior and lightmap sampling</t>
   </si>
 </sst>
 </file>
@@ -394,7 +397,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -425,6 +428,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -446,17 +450,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -467,6 +460,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -681,22 +683,22 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="M1" s="24" t="s">
+      <c r="M1" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
     </row>
     <row r="2" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="31"/>
+      <c r="C2" s="27"/>
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
@@ -727,15 +729,15 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="str">
+      <c r="A3" s="18" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
         <v>v10.0.11_1-build-5423-rt4</v>
       </c>
-      <c r="B3" s="32" t="str">
+      <c r="B3" s="28" t="str">
         <f>"v1.2.7_1-build-" &amp; D3 &amp; "-" &amp; E3</f>
         <v>v1.2.7_1-build-5423-rt4-26.1</v>
       </c>
-      <c r="C3" s="33"/>
+      <c r="C3" s="29"/>
       <c r="D3" s="8" t="str">
         <f>SUM(2601,664,2026,132) &amp; "-rt4"</f>
         <v>5423-rt4</v>
@@ -783,11 +785,11 @@
       <c r="B4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="21"/>
       <c r="G4" s="8" t="s">
         <v>11</v>
       </c>
@@ -820,11 +822,11 @@
         <v>66</v>
       </c>
       <c r="B5" s="6"/>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="24"/>
       <c r="G5" s="10" t="s">
         <v>13</v>
       </c>
@@ -847,7 +849,9 @@
       <c r="Q5" s="14"/>
     </row>
     <row r="6" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
+      <c r="A6" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -2467,12 +2471,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -2511,21 +2515,21 @@
       <c r="A5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="26"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="25" t="str">
+      <c r="B6" s="30" t="str">
         <f>A4 &amp; "." &amp; B4 &amp; "." &amp; C4 &amp; "-" &amp; B5</f>
         <v>v6.0.7-Better_Default_6</v>
       </c>
-      <c r="C6" s="26"/>
+      <c r="C6" s="31"/>
       <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2565,21 +2569,21 @@
       <c r="A10" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="26"/>
+      <c r="C10" s="31"/>
       <c r="D10" s="14"/>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="25" t="str">
+      <c r="B11" s="30" t="str">
         <f>A9 &amp; "." &amp; B9 &amp; "." &amp; C9 &amp; "-" &amp; B10</f>
         <v>v1.4.0-Better_Default_5</v>
       </c>
-      <c r="C11" s="26"/>
+      <c r="C11" s="31"/>
       <c r="D11" s="14"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2619,21 +2623,21 @@
       <c r="A15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="26"/>
+      <c r="C15" s="31"/>
       <c r="D15" s="14"/>
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="25" t="str">
+      <c r="B16" s="30" t="str">
         <f>A14 &amp; "." &amp; B14 &amp; "." &amp; C14 &amp; "-" &amp; B15</f>
         <v>v1.3.0-Better_Default_4</v>
       </c>
-      <c r="C16" s="26"/>
+      <c r="C16" s="31"/>
       <c r="D16" s="14"/>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2673,21 +2677,21 @@
       <c r="A20" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="26"/>
+      <c r="C20" s="31"/>
       <c r="D20" s="14"/>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="25" t="str">
+      <c r="B21" s="30" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
         <v>v1.2.2-Better_Default_3.1</v>
       </c>
-      <c r="C21" s="26"/>
+      <c r="C21" s="31"/>
       <c r="D21" s="14"/>
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2727,21 +2731,21 @@
       <c r="A25" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="26"/>
+      <c r="C25" s="31"/>
       <c r="D25" s="14"/>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="25" t="str">
+      <c r="B26" s="30" t="str">
         <f>A24 &amp; "." &amp; B24 &amp; "." &amp; C24 &amp; "-" &amp; B25</f>
         <v>v1.2.1-Better_Default_3</v>
       </c>
-      <c r="C26" s="26"/>
+      <c r="C26" s="31"/>
       <c r="D26" s="14"/>
     </row>
     <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2781,21 +2785,21 @@
       <c r="A30" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="26"/>
+      <c r="C30" s="31"/>
       <c r="D30" s="14"/>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="25" t="str">
+      <c r="B31" s="30" t="str">
         <f>A29 &amp; "." &amp; B29 &amp; "." &amp; C29 &amp; "-" &amp; B30</f>
         <v>v1.2.0-Better_Default_2</v>
       </c>
-      <c r="C31" s="26"/>
+      <c r="C31" s="31"/>
       <c r="D31" s="14"/>
     </row>
     <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2835,21 +2839,21 @@
       <c r="A35" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="26"/>
+      <c r="C35" s="31"/>
       <c r="D35" s="14"/>
     </row>
     <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="25" t="str">
+      <c r="B36" s="30" t="str">
         <f>A34 &amp; "." &amp; B34 &amp; "." &amp; C34 &amp; "-" &amp; B35</f>
         <v>v1.1.1-Better_Default</v>
       </c>
-      <c r="C36" s="26"/>
+      <c r="C36" s="31"/>
       <c r="D36" s="14"/>
     </row>
     <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2889,30 +2893,25 @@
       <c r="A40" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B40" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="26"/>
+      <c r="C40" s="31"/>
       <c r="D40" s="14"/>
     </row>
     <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="25" t="str">
+      <c r="B41" s="30" t="str">
         <f>A39 &amp; "." &amp; B39 &amp; "." &amp; C39 &amp; "-" &amp; B40</f>
         <v>v1.1.0-Better_Default</v>
       </c>
-      <c r="C41" s="26"/>
+      <c r="C41" s="31"/>
       <c r="D41" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2925,6 +2924,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2E3A0F-1E4D-4BF0-99FF-E669000A48E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6127E2A9-A6EF-471A-A31E-66E577BDC242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="65">
   <si>
     <t>Current version in development</t>
   </si>
@@ -220,18 +220,6 @@
   </si>
   <si>
     <t>Better Default 1.1</t>
-  </si>
-  <si>
-    <t>Classic Reimagined Lite version history</t>
-  </si>
-  <si>
-    <t>v1.2</t>
-  </si>
-  <si>
-    <t>v1.1</t>
-  </si>
-  <si>
-    <t>1.21.6</t>
   </si>
   <si>
     <t>Created Classic Reimagined Lite</t>
@@ -397,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -446,9 +434,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -661,14 +646,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr defaultColWidth="27.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="91.42578125" customWidth="1"/>
     <col min="2" max="2" width="54.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -683,22 +668,15 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="M1" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-    </row>
-    <row r="2" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="27"/>
+      <c r="B2" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="26"/>
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
@@ -712,35 +690,20 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
-      <c r="M2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5423-rt4</v>
-      </c>
-      <c r="B3" s="28" t="str">
+        <v>v10.0.11_1-build-5436-rt4</v>
+      </c>
+      <c r="B3" s="27" t="str">
         <f>"v1.2.7_1-build-" &amp; D3 &amp; "-" &amp; E3</f>
-        <v>v1.2.7_1-build-5423-rt4-26.1</v>
-      </c>
-      <c r="C3" s="29"/>
+        <v>v1.2.7_1-build-5436-rt4-26.1</v>
+      </c>
+      <c r="C3" s="28"/>
       <c r="D3" s="8" t="str">
-        <f>SUM(2601,664,2026,132) &amp; "-rt4"</f>
-        <v>5423-rt4</v>
+        <f>SUM(2601,664,2026,145) &amp; "-rt4"</f>
+        <v>5436-rt4</v>
       </c>
       <c r="E3" s="7">
         <f>K4</f>
@@ -761,24 +724,8 @@
       <c r="K3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="N3" s="8">
-        <v>7</v>
-      </c>
-      <c r="O3" s="8">
-        <v>1</v>
-      </c>
-      <c r="P3" s="8" t="str">
-        <f>J4</f>
-        <v>5423-rt4</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>26.1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
@@ -801,25 +748,15 @@
       </c>
       <c r="J4" s="8" t="str">
         <f>D3</f>
-        <v>5423-rt4</v>
+        <v>5436-rt4</v>
       </c>
       <c r="K4" s="8">
         <v>26.1</v>
       </c>
-      <c r="M4" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="N4" s="11" t="str">
-        <f>"Classic_Reimagined_Lite"</f>
-        <v>Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O4" s="12"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="14"/>
-    </row>
-    <row r="5" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="22" t="s">
@@ -837,20 +774,10 @@
       <c r="I5" s="12"/>
       <c r="J5" s="13"/>
       <c r="K5" s="14"/>
-      <c r="M5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="N5" s="11" t="str">
-        <f>M3 &amp; "." &amp; N3 &amp; "_" &amp; O3 &amp; "-" &amp; N4</f>
-        <v>v1.2.7_1-Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O5" s="12"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="14"/>
-    </row>
-    <row r="6" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -867,18 +794,8 @@
       <c r="I6" s="12"/>
       <c r="J6" s="13"/>
       <c r="K6" s="14"/>
-      <c r="M6" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="N6" s="11" t="str">
-        <f>N5 &amp; "-build-" &amp; P3</f>
-        <v>v1.2.7_1-Classic_Reimagined_Lite-build-5423-rt4</v>
-      </c>
-      <c r="O6" s="12"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="6"/>
-    </row>
-    <row r="7" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -890,25 +807,13 @@
       </c>
       <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5423-rt4</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5436-rt4</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13"/>
       <c r="K7" s="6"/>
-      <c r="M7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -922,21 +827,8 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
-      <c r="M8" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="N8" s="8">
-        <v>6</v>
-      </c>
-      <c r="O8" s="8" t="str">
-        <f>P3</f>
-        <v>5423-rt4</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -956,17 +848,8 @@
         <v>4</v>
       </c>
       <c r="K9" s="6"/>
-      <c r="M9" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="N9" s="15" t="str">
-        <f>N4</f>
-        <v>Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O9" s="16"/>
-      <c r="P9" s="14"/>
-    </row>
-    <row r="10" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -981,23 +864,14 @@
       </c>
       <c r="I10" s="8" t="str">
         <f>J4</f>
-        <v>5423-rt4</v>
+        <v>5436-rt4</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>18</v>
       </c>
       <c r="K10" s="6"/>
-      <c r="M10" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="N10" s="15" t="str">
-        <f>M8 &amp; "." &amp; N8 &amp; "-" &amp; N9</f>
-        <v>v1.2.6-Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O10" s="16"/>
-      <c r="P10" s="14"/>
-    </row>
-    <row r="11" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1014,17 +888,8 @@
       <c r="I11" s="16"/>
       <c r="J11" s="14"/>
       <c r="K11" s="6"/>
-      <c r="M11" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="N11" s="15" t="str">
-        <f>N10 &amp; "-build-" &amp; O8</f>
-        <v>v1.2.6-Classic_Reimagined_Lite-build-5423-rt4</v>
-      </c>
-      <c r="O11" s="16"/>
-      <c r="P11" s="6"/>
-    </row>
-    <row r="12" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -1041,20 +906,8 @@
       <c r="I12" s="16"/>
       <c r="J12" s="14"/>
       <c r="K12" s="6"/>
-      <c r="M12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O12" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1066,26 +919,13 @@
       </c>
       <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5423-rt4</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5436-rt4</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
-      <c r="M13" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="N13" s="8">
-        <v>5</v>
-      </c>
-      <c r="O13" s="8" t="str">
-        <f>P3</f>
-        <v>5423-rt4</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -1105,17 +945,8 @@
         <v>4</v>
       </c>
       <c r="K14" s="6"/>
-      <c r="M14" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="N14" s="15" t="str">
-        <f>N4</f>
-        <v>Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O14" s="16"/>
-      <c r="P14" s="14"/>
-    </row>
-    <row r="15" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -1130,23 +961,14 @@
       </c>
       <c r="I15" s="8" t="str">
         <f>I10</f>
-        <v>5423-rt4</v>
+        <v>5436-rt4</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>19</v>
       </c>
       <c r="K15" s="6"/>
-      <c r="M15" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="N15" s="15" t="str">
-        <f>M13 &amp; "." &amp; N13 &amp; "-" &amp; N14</f>
-        <v>v1.2.5-Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O15" s="16"/>
-      <c r="P15" s="14"/>
-    </row>
-    <row r="16" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -1163,17 +985,8 @@
       <c r="I16" s="16"/>
       <c r="J16" s="14"/>
       <c r="K16" s="6"/>
-      <c r="M16" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="N16" s="15" t="str">
-        <f>N15 &amp; "-build-" &amp; O13</f>
-        <v>v1.2.5-Classic_Reimagined_Lite-build-5423-rt4</v>
-      </c>
-      <c r="O16" s="16"/>
-      <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -1190,20 +1003,8 @@
       <c r="I17" s="16"/>
       <c r="J17" s="14"/>
       <c r="K17" s="6"/>
-      <c r="M17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O17" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -1215,26 +1016,13 @@
       </c>
       <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5423-rt4</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5436-rt4</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
-      <c r="M18" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="N18" s="8">
-        <v>4</v>
-      </c>
-      <c r="O18" s="8" t="str">
-        <f>P3</f>
-        <v>5423-rt4</v>
-      </c>
-      <c r="P18" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -1254,17 +1042,8 @@
         <v>4</v>
       </c>
       <c r="K19" s="6"/>
-      <c r="M19" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="N19" s="15" t="str">
-        <f>N4</f>
-        <v>Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O19" s="16"/>
-      <c r="P19" s="14"/>
-    </row>
-    <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -1279,23 +1058,14 @@
       </c>
       <c r="I20" s="8" t="str">
         <f>I15</f>
-        <v>5423-rt4</v>
+        <v>5436-rt4</v>
       </c>
       <c r="J20" s="8" t="s">
         <v>20</v>
       </c>
       <c r="K20" s="6"/>
-      <c r="M20" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="N20" s="15" t="str">
-        <f>M18 &amp; "." &amp; N18 &amp; "-" &amp; N19</f>
-        <v>v1.2.4-Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O20" s="16"/>
-      <c r="P20" s="14"/>
-    </row>
-    <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -1312,17 +1082,8 @@
       <c r="I21" s="16"/>
       <c r="J21" s="14"/>
       <c r="K21" s="6"/>
-      <c r="M21" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="N21" s="15" t="str">
-        <f>N20 &amp; "-build-" &amp; O18</f>
-        <v>v1.2.4-Classic_Reimagined_Lite-build-5423-rt4</v>
-      </c>
-      <c r="O21" s="16"/>
-      <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -1339,20 +1100,8 @@
       <c r="I22" s="16"/>
       <c r="J22" s="14"/>
       <c r="K22" s="6"/>
-      <c r="M22" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O22" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -1364,26 +1113,13 @@
       </c>
       <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5423-rt4</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5436-rt4</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
-      <c r="M23" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="N23" s="8">
-        <v>3</v>
-      </c>
-      <c r="O23" s="8" t="str">
-        <f>P3</f>
-        <v>5423-rt4</v>
-      </c>
-      <c r="P23" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -1403,17 +1139,8 @@
         <v>4</v>
       </c>
       <c r="K24" s="6"/>
-      <c r="M24" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="N24" s="15" t="str">
-        <f>N4</f>
-        <v>Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O24" s="16"/>
-      <c r="P24" s="14"/>
-    </row>
-    <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -1428,23 +1155,14 @@
       </c>
       <c r="I25" s="8" t="str">
         <f>I20</f>
-        <v>5423-rt4</v>
+        <v>5436-rt4</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>21</v>
       </c>
       <c r="K25" s="6"/>
-      <c r="M25" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="N25" s="15" t="str">
-        <f>M23 &amp; "." &amp; N23 &amp; "-" &amp; N24</f>
-        <v>v1.2.3-Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O25" s="16"/>
-      <c r="P25" s="14"/>
-    </row>
-    <row r="26" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -1461,17 +1179,8 @@
       <c r="I26" s="16"/>
       <c r="J26" s="14"/>
       <c r="K26" s="6"/>
-      <c r="M26" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="N26" s="15" t="str">
-        <f>N25 &amp; "-build-" &amp; O23</f>
-        <v>v1.2.3-Classic_Reimagined_Lite-build-5423-rt4</v>
-      </c>
-      <c r="O26" s="16"/>
-      <c r="P26" s="6"/>
-    </row>
-    <row r="27" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -1488,20 +1197,8 @@
       <c r="I27" s="16"/>
       <c r="J27" s="14"/>
       <c r="K27" s="6"/>
-      <c r="M27" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="N27" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O27" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -1513,26 +1210,13 @@
       </c>
       <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5423-rt4</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5436-rt4</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
-      <c r="M28" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="N28" s="8">
-        <v>2</v>
-      </c>
-      <c r="O28" s="8" t="str">
-        <f>O23</f>
-        <v>5423-rt4</v>
-      </c>
-      <c r="P28" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -1546,17 +1230,8 @@
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
-      <c r="M29" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="N29" s="15" t="str">
-        <f>N24</f>
-        <v>Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O29" s="16"/>
-      <c r="P29" s="14"/>
-    </row>
-    <row r="30" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -1576,17 +1251,8 @@
         <v>4</v>
       </c>
       <c r="K30" s="6"/>
-      <c r="M30" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="N30" s="15" t="str">
-        <f>M28 &amp; "." &amp; N28 &amp; "-" &amp; N29</f>
-        <v>v1.2.2-Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O30" s="16"/>
-      <c r="P30" s="14"/>
-    </row>
-    <row r="31" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -1601,23 +1267,14 @@
       </c>
       <c r="I31" s="8" t="str">
         <f>I25</f>
-        <v>5423-rt4</v>
+        <v>5436-rt4</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>23</v>
       </c>
       <c r="K31" s="6"/>
-      <c r="M31" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="N31" s="15" t="str">
-        <f>N30 &amp; "-build-" &amp; O28</f>
-        <v>v1.2.2-Classic_Reimagined_Lite-build-5423-rt4</v>
-      </c>
-      <c r="O31" s="16"/>
-      <c r="P31" s="6"/>
-    </row>
-    <row r="32" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -1634,20 +1291,8 @@
       <c r="I32" s="16"/>
       <c r="J32" s="14"/>
       <c r="K32" s="6"/>
-      <c r="M32" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="N32" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O32" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -1664,21 +1309,8 @@
       <c r="I33" s="16"/>
       <c r="J33" s="14"/>
       <c r="K33" s="6"/>
-      <c r="M33" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="N33" s="8">
-        <v>1</v>
-      </c>
-      <c r="O33" s="8" t="str">
-        <f>O28</f>
-        <v>5423-rt4</v>
-      </c>
-      <c r="P33" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -1690,22 +1322,13 @@
       </c>
       <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5423-rt4</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5436-rt4</v>
       </c>
       <c r="I34" s="16"/>
       <c r="J34" s="6"/>
       <c r="K34" s="6"/>
-      <c r="M34" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="N34" s="15" t="str">
-        <f>N29</f>
-        <v>Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O34" s="16"/>
-      <c r="P34" s="14"/>
-    </row>
-    <row r="35" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -1719,17 +1342,8 @@
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
       <c r="K35" s="6"/>
-      <c r="M35" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="N35" s="15" t="str">
-        <f>M33 &amp; "." &amp; N33 &amp; "-" &amp; N34</f>
-        <v>v1.2.1-Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O35" s="16"/>
-      <c r="P35" s="14"/>
-    </row>
-    <row r="36" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -1749,17 +1363,8 @@
         <v>4</v>
       </c>
       <c r="K36" s="6"/>
-      <c r="M36" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="N36" s="15" t="str">
-        <f>N35 &amp; "-build-" &amp; O33</f>
-        <v>v1.2.1-Classic_Reimagined_Lite-build-5423-rt4</v>
-      </c>
-      <c r="O36" s="16"/>
-      <c r="P36" s="6"/>
-    </row>
-    <row r="37" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -1774,26 +1379,14 @@
       </c>
       <c r="I37" s="8" t="str">
         <f>I31</f>
-        <v>5423-rt4</v>
+        <v>5436-rt4</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>25</v>
       </c>
       <c r="K37" s="6"/>
-      <c r="M37" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="N37" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O37" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="P37" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -1809,21 +1402,8 @@
       <c r="I38" s="16"/>
       <c r="J38" s="14"/>
       <c r="K38" s="6"/>
-      <c r="M38" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="N38" s="8">
-        <v>0</v>
-      </c>
-      <c r="O38" s="8" t="str">
-        <f>O33</f>
-        <v>5423-rt4</v>
-      </c>
-      <c r="P38" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1840,17 +1420,8 @@
       <c r="I39" s="16"/>
       <c r="J39" s="14"/>
       <c r="K39" s="6"/>
-      <c r="M39" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="N39" s="15" t="str">
-        <f>N34</f>
-        <v>Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O39" s="16"/>
-      <c r="P39" s="14"/>
-    </row>
-    <row r="40" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1862,22 +1433,13 @@
       </c>
       <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5423-rt4</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5436-rt4</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="6"/>
       <c r="K40" s="6"/>
-      <c r="M40" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="N40" s="15" t="str">
-        <f>M38 &amp; "." &amp; N38 &amp; "-" &amp; N39</f>
-        <v>v1.2.0-Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O40" s="16"/>
-      <c r="P40" s="14"/>
-    </row>
-    <row r="41" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1891,17 +1453,8 @@
       <c r="I41" s="6"/>
       <c r="J41" s="6"/>
       <c r="K41" s="6"/>
-      <c r="M41" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="N41" s="15" t="str">
-        <f>N40 &amp; "-build-" &amp; O38</f>
-        <v>v1.2.0-Classic_Reimagined_Lite-build-5423-rt4</v>
-      </c>
-      <c r="O41" s="16"/>
-      <c r="P41" s="6"/>
-    </row>
-    <row r="42" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -1921,20 +1474,8 @@
         <v>4</v>
       </c>
       <c r="K42" s="6"/>
-      <c r="M42" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="N42" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O42" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="P42" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -1949,27 +1490,14 @@
       </c>
       <c r="I43" s="8" t="str">
         <f>I37</f>
-        <v>5423-rt4</v>
+        <v>5436-rt4</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>28</v>
       </c>
       <c r="K43" s="6"/>
-      <c r="M43" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="N43" s="8">
-        <v>1</v>
-      </c>
-      <c r="O43" s="8" t="str">
-        <f>O38</f>
-        <v>5423-rt4</v>
-      </c>
-      <c r="P43" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -1985,17 +1513,8 @@
       <c r="I44" s="16"/>
       <c r="J44" s="14"/>
       <c r="K44" s="6"/>
-      <c r="M44" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="N44" s="15" t="str">
-        <f>N39</f>
-        <v>Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O44" s="16"/>
-      <c r="P44" s="14"/>
-    </row>
-    <row r="45" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -2012,17 +1531,8 @@
       <c r="I45" s="16"/>
       <c r="J45" s="14"/>
       <c r="K45" s="6"/>
-      <c r="M45" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="N45" s="15" t="str">
-        <f>M43 &amp; "." &amp; N43 &amp; "-" &amp; N44</f>
-        <v>v1.1.1-Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O45" s="16"/>
-      <c r="P45" s="14"/>
-    </row>
-    <row r="46" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -2034,22 +1544,13 @@
       </c>
       <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5423-rt4</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5436-rt4</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
-      <c r="M46" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="N46" s="15" t="str">
-        <f>N45 &amp; "-build-" &amp; O43</f>
-        <v>v1.1.1-Classic_Reimagined_Lite-build-5423-rt4</v>
-      </c>
-      <c r="O46" s="16"/>
-      <c r="P46" s="6"/>
-    </row>
-    <row r="47" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -2063,20 +1564,8 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="6"/>
-      <c r="M47" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="N47" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O47" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -2090,21 +1579,8 @@
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
-      <c r="M48" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="N48" s="8">
-        <v>0</v>
-      </c>
-      <c r="O48" s="8" t="str">
-        <f>O43</f>
-        <v>5423-rt4</v>
-      </c>
-      <c r="P48" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -2124,17 +1600,8 @@
         <v>4</v>
       </c>
       <c r="K49" s="6"/>
-      <c r="M49" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="N49" s="15" t="str">
-        <f>N44</f>
-        <v>Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O49" s="16"/>
-      <c r="P49" s="14"/>
-    </row>
-    <row r="50" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -2149,23 +1616,14 @@
       </c>
       <c r="I50" s="8" t="str">
         <f>I43</f>
-        <v>5423-rt4</v>
+        <v>5436-rt4</v>
       </c>
       <c r="J50" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K50" s="6"/>
-      <c r="M50" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="N50" s="15" t="str">
-        <f>M48 &amp; "." &amp; N48 &amp; "-" &amp; N49</f>
-        <v>v1.1.0-Classic_Reimagined_Lite</v>
-      </c>
-      <c r="O50" s="16"/>
-      <c r="P50" s="14"/>
-    </row>
-    <row r="51" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -2181,17 +1639,8 @@
       <c r="I51" s="16"/>
       <c r="J51" s="14"/>
       <c r="K51" s="6"/>
-      <c r="M51" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="N51" s="15" t="str">
-        <f>N50 &amp; "-build-" &amp; O48</f>
-        <v>v1.1.0-Classic_Reimagined_Lite-build-5423-rt4</v>
-      </c>
-      <c r="O51" s="16"/>
-      <c r="P51" s="6"/>
-    </row>
-    <row r="52" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -2209,7 +1658,7 @@
       <c r="J52" s="14"/>
       <c r="K52" s="6"/>
     </row>
-    <row r="53" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -2221,13 +1670,13 @@
       </c>
       <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5423-rt4</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5436-rt4</v>
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
     </row>
-    <row r="54" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -2242,7 +1691,7 @@
       <c r="J54" s="6"/>
       <c r="K54" s="6"/>
     </row>
-    <row r="55" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -2263,7 +1712,7 @@
       </c>
       <c r="K55" s="6"/>
     </row>
-    <row r="56" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -2278,14 +1727,14 @@
       </c>
       <c r="I56" s="8" t="str">
         <f>I50</f>
-        <v>5423-rt4</v>
+        <v>5436-rt4</v>
       </c>
       <c r="J56" s="8" t="s">
         <v>35</v>
       </c>
       <c r="K56" s="6"/>
     </row>
-    <row r="57" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -2302,7 +1751,7 @@
       <c r="J57" s="14"/>
       <c r="K57" s="6"/>
     </row>
-    <row r="58" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -2320,7 +1769,7 @@
       <c r="J58" s="14"/>
       <c r="K58" s="6"/>
     </row>
-    <row r="59" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -2332,13 +1781,13 @@
       </c>
       <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5423-rt4</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5436-rt4</v>
       </c>
       <c r="I59" s="16"/>
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
     </row>
-    <row r="60" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -2353,7 +1802,7 @@
       <c r="J60" s="17"/>
       <c r="K60" s="6"/>
     </row>
-    <row r="61" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -2374,7 +1823,7 @@
       </c>
       <c r="K61" s="6"/>
     </row>
-    <row r="62" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -2389,14 +1838,14 @@
       </c>
       <c r="I62" s="8" t="str">
         <f>I56</f>
-        <v>5423-rt4</v>
+        <v>5436-rt4</v>
       </c>
       <c r="J62" s="8" t="s">
         <v>38</v>
       </c>
       <c r="K62" s="6"/>
     </row>
-    <row r="63" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -2413,7 +1862,7 @@
       <c r="J63" s="14"/>
       <c r="K63" s="6"/>
     </row>
-    <row r="64" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -2443,17 +1892,16 @@
       </c>
       <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5423-rt4</v>
+        <v>v7.11.3-Better_Default_7-build-5436-rt4</v>
       </c>
       <c r="I65" s="16"/>
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="C5:E5"/>
-    <mergeCell ref="M1:Q1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
   </mergeCells>
@@ -2471,12 +1919,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -2515,21 +1963,21 @@
       <c r="A5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="31"/>
+      <c r="C5" s="30"/>
       <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="30" t="str">
+      <c r="B6" s="29" t="str">
         <f>A4 &amp; "." &amp; B4 &amp; "." &amp; C4 &amp; "-" &amp; B5</f>
         <v>v6.0.7-Better_Default_6</v>
       </c>
-      <c r="C6" s="31"/>
+      <c r="C6" s="30"/>
       <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2569,21 +2017,21 @@
       <c r="A10" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="31"/>
+      <c r="C10" s="30"/>
       <c r="D10" s="14"/>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="30" t="str">
+      <c r="B11" s="29" t="str">
         <f>A9 &amp; "." &amp; B9 &amp; "." &amp; C9 &amp; "-" &amp; B10</f>
         <v>v1.4.0-Better_Default_5</v>
       </c>
-      <c r="C11" s="31"/>
+      <c r="C11" s="30"/>
       <c r="D11" s="14"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2623,21 +2071,21 @@
       <c r="A15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="31"/>
+      <c r="C15" s="30"/>
       <c r="D15" s="14"/>
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="30" t="str">
+      <c r="B16" s="29" t="str">
         <f>A14 &amp; "." &amp; B14 &amp; "." &amp; C14 &amp; "-" &amp; B15</f>
         <v>v1.3.0-Better_Default_4</v>
       </c>
-      <c r="C16" s="31"/>
+      <c r="C16" s="30"/>
       <c r="D16" s="14"/>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2677,21 +2125,21 @@
       <c r="A20" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="31"/>
+      <c r="C20" s="30"/>
       <c r="D20" s="14"/>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="30" t="str">
+      <c r="B21" s="29" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
         <v>v1.2.2-Better_Default_3.1</v>
       </c>
-      <c r="C21" s="31"/>
+      <c r="C21" s="30"/>
       <c r="D21" s="14"/>
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2731,21 +2179,21 @@
       <c r="A25" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="31"/>
+      <c r="C25" s="30"/>
       <c r="D25" s="14"/>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="30" t="str">
+      <c r="B26" s="29" t="str">
         <f>A24 &amp; "." &amp; B24 &amp; "." &amp; C24 &amp; "-" &amp; B25</f>
         <v>v1.2.1-Better_Default_3</v>
       </c>
-      <c r="C26" s="31"/>
+      <c r="C26" s="30"/>
       <c r="D26" s="14"/>
     </row>
     <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2785,21 +2233,21 @@
       <c r="A30" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="30" t="s">
+      <c r="B30" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="31"/>
+      <c r="C30" s="30"/>
       <c r="D30" s="14"/>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="30" t="str">
+      <c r="B31" s="29" t="str">
         <f>A29 &amp; "." &amp; B29 &amp; "." &amp; C29 &amp; "-" &amp; B30</f>
         <v>v1.2.0-Better_Default_2</v>
       </c>
-      <c r="C31" s="31"/>
+      <c r="C31" s="30"/>
       <c r="D31" s="14"/>
     </row>
     <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2839,21 +2287,21 @@
       <c r="A35" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="30" t="s">
+      <c r="B35" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="31"/>
+      <c r="C35" s="30"/>
       <c r="D35" s="14"/>
     </row>
     <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="30" t="str">
+      <c r="B36" s="29" t="str">
         <f>A34 &amp; "." &amp; B34 &amp; "." &amp; C34 &amp; "-" &amp; B35</f>
         <v>v1.1.1-Better_Default</v>
       </c>
-      <c r="C36" s="31"/>
+      <c r="C36" s="30"/>
       <c r="D36" s="14"/>
     </row>
     <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2893,25 +2341,30 @@
       <c r="A40" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="30" t="s">
+      <c r="B40" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="31"/>
+      <c r="C40" s="30"/>
       <c r="D40" s="14"/>
     </row>
     <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="30" t="str">
+      <c r="B41" s="29" t="str">
         <f>A39 &amp; "." &amp; B39 &amp; "." &amp; C39 &amp; "-" &amp; B40</f>
         <v>v1.1.0-Better_Default</v>
       </c>
-      <c r="C41" s="31"/>
+      <c r="C41" s="30"/>
       <c r="D41" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2924,11 +2377,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6127E2A9-A6EF-471A-A31E-66E577BDC242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9172E0FF-F816-40AD-B97D-D3C8A97B9314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -225,10 +225,10 @@
     <t>Created Classic Reimagined Lite</t>
   </si>
   <si>
-    <t>Lite version</t>
-  </si>
-  <si>
     <t>Update fog/discard behavior and lightmap sampling</t>
+  </si>
+  <si>
+    <t>Replaced clamped skyfactor with pow-based sky_factor in lightmap shaders</t>
   </si>
 </sst>
 </file>
@@ -385,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -416,7 +416,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -454,6 +453,21 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -654,11 +668,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="35"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="G1" s="2" t="s">
@@ -670,13 +684,11 @@
       <c r="K1" s="2"/>
     </row>
     <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="26"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="25"/>
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
@@ -692,15 +704,12 @@
       <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="str">
+      <c r="A3" s="26" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
         <v>v10.0.11_1-build-5436-rt4</v>
       </c>
-      <c r="B3" s="27" t="str">
-        <f>"v1.2.7_1-build-" &amp; D3 &amp; "-" &amp; E3</f>
-        <v>v1.2.7_1-build-5436-rt4-26.1</v>
-      </c>
-      <c r="C3" s="28"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="27"/>
       <c r="D3" s="8" t="str">
         <f>SUM(2601,664,2026,145) &amp; "-rt4"</f>
         <v>5436-rt4</v>
@@ -732,11 +741,11 @@
       <c r="B4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="21"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="20"/>
       <c r="G4" s="8" t="s">
         <v>11</v>
       </c>
@@ -759,11 +768,11 @@
         <v>62</v>
       </c>
       <c r="B5" s="6"/>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="24"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="23"/>
       <c r="G5" s="10" t="s">
         <v>13</v>
       </c>
@@ -777,7 +786,7 @@
     </row>
     <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -796,7 +805,9 @@
       <c r="K6" s="14"/>
     </row>
     <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
+      <c r="A7" s="6" t="s">
+        <v>64</v>
+      </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -1899,11 +1910,12 @@
       <c r="K65" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="A1:C1"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="C5:E5"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1919,12 +1931,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -1963,21 +1975,21 @@
       <c r="A5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="30"/>
+      <c r="C5" s="29"/>
       <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="29" t="str">
+      <c r="B6" s="28" t="str">
         <f>A4 &amp; "." &amp; B4 &amp; "." &amp; C4 &amp; "-" &amp; B5</f>
         <v>v6.0.7-Better_Default_6</v>
       </c>
-      <c r="C6" s="30"/>
+      <c r="C6" s="29"/>
       <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2017,21 +2029,21 @@
       <c r="A10" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="30"/>
+      <c r="C10" s="29"/>
       <c r="D10" s="14"/>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="29" t="str">
+      <c r="B11" s="28" t="str">
         <f>A9 &amp; "." &amp; B9 &amp; "." &amp; C9 &amp; "-" &amp; B10</f>
         <v>v1.4.0-Better_Default_5</v>
       </c>
-      <c r="C11" s="30"/>
+      <c r="C11" s="29"/>
       <c r="D11" s="14"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2071,21 +2083,21 @@
       <c r="A15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="30"/>
+      <c r="C15" s="29"/>
       <c r="D15" s="14"/>
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="29" t="str">
+      <c r="B16" s="28" t="str">
         <f>A14 &amp; "." &amp; B14 &amp; "." &amp; C14 &amp; "-" &amp; B15</f>
         <v>v1.3.0-Better_Default_4</v>
       </c>
-      <c r="C16" s="30"/>
+      <c r="C16" s="29"/>
       <c r="D16" s="14"/>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2125,21 +2137,21 @@
       <c r="A20" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="30"/>
+      <c r="C20" s="29"/>
       <c r="D20" s="14"/>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="29" t="str">
+      <c r="B21" s="28" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
         <v>v1.2.2-Better_Default_3.1</v>
       </c>
-      <c r="C21" s="30"/>
+      <c r="C21" s="29"/>
       <c r="D21" s="14"/>
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2179,21 +2191,21 @@
       <c r="A25" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="30"/>
+      <c r="C25" s="29"/>
       <c r="D25" s="14"/>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="29" t="str">
+      <c r="B26" s="28" t="str">
         <f>A24 &amp; "." &amp; B24 &amp; "." &amp; C24 &amp; "-" &amp; B25</f>
         <v>v1.2.1-Better_Default_3</v>
       </c>
-      <c r="C26" s="30"/>
+      <c r="C26" s="29"/>
       <c r="D26" s="14"/>
     </row>
     <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2233,21 +2245,21 @@
       <c r="A30" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="29" t="s">
+      <c r="B30" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="30"/>
+      <c r="C30" s="29"/>
       <c r="D30" s="14"/>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="29" t="str">
+      <c r="B31" s="28" t="str">
         <f>A29 &amp; "." &amp; B29 &amp; "." &amp; C29 &amp; "-" &amp; B30</f>
         <v>v1.2.0-Better_Default_2</v>
       </c>
-      <c r="C31" s="30"/>
+      <c r="C31" s="29"/>
       <c r="D31" s="14"/>
     </row>
     <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2287,21 +2299,21 @@
       <c r="A35" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="29" t="s">
+      <c r="B35" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="30"/>
+      <c r="C35" s="29"/>
       <c r="D35" s="14"/>
     </row>
     <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="29" t="str">
+      <c r="B36" s="28" t="str">
         <f>A34 &amp; "." &amp; B34 &amp; "." &amp; C34 &amp; "-" &amp; B35</f>
         <v>v1.1.1-Better_Default</v>
       </c>
-      <c r="C36" s="30"/>
+      <c r="C36" s="29"/>
       <c r="D36" s="14"/>
     </row>
     <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2341,30 +2353,25 @@
       <c r="A40" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="29" t="s">
+      <c r="B40" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="30"/>
+      <c r="C40" s="29"/>
       <c r="D40" s="14"/>
     </row>
     <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="29" t="str">
+      <c r="B41" s="28" t="str">
         <f>A39 &amp; "." &amp; B39 &amp; "." &amp; C39 &amp; "-" &amp; B40</f>
         <v>v1.1.0-Better_Default</v>
       </c>
-      <c r="C41" s="30"/>
+      <c r="C41" s="29"/>
       <c r="D41" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2377,6 +2384,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9172E0FF-F816-40AD-B97D-D3C8A97B9314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FB4EBC-6186-4885-8E29-45ED60F40503}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Active releases and Changelog" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="68">
   <si>
     <t>Current version in development</t>
   </si>
@@ -229,13 +224,22 @@
   </si>
   <si>
     <t>Replaced clamped skyfactor with pow-based sky_factor in lightmap shaders</t>
+  </si>
+  <si>
+    <t>Added classic mob sounds</t>
+  </si>
+  <si>
+    <t>fixed cat sounds</t>
+  </si>
+  <si>
+    <t>Updated pack format (26.1)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -416,6 +420,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -434,16 +447,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -453,21 +472,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -661,18 +665,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K65"/>
-  <sheetFormatPr defaultColWidth="27.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="27.25" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="91.42578125" customWidth="1"/>
-    <col min="2" max="2" width="54.85546875" customWidth="1"/>
+    <col min="1" max="1" width="91.375" customWidth="1"/>
+    <col min="2" max="2" width="54.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:11" ht="16.5">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="35"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="20"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="G1" s="2" t="s">
@@ -683,12 +687,12 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+    <row r="2" spans="1:11" ht="16.5">
+      <c r="A2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="25"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="32"/>
       <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
@@ -703,16 +707,16 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="str">
+    <row r="3" spans="1:11" ht="16.5">
+      <c r="A3" s="27" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5436-rt4</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="27"/>
+        <v>v10.0.11_1-build-5456-rt4</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
       <c r="D3" s="8" t="str">
-        <f>SUM(2601,664,2026,145) &amp; "-rt4"</f>
-        <v>5436-rt4</v>
+        <f>SUM(2601,664,2026,165) &amp; "-rt4"</f>
+        <v>5456-rt4</v>
       </c>
       <c r="E3" s="7">
         <f>K4</f>
@@ -734,18 +738,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="16.5">
       <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="20"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="23"/>
       <c r="G4" s="8" t="s">
         <v>11</v>
       </c>
@@ -757,22 +761,22 @@
       </c>
       <c r="J4" s="8" t="str">
         <f>D3</f>
-        <v>5436-rt4</v>
+        <v>5456-rt4</v>
       </c>
       <c r="K4" s="8">
         <v>26.1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="16.5">
       <c r="A5" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B5" s="6"/>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="23"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="26"/>
       <c r="G5" s="10" t="s">
         <v>13</v>
       </c>
@@ -784,7 +788,7 @@
       <c r="J5" s="13"/>
       <c r="K5" s="14"/>
     </row>
-    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="16.5">
       <c r="A6" s="6" t="s">
         <v>63</v>
       </c>
@@ -804,7 +808,7 @@
       <c r="J6" s="13"/>
       <c r="K6" s="14"/>
     </row>
-    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="16.5">
       <c r="A7" s="6" t="s">
         <v>64</v>
       </c>
@@ -818,14 +822,16 @@
       </c>
       <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5436-rt4</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5456-rt4</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13"/>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
+    <row r="8" spans="1:11" ht="16.5">
+      <c r="A8" s="6" t="s">
+        <v>65</v>
+      </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -839,8 +845,10 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
+    <row r="9" spans="1:11" ht="16.5">
+      <c r="A9" s="6" t="s">
+        <v>66</v>
+      </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -860,8 +868,10 @@
       </c>
       <c r="K9" s="6"/>
     </row>
-    <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
+    <row r="10" spans="1:11" ht="16.5">
+      <c r="A10" s="6" t="s">
+        <v>67</v>
+      </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -875,14 +885,14 @@
       </c>
       <c r="I10" s="8" t="str">
         <f>J4</f>
-        <v>5436-rt4</v>
+        <v>5456-rt4</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>18</v>
       </c>
       <c r="K10" s="6"/>
     </row>
-    <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="16.5">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -900,7 +910,7 @@
       <c r="J11" s="14"/>
       <c r="K11" s="6"/>
     </row>
-    <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="16.5">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -918,7 +928,7 @@
       <c r="J12" s="14"/>
       <c r="K12" s="6"/>
     </row>
-    <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="16.5">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -930,13 +940,13 @@
       </c>
       <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5436-rt4</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5456-rt4</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
     </row>
-    <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="16.5">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -957,7 +967,7 @@
       </c>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="16.5">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -972,14 +982,14 @@
       </c>
       <c r="I15" s="8" t="str">
         <f>I10</f>
-        <v>5436-rt4</v>
+        <v>5456-rt4</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>19</v>
       </c>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="16.5">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -997,7 +1007,7 @@
       <c r="J16" s="14"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="16.5">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -1015,7 +1025,7 @@
       <c r="J17" s="14"/>
       <c r="K17" s="6"/>
     </row>
-    <row r="18" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="16.5">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -1027,13 +1037,13 @@
       </c>
       <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5436-rt4</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5456-rt4</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
     </row>
-    <row r="19" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="16.5">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -1054,7 +1064,7 @@
       </c>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="16.5">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -1069,14 +1079,14 @@
       </c>
       <c r="I20" s="8" t="str">
         <f>I15</f>
-        <v>5436-rt4</v>
+        <v>5456-rt4</v>
       </c>
       <c r="J20" s="8" t="s">
         <v>20</v>
       </c>
       <c r="K20" s="6"/>
     </row>
-    <row r="21" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="16.5">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -1094,7 +1104,7 @@
       <c r="J21" s="14"/>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="16.5">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -1112,7 +1122,7 @@
       <c r="J22" s="14"/>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="16.5">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -1124,13 +1134,13 @@
       </c>
       <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5436-rt4</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5456-rt4</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
     </row>
-    <row r="24" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="16.5">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -1151,7 +1161,7 @@
       </c>
       <c r="K24" s="6"/>
     </row>
-    <row r="25" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="16.5">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -1166,14 +1176,14 @@
       </c>
       <c r="I25" s="8" t="str">
         <f>I20</f>
-        <v>5436-rt4</v>
+        <v>5456-rt4</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>21</v>
       </c>
       <c r="K25" s="6"/>
     </row>
-    <row r="26" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="16.5">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -1191,7 +1201,7 @@
       <c r="J26" s="14"/>
       <c r="K26" s="6"/>
     </row>
-    <row r="27" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="16.5">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -1209,7 +1219,7 @@
       <c r="J27" s="14"/>
       <c r="K27" s="6"/>
     </row>
-    <row r="28" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="16.5">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -1221,13 +1231,13 @@
       </c>
       <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5436-rt4</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5456-rt4</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
     </row>
-    <row r="29" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="16.5">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -1242,7 +1252,7 @@
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
     </row>
-    <row r="30" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="16.5">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -1263,7 +1273,7 @@
       </c>
       <c r="K30" s="6"/>
     </row>
-    <row r="31" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="16.5">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -1278,14 +1288,14 @@
       </c>
       <c r="I31" s="8" t="str">
         <f>I25</f>
-        <v>5436-rt4</v>
+        <v>5456-rt4</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>23</v>
       </c>
       <c r="K31" s="6"/>
     </row>
-    <row r="32" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="16.5">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -1303,7 +1313,7 @@
       <c r="J32" s="14"/>
       <c r="K32" s="6"/>
     </row>
-    <row r="33" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="16.5">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -1321,7 +1331,7 @@
       <c r="J33" s="14"/>
       <c r="K33" s="6"/>
     </row>
-    <row r="34" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="16.5">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -1333,13 +1343,13 @@
       </c>
       <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5436-rt4</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5456-rt4</v>
       </c>
       <c r="I34" s="16"/>
       <c r="J34" s="6"/>
       <c r="K34" s="6"/>
     </row>
-    <row r="35" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="16.5">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -1354,7 +1364,7 @@
       <c r="J35" s="6"/>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="16.5">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -1375,7 +1385,7 @@
       </c>
       <c r="K36" s="6"/>
     </row>
-    <row r="37" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="16.5">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -1390,14 +1400,14 @@
       </c>
       <c r="I37" s="8" t="str">
         <f>I31</f>
-        <v>5436-rt4</v>
+        <v>5456-rt4</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>25</v>
       </c>
       <c r="K37" s="6"/>
     </row>
-    <row r="38" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" ht="16.5">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -1414,7 +1424,7 @@
       <c r="J38" s="14"/>
       <c r="K38" s="6"/>
     </row>
-    <row r="39" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="16.5">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1432,7 +1442,7 @@
       <c r="J39" s="14"/>
       <c r="K39" s="6"/>
     </row>
-    <row r="40" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="16.5">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1444,13 +1454,13 @@
       </c>
       <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5436-rt4</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5456-rt4</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="6"/>
       <c r="K40" s="6"/>
     </row>
-    <row r="41" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="16.5">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1465,7 +1475,7 @@
       <c r="J41" s="6"/>
       <c r="K41" s="6"/>
     </row>
-    <row r="42" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="16.5">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -1486,7 +1496,7 @@
       </c>
       <c r="K42" s="6"/>
     </row>
-    <row r="43" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="16.5">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -1501,14 +1511,14 @@
       </c>
       <c r="I43" s="8" t="str">
         <f>I37</f>
-        <v>5436-rt4</v>
+        <v>5456-rt4</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>28</v>
       </c>
       <c r="K43" s="6"/>
     </row>
-    <row r="44" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="16.5">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -1525,7 +1535,7 @@
       <c r="J44" s="14"/>
       <c r="K44" s="6"/>
     </row>
-    <row r="45" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="16.5">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -1543,7 +1553,7 @@
       <c r="J45" s="14"/>
       <c r="K45" s="6"/>
     </row>
-    <row r="46" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" ht="16.5">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -1555,13 +1565,13 @@
       </c>
       <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5436-rt4</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5456-rt4</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
     </row>
-    <row r="47" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" ht="16.5">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -1576,7 +1586,7 @@
       <c r="J47" s="2"/>
       <c r="K47" s="6"/>
     </row>
-    <row r="48" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="16.5">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -1591,7 +1601,7 @@
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
     </row>
-    <row r="49" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="16.5">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -1612,7 +1622,7 @@
       </c>
       <c r="K49" s="6"/>
     </row>
-    <row r="50" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" ht="16.5">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -1627,14 +1637,14 @@
       </c>
       <c r="I50" s="8" t="str">
         <f>I43</f>
-        <v>5436-rt4</v>
+        <v>5456-rt4</v>
       </c>
       <c r="J50" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K50" s="6"/>
     </row>
-    <row r="51" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" ht="16.5">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -1651,7 +1661,7 @@
       <c r="J51" s="14"/>
       <c r="K51" s="6"/>
     </row>
-    <row r="52" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" ht="16.5">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -1669,7 +1679,7 @@
       <c r="J52" s="14"/>
       <c r="K52" s="6"/>
     </row>
-    <row r="53" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" ht="16.5">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -1681,13 +1691,13 @@
       </c>
       <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5436-rt4</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5456-rt4</v>
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
     </row>
-    <row r="54" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" ht="16.5">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -1702,7 +1712,7 @@
       <c r="J54" s="6"/>
       <c r="K54" s="6"/>
     </row>
-    <row r="55" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" ht="16.5">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -1723,7 +1733,7 @@
       </c>
       <c r="K55" s="6"/>
     </row>
-    <row r="56" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" ht="16.5">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -1738,14 +1748,14 @@
       </c>
       <c r="I56" s="8" t="str">
         <f>I50</f>
-        <v>5436-rt4</v>
+        <v>5456-rt4</v>
       </c>
       <c r="J56" s="8" t="s">
         <v>35</v>
       </c>
       <c r="K56" s="6"/>
     </row>
-    <row r="57" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" ht="16.5">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -1762,7 +1772,7 @@
       <c r="J57" s="14"/>
       <c r="K57" s="6"/>
     </row>
-    <row r="58" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" ht="16.5">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -1780,7 +1790,7 @@
       <c r="J58" s="14"/>
       <c r="K58" s="6"/>
     </row>
-    <row r="59" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" ht="16.5">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -1792,13 +1802,13 @@
       </c>
       <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5436-rt4</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5456-rt4</v>
       </c>
       <c r="I59" s="16"/>
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
     </row>
-    <row r="60" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" ht="16.5">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -1813,7 +1823,7 @@
       <c r="J60" s="17"/>
       <c r="K60" s="6"/>
     </row>
-    <row r="61" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" ht="16.5">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -1834,7 +1844,7 @@
       </c>
       <c r="K61" s="6"/>
     </row>
-    <row r="62" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" ht="16.5">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -1849,14 +1859,14 @@
       </c>
       <c r="I62" s="8" t="str">
         <f>I56</f>
-        <v>5436-rt4</v>
+        <v>5456-rt4</v>
       </c>
       <c r="J62" s="8" t="s">
         <v>38</v>
       </c>
       <c r="K62" s="6"/>
     </row>
-    <row r="63" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" ht="16.5">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -1873,7 +1883,7 @@
       <c r="J63" s="14"/>
       <c r="K63" s="6"/>
     </row>
-    <row r="64" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" ht="16.5">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -1891,7 +1901,7 @@
       <c r="J64" s="14"/>
       <c r="K64" s="6"/>
     </row>
-    <row r="65" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" ht="16.5">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -1903,7 +1913,7 @@
       </c>
       <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5436-rt4</v>
+        <v>v7.11.3-Better_Default_7-build-5456-rt4</v>
       </c>
       <c r="I65" s="16"/>
       <c r="J65" s="6"/>
@@ -1925,25 +1935,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="4" width="27.42578125" customWidth="1"/>
+    <col min="1" max="4" width="27.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:4" ht="16.5">
+      <c r="A1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-    </row>
-    <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+    </row>
+    <row r="2" spans="1:4" ht="16.5">
       <c r="A2" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="16.5">
       <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
@@ -1957,7 +1967,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="16.5">
       <c r="A4" s="8" t="s">
         <v>43</v>
       </c>
@@ -1971,33 +1981,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="16.5">
       <c r="A5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="29"/>
+      <c r="C5" s="34"/>
       <c r="D5" s="14"/>
     </row>
-    <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="16.5">
       <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="28" t="str">
+      <c r="B6" s="33" t="str">
         <f>A4 &amp; "." &amp; B4 &amp; "." &amp; C4 &amp; "-" &amp; B5</f>
         <v>v6.0.7-Better_Default_6</v>
       </c>
-      <c r="C6" s="29"/>
+      <c r="C6" s="34"/>
       <c r="D6" s="14"/>
     </row>
-    <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="16.5">
       <c r="A7" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="16.5">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
@@ -2011,7 +2021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="16.5">
       <c r="A9" s="8" t="s">
         <v>47</v>
       </c>
@@ -2025,33 +2035,33 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="16.5">
       <c r="A10" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="29"/>
+      <c r="C10" s="34"/>
       <c r="D10" s="14"/>
     </row>
-    <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="16.5">
       <c r="A11" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="28" t="str">
+      <c r="B11" s="33" t="str">
         <f>A9 &amp; "." &amp; B9 &amp; "." &amp; C9 &amp; "-" &amp; B10</f>
         <v>v1.4.0-Better_Default_5</v>
       </c>
-      <c r="C11" s="29"/>
+      <c r="C11" s="34"/>
       <c r="D11" s="14"/>
     </row>
-    <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="16.5">
       <c r="A12" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="16.5">
       <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
@@ -2065,7 +2075,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="16.5">
       <c r="A14" s="8" t="s">
         <v>47</v>
       </c>
@@ -2079,33 +2089,33 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="16.5">
       <c r="A15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="29"/>
+      <c r="C15" s="34"/>
       <c r="D15" s="14"/>
     </row>
-    <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="16.5">
       <c r="A16" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="28" t="str">
+      <c r="B16" s="33" t="str">
         <f>A14 &amp; "." &amp; B14 &amp; "." &amp; C14 &amp; "-" &amp; B15</f>
         <v>v1.3.0-Better_Default_4</v>
       </c>
-      <c r="C16" s="29"/>
+      <c r="C16" s="34"/>
       <c r="D16" s="14"/>
     </row>
-    <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="16.5">
       <c r="A17" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="16.5">
       <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
@@ -2119,7 +2129,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="16.5">
       <c r="A19" s="8" t="s">
         <v>47</v>
       </c>
@@ -2133,33 +2143,33 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="16.5">
       <c r="A20" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="29"/>
+      <c r="C20" s="34"/>
       <c r="D20" s="14"/>
     </row>
-    <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="16.5">
       <c r="A21" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="28" t="str">
+      <c r="B21" s="33" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
         <v>v1.2.2-Better_Default_3.1</v>
       </c>
-      <c r="C21" s="29"/>
+      <c r="C21" s="34"/>
       <c r="D21" s="14"/>
     </row>
-    <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="16.5">
       <c r="A22" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="16.5">
       <c r="A23" s="4" t="s">
         <v>17</v>
       </c>
@@ -2173,7 +2183,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="16.5">
       <c r="A24" s="8" t="s">
         <v>47</v>
       </c>
@@ -2187,33 +2197,33 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="16.5">
       <c r="A25" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="29"/>
+      <c r="C25" s="34"/>
       <c r="D25" s="14"/>
     </row>
-    <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="16.5">
       <c r="A26" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="28" t="str">
+      <c r="B26" s="33" t="str">
         <f>A24 &amp; "." &amp; B24 &amp; "." &amp; C24 &amp; "-" &amp; B25</f>
         <v>v1.2.1-Better_Default_3</v>
       </c>
-      <c r="C26" s="29"/>
+      <c r="C26" s="34"/>
       <c r="D26" s="14"/>
     </row>
-    <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="16.5">
       <c r="A27" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="16.5">
       <c r="A28" s="4" t="s">
         <v>17</v>
       </c>
@@ -2227,7 +2237,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="16.5">
       <c r="A29" s="8" t="s">
         <v>47</v>
       </c>
@@ -2241,33 +2251,33 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="16.5">
       <c r="A30" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="29"/>
+      <c r="C30" s="34"/>
       <c r="D30" s="14"/>
     </row>
-    <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="16.5">
       <c r="A31" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="28" t="str">
+      <c r="B31" s="33" t="str">
         <f>A29 &amp; "." &amp; B29 &amp; "." &amp; C29 &amp; "-" &amp; B30</f>
         <v>v1.2.0-Better_Default_2</v>
       </c>
-      <c r="C31" s="29"/>
+      <c r="C31" s="34"/>
       <c r="D31" s="14"/>
     </row>
-    <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="16.5">
       <c r="A32" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="16.5">
       <c r="A33" s="4" t="s">
         <v>17</v>
       </c>
@@ -2281,7 +2291,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="16.5">
       <c r="A34" s="8" t="s">
         <v>47</v>
       </c>
@@ -2295,33 +2305,33 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="16.5">
       <c r="A35" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="28" t="s">
+      <c r="B35" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="29"/>
+      <c r="C35" s="34"/>
       <c r="D35" s="14"/>
     </row>
-    <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="16.5">
       <c r="A36" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="28" t="str">
+      <c r="B36" s="33" t="str">
         <f>A34 &amp; "." &amp; B34 &amp; "." &amp; C34 &amp; "-" &amp; B35</f>
         <v>v1.1.1-Better_Default</v>
       </c>
-      <c r="C36" s="29"/>
+      <c r="C36" s="34"/>
       <c r="D36" s="14"/>
     </row>
-    <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="16.5">
       <c r="A37" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="16.5">
       <c r="A38" s="4" t="s">
         <v>17</v>
       </c>
@@ -2335,7 +2345,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="16.5">
       <c r="A39" s="8" t="s">
         <v>47</v>
       </c>
@@ -2349,25 +2359,25 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="16.5">
       <c r="A40" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="28" t="s">
+      <c r="B40" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="29"/>
+      <c r="C40" s="34"/>
       <c r="D40" s="14"/>
     </row>
-    <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="16.5">
       <c r="A41" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="28" t="str">
+      <c r="B41" s="33" t="str">
         <f>A39 &amp; "." &amp; B39 &amp; "." &amp; C39 &amp; "-" &amp; B40</f>
         <v>v1.1.0-Better_Default</v>
       </c>
-      <c r="C41" s="29"/>
+      <c r="C41" s="34"/>
       <c r="D41" s="14"/>
     </row>
   </sheetData>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FB4EBC-6186-4885-8E29-45ED60F40503}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209B862D-2829-40BE-B36E-88771061853A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="70">
   <si>
     <t>Current version in development</t>
   </si>
@@ -233,6 +238,12 @@
   </si>
   <si>
     <t>Updated pack format (26.1)</t>
+  </si>
+  <si>
+    <t>Fixed grass rendering</t>
+  </si>
+  <si>
+    <t>Added baby mob textures</t>
   </si>
 </sst>
 </file>
@@ -769,7 +780,7 @@
     </row>
     <row r="5" spans="1:11" ht="16.5">
       <c r="A5" s="6" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="24" t="s">
@@ -790,7 +801,7 @@
     </row>
     <row r="6" spans="1:11" ht="16.5">
       <c r="A6" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -810,7 +821,7 @@
     </row>
     <row r="7" spans="1:11" ht="16.5">
       <c r="A7" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -830,7 +841,7 @@
     </row>
     <row r="8" spans="1:11" ht="16.5">
       <c r="A8" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -847,7 +858,7 @@
     </row>
     <row r="9" spans="1:11" ht="16.5">
       <c r="A9" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -870,7 +881,7 @@
     </row>
     <row r="10" spans="1:11" ht="16.5">
       <c r="A10" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -893,7 +904,9 @@
       <c r="K10" s="6"/>
     </row>
     <row r="11" spans="1:11" ht="16.5">
-      <c r="A11" s="6"/>
+      <c r="A11" s="6" t="s">
+        <v>63</v>
+      </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -911,7 +924,9 @@
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" ht="16.5">
-      <c r="A12" s="6"/>
+      <c r="A12" s="6" t="s">
+        <v>67</v>
+      </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -1920,6 +1935,9 @@
       <c r="K65" s="6"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:A12">
+    <sortCondition ref="A12"/>
+  </sortState>
   <mergeCells count="5">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="C4:E4"/>
@@ -2382,6 +2400,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2394,11 +2417,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209B862D-2829-40BE-B36E-88771061853A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18EEB19B-E37D-49D9-BAEB-1A46457EB369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="71">
   <si>
     <t>Current version in development</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>Added baby mob textures</t>
+  </si>
+  <si>
+    <t>Fixed compatibility issue with 26.1</t>
   </si>
 </sst>
 </file>
@@ -721,13 +724,13 @@
     <row r="3" spans="1:11" ht="16.5">
       <c r="A3" s="27" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5456-rt4</v>
+        <v>v10.0.11_1-build-5459-rt4</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="29"/>
       <c r="D3" s="8" t="str">
-        <f>SUM(2601,664,2026,165) &amp; "-rt4"</f>
-        <v>5456-rt4</v>
+        <f>SUM(2601,664,2026,168) &amp; "-rt4"</f>
+        <v>5459-rt4</v>
       </c>
       <c r="E3" s="7">
         <f>K4</f>
@@ -772,7 +775,7 @@
       </c>
       <c r="J4" s="8" t="str">
         <f>D3</f>
-        <v>5456-rt4</v>
+        <v>5459-rt4</v>
       </c>
       <c r="K4" s="8">
         <v>26.1</v>
@@ -833,7 +836,7 @@
       </c>
       <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5456-rt4</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5459-rt4</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13"/>
@@ -858,7 +861,7 @@
     </row>
     <row r="9" spans="1:11" ht="16.5">
       <c r="A9" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -881,7 +884,7 @@
     </row>
     <row r="10" spans="1:11" ht="16.5">
       <c r="A10" s="6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -896,7 +899,7 @@
       </c>
       <c r="I10" s="8" t="str">
         <f>J4</f>
-        <v>5456-rt4</v>
+        <v>5459-rt4</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>18</v>
@@ -905,7 +908,7 @@
     </row>
     <row r="11" spans="1:11" ht="16.5">
       <c r="A11" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -925,7 +928,7 @@
     </row>
     <row r="12" spans="1:11" ht="16.5">
       <c r="A12" s="6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -944,7 +947,9 @@
       <c r="K12" s="6"/>
     </row>
     <row r="13" spans="1:11" ht="16.5">
-      <c r="A13" s="6"/>
+      <c r="A13" s="6" t="s">
+        <v>67</v>
+      </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -955,7 +960,7 @@
       </c>
       <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5456-rt4</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5459-rt4</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="6"/>
@@ -997,7 +1002,7 @@
       </c>
       <c r="I15" s="8" t="str">
         <f>I10</f>
-        <v>5456-rt4</v>
+        <v>5459-rt4</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>19</v>
@@ -1052,7 +1057,7 @@
       </c>
       <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5456-rt4</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5459-rt4</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="6"/>
@@ -1094,7 +1099,7 @@
       </c>
       <c r="I20" s="8" t="str">
         <f>I15</f>
-        <v>5456-rt4</v>
+        <v>5459-rt4</v>
       </c>
       <c r="J20" s="8" t="s">
         <v>20</v>
@@ -1149,7 +1154,7 @@
       </c>
       <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5456-rt4</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5459-rt4</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="6"/>
@@ -1191,7 +1196,7 @@
       </c>
       <c r="I25" s="8" t="str">
         <f>I20</f>
-        <v>5456-rt4</v>
+        <v>5459-rt4</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>21</v>
@@ -1246,7 +1251,7 @@
       </c>
       <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5456-rt4</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5459-rt4</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="6"/>
@@ -1303,7 +1308,7 @@
       </c>
       <c r="I31" s="8" t="str">
         <f>I25</f>
-        <v>5456-rt4</v>
+        <v>5459-rt4</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>23</v>
@@ -1358,7 +1363,7 @@
       </c>
       <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5456-rt4</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5459-rt4</v>
       </c>
       <c r="I34" s="16"/>
       <c r="J34" s="6"/>
@@ -1415,7 +1420,7 @@
       </c>
       <c r="I37" s="8" t="str">
         <f>I31</f>
-        <v>5456-rt4</v>
+        <v>5459-rt4</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>25</v>
@@ -1469,7 +1474,7 @@
       </c>
       <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5456-rt4</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5459-rt4</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="6"/>
@@ -1526,7 +1531,7 @@
       </c>
       <c r="I43" s="8" t="str">
         <f>I37</f>
-        <v>5456-rt4</v>
+        <v>5459-rt4</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>28</v>
@@ -1580,7 +1585,7 @@
       </c>
       <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5456-rt4</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5459-rt4</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="6"/>
@@ -1652,7 +1657,7 @@
       </c>
       <c r="I50" s="8" t="str">
         <f>I43</f>
-        <v>5456-rt4</v>
+        <v>5459-rt4</v>
       </c>
       <c r="J50" s="8" t="s">
         <v>33</v>
@@ -1706,7 +1711,7 @@
       </c>
       <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5456-rt4</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5459-rt4</v>
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="6"/>
@@ -1763,7 +1768,7 @@
       </c>
       <c r="I56" s="8" t="str">
         <f>I50</f>
-        <v>5456-rt4</v>
+        <v>5459-rt4</v>
       </c>
       <c r="J56" s="8" t="s">
         <v>35</v>
@@ -1817,7 +1822,7 @@
       </c>
       <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5456-rt4</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5459-rt4</v>
       </c>
       <c r="I59" s="16"/>
       <c r="J59" s="6"/>
@@ -1874,7 +1879,7 @@
       </c>
       <c r="I62" s="8" t="str">
         <f>I56</f>
-        <v>5456-rt4</v>
+        <v>5459-rt4</v>
       </c>
       <c r="J62" s="8" t="s">
         <v>38</v>
@@ -1928,15 +1933,15 @@
       </c>
       <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5456-rt4</v>
+        <v>v7.11.3-Better_Default_7-build-5459-rt4</v>
       </c>
       <c r="I65" s="16"/>
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:A12">
-    <sortCondition ref="A12"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:A13">
+    <sortCondition ref="A13"/>
   </sortState>
   <mergeCells count="5">
     <mergeCell ref="A1:C1"/>
@@ -2400,11 +2405,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2417,6 +2417,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18EEB19B-E37D-49D9-BAEB-1A46457EB369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F12E9D-D1A4-4E9D-8B99-F7171A8B5DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="67">
   <si>
     <t>Current version in development</t>
   </si>
@@ -222,38 +222,26 @@
     <t>Better Default 1.1</t>
   </si>
   <si>
-    <t>Created Classic Reimagined Lite</t>
-  </si>
-  <si>
-    <t>Update fog/discard behavior and lightmap sampling</t>
-  </si>
-  <si>
-    <t>Replaced clamped skyfactor with pow-based sky_factor in lightmap shaders</t>
-  </si>
-  <si>
-    <t>Added classic mob sounds</t>
-  </si>
-  <si>
-    <t>fixed cat sounds</t>
-  </si>
-  <si>
-    <t>Updated pack format (26.1)</t>
-  </si>
-  <si>
-    <t>Fixed grass rendering</t>
-  </si>
-  <si>
-    <t>Added baby mob textures</t>
-  </si>
-  <si>
-    <t>Fixed compatibility issue with 26.1</t>
+    <t>Optimized textures for Vulkan's memory buffer</t>
+  </si>
+  <si>
+    <t>Improved shaders</t>
+  </si>
+  <si>
+    <t>Added 26.2 compatibility</t>
+  </si>
+  <si>
+    <t>Simplified animated textures to less sprites</t>
+  </si>
+  <si>
+    <t>Optimized VRAM usage by 17%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -679,13 +667,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K65"/>
-  <sheetFormatPr defaultColWidth="27.25" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="27.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="91.375" customWidth="1"/>
-    <col min="2" max="2" width="54.875" customWidth="1"/>
+    <col min="1" max="1" width="91.42578125" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.5">
+    <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -701,7 +689,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" ht="16.5">
+    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
         <v>2</v>
       </c>
@@ -721,16 +709,16 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:11" ht="16.5">
+    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5459-rt4</v>
+        <v>v10.0.11_1-build-5460-rt4</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="29"/>
       <c r="D3" s="8" t="str">
-        <f>SUM(2601,664,2026,168) &amp; "-rt4"</f>
-        <v>5459-rt4</v>
+        <f>SUM(2601,664,2026,169) &amp; "-rt4"</f>
+        <v>5460-rt4</v>
       </c>
       <c r="E3" s="7">
         <f>K4</f>
@@ -752,7 +740,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="16.5">
+    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
@@ -775,15 +763,15 @@
       </c>
       <c r="J4" s="8" t="str">
         <f>D3</f>
-        <v>5459-rt4</v>
+        <v>5460-rt4</v>
       </c>
       <c r="K4" s="8">
         <v>26.1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="16.5">
+    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="24" t="s">
@@ -802,9 +790,9 @@
       <c r="J5" s="13"/>
       <c r="K5" s="14"/>
     </row>
-    <row r="6" spans="1:11" ht="16.5">
+    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -822,7 +810,7 @@
       <c r="J6" s="13"/>
       <c r="K6" s="14"/>
     </row>
-    <row r="7" spans="1:11" ht="16.5">
+    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>62</v>
       </c>
@@ -836,13 +824,13 @@
       </c>
       <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5459-rt4</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5460-rt4</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13"/>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" spans="1:11" ht="16.5">
+    <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>66</v>
       </c>
@@ -859,9 +847,9 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" ht="16.5">
+    <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -882,10 +870,8 @@
       </c>
       <c r="K9" s="6"/>
     </row>
-    <row r="10" spans="1:11" ht="16.5">
-      <c r="A10" s="6" t="s">
-        <v>68</v>
-      </c>
+    <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -899,17 +885,15 @@
       </c>
       <c r="I10" s="8" t="str">
         <f>J4</f>
-        <v>5459-rt4</v>
+        <v>5460-rt4</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>18</v>
       </c>
       <c r="K10" s="6"/>
     </row>
-    <row r="11" spans="1:11" ht="16.5">
-      <c r="A11" s="6" t="s">
-        <v>64</v>
-      </c>
+    <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -926,10 +910,8 @@
       <c r="J11" s="14"/>
       <c r="K11" s="6"/>
     </row>
-    <row r="12" spans="1:11" ht="16.5">
-      <c r="A12" s="6" t="s">
-        <v>63</v>
-      </c>
+    <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -946,10 +928,8 @@
       <c r="J12" s="14"/>
       <c r="K12" s="6"/>
     </row>
-    <row r="13" spans="1:11" ht="16.5">
-      <c r="A13" s="6" t="s">
-        <v>67</v>
-      </c>
+    <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -960,13 +940,13 @@
       </c>
       <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5459-rt4</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5460-rt4</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
     </row>
-    <row r="14" spans="1:11" ht="16.5">
+    <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -987,7 +967,7 @@
       </c>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="1:11" ht="16.5">
+    <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -1002,14 +982,14 @@
       </c>
       <c r="I15" s="8" t="str">
         <f>I10</f>
-        <v>5459-rt4</v>
+        <v>5460-rt4</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>19</v>
       </c>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="1:11" ht="16.5">
+    <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -1027,7 +1007,7 @@
       <c r="J16" s="14"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="1:11" ht="16.5">
+    <row r="17" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -1045,7 +1025,7 @@
       <c r="J17" s="14"/>
       <c r="K17" s="6"/>
     </row>
-    <row r="18" spans="1:11" ht="16.5">
+    <row r="18" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -1057,13 +1037,13 @@
       </c>
       <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5459-rt4</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5460-rt4</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
     </row>
-    <row r="19" spans="1:11" ht="16.5">
+    <row r="19" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -1084,7 +1064,7 @@
       </c>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:11" ht="16.5">
+    <row r="20" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -1099,14 +1079,14 @@
       </c>
       <c r="I20" s="8" t="str">
         <f>I15</f>
-        <v>5459-rt4</v>
+        <v>5460-rt4</v>
       </c>
       <c r="J20" s="8" t="s">
         <v>20</v>
       </c>
       <c r="K20" s="6"/>
     </row>
-    <row r="21" spans="1:11" ht="16.5">
+    <row r="21" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -1124,7 +1104,7 @@
       <c r="J21" s="14"/>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" spans="1:11" ht="16.5">
+    <row r="22" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -1142,7 +1122,7 @@
       <c r="J22" s="14"/>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="1:11" ht="16.5">
+    <row r="23" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -1154,13 +1134,13 @@
       </c>
       <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5459-rt4</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5460-rt4</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
     </row>
-    <row r="24" spans="1:11" ht="16.5">
+    <row r="24" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -1181,7 +1161,7 @@
       </c>
       <c r="K24" s="6"/>
     </row>
-    <row r="25" spans="1:11" ht="16.5">
+    <row r="25" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -1196,14 +1176,14 @@
       </c>
       <c r="I25" s="8" t="str">
         <f>I20</f>
-        <v>5459-rt4</v>
+        <v>5460-rt4</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>21</v>
       </c>
       <c r="K25" s="6"/>
     </row>
-    <row r="26" spans="1:11" ht="16.5">
+    <row r="26" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -1221,7 +1201,7 @@
       <c r="J26" s="14"/>
       <c r="K26" s="6"/>
     </row>
-    <row r="27" spans="1:11" ht="16.5">
+    <row r="27" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -1239,7 +1219,7 @@
       <c r="J27" s="14"/>
       <c r="K27" s="6"/>
     </row>
-    <row r="28" spans="1:11" ht="16.5">
+    <row r="28" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -1251,13 +1231,13 @@
       </c>
       <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5459-rt4</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5460-rt4</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
     </row>
-    <row r="29" spans="1:11" ht="16.5">
+    <row r="29" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -1272,7 +1252,7 @@
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
     </row>
-    <row r="30" spans="1:11" ht="16.5">
+    <row r="30" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -1293,7 +1273,7 @@
       </c>
       <c r="K30" s="6"/>
     </row>
-    <row r="31" spans="1:11" ht="16.5">
+    <row r="31" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -1308,14 +1288,14 @@
       </c>
       <c r="I31" s="8" t="str">
         <f>I25</f>
-        <v>5459-rt4</v>
+        <v>5460-rt4</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>23</v>
       </c>
       <c r="K31" s="6"/>
     </row>
-    <row r="32" spans="1:11" ht="16.5">
+    <row r="32" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -1333,7 +1313,7 @@
       <c r="J32" s="14"/>
       <c r="K32" s="6"/>
     </row>
-    <row r="33" spans="1:11" ht="16.5">
+    <row r="33" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -1351,7 +1331,7 @@
       <c r="J33" s="14"/>
       <c r="K33" s="6"/>
     </row>
-    <row r="34" spans="1:11" ht="16.5">
+    <row r="34" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -1363,13 +1343,13 @@
       </c>
       <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5459-rt4</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5460-rt4</v>
       </c>
       <c r="I34" s="16"/>
       <c r="J34" s="6"/>
       <c r="K34" s="6"/>
     </row>
-    <row r="35" spans="1:11" ht="16.5">
+    <row r="35" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -1384,7 +1364,7 @@
       <c r="J35" s="6"/>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" spans="1:11" ht="16.5">
+    <row r="36" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -1405,7 +1385,7 @@
       </c>
       <c r="K36" s="6"/>
     </row>
-    <row r="37" spans="1:11" ht="16.5">
+    <row r="37" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -1420,14 +1400,14 @@
       </c>
       <c r="I37" s="8" t="str">
         <f>I31</f>
-        <v>5459-rt4</v>
+        <v>5460-rt4</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>25</v>
       </c>
       <c r="K37" s="6"/>
     </row>
-    <row r="38" spans="1:11" ht="16.5">
+    <row r="38" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -1444,7 +1424,7 @@
       <c r="J38" s="14"/>
       <c r="K38" s="6"/>
     </row>
-    <row r="39" spans="1:11" ht="16.5">
+    <row r="39" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -1462,7 +1442,7 @@
       <c r="J39" s="14"/>
       <c r="K39" s="6"/>
     </row>
-    <row r="40" spans="1:11" ht="16.5">
+    <row r="40" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -1474,13 +1454,13 @@
       </c>
       <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5459-rt4</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5460-rt4</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="6"/>
       <c r="K40" s="6"/>
     </row>
-    <row r="41" spans="1:11" ht="16.5">
+    <row r="41" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -1495,7 +1475,7 @@
       <c r="J41" s="6"/>
       <c r="K41" s="6"/>
     </row>
-    <row r="42" spans="1:11" ht="16.5">
+    <row r="42" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -1516,7 +1496,7 @@
       </c>
       <c r="K42" s="6"/>
     </row>
-    <row r="43" spans="1:11" ht="16.5">
+    <row r="43" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -1531,14 +1511,14 @@
       </c>
       <c r="I43" s="8" t="str">
         <f>I37</f>
-        <v>5459-rt4</v>
+        <v>5460-rt4</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>28</v>
       </c>
       <c r="K43" s="6"/>
     </row>
-    <row r="44" spans="1:11" ht="16.5">
+    <row r="44" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -1555,7 +1535,7 @@
       <c r="J44" s="14"/>
       <c r="K44" s="6"/>
     </row>
-    <row r="45" spans="1:11" ht="16.5">
+    <row r="45" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -1573,7 +1553,7 @@
       <c r="J45" s="14"/>
       <c r="K45" s="6"/>
     </row>
-    <row r="46" spans="1:11" ht="16.5">
+    <row r="46" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -1585,13 +1565,13 @@
       </c>
       <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5459-rt4</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5460-rt4</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
     </row>
-    <row r="47" spans="1:11" ht="16.5">
+    <row r="47" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -1606,7 +1586,7 @@
       <c r="J47" s="2"/>
       <c r="K47" s="6"/>
     </row>
-    <row r="48" spans="1:11" ht="16.5">
+    <row r="48" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -1621,7 +1601,7 @@
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
     </row>
-    <row r="49" spans="1:11" ht="16.5">
+    <row r="49" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -1642,7 +1622,7 @@
       </c>
       <c r="K49" s="6"/>
     </row>
-    <row r="50" spans="1:11" ht="16.5">
+    <row r="50" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -1657,14 +1637,14 @@
       </c>
       <c r="I50" s="8" t="str">
         <f>I43</f>
-        <v>5459-rt4</v>
+        <v>5460-rt4</v>
       </c>
       <c r="J50" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K50" s="6"/>
     </row>
-    <row r="51" spans="1:11" ht="16.5">
+    <row r="51" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -1681,7 +1661,7 @@
       <c r="J51" s="14"/>
       <c r="K51" s="6"/>
     </row>
-    <row r="52" spans="1:11" ht="16.5">
+    <row r="52" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -1699,7 +1679,7 @@
       <c r="J52" s="14"/>
       <c r="K52" s="6"/>
     </row>
-    <row r="53" spans="1:11" ht="16.5">
+    <row r="53" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -1711,13 +1691,13 @@
       </c>
       <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5459-rt4</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5460-rt4</v>
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
     </row>
-    <row r="54" spans="1:11" ht="16.5">
+    <row r="54" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -1732,7 +1712,7 @@
       <c r="J54" s="6"/>
       <c r="K54" s="6"/>
     </row>
-    <row r="55" spans="1:11" ht="16.5">
+    <row r="55" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -1753,7 +1733,7 @@
       </c>
       <c r="K55" s="6"/>
     </row>
-    <row r="56" spans="1:11" ht="16.5">
+    <row r="56" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -1768,14 +1748,14 @@
       </c>
       <c r="I56" s="8" t="str">
         <f>I50</f>
-        <v>5459-rt4</v>
+        <v>5460-rt4</v>
       </c>
       <c r="J56" s="8" t="s">
         <v>35</v>
       </c>
       <c r="K56" s="6"/>
     </row>
-    <row r="57" spans="1:11" ht="16.5">
+    <row r="57" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -1792,7 +1772,7 @@
       <c r="J57" s="14"/>
       <c r="K57" s="6"/>
     </row>
-    <row r="58" spans="1:11" ht="16.5">
+    <row r="58" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -1810,7 +1790,7 @@
       <c r="J58" s="14"/>
       <c r="K58" s="6"/>
     </row>
-    <row r="59" spans="1:11" ht="16.5">
+    <row r="59" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -1822,13 +1802,13 @@
       </c>
       <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5459-rt4</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5460-rt4</v>
       </c>
       <c r="I59" s="16"/>
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
     </row>
-    <row r="60" spans="1:11" ht="16.5">
+    <row r="60" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -1843,7 +1823,7 @@
       <c r="J60" s="17"/>
       <c r="K60" s="6"/>
     </row>
-    <row r="61" spans="1:11" ht="16.5">
+    <row r="61" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -1864,7 +1844,7 @@
       </c>
       <c r="K61" s="6"/>
     </row>
-    <row r="62" spans="1:11" ht="16.5">
+    <row r="62" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -1879,14 +1859,14 @@
       </c>
       <c r="I62" s="8" t="str">
         <f>I56</f>
-        <v>5459-rt4</v>
+        <v>5460-rt4</v>
       </c>
       <c r="J62" s="8" t="s">
         <v>38</v>
       </c>
       <c r="K62" s="6"/>
     </row>
-    <row r="63" spans="1:11" ht="16.5">
+    <row r="63" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -1903,7 +1883,7 @@
       <c r="J63" s="14"/>
       <c r="K63" s="6"/>
     </row>
-    <row r="64" spans="1:11" ht="16.5">
+    <row r="64" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -1921,7 +1901,7 @@
       <c r="J64" s="14"/>
       <c r="K64" s="6"/>
     </row>
-    <row r="65" spans="1:11" ht="16.5">
+    <row r="65" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -1933,15 +1913,15 @@
       </c>
       <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5459-rt4</v>
+        <v>v7.11.3-Better_Default_7-build-5460-rt4</v>
       </c>
       <c r="I65" s="16"/>
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:A13">
-    <sortCondition ref="A13"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:A9">
+    <sortCondition ref="A9"/>
   </sortState>
   <mergeCells count="5">
     <mergeCell ref="A1:C1"/>
@@ -1958,12 +1938,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="27.375" customWidth="1"/>
+    <col min="1" max="4" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5">
+    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="35" t="s">
         <v>40</v>
       </c>
@@ -1971,12 +1951,12 @@
       <c r="C1" s="35"/>
       <c r="D1" s="35"/>
     </row>
-    <row r="2" spans="1:4" ht="16.5">
+    <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16.5">
+    <row r="3" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
@@ -1990,7 +1970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="16.5">
+    <row r="4" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>43</v>
       </c>
@@ -2004,7 +1984,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="16.5">
+    <row r="5" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>13</v>
       </c>
@@ -2014,7 +1994,7 @@
       <c r="C5" s="34"/>
       <c r="D5" s="14"/>
     </row>
-    <row r="6" spans="1:4" ht="16.5">
+    <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
@@ -2025,12 +2005,12 @@
       <c r="C6" s="34"/>
       <c r="D6" s="14"/>
     </row>
-    <row r="7" spans="1:4" ht="16.5">
+    <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="16.5">
+    <row r="8" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
@@ -2044,7 +2024,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="16.5">
+    <row r="9" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>47</v>
       </c>
@@ -2058,7 +2038,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="16.5">
+    <row r="10" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>13</v>
       </c>
@@ -2068,7 +2048,7 @@
       <c r="C10" s="34"/>
       <c r="D10" s="14"/>
     </row>
-    <row r="11" spans="1:4" ht="16.5">
+    <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>15</v>
       </c>
@@ -2079,12 +2059,12 @@
       <c r="C11" s="34"/>
       <c r="D11" s="14"/>
     </row>
-    <row r="12" spans="1:4" ht="16.5">
+    <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="16.5">
+    <row r="13" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
@@ -2098,7 +2078,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="16.5">
+    <row r="14" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>47</v>
       </c>
@@ -2112,7 +2092,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="16.5">
+    <row r="15" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>13</v>
       </c>
@@ -2122,7 +2102,7 @@
       <c r="C15" s="34"/>
       <c r="D15" s="14"/>
     </row>
-    <row r="16" spans="1:4" ht="16.5">
+    <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>15</v>
       </c>
@@ -2133,12 +2113,12 @@
       <c r="C16" s="34"/>
       <c r="D16" s="14"/>
     </row>
-    <row r="17" spans="1:4" ht="16.5">
+    <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="16.5">
+    <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
@@ -2152,7 +2132,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="16.5">
+    <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>47</v>
       </c>
@@ -2166,7 +2146,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="16.5">
+    <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>13</v>
       </c>
@@ -2176,7 +2156,7 @@
       <c r="C20" s="34"/>
       <c r="D20" s="14"/>
     </row>
-    <row r="21" spans="1:4" ht="16.5">
+    <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>15</v>
       </c>
@@ -2187,12 +2167,12 @@
       <c r="C21" s="34"/>
       <c r="D21" s="14"/>
     </row>
-    <row r="22" spans="1:4" ht="16.5">
+    <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="16.5">
+    <row r="23" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>17</v>
       </c>
@@ -2206,7 +2186,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="16.5">
+    <row r="24" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>47</v>
       </c>
@@ -2220,7 +2200,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="16.5">
+    <row r="25" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>13</v>
       </c>
@@ -2230,7 +2210,7 @@
       <c r="C25" s="34"/>
       <c r="D25" s="14"/>
     </row>
-    <row r="26" spans="1:4" ht="16.5">
+    <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>15</v>
       </c>
@@ -2241,12 +2221,12 @@
       <c r="C26" s="34"/>
       <c r="D26" s="14"/>
     </row>
-    <row r="27" spans="1:4" ht="16.5">
+    <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="16.5">
+    <row r="28" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>17</v>
       </c>
@@ -2260,7 +2240,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="16.5">
+    <row r="29" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>47</v>
       </c>
@@ -2274,7 +2254,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="16.5">
+    <row r="30" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
         <v>13</v>
       </c>
@@ -2284,7 +2264,7 @@
       <c r="C30" s="34"/>
       <c r="D30" s="14"/>
     </row>
-    <row r="31" spans="1:4" ht="16.5">
+    <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>15</v>
       </c>
@@ -2295,12 +2275,12 @@
       <c r="C31" s="34"/>
       <c r="D31" s="14"/>
     </row>
-    <row r="32" spans="1:4" ht="16.5">
+    <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="16.5">
+    <row r="33" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>17</v>
       </c>
@@ -2314,7 +2294,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="16.5">
+    <row r="34" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>47</v>
       </c>
@@ -2328,7 +2308,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="16.5">
+    <row r="35" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>13</v>
       </c>
@@ -2338,7 +2318,7 @@
       <c r="C35" s="34"/>
       <c r="D35" s="14"/>
     </row>
-    <row r="36" spans="1:4" ht="16.5">
+    <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
         <v>15</v>
       </c>
@@ -2349,12 +2329,12 @@
       <c r="C36" s="34"/>
       <c r="D36" s="14"/>
     </row>
-    <row r="37" spans="1:4" ht="16.5">
+    <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="16.5">
+    <row r="38" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>17</v>
       </c>
@@ -2368,7 +2348,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="16.5">
+    <row r="39" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>47</v>
       </c>
@@ -2382,7 +2362,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="16.5">
+    <row r="40" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
         <v>13</v>
       </c>
@@ -2392,7 +2372,7 @@
       <c r="C40" s="34"/>
       <c r="D40" s="14"/>
     </row>
-    <row r="41" spans="1:4" ht="16.5">
+    <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>15</v>
       </c>
@@ -2405,6 +2385,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2417,11 +2402,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F12E9D-D1A4-4E9D-8B99-F7171A8B5DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C22CAD-C5D0-4910-A1F1-809956548B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="68">
   <si>
     <t>Current version in development</t>
   </si>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t>Optimized VRAM usage by 17%</t>
+  </si>
+  <si>
+    <t>Added sulfur cube textures</t>
   </si>
 </sst>
 </file>
@@ -871,7 +874,9 @@
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
+      <c r="A10" s="6" t="s">
+        <v>67</v>
+      </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -2385,11 +2390,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2402,6 +2402,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C22CAD-C5D0-4910-A1F1-809956548B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BDF8E16-96B6-416D-AFAA-4CD3AB472076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="70">
   <si>
     <t>Current version in development</t>
   </si>
@@ -238,6 +238,12 @@
   </si>
   <si>
     <t>Added sulfur cube textures</t>
+  </si>
+  <si>
+    <t>Added sulfur cube goo particle texture</t>
+  </si>
+  <si>
+    <t>Fixed lightmap shader</t>
   </si>
 </sst>
 </file>
@@ -898,7 +904,9 @@
       <c r="K10" s="6"/>
     </row>
     <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
+      <c r="A11" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -916,7 +924,9 @@
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
+      <c r="A12" s="6" t="s">
+        <v>69</v>
+      </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -2390,6 +2400,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2402,11 +2417,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BDF8E16-96B6-416D-AFAA-4CD3AB472076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF0CA08D-B593-4C80-BF3C-23424AB19EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="71">
   <si>
     <t>Current version in development</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>Fixed lightmap shader</t>
+  </si>
+  <si>
+    <t>Added noxious gas particle textures</t>
   </si>
 </sst>
 </file>
@@ -721,13 +724,13 @@
     <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D3</f>
-        <v>v10.0.11_1-build-5460-rt4</v>
+        <v>v10.0.11_1-build-5465-rt4</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="29"/>
       <c r="D3" s="8" t="str">
-        <f>SUM(2601,664,2026,169) &amp; "-rt4"</f>
-        <v>5460-rt4</v>
+        <f>SUM(2601,664,2026,174) &amp; "-rt4"</f>
+        <v>5465-rt4</v>
       </c>
       <c r="E3" s="7">
         <f>K4</f>
@@ -772,7 +775,7 @@
       </c>
       <c r="J4" s="8" t="str">
         <f>D3</f>
-        <v>5460-rt4</v>
+        <v>5465-rt4</v>
       </c>
       <c r="K4" s="8">
         <v>26.1</v>
@@ -833,7 +836,7 @@
       </c>
       <c r="H7" s="11" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5460-rt4</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5465-rt4</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13"/>
@@ -896,7 +899,7 @@
       </c>
       <c r="I10" s="8" t="str">
         <f>J4</f>
-        <v>5460-rt4</v>
+        <v>5465-rt4</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>18</v>
@@ -944,7 +947,9 @@
       <c r="K12" s="6"/>
     </row>
     <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
+      <c r="A13" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -955,7 +960,7 @@
       </c>
       <c r="H13" s="15" t="str">
         <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5460-rt4</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5465-rt4</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="6"/>
@@ -997,7 +1002,7 @@
       </c>
       <c r="I15" s="8" t="str">
         <f>I10</f>
-        <v>5460-rt4</v>
+        <v>5465-rt4</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>19</v>
@@ -1052,7 +1057,7 @@
       </c>
       <c r="H18" s="15" t="str">
         <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5460-rt4</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5465-rt4</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="6"/>
@@ -1094,7 +1099,7 @@
       </c>
       <c r="I20" s="8" t="str">
         <f>I15</f>
-        <v>5460-rt4</v>
+        <v>5465-rt4</v>
       </c>
       <c r="J20" s="8" t="s">
         <v>20</v>
@@ -1149,7 +1154,7 @@
       </c>
       <c r="H23" s="15" t="str">
         <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5460-rt4</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5465-rt4</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="6"/>
@@ -1191,7 +1196,7 @@
       </c>
       <c r="I25" s="8" t="str">
         <f>I20</f>
-        <v>5460-rt4</v>
+        <v>5465-rt4</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>21</v>
@@ -1246,7 +1251,7 @@
       </c>
       <c r="H28" s="15" t="str">
         <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5460-rt4</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5465-rt4</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="6"/>
@@ -1303,7 +1308,7 @@
       </c>
       <c r="I31" s="8" t="str">
         <f>I25</f>
-        <v>5460-rt4</v>
+        <v>5465-rt4</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>23</v>
@@ -1358,7 +1363,7 @@
       </c>
       <c r="H34" s="15" t="str">
         <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5460-rt4</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5465-rt4</v>
       </c>
       <c r="I34" s="16"/>
       <c r="J34" s="6"/>
@@ -1415,7 +1420,7 @@
       </c>
       <c r="I37" s="8" t="str">
         <f>I31</f>
-        <v>5460-rt4</v>
+        <v>5465-rt4</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>25</v>
@@ -1469,7 +1474,7 @@
       </c>
       <c r="H40" s="15" t="str">
         <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5460-rt4</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5465-rt4</v>
       </c>
       <c r="I40" s="16"/>
       <c r="J40" s="6"/>
@@ -1526,7 +1531,7 @@
       </c>
       <c r="I43" s="8" t="str">
         <f>I37</f>
-        <v>5460-rt4</v>
+        <v>5465-rt4</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>28</v>
@@ -1580,7 +1585,7 @@
       </c>
       <c r="H46" s="15" t="str">
         <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5460-rt4</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5465-rt4</v>
       </c>
       <c r="I46" s="16"/>
       <c r="J46" s="6"/>
@@ -1652,7 +1657,7 @@
       </c>
       <c r="I50" s="8" t="str">
         <f>I43</f>
-        <v>5460-rt4</v>
+        <v>5465-rt4</v>
       </c>
       <c r="J50" s="8" t="s">
         <v>33</v>
@@ -1706,7 +1711,7 @@
       </c>
       <c r="H53" s="15" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5460-rt4</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5465-rt4</v>
       </c>
       <c r="I53" s="16"/>
       <c r="J53" s="6"/>
@@ -1763,7 +1768,7 @@
       </c>
       <c r="I56" s="8" t="str">
         <f>I50</f>
-        <v>5460-rt4</v>
+        <v>5465-rt4</v>
       </c>
       <c r="J56" s="8" t="s">
         <v>35</v>
@@ -1817,7 +1822,7 @@
       </c>
       <c r="H59" s="15" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5460-rt4</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5465-rt4</v>
       </c>
       <c r="I59" s="16"/>
       <c r="J59" s="6"/>
@@ -1874,7 +1879,7 @@
       </c>
       <c r="I62" s="8" t="str">
         <f>I56</f>
-        <v>5460-rt4</v>
+        <v>5465-rt4</v>
       </c>
       <c r="J62" s="8" t="s">
         <v>38</v>
@@ -1928,7 +1933,7 @@
       </c>
       <c r="H65" s="15" t="str">
         <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5460-rt4</v>
+        <v>v7.11.3-Better_Default_7-build-5465-rt4</v>
       </c>
       <c r="I65" s="16"/>
       <c r="J65" s="6"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF0CA08D-B593-4C80-BF3C-23424AB19EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64E119C-E36A-4ACC-B384-8866CD77C744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="73">
   <si>
     <t>Current version in development</t>
   </si>
@@ -247,6 +247,12 @@
   </si>
   <si>
     <t>Added noxious gas particle textures</t>
+  </si>
+  <si>
+    <t>Added sulfur cube bucket texture</t>
+  </si>
+  <si>
+    <t>Added sulfur cube spawn egg item definition</t>
   </si>
 </sst>
 </file>
@@ -804,7 +810,7 @@
     </row>
     <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -824,7 +830,7 @@
     </row>
     <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -844,7 +850,7 @@
     </row>
     <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -861,7 +867,7 @@
     </row>
     <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -908,7 +914,7 @@
     </row>
     <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -928,7 +934,7 @@
     </row>
     <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -948,7 +954,7 @@
     </row>
     <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -967,7 +973,9 @@
       <c r="K13" s="6"/>
     </row>
     <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
+      <c r="A14" s="6" t="s">
+        <v>66</v>
+      </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -988,7 +996,9 @@
       <c r="K14" s="6"/>
     </row>
     <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
+      <c r="A15" s="6" t="s">
+        <v>65</v>
+      </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -1940,8 +1950,8 @@
       <c r="K65" s="6"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:A9">
-    <sortCondition ref="A9"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:A15">
+    <sortCondition ref="A15"/>
   </sortState>
   <mergeCells count="5">
     <mergeCell ref="A1:C1"/>
@@ -2405,11 +2415,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2422,6 +2427,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64E119C-E36A-4ACC-B384-8866CD77C744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1834179F-CF21-44A0-9CF3-A103183CD1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="76">
   <si>
     <t>Current version in development</t>
   </si>
@@ -253,6 +253,15 @@
   </si>
   <si>
     <t>Added sulfur cube spawn egg item definition</t>
+  </si>
+  <si>
+    <t>Added cinnabar block textures</t>
+  </si>
+  <si>
+    <t>Added sulfur block textures</t>
+  </si>
+  <si>
+    <t>Removed chain/old lantern textures</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1029,9 @@
       <c r="K15" s="6"/>
     </row>
     <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
+      <c r="A16" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -1038,7 +1049,9 @@
       <c r="K16" s="6"/>
     </row>
     <row r="17" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
+      <c r="A17" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -1056,7 +1069,9 @@
       <c r="K17" s="6"/>
     </row>
     <row r="18" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="6"/>
+      <c r="A18" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -2415,6 +2430,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2427,11 +2447,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1834179F-CF21-44A0-9CF3-A103183CD1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB704AFE-8F6B-4830-B493-BAC87DC715FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -819,7 +819,7 @@
     </row>
     <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -839,7 +839,7 @@
     </row>
     <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -859,7 +859,7 @@
     </row>
     <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -876,7 +876,7 @@
     </row>
     <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -899,7 +899,7 @@
     </row>
     <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -923,7 +923,7 @@
     </row>
     <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -943,7 +943,7 @@
     </row>
     <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -963,7 +963,7 @@
     </row>
     <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -983,7 +983,7 @@
     </row>
     <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -1006,7 +1006,7 @@
     </row>
     <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -1030,7 +1030,7 @@
     </row>
     <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="17" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -1070,7 +1070,7 @@
     </row>
     <row r="18" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -1965,8 +1965,8 @@
       <c r="K65" s="6"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:A15">
-    <sortCondition ref="A15"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:A18">
+    <sortCondition ref="A18"/>
   </sortState>
   <mergeCells count="5">
     <mergeCell ref="A1:C1"/>
@@ -2430,11 +2430,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2447,6 +2442,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB704AFE-8F6B-4830-B493-BAC87DC715FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A31AFB5B-423E-4A38-8000-8877D7BAA7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="66">
   <si>
     <t>Current version in development</t>
   </si>
@@ -222,46 +222,16 @@
     <t>Better Default 1.1</t>
   </si>
   <si>
-    <t>Optimized textures for Vulkan's memory buffer</t>
-  </si>
-  <si>
-    <t>Improved shaders</t>
-  </si>
-  <si>
-    <t>Added 26.2 compatibility</t>
-  </si>
-  <si>
-    <t>Simplified animated textures to less sprites</t>
-  </si>
-  <si>
-    <t>Optimized VRAM usage by 17%</t>
-  </si>
-  <si>
-    <t>Added sulfur cube textures</t>
-  </si>
-  <si>
-    <t>Added sulfur cube goo particle texture</t>
-  </si>
-  <si>
-    <t>Fixed lightmap shader</t>
-  </si>
-  <si>
-    <t>Added noxious gas particle textures</t>
-  </si>
-  <si>
-    <t>Added sulfur cube bucket texture</t>
-  </si>
-  <si>
-    <t>Added sulfur cube spawn egg item definition</t>
-  </si>
-  <si>
-    <t>Added cinnabar block textures</t>
-  </si>
-  <si>
-    <t>Added sulfur block textures</t>
-  </si>
-  <si>
-    <t>Removed chain/old lantern textures</t>
+    <t>Added sign block models</t>
+  </si>
+  <si>
+    <t>Fixed chicken sound effects</t>
+  </si>
+  <si>
+    <t>Fixed cooked cooked_beef texture</t>
+  </si>
+  <si>
+    <t>Fixed cooked cooked_porkchop texture</t>
   </si>
 </sst>
 </file>
@@ -798,7 +768,7 @@
     </row>
     <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="24" t="s">
@@ -819,7 +789,7 @@
     </row>
     <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -839,7 +809,7 @@
     </row>
     <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -859,7 +829,7 @@
     </row>
     <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -875,9 +845,7 @@
       <c r="K8" s="6"/>
     </row>
     <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>71</v>
-      </c>
+      <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -898,9 +866,7 @@
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>68</v>
-      </c>
+      <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -922,9 +888,7 @@
       <c r="K10" s="6"/>
     </row>
     <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>72</v>
-      </c>
+      <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -942,9 +906,7 @@
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>67</v>
-      </c>
+      <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -962,9 +924,7 @@
       <c r="K12" s="6"/>
     </row>
     <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>69</v>
-      </c>
+      <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -982,9 +942,7 @@
       <c r="K13" s="6"/>
     </row>
     <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>63</v>
-      </c>
+      <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -1005,9 +963,7 @@
       <c r="K14" s="6"/>
     </row>
     <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>62</v>
-      </c>
+      <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -1029,9 +985,7 @@
       <c r="K15" s="6"/>
     </row>
     <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>66</v>
-      </c>
+      <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -1049,9 +1003,7 @@
       <c r="K16" s="6"/>
     </row>
     <row r="17" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
-        <v>75</v>
-      </c>
+      <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -1069,9 +1021,7 @@
       <c r="K17" s="6"/>
     </row>
     <row r="18" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>65</v>
-      </c>
+      <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -2430,6 +2380,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2442,11 +2397,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hexy\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD3B178-1635-447C-BBFB-45D6FF627C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDEDD18E-E420-4BC3-9D65-12BCC1CB0413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="74">
   <si>
     <t>Current version in development</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>Base build</t>
+  </si>
+  <si>
+    <t>Fixed bed models and textures (26.2+)</t>
   </si>
 </sst>
 </file>
@@ -952,6 +955,9 @@
       <c r="J12" s="16"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>73</v>
+      </c>
       <c r="G13" s="12" t="s">
         <v>15</v>
       </c>
@@ -2008,11 +2014,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2025,6 +2026,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDEDD18E-E420-4BC3-9D65-12BCC1CB0413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2951B5A-E510-42D4-9491-E71B202CB42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="77">
   <si>
     <t>Current version in development</t>
   </si>
@@ -256,6 +256,15 @@
   </si>
   <si>
     <t>Fixed bed models and textures (26.2+)</t>
+  </si>
+  <si>
+    <t>Added purpur pillar and quartz pillar side textures</t>
+  </si>
+  <si>
+    <t>Added small sulfur cube texture</t>
+  </si>
+  <si>
+    <t>Updated pack format to 88</t>
   </si>
 </sst>
 </file>
@@ -968,6 +977,9 @@
       <c r="I13" s="18"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>74</v>
+      </c>
       <c r="G14" s="10" t="s">
         <v>17</v>
       </c>
@@ -982,6 +994,9 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>75</v>
+      </c>
       <c r="G15" s="11" t="s">
         <v>11</v>
       </c>
@@ -997,6 +1012,9 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="G16" s="12" t="s">
         <v>13</v>
       </c>
@@ -2014,6 +2032,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2026,11 +2049,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2951B5A-E510-42D4-9491-E71B202CB42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD1695E-1116-4B5B-93A4-9811064C37FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -897,7 +897,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C9" s="29" t="s">
         <v>12</v>
@@ -919,7 +919,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>11</v>
@@ -937,7 +937,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>13</v>
@@ -951,7 +951,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>14</v>
@@ -965,7 +965,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>15</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>17</v>
@@ -995,7 +995,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>11</v>
@@ -1571,8 +1571,8 @@
       <c r="I65" s="18"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:A18">
-    <sortCondition ref="A18"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:A16">
+    <sortCondition ref="A16"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
@@ -2032,11 +2032,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2049,6 +2044,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD1695E-1116-4B5B-93A4-9811064C37FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57BE188-9B09-43B6-8F03-06D69D7AC994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="69">
   <si>
     <t>Current version in development</t>
   </si>
@@ -222,18 +222,6 @@
     <t>Better Default 1.1</t>
   </si>
   <si>
-    <t>Added sign block models</t>
-  </si>
-  <si>
-    <t>Fixed chicken sound effects</t>
-  </si>
-  <si>
-    <t>Fixed cooked cooked_beef texture</t>
-  </si>
-  <si>
-    <t>Fixed cooked cooked_porkchop texture</t>
-  </si>
-  <si>
     <t>Branch</t>
   </si>
   <si>
@@ -253,18 +241,6 @@
   </si>
   <si>
     <t>Base build</t>
-  </si>
-  <si>
-    <t>Fixed bed models and textures (26.2+)</t>
-  </si>
-  <si>
-    <t>Added purpur pillar and quartz pillar side textures</t>
-  </si>
-  <si>
-    <t>Added small sulfur cube texture</t>
-  </si>
-  <si>
-    <t>Updated pack format to 88</t>
   </si>
 </sst>
 </file>
@@ -748,10 +724,10 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="37" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C2"/>
       <c r="D2"/>
@@ -761,10 +737,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="37" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C3"/>
       <c r="D3"/>
@@ -786,10 +762,10 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="37" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C4"/>
       <c r="D4"/>
@@ -812,7 +788,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="37" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B5" s="33" t="str">
         <f>B2&amp;B3&amp;B4</f>
@@ -896,9 +872,6 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>74</v>
-      </c>
       <c r="C9" s="29" t="s">
         <v>12</v>
       </c>
@@ -918,9 +891,6 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>62</v>
-      </c>
       <c r="G10" s="11" t="s">
         <v>11</v>
       </c>
@@ -936,9 +906,6 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>75</v>
-      </c>
       <c r="G11" s="12" t="s">
         <v>13</v>
       </c>
@@ -950,9 +917,6 @@
       <c r="J11" s="16"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>73</v>
-      </c>
       <c r="G12" s="12" t="s">
         <v>14</v>
       </c>
@@ -964,9 +928,6 @@
       <c r="J12" s="16"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>63</v>
-      </c>
       <c r="G13" s="12" t="s">
         <v>15</v>
       </c>
@@ -977,9 +938,6 @@
       <c r="I13" s="18"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>64</v>
-      </c>
       <c r="G14" s="10" t="s">
         <v>17</v>
       </c>
@@ -994,9 +952,6 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>65</v>
-      </c>
       <c r="G15" s="11" t="s">
         <v>11</v>
       </c>
@@ -1012,9 +967,6 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="G16" s="12" t="s">
         <v>13</v>
       </c>
@@ -2032,6 +1984,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2044,11 +2001,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57BE188-9B09-43B6-8F03-06D69D7AC994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA36BE1-BF2D-4F97-9ABD-E2A5496EA53E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="73">
   <si>
     <t>Current version in development</t>
   </si>
@@ -241,6 +241,18 @@
   </si>
   <si>
     <t>Base build</t>
+  </si>
+  <si>
+    <t>Added new sign textures</t>
+  </si>
+  <si>
+    <t>Added new bed textures</t>
+  </si>
+  <si>
+    <t>Removed unnecessary models</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimized resource pack </t>
   </si>
 </sst>
 </file>
@@ -872,6 +884,9 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>70</v>
+      </c>
       <c r="C9" s="29" t="s">
         <v>12</v>
       </c>
@@ -891,6 +906,9 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="G10" s="11" t="s">
         <v>11</v>
       </c>
@@ -906,6 +924,9 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>72</v>
+      </c>
       <c r="G11" s="12" t="s">
         <v>13</v>
       </c>
@@ -917,6 +938,9 @@
       <c r="J11" s="16"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>71</v>
+      </c>
       <c r="G12" s="12" t="s">
         <v>14</v>
       </c>
@@ -1523,8 +1547,8 @@
       <c r="I65" s="18"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:A16">
-    <sortCondition ref="A16"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:A12">
+    <sortCondition ref="A12"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
@@ -1984,11 +2008,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2001,6 +2020,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA36BE1-BF2D-4F97-9ABD-E2A5496EA53E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D723D6-FCC1-4EE2-A3C5-11971B6E70D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="74">
   <si>
     <t>Current version in development</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t xml:space="preserve">Optimized resource pack </t>
+  </si>
+  <si>
+    <t>Updated small sulfur cube texture</t>
   </si>
 </sst>
 </file>
@@ -952,6 +955,9 @@
       <c r="J12" s="16"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>73</v>
+      </c>
       <c r="G13" s="12" t="s">
         <v>15</v>
       </c>
@@ -2008,6 +2014,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2020,11 +2031,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D723D6-FCC1-4EE2-A3C5-11971B6E70D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A620B0CB-DE8B-45D5-82F3-5ADA58F69C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="73">
   <si>
     <t>Current version in development</t>
   </si>
@@ -225,21 +225,12 @@
     <t>Branch</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>Month</t>
   </si>
   <si>
-    <t>05</t>
-  </si>
-  <si>
     <t>Seasonal drop</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>Base build</t>
   </si>
   <si>
@@ -256,6 +247,12 @@
   </si>
   <si>
     <t>Updated small sulfur cube texture</t>
+  </si>
+  <si>
+    <t>Updated pack format to 88</t>
+  </si>
+  <si>
+    <t>Classic Reimagined 11 version history</t>
   </si>
 </sst>
 </file>
@@ -317,7 +314,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -367,6 +364,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -444,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -455,7 +458,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -476,8 +478,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -500,8 +500,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -522,6 +520,23 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -713,854 +728,934 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr defaultColWidth="27.28515625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.5703125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="36.7109375" style="7" customWidth="1"/>
-    <col min="3" max="16384" width="27.28515625" style="7"/>
+    <col min="1" max="1" width="36.5703125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="36.7109375" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="27.28515625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="G1" s="8" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="35"/>
+      <c r="G1" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="44">
+        <v>5</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" s="44">
+        <v>2</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="44">
+        <v>6</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="10">
+        <v>11</v>
+      </c>
+      <c r="I4" s="10">
+        <v>2</v>
+      </c>
+      <c r="J4" s="10" t="str">
+        <f>D7</f>
+        <v>5206-rt5</v>
+      </c>
+      <c r="K4" s="10">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="45" t="str">
+        <f>B2&amp;B3&amp;0&amp;0+B4</f>
+        <v>5206</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="12" t="str">
+        <f>"Classic_Reimagined_11" &amp; G2</f>
+        <v>Classic_Reimagined_11_SE_2.1</v>
+      </c>
+      <c r="I5" s="13"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="15"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="40"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="12" t="str">
+        <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-" &amp; H5</f>
+        <v>v10.0.11_2-Classic_Reimagined_11_SE_2.1</v>
+      </c>
+      <c r="I6" s="13"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="15"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="str">
+        <f>G11 &amp; "." &amp; H11 &amp; "_" &amp; I11 &amp; "-build-" &amp; D7</f>
+        <v>v10.0.11_1-build-5206-rt5</v>
+      </c>
+      <c r="B7" s="30"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="10" t="str">
+        <f>B5&amp;"-rt"&amp;B2</f>
+        <v>5206-rt5</v>
+      </c>
+      <c r="E7" s="21">
+        <f>K11</f>
+        <v>26.1</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="12" t="str">
+        <f>H6 &amp; "-build-" &amp; J4</f>
+        <v>v10.0.11_2-Classic_Reimagined_11_SE_2.1-build-5206-rt5</v>
+      </c>
+      <c r="I7" s="13"/>
+      <c r="J7" s="14"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="24"/>
+      <c r="E8" s="25"/>
+      <c r="G8" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="G2" s="9" t="s">
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="27"/>
+      <c r="E9" s="28"/>
+      <c r="G9" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="G3" s="10" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H10" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I10" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J10" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="G4" s="11" t="s">
+      <c r="K10" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H11" s="10">
         <v>11</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I11" s="10">
         <v>1</v>
       </c>
-      <c r="J4" s="11" t="str">
-        <f>D7</f>
-        <v>5052-rt5</v>
-      </c>
-      <c r="K4" s="11">
+      <c r="J11" s="10" t="str">
+        <f>J4</f>
+        <v>5206-rt5</v>
+      </c>
+      <c r="K11" s="10">
         <v>26.1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="37" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="33" t="str">
-        <f>B2&amp;B3&amp;B4</f>
-        <v>5052</v>
-      </c>
-      <c r="C5"/>
-      <c r="D5"/>
-      <c r="G5" s="12" t="s">
+      <c r="G12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="13" t="str">
-        <f>"Classic_Reimagined_10" &amp; G2</f>
+      <c r="H12" s="12" t="str">
+        <f>"Classic_Reimagined_10" &amp; G9</f>
         <v>Classic_Reimagined_10_SE_2.1</v>
       </c>
-      <c r="I5" s="14"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="16"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="10" t="s">
+      <c r="I12" s="13"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="15"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="12" t="str">
+        <f>G11 &amp; "." &amp; H11 &amp; "_" &amp; I11 &amp; "-" &amp; H12</f>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1</v>
+      </c>
+      <c r="I13" s="13"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="15"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="12" t="str">
+        <f>H13 &amp; "-build-" &amp; J11</f>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5206-rt5</v>
+      </c>
+      <c r="I14" s="13"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G15" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G16" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="I16" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" s="12" t="s">
+      <c r="J16" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G17" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="10">
+        <v>10</v>
+      </c>
+      <c r="I17" s="10" t="str">
+        <f>J11</f>
+        <v>5206-rt5</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G18" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="16" t="str">
+        <f>"Classic_Reimagined_10" &amp; G15</f>
+        <v>Classic_Reimagined_10_SE_2</v>
+      </c>
+      <c r="I18" s="17"/>
+      <c r="J18" s="15"/>
+    </row>
+    <row r="19" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G19" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="13" t="str">
-        <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-" &amp; H5</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1</v>
-      </c>
-      <c r="I6" s="14"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="16"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="str">
-        <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D7</f>
-        <v>v10.0.11_1-build-5052-rt5</v>
-      </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="11" t="str">
-        <f>B5&amp;"-rt"&amp;B2</f>
-        <v>5052-rt5</v>
-      </c>
-      <c r="E7" s="24">
-        <f>K4</f>
-        <v>26.1</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="13" t="str">
-        <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5052-rt5</v>
-      </c>
-      <c r="I7" s="14"/>
-      <c r="J7" s="15"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="28"/>
-      <c r="G8" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="31"/>
-      <c r="G9" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="11">
-        <v>10</v>
-      </c>
-      <c r="I10" s="11" t="str">
-        <f>J4</f>
-        <v>5052-rt5</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="17" t="str">
-        <f>"Classic_Reimagined_10" &amp; G8</f>
-        <v>Classic_Reimagined_10_SE_2</v>
-      </c>
-      <c r="I11" s="18"/>
-      <c r="J11" s="16"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="17" t="str">
-        <f>G10 &amp; "." &amp; H10 &amp; "-" &amp; H11</f>
+      <c r="H19" s="16" t="str">
+        <f>G17 &amp; "." &amp; H17 &amp; "-" &amp; H18</f>
         <v>v10.0.10-Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I12" s="18"/>
-      <c r="J12" s="16"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" s="17" t="str">
-        <f>H12 &amp; "-build-" &amp; I10</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5052-rt5</v>
-      </c>
-      <c r="I13" s="18"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G14" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G15" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" s="11">
-        <v>9</v>
-      </c>
-      <c r="I15" s="11" t="str">
-        <f>I10</f>
-        <v>5052-rt5</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G16" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="17" t="str">
-        <f>H11</f>
-        <v>Classic_Reimagined_10_SE_2</v>
-      </c>
-      <c r="I16" s="18"/>
-      <c r="J16" s="16"/>
-    </row>
-    <row r="17" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G17" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="17" t="str">
-        <f>G15 &amp; "." &amp; H15 &amp; "-" &amp; H16</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2</v>
-      </c>
-      <c r="I17" s="18"/>
-      <c r="J17" s="16"/>
-    </row>
-    <row r="18" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G18" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="17" t="str">
-        <f>H17 &amp; "-build-" &amp; I15</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5052-rt5</v>
-      </c>
-      <c r="I18" s="18"/>
-    </row>
-    <row r="19" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G19" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>4</v>
-      </c>
+      <c r="I19" s="17"/>
+      <c r="J19" s="15"/>
     </row>
     <row r="20" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G20" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="16" t="str">
+        <f>H19 &amp; "-build-" &amp; I17</f>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5206-rt5</v>
+      </c>
+      <c r="I20" s="17"/>
+    </row>
+    <row r="21" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G22" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="11">
-        <v>7</v>
-      </c>
-      <c r="I20" s="11" t="str">
-        <f>I15</f>
-        <v>5052-rt5</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G21" s="12" t="s">
+      <c r="H22" s="10">
+        <v>9</v>
+      </c>
+      <c r="I22" s="10" t="str">
+        <f>I17</f>
+        <v>5206-rt5</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G23" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H21" s="17" t="str">
-        <f>H16</f>
+      <c r="H23" s="16" t="str">
+        <f>H18</f>
         <v>Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I21" s="18"/>
-      <c r="J21" s="16"/>
-    </row>
-    <row r="22" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G22" s="12" t="s">
+      <c r="I23" s="17"/>
+      <c r="J23" s="15"/>
+    </row>
+    <row r="24" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G24" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H22" s="17" t="str">
-        <f>G20 &amp; "." &amp; H20 &amp; "-" &amp; H21</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2</v>
-      </c>
-      <c r="I22" s="18"/>
-      <c r="J22" s="16"/>
-    </row>
-    <row r="23" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G23" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" s="17" t="str">
-        <f>H22 &amp; "-build-" &amp; I20</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5052-rt5</v>
-      </c>
-      <c r="I23" s="18"/>
-    </row>
-    <row r="24" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G24" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>4</v>
-      </c>
+      <c r="H24" s="16" t="str">
+        <f>G22 &amp; "." &amp; H22 &amp; "-" &amp; H23</f>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2</v>
+      </c>
+      <c r="I24" s="17"/>
+      <c r="J24" s="15"/>
     </row>
     <row r="25" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G25" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="16" t="str">
+        <f>H24 &amp; "-build-" &amp; I22</f>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5206-rt5</v>
+      </c>
+      <c r="I25" s="17"/>
+    </row>
+    <row r="26" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G26" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G27" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H25" s="11">
-        <v>4</v>
-      </c>
-      <c r="I25" s="11" t="str">
-        <f>I20</f>
-        <v>5052-rt5</v>
-      </c>
-      <c r="J25" s="11" t="s">
+      <c r="H27" s="10">
+        <v>7</v>
+      </c>
+      <c r="I27" s="10" t="str">
+        <f>I22</f>
+        <v>5206-rt5</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G28" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="16" t="str">
+        <f>H23</f>
+        <v>Classic_Reimagined_10_SE_2</v>
+      </c>
+      <c r="I28" s="17"/>
+      <c r="J28" s="15"/>
+    </row>
+    <row r="29" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G29" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="16" t="str">
+        <f>G27 &amp; "." &amp; H27 &amp; "-" &amp; H28</f>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2</v>
+      </c>
+      <c r="I29" s="17"/>
+      <c r="J29" s="15"/>
+    </row>
+    <row r="30" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G30" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="16" t="str">
+        <f>H29 &amp; "-build-" &amp; I27</f>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5206-rt5</v>
+      </c>
+      <c r="I30" s="17"/>
+    </row>
+    <row r="31" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G31" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G32" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="10">
+        <v>4</v>
+      </c>
+      <c r="I32" s="10" t="str">
+        <f>I27</f>
+        <v>5206-rt5</v>
+      </c>
+      <c r="J32" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G26" s="12" t="s">
+    <row r="33" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G33" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H26" s="17" t="str">
-        <f>H21</f>
+      <c r="H33" s="16" t="str">
+        <f>H28</f>
         <v>Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I26" s="18"/>
-      <c r="J26" s="16"/>
-    </row>
-    <row r="27" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G27" s="12" t="s">
+      <c r="I33" s="17"/>
+      <c r="J33" s="15"/>
+    </row>
+    <row r="34" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G34" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H27" s="17" t="str">
-        <f>G25 &amp; "." &amp; H25 &amp; "-" &amp; H26</f>
+      <c r="H34" s="16" t="str">
+        <f>G32 &amp; "." &amp; H32 &amp; "-" &amp; H33</f>
         <v>v10.0.4-Classic_Reimagined_10_SE_2</v>
       </c>
-      <c r="I27" s="18"/>
-      <c r="J27" s="16"/>
-    </row>
-    <row r="28" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G28" s="12" t="s">
+      <c r="I34" s="17"/>
+      <c r="J34" s="15"/>
+    </row>
+    <row r="35" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G35" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H28" s="17" t="str">
-        <f>H27 &amp; "-build-" &amp; I25</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5052-rt5</v>
-      </c>
-      <c r="I28" s="18"/>
-    </row>
-    <row r="29" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G29" s="9" t="s">
+      <c r="H35" s="16" t="str">
+        <f>H34 &amp; "-build-" &amp; I32</f>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5206-rt5</v>
+      </c>
+      <c r="I35" s="17"/>
+    </row>
+    <row r="36" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G36" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G30" s="10" t="s">
+    <row r="37" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G37" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H30" s="10" t="s">
+      <c r="H37" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I30" s="10" t="s">
+      <c r="I37" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="J30" s="10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G31" s="11" t="s">
+      <c r="J37" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G38" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H31" s="11">
+      <c r="H38" s="10">
         <v>3</v>
       </c>
-      <c r="I31" s="11" t="str">
-        <f>I25</f>
-        <v>5052-rt5</v>
-      </c>
-      <c r="J31" s="11" t="s">
+      <c r="I38" s="10" t="str">
+        <f>I32</f>
+        <v>5206-rt5</v>
+      </c>
+      <c r="J38" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G32" s="12" t="s">
+    <row r="39" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G39" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H32" s="17" t="str">
-        <f>"Classic_Reimagined_10" &amp; G29</f>
+      <c r="H39" s="16" t="str">
+        <f>"Classic_Reimagined_10" &amp; G36</f>
         <v>Classic_Reimagined_10_SE</v>
       </c>
-      <c r="I32" s="18"/>
-      <c r="J32" s="16"/>
-    </row>
-    <row r="33" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G33" s="12" t="s">
+      <c r="I39" s="17"/>
+      <c r="J39" s="15"/>
+    </row>
+    <row r="40" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G40" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="17" t="str">
-        <f>G31 &amp; "." &amp; H31 &amp; "-" &amp; H32</f>
+      <c r="H40" s="16" t="str">
+        <f>G38 &amp; "." &amp; H38 &amp; "-" &amp; H39</f>
         <v>v10.0.3-Classic_Reimagined_10_SE</v>
       </c>
-      <c r="I33" s="18"/>
-      <c r="J33" s="16"/>
-    </row>
-    <row r="34" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G34" s="12" t="s">
+      <c r="I40" s="17"/>
+      <c r="J40" s="15"/>
+    </row>
+    <row r="41" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G41" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H34" s="17" t="str">
-        <f>H33 &amp; "-build-" &amp; I31</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5052-rt5</v>
-      </c>
-      <c r="I34" s="18"/>
-    </row>
-    <row r="35" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G35" s="9" t="s">
+      <c r="H41" s="16" t="str">
+        <f>H40 &amp; "-build-" &amp; I38</f>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5206-rt5</v>
+      </c>
+      <c r="I41" s="17"/>
+    </row>
+    <row r="42" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G42" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G36" s="10" t="s">
+    <row r="43" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G43" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H43" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I36" s="10" t="s">
+      <c r="I43" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="J36" s="10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G37" s="11" t="s">
+      <c r="J43" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G44" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H37" s="11">
+      <c r="H44" s="10">
         <v>2</v>
       </c>
-      <c r="I37" s="11" t="str">
-        <f>I31</f>
-        <v>5052-rt5</v>
-      </c>
-      <c r="J37" s="11" t="s">
+      <c r="I44" s="10" t="str">
+        <f>I38</f>
+        <v>5206-rt5</v>
+      </c>
+      <c r="J44" s="10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G38" s="12" t="s">
+    <row r="45" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G45" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H38" s="17" t="s">
+      <c r="H45" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I38" s="18"/>
-      <c r="J38" s="16"/>
-    </row>
-    <row r="39" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G39" s="12" t="s">
+      <c r="I45" s="17"/>
+      <c r="J45" s="15"/>
+    </row>
+    <row r="46" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G46" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H39" s="17" t="str">
-        <f>G37 &amp; "." &amp; H37 &amp; "-" &amp; H38</f>
+      <c r="H46" s="16" t="str">
+        <f>G44 &amp; "." &amp; H44 &amp; "-" &amp; H45</f>
         <v>v10.0.2-Classic_Reimagined_10s</v>
       </c>
-      <c r="I39" s="18"/>
-      <c r="J39" s="16"/>
-    </row>
-    <row r="40" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G40" s="12" t="s">
+      <c r="I46" s="17"/>
+      <c r="J46" s="15"/>
+    </row>
+    <row r="47" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G47" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H40" s="17" t="str">
-        <f>H39 &amp; "-build-" &amp; I37</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5052-rt5</v>
-      </c>
-      <c r="I40" s="18"/>
-    </row>
-    <row r="41" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G41" s="9" t="s">
+      <c r="H47" s="16" t="str">
+        <f>H46 &amp; "-build-" &amp; I44</f>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5206-rt5</v>
+      </c>
+      <c r="I47" s="17"/>
+    </row>
+    <row r="48" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G48" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G42" s="10" t="s">
+    <row r="49" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G49" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H42" s="10" t="s">
+      <c r="H49" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I42" s="10" t="s">
+      <c r="I49" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="J42" s="10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G43" s="11" t="s">
+      <c r="J49" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G50" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H43" s="11">
+      <c r="H50" s="10">
         <v>1</v>
       </c>
-      <c r="I43" s="11" t="str">
-        <f>I37</f>
-        <v>5052-rt5</v>
-      </c>
-      <c r="J43" s="11" t="s">
+      <c r="I50" s="10" t="str">
+        <f>I44</f>
+        <v>5206-rt5</v>
+      </c>
+      <c r="J50" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G44" s="12" t="s">
+    <row r="51" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G51" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H44" s="17" t="s">
+      <c r="H51" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="I44" s="18"/>
-      <c r="J44" s="16"/>
-    </row>
-    <row r="45" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G45" s="12" t="s">
+      <c r="I51" s="17"/>
+      <c r="J51" s="15"/>
+    </row>
+    <row r="52" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G52" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H45" s="17" t="str">
-        <f>G43 &amp; "." &amp; H43 &amp; "-" &amp; H44</f>
+      <c r="H52" s="16" t="str">
+        <f>G50 &amp; "." &amp; H50 &amp; "-" &amp; H51</f>
         <v>v10.0.1-Classic_Reimagined_10</v>
       </c>
-      <c r="I45" s="18"/>
-      <c r="J45" s="16"/>
-    </row>
-    <row r="46" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G46" s="12" t="s">
+      <c r="I52" s="17"/>
+      <c r="J52" s="15"/>
+    </row>
+    <row r="53" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G53" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H46" s="17" t="str">
-        <f>H45 &amp; "-build-" &amp; I43</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5052-rt5</v>
-      </c>
-      <c r="I46" s="18"/>
-    </row>
-    <row r="47" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G47" s="8" t="s">
+      <c r="H53" s="16" t="str">
+        <f>H52 &amp; "-build-" &amp; I50</f>
+        <v>v10.0.1-Classic_Reimagined_10-build-5206-rt5</v>
+      </c>
+      <c r="I53" s="17"/>
+    </row>
+    <row r="54" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G54" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-    </row>
-    <row r="48" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G48" s="9" t="s">
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
+    </row>
+    <row r="55" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G55" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G49" s="10" t="s">
+    <row r="56" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G56" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="H56" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I49" s="10" t="s">
+      <c r="I56" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="J49" s="10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G50" s="11" t="s">
+      <c r="J56" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G57" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H50" s="11">
+      <c r="H57" s="10">
         <v>32</v>
       </c>
-      <c r="I50" s="11" t="str">
-        <f>I43</f>
-        <v>5052-rt5</v>
-      </c>
-      <c r="J50" s="11" t="s">
+      <c r="I57" s="10" t="str">
+        <f>I50</f>
+        <v>5206-rt5</v>
+      </c>
+      <c r="J57" s="10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G51" s="12" t="s">
+    <row r="58" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G58" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H51" s="17" t="s">
+      <c r="H58" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="I51" s="18"/>
-      <c r="J51" s="16"/>
-    </row>
-    <row r="52" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G52" s="12" t="s">
+      <c r="I58" s="17"/>
+      <c r="J58" s="15"/>
+    </row>
+    <row r="59" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G59" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H52" s="17" t="str">
-        <f>G50 &amp; "." &amp; H50 &amp; "-" &amp; H51</f>
+      <c r="H59" s="16" t="str">
+        <f>G57 &amp; "." &amp; H57 &amp; "-" &amp; H58</f>
         <v>v8.10.32-Classic_Reimagined_8</v>
       </c>
-      <c r="I52" s="18"/>
-      <c r="J52" s="16"/>
-    </row>
-    <row r="53" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G53" s="12" t="s">
+      <c r="I59" s="17"/>
+      <c r="J59" s="15"/>
+    </row>
+    <row r="60" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G60" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H53" s="17" t="str">
-        <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5052-rt5</v>
-      </c>
-      <c r="I53" s="18"/>
-    </row>
-    <row r="54" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G54" s="9" t="s">
+      <c r="H60" s="16" t="str">
+        <f>H59 &amp; "-build-" &amp; I57</f>
+        <v>v8.10.32-Classic_Reimagined_8-build-5206-rt5</v>
+      </c>
+      <c r="I60" s="17"/>
+    </row>
+    <row r="61" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G61" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G55" s="10" t="s">
+    <row r="62" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G62" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H55" s="10" t="s">
+      <c r="H62" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I55" s="10" t="s">
+      <c r="I62" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="J55" s="10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G56" s="11" t="s">
+      <c r="J62" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G63" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H56" s="11">
+      <c r="H63" s="10">
         <v>31</v>
       </c>
-      <c r="I56" s="11" t="str">
-        <f>I50</f>
-        <v>5052-rt5</v>
-      </c>
-      <c r="J56" s="11" t="s">
+      <c r="I63" s="10" t="str">
+        <f>I57</f>
+        <v>5206-rt5</v>
+      </c>
+      <c r="J63" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G57" s="12" t="s">
+    <row r="64" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G64" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H57" s="17" t="s">
+      <c r="H64" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="I57" s="18"/>
-      <c r="J57" s="16"/>
-    </row>
-    <row r="58" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G58" s="12" t="s">
+      <c r="I64" s="17"/>
+      <c r="J64" s="15"/>
+    </row>
+    <row r="65" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G65" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H58" s="17" t="str">
-        <f>G56 &amp; "." &amp; H56 &amp; "-" &amp; H57</f>
+      <c r="H65" s="16" t="str">
+        <f>G63 &amp; "." &amp; H63 &amp; "-" &amp; H64</f>
         <v>v8.10.31-Classic_Reimagined_8</v>
       </c>
-      <c r="I58" s="18"/>
-      <c r="J58" s="16"/>
-    </row>
-    <row r="59" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G59" s="12" t="s">
+      <c r="I65" s="17"/>
+      <c r="J65" s="15"/>
+    </row>
+    <row r="66" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G66" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H59" s="17" t="str">
-        <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5052-rt5</v>
-      </c>
-      <c r="I59" s="18"/>
-    </row>
-    <row r="60" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G60" s="32" t="s">
+      <c r="H66" s="16" t="str">
+        <f>H65 &amp; "-build-" &amp; I63</f>
+        <v>v8.10.31-Classic_Reimagined_8-build-5206-rt5</v>
+      </c>
+      <c r="I66" s="17"/>
+    </row>
+    <row r="67" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G67" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="H60" s="32"/>
-      <c r="I60" s="32"/>
-      <c r="J60" s="32"/>
-    </row>
-    <row r="61" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G61" s="10" t="s">
+      <c r="H67" s="29"/>
+      <c r="I67" s="29"/>
+      <c r="J67" s="29"/>
+    </row>
+    <row r="68" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G68" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H61" s="10" t="s">
+      <c r="H68" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I61" s="10" t="s">
+      <c r="I68" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="J61" s="10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G62" s="11" t="s">
+      <c r="J68" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G69" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H62" s="11">
+      <c r="H69" s="10">
         <v>3</v>
       </c>
-      <c r="I62" s="11" t="str">
-        <f>I56</f>
-        <v>5052-rt5</v>
-      </c>
-      <c r="J62" s="11" t="s">
+      <c r="I69" s="10" t="str">
+        <f>I63</f>
+        <v>5206-rt5</v>
+      </c>
+      <c r="J69" s="10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="63" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G63" s="12" t="s">
+    <row r="70" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G70" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H63" s="17" t="s">
+      <c r="H70" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I63" s="18"/>
-      <c r="J63" s="16"/>
-    </row>
-    <row r="64" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G64" s="12" t="s">
+      <c r="I70" s="17"/>
+      <c r="J70" s="15"/>
+    </row>
+    <row r="71" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G71" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H64" s="17" t="str">
-        <f>G62 &amp; "." &amp; H62 &amp; "-" &amp; H63</f>
+      <c r="H71" s="16" t="str">
+        <f>G69 &amp; "." &amp; H69 &amp; "-" &amp; H70</f>
         <v>v7.11.3-Better_Default_7</v>
       </c>
-      <c r="I64" s="18"/>
-      <c r="J64" s="16"/>
-    </row>
-    <row r="65" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G65" s="12" t="s">
+      <c r="I71" s="17"/>
+      <c r="J71" s="15"/>
+    </row>
+    <row r="72" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G72" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H65" s="17" t="str">
-        <f>H64 &amp; "-build-" &amp; I62</f>
-        <v>v7.11.3-Better_Default_7-build-5052-rt5</v>
-      </c>
-      <c r="I65" s="18"/>
+      <c r="H72" s="16" t="str">
+        <f>H71 &amp; "-build-" &amp; I69</f>
+        <v>v7.11.3-Better_Default_7-build-5206-rt5</v>
+      </c>
+      <c r="I72" s="17"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:A12">
-    <sortCondition ref="A12"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B4">
+    <sortCondition descending="1" ref="A3:A4"/>
   </sortState>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A6:C6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1573,12 +1668,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1617,21 +1712,21 @@
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="37"/>
       <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="41" t="str">
+      <c r="B6" s="36" t="str">
         <f>A4 &amp; "." &amp; B4 &amp; "." &amp; C4 &amp; "-" &amp; B5</f>
         <v>v6.0.7-Better_Default_6</v>
       </c>
-      <c r="C6" s="42"/>
+      <c r="C6" s="37"/>
       <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1671,21 +1766,21 @@
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="37"/>
       <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="41" t="str">
+      <c r="B11" s="36" t="str">
         <f>A9 &amp; "." &amp; B9 &amp; "." &amp; C9 &amp; "-" &amp; B10</f>
         <v>v1.4.0-Better_Default_5</v>
       </c>
-      <c r="C11" s="42"/>
+      <c r="C11" s="37"/>
       <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1725,21 +1820,21 @@
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="42"/>
+      <c r="C15" s="37"/>
       <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="41" t="str">
+      <c r="B16" s="36" t="str">
         <f>A14 &amp; "." &amp; B14 &amp; "." &amp; C14 &amp; "-" &amp; B15</f>
         <v>v1.3.0-Better_Default_4</v>
       </c>
-      <c r="C16" s="42"/>
+      <c r="C16" s="37"/>
       <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1779,21 +1874,21 @@
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="42"/>
+      <c r="C20" s="37"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="41" t="str">
+      <c r="B21" s="36" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
         <v>v1.2.2-Better_Default_3.1</v>
       </c>
-      <c r="C21" s="42"/>
+      <c r="C21" s="37"/>
       <c r="D21" s="5"/>
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1833,21 +1928,21 @@
       <c r="A25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="41" t="s">
+      <c r="B25" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="42"/>
+      <c r="C25" s="37"/>
       <c r="D25" s="5"/>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="41" t="str">
+      <c r="B26" s="36" t="str">
         <f>A24 &amp; "." &amp; B24 &amp; "." &amp; C24 &amp; "-" &amp; B25</f>
         <v>v1.2.1-Better_Default_3</v>
       </c>
-      <c r="C26" s="42"/>
+      <c r="C26" s="37"/>
       <c r="D26" s="5"/>
     </row>
     <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1887,21 +1982,21 @@
       <c r="A30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="41" t="s">
+      <c r="B30" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="42"/>
+      <c r="C30" s="37"/>
       <c r="D30" s="5"/>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="41" t="str">
+      <c r="B31" s="36" t="str">
         <f>A29 &amp; "." &amp; B29 &amp; "." &amp; C29 &amp; "-" &amp; B30</f>
         <v>v1.2.0-Better_Default_2</v>
       </c>
-      <c r="C31" s="42"/>
+      <c r="C31" s="37"/>
       <c r="D31" s="5"/>
     </row>
     <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1941,21 +2036,21 @@
       <c r="A35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="41" t="s">
+      <c r="B35" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="42"/>
+      <c r="C35" s="37"/>
       <c r="D35" s="5"/>
     </row>
     <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="41" t="str">
+      <c r="B36" s="36" t="str">
         <f>A34 &amp; "." &amp; B34 &amp; "." &amp; C34 &amp; "-" &amp; B35</f>
         <v>v1.1.1-Better_Default</v>
       </c>
-      <c r="C36" s="42"/>
+      <c r="C36" s="37"/>
       <c r="D36" s="5"/>
     </row>
     <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1995,30 +2090,25 @@
       <c r="A40" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="41" t="s">
+      <c r="B40" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="42"/>
+      <c r="C40" s="37"/>
       <c r="D40" s="5"/>
     </row>
     <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="41" t="str">
+      <c r="B41" s="36" t="str">
         <f>A39 &amp; "." &amp; B39 &amp; "." &amp; C39 &amp; "-" &amp; B40</f>
         <v>v1.1.0-Better_Default</v>
       </c>
-      <c r="C41" s="42"/>
+      <c r="C41" s="37"/>
       <c r="D41" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2031,6 +2121,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A620B0CB-DE8B-45D5-82F3-5ADA58F69C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09914AB5-BF8D-4A0D-B783-6884B4DBBBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -503,6 +503,14 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -510,15 +518,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -530,13 +529,14 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -737,26 +737,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="35"/>
-      <c r="G1" s="42" t="s">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="39"/>
+      <c r="G1" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="44">
+      <c r="B2" s="35">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
@@ -767,7 +767,7 @@
       <c r="A3" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="44">
+      <c r="B3" s="35">
         <v>2</v>
       </c>
       <c r="G3" s="9" t="s">
@@ -790,7 +790,7 @@
       <c r="A4" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="44">
+      <c r="B4" s="35">
         <v>6</v>
       </c>
       <c r="G4" s="10" t="s">
@@ -807,15 +807,15 @@
         <v>5206-rt5</v>
       </c>
       <c r="K4" s="10">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="45" t="str">
-        <f>B2&amp;B3&amp;0&amp;0+B4</f>
+      <c r="B5" s="36">
+        <f>(B2*1000)+(B3*100)+B4</f>
         <v>5206</v>
       </c>
       <c r="G5" s="11" t="s">
@@ -830,11 +830,11 @@
       <c r="K5" s="15"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="41"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="42"/>
       <c r="D6" s="9" t="s">
         <v>3</v>
       </c>
@@ -1668,12 +1668,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1712,21 +1712,21 @@
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="37"/>
+      <c r="C5" s="44"/>
       <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="36" t="str">
+      <c r="B6" s="43" t="str">
         <f>A4 &amp; "." &amp; B4 &amp; "." &amp; C4 &amp; "-" &amp; B5</f>
         <v>v6.0.7-Better_Default_6</v>
       </c>
-      <c r="C6" s="37"/>
+      <c r="C6" s="44"/>
       <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1766,21 +1766,21 @@
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="37"/>
+      <c r="C10" s="44"/>
       <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="36" t="str">
+      <c r="B11" s="43" t="str">
         <f>A9 &amp; "." &amp; B9 &amp; "." &amp; C9 &amp; "-" &amp; B10</f>
         <v>v1.4.0-Better_Default_5</v>
       </c>
-      <c r="C11" s="37"/>
+      <c r="C11" s="44"/>
       <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1820,21 +1820,21 @@
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="37"/>
+      <c r="C15" s="44"/>
       <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="36" t="str">
+      <c r="B16" s="43" t="str">
         <f>A14 &amp; "." &amp; B14 &amp; "." &amp; C14 &amp; "-" &amp; B15</f>
         <v>v1.3.0-Better_Default_4</v>
       </c>
-      <c r="C16" s="37"/>
+      <c r="C16" s="44"/>
       <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1874,21 +1874,21 @@
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="37"/>
+      <c r="C20" s="44"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="36" t="str">
+      <c r="B21" s="43" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
         <v>v1.2.2-Better_Default_3.1</v>
       </c>
-      <c r="C21" s="37"/>
+      <c r="C21" s="44"/>
       <c r="D21" s="5"/>
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1928,21 +1928,21 @@
       <c r="A25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="36" t="s">
+      <c r="B25" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="37"/>
+      <c r="C25" s="44"/>
       <c r="D25" s="5"/>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="36" t="str">
+      <c r="B26" s="43" t="str">
         <f>A24 &amp; "." &amp; B24 &amp; "." &amp; C24 &amp; "-" &amp; B25</f>
         <v>v1.2.1-Better_Default_3</v>
       </c>
-      <c r="C26" s="37"/>
+      <c r="C26" s="44"/>
       <c r="D26" s="5"/>
     </row>
     <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1982,21 +1982,21 @@
       <c r="A30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="36" t="s">
+      <c r="B30" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="37"/>
+      <c r="C30" s="44"/>
       <c r="D30" s="5"/>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="36" t="str">
+      <c r="B31" s="43" t="str">
         <f>A29 &amp; "." &amp; B29 &amp; "." &amp; C29 &amp; "-" &amp; B30</f>
         <v>v1.2.0-Better_Default_2</v>
       </c>
-      <c r="C31" s="37"/>
+      <c r="C31" s="44"/>
       <c r="D31" s="5"/>
     </row>
     <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2036,21 +2036,21 @@
       <c r="A35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="36" t="s">
+      <c r="B35" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="37"/>
+      <c r="C35" s="44"/>
       <c r="D35" s="5"/>
     </row>
     <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="36" t="str">
+      <c r="B36" s="43" t="str">
         <f>A34 &amp; "." &amp; B34 &amp; "." &amp; C34 &amp; "-" &amp; B35</f>
         <v>v1.1.1-Better_Default</v>
       </c>
-      <c r="C36" s="37"/>
+      <c r="C36" s="44"/>
       <c r="D36" s="5"/>
     </row>
     <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2090,21 +2090,21 @@
       <c r="A40" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="36" t="s">
+      <c r="B40" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="37"/>
+      <c r="C40" s="44"/>
       <c r="D40" s="5"/>
     </row>
     <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="36" t="str">
+      <c r="B41" s="43" t="str">
         <f>A39 &amp; "." &amp; B39 &amp; "." &amp; C39 &amp; "-" &amp; B40</f>
         <v>v1.1.0-Better_Default</v>
       </c>
-      <c r="C41" s="37"/>
+      <c r="C41" s="44"/>
       <c r="D41" s="5"/>
     </row>
   </sheetData>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09914AB5-BF8D-4A0D-B783-6884B4DBBBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3423C626-9722-4AA1-BC4E-DC4A709EF100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -481,8 +481,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -500,7 +498,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -536,6 +533,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -737,26 +743,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="39"/>
-      <c r="G1" s="33" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="36"/>
+      <c r="G1" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="35">
+      <c r="B2" s="32">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
@@ -764,10 +770,10 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="35">
+      <c r="B3" s="32">
         <v>2</v>
       </c>
       <c r="G3" s="9" t="s">
@@ -787,10 +793,10 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="35">
+      <c r="B4" s="32">
         <v>6</v>
       </c>
       <c r="G4" s="10" t="s">
@@ -811,10 +817,10 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="36">
+      <c r="B5" s="33">
         <f>(B2*1000)+(B3*100)+B4</f>
         <v>5206</v>
       </c>
@@ -830,11 +836,11 @@
       <c r="K5" s="15"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="42"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="39"/>
       <c r="D6" s="9" t="s">
         <v>3</v>
       </c>
@@ -853,19 +859,19 @@
       <c r="K6" s="15"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="str">
+      <c r="A7" s="43" t="str">
         <f>G11 &amp; "." &amp; H11 &amp; "_" &amp; I11 &amp; "-build-" &amp; D7</f>
         <v>v10.0.11_1-build-5206-rt5</v>
       </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="20"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="45"/>
       <c r="D7" s="10" t="str">
         <f>B5&amp;"-rt"&amp;B2</f>
         <v>5206-rt5</v>
       </c>
-      <c r="E7" s="21">
-        <f>K11</f>
-        <v>26.1</v>
+      <c r="E7" s="19">
+        <f>K4</f>
+        <v>26.2</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>15</v>
@@ -878,17 +884,17 @@
       <c r="J7" s="14"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="25"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="23"/>
       <c r="G8" s="7" t="s">
         <v>1</v>
       </c>
@@ -901,11 +907,11 @@
       <c r="A9" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="27"/>
-      <c r="E9" s="28"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
       <c r="G9" s="8" t="s">
         <v>5</v>
       </c>
@@ -1579,12 +1585,12 @@
       <c r="I66" s="17"/>
     </row>
     <row r="67" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G67" s="29" t="s">
+      <c r="G67" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="H67" s="29"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="29"/>
+      <c r="H67" s="27"/>
+      <c r="I67" s="27"/>
+      <c r="J67" s="27"/>
     </row>
     <row r="68" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G68" s="9" t="s">
@@ -1650,9 +1656,10 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B4">
     <sortCondition descending="1" ref="A3:A4"/>
   </sortState>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1668,12 +1675,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1712,21 +1719,21 @@
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="44"/>
+      <c r="C5" s="41"/>
       <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="43" t="str">
+      <c r="B6" s="40" t="str">
         <f>A4 &amp; "." &amp; B4 &amp; "." &amp; C4 &amp; "-" &amp; B5</f>
         <v>v6.0.7-Better_Default_6</v>
       </c>
-      <c r="C6" s="44"/>
+      <c r="C6" s="41"/>
       <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1766,21 +1773,21 @@
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="44"/>
+      <c r="C10" s="41"/>
       <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="43" t="str">
+      <c r="B11" s="40" t="str">
         <f>A9 &amp; "." &amp; B9 &amp; "." &amp; C9 &amp; "-" &amp; B10</f>
         <v>v1.4.0-Better_Default_5</v>
       </c>
-      <c r="C11" s="44"/>
+      <c r="C11" s="41"/>
       <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1820,21 +1827,21 @@
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="44"/>
+      <c r="C15" s="41"/>
       <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="43" t="str">
+      <c r="B16" s="40" t="str">
         <f>A14 &amp; "." &amp; B14 &amp; "." &amp; C14 &amp; "-" &amp; B15</f>
         <v>v1.3.0-Better_Default_4</v>
       </c>
-      <c r="C16" s="44"/>
+      <c r="C16" s="41"/>
       <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1874,21 +1881,21 @@
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="44"/>
+      <c r="C20" s="41"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="43" t="str">
+      <c r="B21" s="40" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
         <v>v1.2.2-Better_Default_3.1</v>
       </c>
-      <c r="C21" s="44"/>
+      <c r="C21" s="41"/>
       <c r="D21" s="5"/>
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1928,21 +1935,21 @@
       <c r="A25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="44"/>
+      <c r="C25" s="41"/>
       <c r="D25" s="5"/>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="43" t="str">
+      <c r="B26" s="40" t="str">
         <f>A24 &amp; "." &amp; B24 &amp; "." &amp; C24 &amp; "-" &amp; B25</f>
         <v>v1.2.1-Better_Default_3</v>
       </c>
-      <c r="C26" s="44"/>
+      <c r="C26" s="41"/>
       <c r="D26" s="5"/>
     </row>
     <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1982,21 +1989,21 @@
       <c r="A30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="43" t="s">
+      <c r="B30" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="44"/>
+      <c r="C30" s="41"/>
       <c r="D30" s="5"/>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="43" t="str">
+      <c r="B31" s="40" t="str">
         <f>A29 &amp; "." &amp; B29 &amp; "." &amp; C29 &amp; "-" &amp; B30</f>
         <v>v1.2.0-Better_Default_2</v>
       </c>
-      <c r="C31" s="44"/>
+      <c r="C31" s="41"/>
       <c r="D31" s="5"/>
     </row>
     <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2036,21 +2043,21 @@
       <c r="A35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="43" t="s">
+      <c r="B35" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="44"/>
+      <c r="C35" s="41"/>
       <c r="D35" s="5"/>
     </row>
     <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="43" t="str">
+      <c r="B36" s="40" t="str">
         <f>A34 &amp; "." &amp; B34 &amp; "." &amp; C34 &amp; "-" &amp; B35</f>
         <v>v1.1.1-Better_Default</v>
       </c>
-      <c r="C36" s="44"/>
+      <c r="C36" s="41"/>
       <c r="D36" s="5"/>
     </row>
     <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2090,25 +2097,30 @@
       <c r="A40" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="43" t="s">
+      <c r="B40" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="44"/>
+      <c r="C40" s="41"/>
       <c r="D40" s="5"/>
     </row>
     <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="43" t="str">
+      <c r="B41" s="40" t="str">
         <f>A39 &amp; "." &amp; B39 &amp; "." &amp; C39 &amp; "-" &amp; B40</f>
         <v>v1.1.0-Better_Default</v>
       </c>
-      <c r="C41" s="44"/>
+      <c r="C41" s="41"/>
       <c r="D41" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2121,11 +2133,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3423C626-9722-4AA1-BC4E-DC4A709EF100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E846C9D-5065-44FA-9308-1356FE1A3AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="74">
   <si>
     <t>Current version in development</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>Classic Reimagined 11 version history</t>
+  </si>
+  <si>
+    <t>Updated bat model</t>
   </si>
 </sst>
 </file>
@@ -526,6 +529,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -533,15 +545,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -859,12 +862,12 @@
       <c r="K6" s="15"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="43" t="str">
+      <c r="A7" s="40" t="str">
         <f>G11 &amp; "." &amp; H11 &amp; "_" &amp; I11 &amp; "-build-" &amp; D7</f>
         <v>v10.0.11_1-build-5206-rt5</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="45"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="42"/>
       <c r="D7" s="10" t="str">
         <f>B5&amp;"-rt"&amp;B2</f>
         <v>5206-rt5</v>
@@ -1002,6 +1005,9 @@
       <c r="J14" s="14"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="G15" s="8" t="s">
         <v>16</v>
       </c>
@@ -1675,12 +1681,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1719,21 +1725,21 @@
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="41"/>
+      <c r="C5" s="44"/>
       <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="40" t="str">
+      <c r="B6" s="43" t="str">
         <f>A4 &amp; "." &amp; B4 &amp; "." &amp; C4 &amp; "-" &amp; B5</f>
         <v>v6.0.7-Better_Default_6</v>
       </c>
-      <c r="C6" s="41"/>
+      <c r="C6" s="44"/>
       <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1773,21 +1779,21 @@
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="41"/>
+      <c r="C10" s="44"/>
       <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="40" t="str">
+      <c r="B11" s="43" t="str">
         <f>A9 &amp; "." &amp; B9 &amp; "." &amp; C9 &amp; "-" &amp; B10</f>
         <v>v1.4.0-Better_Default_5</v>
       </c>
-      <c r="C11" s="41"/>
+      <c r="C11" s="44"/>
       <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1827,21 +1833,21 @@
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="41"/>
+      <c r="C15" s="44"/>
       <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="40" t="str">
+      <c r="B16" s="43" t="str">
         <f>A14 &amp; "." &amp; B14 &amp; "." &amp; C14 &amp; "-" &amp; B15</f>
         <v>v1.3.0-Better_Default_4</v>
       </c>
-      <c r="C16" s="41"/>
+      <c r="C16" s="44"/>
       <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1881,21 +1887,21 @@
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="41"/>
+      <c r="C20" s="44"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="40" t="str">
+      <c r="B21" s="43" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
         <v>v1.2.2-Better_Default_3.1</v>
       </c>
-      <c r="C21" s="41"/>
+      <c r="C21" s="44"/>
       <c r="D21" s="5"/>
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1935,21 +1941,21 @@
       <c r="A25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="41"/>
+      <c r="C25" s="44"/>
       <c r="D25" s="5"/>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="40" t="str">
+      <c r="B26" s="43" t="str">
         <f>A24 &amp; "." &amp; B24 &amp; "." &amp; C24 &amp; "-" &amp; B25</f>
         <v>v1.2.1-Better_Default_3</v>
       </c>
-      <c r="C26" s="41"/>
+      <c r="C26" s="44"/>
       <c r="D26" s="5"/>
     </row>
     <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1989,21 +1995,21 @@
       <c r="A30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="40" t="s">
+      <c r="B30" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="41"/>
+      <c r="C30" s="44"/>
       <c r="D30" s="5"/>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="40" t="str">
+      <c r="B31" s="43" t="str">
         <f>A29 &amp; "." &amp; B29 &amp; "." &amp; C29 &amp; "-" &amp; B30</f>
         <v>v1.2.0-Better_Default_2</v>
       </c>
-      <c r="C31" s="41"/>
+      <c r="C31" s="44"/>
       <c r="D31" s="5"/>
     </row>
     <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2043,21 +2049,21 @@
       <c r="A35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="40" t="s">
+      <c r="B35" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="41"/>
+      <c r="C35" s="44"/>
       <c r="D35" s="5"/>
     </row>
     <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="40" t="str">
+      <c r="B36" s="43" t="str">
         <f>A34 &amp; "." &amp; B34 &amp; "." &amp; C34 &amp; "-" &amp; B35</f>
         <v>v1.1.1-Better_Default</v>
       </c>
-      <c r="C36" s="41"/>
+      <c r="C36" s="44"/>
       <c r="D36" s="5"/>
     </row>
     <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2097,30 +2103,25 @@
       <c r="A40" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="40" t="s">
+      <c r="B40" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="41"/>
+      <c r="C40" s="44"/>
       <c r="D40" s="5"/>
     </row>
     <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="40" t="str">
+      <c r="B41" s="43" t="str">
         <f>A39 &amp; "." &amp; B39 &amp; "." &amp; C39 &amp; "-" &amp; B40</f>
         <v>v1.1.0-Better_Default</v>
       </c>
-      <c r="C41" s="41"/>
+      <c r="C41" s="44"/>
       <c r="D41" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2133,6 +2134,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E846C9D-5065-44FA-9308-1356FE1A3AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEBF46A-71EE-4671-8B8E-B523365BC759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="76">
   <si>
     <t>Current version in development</t>
   </si>
@@ -256,6 +256,12 @@
   </si>
   <si>
     <t>Updated bat model</t>
+  </si>
+  <si>
+    <t>Changed rabbit model</t>
+  </si>
+  <si>
+    <t>Changed sky orientation</t>
   </si>
 </sst>
 </file>
@@ -1013,6 +1019,9 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="G16" s="9" t="s">
         <v>17</v>
       </c>
@@ -1026,7 +1035,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="7:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="G17" s="10" t="s">
         <v>11</v>
       </c>
@@ -1041,7 +1053,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="7:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G18" s="11" t="s">
         <v>13</v>
       </c>
@@ -1052,7 +1064,7 @@
       <c r="I18" s="17"/>
       <c r="J18" s="15"/>
     </row>
-    <row r="19" spans="7:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G19" s="11" t="s">
         <v>14</v>
       </c>
@@ -1063,7 +1075,7 @@
       <c r="I19" s="17"/>
       <c r="J19" s="15"/>
     </row>
-    <row r="20" spans="7:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G20" s="11" t="s">
         <v>15</v>
       </c>
@@ -1073,7 +1085,7 @@
       </c>
       <c r="I20" s="17"/>
     </row>
-    <row r="21" spans="7:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G21" s="9" t="s">
         <v>17</v>
       </c>
@@ -1087,7 +1099,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="7:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G22" s="10" t="s">
         <v>11</v>
       </c>
@@ -1102,7 +1114,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="7:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G23" s="11" t="s">
         <v>13</v>
       </c>
@@ -1113,7 +1125,7 @@
       <c r="I23" s="17"/>
       <c r="J23" s="15"/>
     </row>
-    <row r="24" spans="7:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G24" s="11" t="s">
         <v>14</v>
       </c>
@@ -1124,7 +1136,7 @@
       <c r="I24" s="17"/>
       <c r="J24" s="15"/>
     </row>
-    <row r="25" spans="7:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G25" s="11" t="s">
         <v>15</v>
       </c>
@@ -1134,7 +1146,7 @@
       </c>
       <c r="I25" s="17"/>
     </row>
-    <row r="26" spans="7:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G26" s="9" t="s">
         <v>17</v>
       </c>
@@ -1148,7 +1160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="7:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G27" s="10" t="s">
         <v>11</v>
       </c>
@@ -1163,7 +1175,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="7:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G28" s="11" t="s">
         <v>13</v>
       </c>
@@ -1174,7 +1186,7 @@
       <c r="I28" s="17"/>
       <c r="J28" s="15"/>
     </row>
-    <row r="29" spans="7:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G29" s="11" t="s">
         <v>14</v>
       </c>
@@ -1185,7 +1197,7 @@
       <c r="I29" s="17"/>
       <c r="J29" s="15"/>
     </row>
-    <row r="30" spans="7:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G30" s="11" t="s">
         <v>15</v>
       </c>
@@ -1195,7 +1207,7 @@
       </c>
       <c r="I30" s="17"/>
     </row>
-    <row r="31" spans="7:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G31" s="9" t="s">
         <v>17</v>
       </c>
@@ -1209,7 +1221,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="7:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G32" s="10" t="s">
         <v>11</v>
       </c>
@@ -2122,6 +2134,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2134,11 +2151,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEBF46A-71EE-4671-8B8E-B523365BC759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2373F72D-9380-4E1C-9ECE-12673A8980BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="77">
   <si>
     <t>Current version in development</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>Changed sky orientation</t>
+  </si>
+  <si>
+    <t>Release year</t>
   </si>
 </sst>
 </file>
@@ -526,24 +529,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -553,6 +538,12 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -743,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr defaultColWidth="27.28515625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36.5703125" style="6" customWidth="1"/>
@@ -783,7 +774,7 @@
         <v>64</v>
       </c>
       <c r="B3" s="32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>2</v>
@@ -806,7 +797,7 @@
         <v>63</v>
       </c>
       <c r="B4" s="32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>11</v>
@@ -815,23 +806,22 @@
         <v>11</v>
       </c>
       <c r="I4" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" s="10" t="str">
-        <f>D7</f>
-        <v>5206-rt5</v>
+        <f>D8</f>
+        <v>5307-rt5</v>
       </c>
       <c r="K4" s="10">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" s="33">
-        <f>(B2*1000)+(B3*100)+B4</f>
-        <v>5206</v>
+        <v>76</v>
+      </c>
+      <c r="B5" s="32">
+        <v>2026</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>13</v>
@@ -845,137 +835,144 @@
       <c r="K5" s="15"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="37" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>4</v>
+      <c r="A6" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="33">
+        <f>(B2*1000)+(B3*100)+B4+((B5-2026)*1000)</f>
+        <v>5307</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="12" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-" &amp; H5</f>
-        <v>v10.0.11_2-Classic_Reimagined_11_SE_2.1</v>
+        <v>v10.0.11_3-Classic_Reimagined_11_SE_2.1</v>
       </c>
       <c r="I6" s="13"/>
       <c r="J6" s="14"/>
       <c r="K6" s="15"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="40" t="str">
-        <f>G11 &amp; "." &amp; H11 &amp; "_" &amp; I11 &amp; "-build-" &amp; D7</f>
-        <v>v10.0.11_1-build-5206-rt5</v>
+      <c r="A7" s="40" t="s">
+        <v>2</v>
       </c>
       <c r="B7" s="41"/>
       <c r="C7" s="42"/>
-      <c r="D7" s="10" t="str">
-        <f>B5&amp;"-rt"&amp;B2</f>
-        <v>5206-rt5</v>
-      </c>
-      <c r="E7" s="19">
-        <f>K4</f>
-        <v>26.2</v>
+      <c r="D7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>4</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="12" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_2-Classic_Reimagined_11_SE_2.1-build-5206-rt5</v>
+        <v>v10.0.11_3-Classic_Reimagined_11_SE_2.1-build-5307-rt5</v>
       </c>
       <c r="I7" s="13"/>
       <c r="J7" s="14"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="43" t="str">
+        <f>G17 &amp; "." &amp; H17 &amp; "_" &amp; I17 &amp; "-build-" &amp; D8</f>
+        <v>v10.0.11_1-build-5307-rt5</v>
+      </c>
+      <c r="B8" s="44"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="10" t="str">
+        <f>B6&amp;"-rt"&amp;B2</f>
+        <v>5307-rt5</v>
+      </c>
+      <c r="E8" s="19">
+        <f>K10</f>
+        <v>26.2</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B9" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C9" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="23"/>
-      <c r="G8" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
-      <c r="G9" s="8" t="s">
-        <v>5</v>
+      <c r="D9" s="22"/>
+      <c r="E9" s="23"/>
+      <c r="G9" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="25"/>
+      <c r="E10" s="26"/>
+      <c r="G10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="10">
+        <v>11</v>
+      </c>
+      <c r="I10" s="10">
         <v>2</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>4</v>
+      <c r="J10" s="10" t="str">
+        <f>J4</f>
+        <v>5307-rt5</v>
+      </c>
+      <c r="K10" s="10">
+        <v>26.2</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="10">
-        <v>11</v>
-      </c>
-      <c r="I11" s="10">
-        <v>1</v>
-      </c>
-      <c r="J11" s="10" t="str">
-        <f>J4</f>
-        <v>5206-rt5</v>
-      </c>
-      <c r="K11" s="10">
-        <v>26.1</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="12" t="str">
+        <f>"Classic_Reimagined_11" &amp; G8</f>
+        <v>Classic_Reimagined_11_SE_2.1</v>
+      </c>
+      <c r="I11" s="13"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="15"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="12" t="str">
-        <f>"Classic_Reimagined_10" &amp; G9</f>
-        <v>Classic_Reimagined_10_SE_2.1</v>
+        <f>G10 &amp; "." &amp; H10 &amp; "_" &amp; I10 &amp; "-" &amp; H11</f>
+        <v>v10.0.11_2-Classic_Reimagined_11_SE_2.1</v>
       </c>
       <c r="I12" s="13"/>
       <c r="J12" s="14"/>
@@ -983,295 +980,304 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H13" s="12" t="str">
-        <f>G11 &amp; "." &amp; H11 &amp; "_" &amp; I11 &amp; "-" &amp; H12</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1</v>
+        <f>H12 &amp; "-build-" &amp; J10</f>
+        <v>v10.0.11_2-Classic_Reimagined_11_SE_2.1-build-5307-rt5</v>
       </c>
       <c r="I13" s="13"/>
       <c r="J13" s="14"/>
-      <c r="K13" s="15"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="12" t="str">
-        <f>H13 &amp; "-build-" &amp; J11</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5206-rt5</v>
-      </c>
-      <c r="I14" s="13"/>
-      <c r="J14" s="14"/>
+        <v>70</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>6</v>
       </c>
       <c r="I16" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J16" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="J16" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K16" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>11</v>
       </c>
       <c r="H17" s="10">
-        <v>10</v>
-      </c>
-      <c r="I17" s="10" t="str">
-        <f>J11</f>
-        <v>5206-rt5</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="I17" s="10">
+        <v>1</v>
+      </c>
+      <c r="J17" s="10" t="str">
+        <f>J10</f>
+        <v>5307-rt5</v>
+      </c>
+      <c r="K17" s="10">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="G18" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H18" s="16" t="str">
+      <c r="H18" s="12" t="str">
         <f>"Classic_Reimagined_10" &amp; G15</f>
-        <v>Classic_Reimagined_10_SE_2</v>
-      </c>
-      <c r="I18" s="17"/>
-      <c r="J18" s="15"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+        <v>Classic_Reimagined_10_SE_2.1</v>
+      </c>
+      <c r="I18" s="13"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="15"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G19" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="16" t="str">
-        <f>G17 &amp; "." &amp; H17 &amp; "-" &amp; H18</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2</v>
-      </c>
-      <c r="I19" s="17"/>
-      <c r="J19" s="15"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H19" s="12" t="str">
+        <f>G17 &amp; "." &amp; H17 &amp; "_" &amp; I17 &amp; "-" &amp; H18</f>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1</v>
+      </c>
+      <c r="I19" s="13"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="15"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G20" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="16" t="str">
-        <f>H19 &amp; "-build-" &amp; I17</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5206-rt5</v>
-      </c>
-      <c r="I20" s="17"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G21" s="9" t="s">
+      <c r="H20" s="12" t="str">
+        <f>H19 &amp; "-build-" &amp; J17</f>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5307-rt5</v>
+      </c>
+      <c r="I20" s="13"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G21" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G22" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H22" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I22" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="J21" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G22" s="10" t="s">
+      <c r="J22" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G23" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H22" s="10">
-        <v>9</v>
-      </c>
-      <c r="I22" s="10" t="str">
-        <f>I17</f>
-        <v>5206-rt5</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G23" s="11" t="s">
+      <c r="H23" s="10">
+        <v>10</v>
+      </c>
+      <c r="I23" s="10" t="str">
+        <f>J17</f>
+        <v>5307-rt5</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G24" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H23" s="16" t="str">
-        <f>H18</f>
+      <c r="H24" s="16" t="str">
+        <f>"Classic_Reimagined_10" &amp; G21</f>
         <v>Classic_Reimagined_10_SE_2</v>
-      </c>
-      <c r="I23" s="17"/>
-      <c r="J23" s="15"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G24" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" s="16" t="str">
-        <f>G22 &amp; "." &amp; H22 &amp; "-" &amp; H23</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2</v>
       </c>
       <c r="I24" s="17"/>
       <c r="J24" s="15"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G25" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="16" t="str">
+        <f>G23 &amp; "." &amp; H23 &amp; "-" &amp; H24</f>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2</v>
+      </c>
+      <c r="I25" s="17"/>
+      <c r="J25" s="15"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G26" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H25" s="16" t="str">
-        <f>H24 &amp; "-build-" &amp; I22</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5206-rt5</v>
-      </c>
-      <c r="I25" s="17"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G26" s="9" t="s">
+      <c r="H26" s="16" t="str">
+        <f>H25 &amp; "-build-" &amp; I23</f>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5307-rt5</v>
+      </c>
+      <c r="I26" s="17"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G27" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H27" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I26" s="9" t="s">
+      <c r="I27" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="J26" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G27" s="10" t="s">
+      <c r="J27" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G28" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H27" s="10">
-        <v>7</v>
-      </c>
-      <c r="I27" s="10" t="str">
-        <f>I22</f>
-        <v>5206-rt5</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G28" s="11" t="s">
+      <c r="H28" s="10">
+        <v>9</v>
+      </c>
+      <c r="I28" s="10" t="str">
+        <f>I23</f>
+        <v>5307-rt5</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G29" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H28" s="16" t="str">
-        <f>H23</f>
+      <c r="H29" s="16" t="str">
+        <f>H24</f>
         <v>Classic_Reimagined_10_SE_2</v>
-      </c>
-      <c r="I28" s="17"/>
-      <c r="J28" s="15"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G29" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29" s="16" t="str">
-        <f>G27 &amp; "." &amp; H27 &amp; "-" &amp; H28</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2</v>
       </c>
       <c r="I29" s="17"/>
       <c r="J29" s="15"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G30" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="16" t="str">
+        <f>G28 &amp; "." &amp; H28 &amp; "-" &amp; H29</f>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2</v>
+      </c>
+      <c r="I30" s="17"/>
+      <c r="J30" s="15"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G31" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H30" s="16" t="str">
-        <f>H29 &amp; "-build-" &amp; I27</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5206-rt5</v>
-      </c>
-      <c r="I30" s="17"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G31" s="9" t="s">
+      <c r="H31" s="16" t="str">
+        <f>H30 &amp; "-build-" &amp; I28</f>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5307-rt5</v>
+      </c>
+      <c r="I31" s="17"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G32" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="H32" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I31" s="9" t="s">
+      <c r="I32" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="J31" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G32" s="10" t="s">
+      <c r="J32" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G33" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H32" s="10">
-        <v>4</v>
-      </c>
-      <c r="I32" s="10" t="str">
-        <f>I27</f>
-        <v>5206-rt5</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G33" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H33" s="16" t="str">
-        <f>H28</f>
-        <v>Classic_Reimagined_10_SE_2</v>
-      </c>
-      <c r="I33" s="17"/>
-      <c r="J33" s="15"/>
+      <c r="H33" s="10">
+        <v>7</v>
+      </c>
+      <c r="I33" s="10" t="str">
+        <f>I28</f>
+        <v>5307-rt5</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="34" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G34" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H34" s="16" t="str">
-        <f>G32 &amp; "." &amp; H32 &amp; "-" &amp; H33</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2</v>
+        <f>H29</f>
+        <v>Classic_Reimagined_10_SE_2</v>
       </c>
       <c r="I34" s="17"/>
       <c r="J34" s="15"/>
     </row>
     <row r="35" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G35" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" s="16" t="str">
+        <f>G33 &amp; "." &amp; H33 &amp; "-" &amp; H34</f>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2</v>
+      </c>
+      <c r="I35" s="17"/>
+      <c r="J35" s="15"/>
+    </row>
+    <row r="36" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G36" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H35" s="16" t="str">
-        <f>H34 &amp; "-build-" &amp; I32</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5206-rt5</v>
-      </c>
-      <c r="I35" s="17"/>
-    </row>
-    <row r="36" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G36" s="8" t="s">
-        <v>22</v>
-      </c>
+      <c r="H36" s="16" t="str">
+        <f>H35 &amp; "-build-" &amp; I33</f>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5307-rt5</v>
+      </c>
+      <c r="I36" s="17"/>
     </row>
     <row r="37" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G37" s="9" t="s">
@@ -1292,14 +1298,14 @@
         <v>11</v>
       </c>
       <c r="H38" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I38" s="10" t="str">
-        <f>I32</f>
-        <v>5206-rt5</v>
+        <f>I33</f>
+        <v>5307-rt5</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="7:10" x14ac:dyDescent="0.3">
@@ -1307,8 +1313,8 @@
         <v>13</v>
       </c>
       <c r="H39" s="16" t="str">
-        <f>"Classic_Reimagined_10" &amp; G36</f>
-        <v>Classic_Reimagined_10_SE</v>
+        <f>H34</f>
+        <v>Classic_Reimagined_10_SE_2</v>
       </c>
       <c r="I39" s="17"/>
       <c r="J39" s="15"/>
@@ -1319,7 +1325,7 @@
       </c>
       <c r="H40" s="16" t="str">
         <f>G38 &amp; "." &amp; H38 &amp; "-" &amp; H39</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2</v>
       </c>
       <c r="I40" s="17"/>
       <c r="J40" s="15"/>
@@ -1330,13 +1336,13 @@
       </c>
       <c r="H41" s="16" t="str">
         <f>H40 &amp; "-build-" &amp; I38</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5206-rt5</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5307-rt5</v>
       </c>
       <c r="I41" s="17"/>
     </row>
     <row r="42" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G42" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="7:10" x14ac:dyDescent="0.3">
@@ -1358,22 +1364,23 @@
         <v>11</v>
       </c>
       <c r="H44" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I44" s="10" t="str">
         <f>I38</f>
-        <v>5206-rt5</v>
+        <v>5307-rt5</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G45" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H45" s="16" t="s">
-        <v>26</v>
+      <c r="H45" s="16" t="str">
+        <f>"Classic_Reimagined_10" &amp; G42</f>
+        <v>Classic_Reimagined_10_SE</v>
       </c>
       <c r="I45" s="17"/>
       <c r="J45" s="15"/>
@@ -1384,7 +1391,7 @@
       </c>
       <c r="H46" s="16" t="str">
         <f>G44 &amp; "." &amp; H44 &amp; "-" &amp; H45</f>
-        <v>v10.0.2-Classic_Reimagined_10s</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE</v>
       </c>
       <c r="I46" s="17"/>
       <c r="J46" s="15"/>
@@ -1395,13 +1402,13 @@
       </c>
       <c r="H47" s="16" t="str">
         <f>H46 &amp; "-build-" &amp; I44</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5206-rt5</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5307-rt5</v>
       </c>
       <c r="I47" s="17"/>
     </row>
     <row r="48" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G48" s="8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="7:10" x14ac:dyDescent="0.3">
@@ -1423,14 +1430,14 @@
         <v>11</v>
       </c>
       <c r="H50" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50" s="10" t="str">
         <f>I44</f>
-        <v>5206-rt5</v>
+        <v>5307-rt5</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="7:10" x14ac:dyDescent="0.3">
@@ -1438,7 +1445,7 @@
         <v>13</v>
       </c>
       <c r="H51" s="16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I51" s="17"/>
       <c r="J51" s="15"/>
@@ -1449,7 +1456,7 @@
       </c>
       <c r="H52" s="16" t="str">
         <f>G50 &amp; "." &amp; H50 &amp; "-" &amp; H51</f>
-        <v>v10.0.1-Classic_Reimagined_10</v>
+        <v>v10.0.2-Classic_Reimagined_10s</v>
       </c>
       <c r="I52" s="17"/>
       <c r="J52" s="15"/>
@@ -1460,82 +1467,82 @@
       </c>
       <c r="H53" s="16" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5206-rt5</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5307-rt5</v>
       </c>
       <c r="I53" s="17"/>
     </row>
     <row r="54" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G54" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
+      <c r="G54" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="55" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G55" s="8" t="s">
-        <v>31</v>
+      <c r="G55" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="J55" s="9" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G56" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H56" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I56" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="J56" s="9" t="s">
-        <v>4</v>
+      <c r="G56" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H56" s="10">
+        <v>1</v>
+      </c>
+      <c r="I56" s="10" t="str">
+        <f>I50</f>
+        <v>5307-rt5</v>
+      </c>
+      <c r="J56" s="10" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="57" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G57" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="H57" s="10">
-        <v>32</v>
-      </c>
-      <c r="I57" s="10" t="str">
-        <f>I50</f>
-        <v>5206-rt5</v>
-      </c>
-      <c r="J57" s="10" t="s">
-        <v>33</v>
-      </c>
+      <c r="G57" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H57" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="I57" s="17"/>
+      <c r="J57" s="15"/>
     </row>
     <row r="58" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G58" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H58" s="16" t="s">
-        <v>34</v>
+        <v>14</v>
+      </c>
+      <c r="H58" s="16" t="str">
+        <f>G56 &amp; "." &amp; H56 &amp; "-" &amp; H57</f>
+        <v>v10.0.1-Classic_Reimagined_10</v>
       </c>
       <c r="I58" s="17"/>
       <c r="J58" s="15"/>
     </row>
     <row r="59" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G59" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H59" s="16" t="str">
-        <f>G57 &amp; "." &amp; H57 &amp; "-" &amp; H58</f>
-        <v>v8.10.32-Classic_Reimagined_8</v>
+        <f>H58 &amp; "-build-" &amp; I56</f>
+        <v>v10.0.1-Classic_Reimagined_10-build-5307-rt5</v>
       </c>
       <c r="I59" s="17"/>
-      <c r="J59" s="15"/>
     </row>
     <row r="60" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G60" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H60" s="16" t="str">
-        <f>H59 &amp; "-build-" &amp; I57</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5206-rt5</v>
-      </c>
-      <c r="I60" s="17"/>
+      <c r="G60" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7"/>
     </row>
     <row r="61" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G61" s="8" t="s">
@@ -1561,14 +1568,14 @@
         <v>32</v>
       </c>
       <c r="H63" s="10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I63" s="10" t="str">
-        <f>I57</f>
-        <v>5206-rt5</v>
+        <f>I56</f>
+        <v>5307-rt5</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64" spans="7:10" x14ac:dyDescent="0.3">
@@ -1587,7 +1594,7 @@
       </c>
       <c r="H65" s="16" t="str">
         <f>G63 &amp; "." &amp; H63 &amp; "-" &amp; H64</f>
-        <v>v8.10.31-Classic_Reimagined_8</v>
+        <v>v8.10.32-Classic_Reimagined_8</v>
       </c>
       <c r="I65" s="17"/>
       <c r="J65" s="15"/>
@@ -1598,17 +1605,14 @@
       </c>
       <c r="H66" s="16" t="str">
         <f>H65 &amp; "-build-" &amp; I63</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5206-rt5</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5307-rt5</v>
       </c>
       <c r="I66" s="17"/>
     </row>
     <row r="67" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G67" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="H67" s="27"/>
-      <c r="I67" s="27"/>
-      <c r="J67" s="27"/>
+      <c r="G67" s="8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="68" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G68" s="9" t="s">
@@ -1626,17 +1630,17 @@
     </row>
     <row r="69" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G69" s="10" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H69" s="10">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="I69" s="10" t="str">
         <f>I63</f>
-        <v>5206-rt5</v>
+        <v>5307-rt5</v>
       </c>
       <c r="J69" s="10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" spans="7:10" x14ac:dyDescent="0.3">
@@ -1644,7 +1648,7 @@
         <v>13</v>
       </c>
       <c r="H70" s="16" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I70" s="17"/>
       <c r="J70" s="15"/>
@@ -1655,7 +1659,7 @@
       </c>
       <c r="H71" s="16" t="str">
         <f>G69 &amp; "." &amp; H69 &amp; "-" &amp; H70</f>
-        <v>v7.11.3-Better_Default_7</v>
+        <v>v8.10.31-Classic_Reimagined_8</v>
       </c>
       <c r="I71" s="17"/>
       <c r="J71" s="15"/>
@@ -1666,18 +1670,84 @@
       </c>
       <c r="H72" s="16" t="str">
         <f>H71 &amp; "-build-" &amp; I69</f>
-        <v>v7.11.3-Better_Default_7-build-5206-rt5</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5307-rt5</v>
       </c>
       <c r="I72" s="17"/>
+    </row>
+    <row r="73" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G73" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="H73" s="27"/>
+      <c r="I73" s="27"/>
+      <c r="J73" s="27"/>
+    </row>
+    <row r="74" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G74" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="J74" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G75" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H75" s="10">
+        <v>3</v>
+      </c>
+      <c r="I75" s="10" t="str">
+        <f>I69</f>
+        <v>5307-rt5</v>
+      </c>
+      <c r="J75" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="76" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G76" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H76" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="I76" s="17"/>
+      <c r="J76" s="15"/>
+    </row>
+    <row r="77" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G77" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H77" s="16" t="str">
+        <f>G75 &amp; "." &amp; H75 &amp; "-" &amp; H76</f>
+        <v>v7.11.3-Better_Default_7</v>
+      </c>
+      <c r="I77" s="17"/>
+      <c r="J77" s="15"/>
+    </row>
+    <row r="78" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G78" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" s="16" t="str">
+        <f>H77 &amp; "-build-" &amp; I75</f>
+        <v>v7.11.3-Better_Default_7-build-5307-rt5</v>
+      </c>
+      <c r="I78" s="17"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B4">
     <sortCondition descending="1" ref="A3:A4"/>
   </sortState>
-  <mergeCells count="3">
+  <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1693,12 +1763,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1737,21 +1807,21 @@
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="44"/>
+      <c r="C5" s="38"/>
       <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="43" t="str">
+      <c r="B6" s="37" t="str">
         <f>A4 &amp; "." &amp; B4 &amp; "." &amp; C4 &amp; "-" &amp; B5</f>
         <v>v6.0.7-Better_Default_6</v>
       </c>
-      <c r="C6" s="44"/>
+      <c r="C6" s="38"/>
       <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1791,21 +1861,21 @@
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="44"/>
+      <c r="C10" s="38"/>
       <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="43" t="str">
+      <c r="B11" s="37" t="str">
         <f>A9 &amp; "." &amp; B9 &amp; "." &amp; C9 &amp; "-" &amp; B10</f>
         <v>v1.4.0-Better_Default_5</v>
       </c>
-      <c r="C11" s="44"/>
+      <c r="C11" s="38"/>
       <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1845,21 +1915,21 @@
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="44"/>
+      <c r="C15" s="38"/>
       <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="43" t="str">
+      <c r="B16" s="37" t="str">
         <f>A14 &amp; "." &amp; B14 &amp; "." &amp; C14 &amp; "-" &amp; B15</f>
         <v>v1.3.0-Better_Default_4</v>
       </c>
-      <c r="C16" s="44"/>
+      <c r="C16" s="38"/>
       <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1899,21 +1969,21 @@
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="44"/>
+      <c r="C20" s="38"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="43" t="str">
+      <c r="B21" s="37" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
         <v>v1.2.2-Better_Default_3.1</v>
       </c>
-      <c r="C21" s="44"/>
+      <c r="C21" s="38"/>
       <c r="D21" s="5"/>
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1953,21 +2023,21 @@
       <c r="A25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="44"/>
+      <c r="C25" s="38"/>
       <c r="D25" s="5"/>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="43" t="str">
+      <c r="B26" s="37" t="str">
         <f>A24 &amp; "." &amp; B24 &amp; "." &amp; C24 &amp; "-" &amp; B25</f>
         <v>v1.2.1-Better_Default_3</v>
       </c>
-      <c r="C26" s="44"/>
+      <c r="C26" s="38"/>
       <c r="D26" s="5"/>
     </row>
     <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2007,21 +2077,21 @@
       <c r="A30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="43" t="s">
+      <c r="B30" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="44"/>
+      <c r="C30" s="38"/>
       <c r="D30" s="5"/>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="43" t="str">
+      <c r="B31" s="37" t="str">
         <f>A29 &amp; "." &amp; B29 &amp; "." &amp; C29 &amp; "-" &amp; B30</f>
         <v>v1.2.0-Better_Default_2</v>
       </c>
-      <c r="C31" s="44"/>
+      <c r="C31" s="38"/>
       <c r="D31" s="5"/>
     </row>
     <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2061,21 +2131,21 @@
       <c r="A35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="43" t="s">
+      <c r="B35" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="44"/>
+      <c r="C35" s="38"/>
       <c r="D35" s="5"/>
     </row>
     <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="43" t="str">
+      <c r="B36" s="37" t="str">
         <f>A34 &amp; "." &amp; B34 &amp; "." &amp; C34 &amp; "-" &amp; B35</f>
         <v>v1.1.1-Better_Default</v>
       </c>
-      <c r="C36" s="44"/>
+      <c r="C36" s="38"/>
       <c r="D36" s="5"/>
     </row>
     <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2115,21 +2185,21 @@
       <c r="A40" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="43" t="s">
+      <c r="B40" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="44"/>
+      <c r="C40" s="38"/>
       <c r="D40" s="5"/>
     </row>
     <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="43" t="str">
+      <c r="B41" s="37" t="str">
         <f>A39 &amp; "." &amp; B39 &amp; "." &amp; C39 &amp; "-" &amp; B40</f>
         <v>v1.1.0-Better_Default</v>
       </c>
-      <c r="C41" s="44"/>
+      <c r="C41" s="38"/>
       <c r="D41" s="5"/>
     </row>
   </sheetData>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2373F72D-9380-4E1C-9ECE-12673A8980BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990600E1-6878-4CBE-99FB-D615289399C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="78">
   <si>
     <t>Current version in development</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>Release year</t>
+  </si>
+  <si>
+    <t>Added 26.3 content</t>
   </si>
 </sst>
 </file>
@@ -520,6 +523,12 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -538,12 +547,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -743,13 +746,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="36"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="42"/>
       <c r="G1" s="30" t="s">
         <v>72</v>
       </c>
@@ -854,11 +857,11 @@
       <c r="K6" s="15"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="42"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="36"/>
       <c r="D7" s="9" t="s">
         <v>3</v>
       </c>
@@ -876,12 +879,12 @@
       <c r="J7" s="14"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="43" t="str">
-        <f>G17 &amp; "." &amp; H17 &amp; "_" &amp; I17 &amp; "-build-" &amp; D8</f>
-        <v>v10.0.11_1-build-5307-rt5</v>
-      </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="45"/>
+      <c r="A8" s="37" t="str">
+        <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D8</f>
+        <v>v10.0.11_3-build-5307-rt5</v>
+      </c>
+      <c r="B8" s="38"/>
+      <c r="C8" s="39"/>
       <c r="D8" s="10" t="str">
         <f>B6&amp;"-rt"&amp;B2</f>
         <v>5307-rt5</v>
@@ -1069,6 +1072,9 @@
       <c r="K18" s="15"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="G19" s="11" t="s">
         <v>14</v>
       </c>
@@ -1763,12 +1769,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1807,21 +1813,21 @@
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="38"/>
+      <c r="C5" s="44"/>
       <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="37" t="str">
+      <c r="B6" s="43" t="str">
         <f>A4 &amp; "." &amp; B4 &amp; "." &amp; C4 &amp; "-" &amp; B5</f>
         <v>v6.0.7-Better_Default_6</v>
       </c>
-      <c r="C6" s="38"/>
+      <c r="C6" s="44"/>
       <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1861,21 +1867,21 @@
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="37" t="s">
+      <c r="B10" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="38"/>
+      <c r="C10" s="44"/>
       <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="37" t="str">
+      <c r="B11" s="43" t="str">
         <f>A9 &amp; "." &amp; B9 &amp; "." &amp; C9 &amp; "-" &amp; B10</f>
         <v>v1.4.0-Better_Default_5</v>
       </c>
-      <c r="C11" s="38"/>
+      <c r="C11" s="44"/>
       <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1915,21 +1921,21 @@
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="38"/>
+      <c r="C15" s="44"/>
       <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="37" t="str">
+      <c r="B16" s="43" t="str">
         <f>A14 &amp; "." &amp; B14 &amp; "." &amp; C14 &amp; "-" &amp; B15</f>
         <v>v1.3.0-Better_Default_4</v>
       </c>
-      <c r="C16" s="38"/>
+      <c r="C16" s="44"/>
       <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1969,21 +1975,21 @@
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="38"/>
+      <c r="C20" s="44"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="37" t="str">
+      <c r="B21" s="43" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
         <v>v1.2.2-Better_Default_3.1</v>
       </c>
-      <c r="C21" s="38"/>
+      <c r="C21" s="44"/>
       <c r="D21" s="5"/>
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2023,21 +2029,21 @@
       <c r="A25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="37" t="s">
+      <c r="B25" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="38"/>
+      <c r="C25" s="44"/>
       <c r="D25" s="5"/>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="37" t="str">
+      <c r="B26" s="43" t="str">
         <f>A24 &amp; "." &amp; B24 &amp; "." &amp; C24 &amp; "-" &amp; B25</f>
         <v>v1.2.1-Better_Default_3</v>
       </c>
-      <c r="C26" s="38"/>
+      <c r="C26" s="44"/>
       <c r="D26" s="5"/>
     </row>
     <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2077,21 +2083,21 @@
       <c r="A30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="37" t="s">
+      <c r="B30" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="38"/>
+      <c r="C30" s="44"/>
       <c r="D30" s="5"/>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="37" t="str">
+      <c r="B31" s="43" t="str">
         <f>A29 &amp; "." &amp; B29 &amp; "." &amp; C29 &amp; "-" &amp; B30</f>
         <v>v1.2.0-Better_Default_2</v>
       </c>
-      <c r="C31" s="38"/>
+      <c r="C31" s="44"/>
       <c r="D31" s="5"/>
     </row>
     <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2131,21 +2137,21 @@
       <c r="A35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="37" t="s">
+      <c r="B35" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="38"/>
+      <c r="C35" s="44"/>
       <c r="D35" s="5"/>
     </row>
     <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="37" t="str">
+      <c r="B36" s="43" t="str">
         <f>A34 &amp; "." &amp; B34 &amp; "." &amp; C34 &amp; "-" &amp; B35</f>
         <v>v1.1.1-Better_Default</v>
       </c>
-      <c r="C36" s="38"/>
+      <c r="C36" s="44"/>
       <c r="D36" s="5"/>
     </row>
     <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2185,30 +2191,25 @@
       <c r="A40" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="37" t="s">
+      <c r="B40" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="38"/>
+      <c r="C40" s="44"/>
       <c r="D40" s="5"/>
     </row>
     <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="37" t="str">
+      <c r="B41" s="43" t="str">
         <f>A39 &amp; "." &amp; B39 &amp; "." &amp; C39 &amp; "-" &amp; B40</f>
         <v>v1.1.0-Better_Default</v>
       </c>
-      <c r="C41" s="38"/>
+      <c r="C41" s="44"/>
       <c r="D41" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2221,6 +2222,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990600E1-6878-4CBE-99FB-D615289399C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E270F9E-9662-428D-A70C-1FD6F16F5BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -500,18 +500,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -523,9 +511,6 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -545,6 +530,33 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -746,26 +758,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="42"/>
-      <c r="G1" s="30" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="33"/>
+      <c r="G1" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="32">
+      <c r="B2" s="26">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
@@ -773,10 +785,10 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="32">
+      <c r="B3" s="26">
         <v>3</v>
       </c>
       <c r="G3" s="9" t="s">
@@ -796,10 +808,10 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="32">
+      <c r="B4" s="26">
         <v>7</v>
       </c>
       <c r="G4" s="10" t="s">
@@ -820,10 +832,10 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="26">
         <v>2026</v>
       </c>
       <c r="G5" s="11" t="s">
@@ -838,10 +850,10 @@
       <c r="K5" s="15"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="27">
         <f>(B2*1000)+(B3*100)+B4+((B5-2026)*1000)</f>
         <v>5307</v>
       </c>
@@ -857,11 +869,11 @@
       <c r="K6" s="15"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="36"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="45"/>
       <c r="D7" s="9" t="s">
         <v>3</v>
       </c>
@@ -879,12 +891,12 @@
       <c r="J7" s="14"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="37" t="str">
+      <c r="A8" s="28" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D8</f>
         <v>v10.0.11_3-build-5307-rt5</v>
       </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="39"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="30"/>
       <c r="D8" s="10" t="str">
         <f>B6&amp;"-rt"&amp;B2</f>
         <v>5307-rt5</v>
@@ -901,14 +913,14 @@
       <c r="A9" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="23"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="39"/>
       <c r="G9" s="9" t="s">
         <v>2</v>
       </c>
@@ -929,11 +941,11 @@
       <c r="A10" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="26"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="42"/>
       <c r="G10" s="10" t="s">
         <v>11</v>
       </c>
@@ -1681,12 +1693,12 @@
       <c r="I72" s="17"/>
     </row>
     <row r="73" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G73" s="27" t="s">
+      <c r="G73" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="H73" s="27"/>
-      <c r="I73" s="27"/>
-      <c r="J73" s="27"/>
+      <c r="H73" s="21"/>
+      <c r="I73" s="21"/>
+      <c r="J73" s="21"/>
     </row>
     <row r="74" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G74" s="9" t="s">
@@ -1752,8 +1764,11 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B4">
     <sortCondition descending="1" ref="A3:A4"/>
   </sortState>
-  <mergeCells count="1">
+  <mergeCells count="4">
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="A7:C7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1769,12 +1784,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1813,21 +1828,21 @@
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="44"/>
+      <c r="C5" s="35"/>
       <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="43" t="str">
+      <c r="B6" s="34" t="str">
         <f>A4 &amp; "." &amp; B4 &amp; "." &amp; C4 &amp; "-" &amp; B5</f>
         <v>v6.0.7-Better_Default_6</v>
       </c>
-      <c r="C6" s="44"/>
+      <c r="C6" s="35"/>
       <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1867,21 +1882,21 @@
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="44"/>
+      <c r="C10" s="35"/>
       <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="43" t="str">
+      <c r="B11" s="34" t="str">
         <f>A9 &amp; "." &amp; B9 &amp; "." &amp; C9 &amp; "-" &amp; B10</f>
         <v>v1.4.0-Better_Default_5</v>
       </c>
-      <c r="C11" s="44"/>
+      <c r="C11" s="35"/>
       <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1921,21 +1936,21 @@
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="44"/>
+      <c r="C15" s="35"/>
       <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="43" t="str">
+      <c r="B16" s="34" t="str">
         <f>A14 &amp; "." &amp; B14 &amp; "." &amp; C14 &amp; "-" &amp; B15</f>
         <v>v1.3.0-Better_Default_4</v>
       </c>
-      <c r="C16" s="44"/>
+      <c r="C16" s="35"/>
       <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1975,21 +1990,21 @@
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="44"/>
+      <c r="C20" s="35"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="43" t="str">
+      <c r="B21" s="34" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
         <v>v1.2.2-Better_Default_3.1</v>
       </c>
-      <c r="C21" s="44"/>
+      <c r="C21" s="35"/>
       <c r="D21" s="5"/>
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2029,21 +2044,21 @@
       <c r="A25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="44"/>
+      <c r="C25" s="35"/>
       <c r="D25" s="5"/>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="43" t="str">
+      <c r="B26" s="34" t="str">
         <f>A24 &amp; "." &amp; B24 &amp; "." &amp; C24 &amp; "-" &amp; B25</f>
         <v>v1.2.1-Better_Default_3</v>
       </c>
-      <c r="C26" s="44"/>
+      <c r="C26" s="35"/>
       <c r="D26" s="5"/>
     </row>
     <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2083,21 +2098,21 @@
       <c r="A30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="43" t="s">
+      <c r="B30" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="44"/>
+      <c r="C30" s="35"/>
       <c r="D30" s="5"/>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="43" t="str">
+      <c r="B31" s="34" t="str">
         <f>A29 &amp; "." &amp; B29 &amp; "." &amp; C29 &amp; "-" &amp; B30</f>
         <v>v1.2.0-Better_Default_2</v>
       </c>
-      <c r="C31" s="44"/>
+      <c r="C31" s="35"/>
       <c r="D31" s="5"/>
     </row>
     <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2137,21 +2152,21 @@
       <c r="A35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="43" t="s">
+      <c r="B35" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="44"/>
+      <c r="C35" s="35"/>
       <c r="D35" s="5"/>
     </row>
     <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="43" t="str">
+      <c r="B36" s="34" t="str">
         <f>A34 &amp; "." &amp; B34 &amp; "." &amp; C34 &amp; "-" &amp; B35</f>
         <v>v1.1.1-Better_Default</v>
       </c>
-      <c r="C36" s="44"/>
+      <c r="C36" s="35"/>
       <c r="D36" s="5"/>
     </row>
     <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2191,25 +2206,30 @@
       <c r="A40" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="43" t="s">
+      <c r="B40" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="44"/>
+      <c r="C40" s="35"/>
       <c r="D40" s="5"/>
     </row>
     <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="43" t="str">
+      <c r="B41" s="34" t="str">
         <f>A39 &amp; "." &amp; B39 &amp; "." &amp; C39 &amp; "-" &amp; B40</f>
         <v>v1.1.0-Better_Default</v>
       </c>
-      <c r="C41" s="44"/>
+      <c r="C41" s="35"/>
       <c r="D41" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2222,11 +2242,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E270F9E-9662-428D-A70C-1FD6F16F5BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BFB7825-6E3F-42F8-B5DB-2B7950B9E675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="68">
   <si>
     <t>Current version in development</t>
   </si>
@@ -234,40 +234,10 @@
     <t>Base build</t>
   </si>
   <si>
-    <t>Added new sign textures</t>
-  </si>
-  <si>
-    <t>Added new bed textures</t>
-  </si>
-  <si>
-    <t>Removed unnecessary models</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimized resource pack </t>
-  </si>
-  <si>
-    <t>Updated small sulfur cube texture</t>
-  </si>
-  <si>
-    <t>Updated pack format to 88</t>
-  </si>
-  <si>
     <t>Classic Reimagined 11 version history</t>
   </si>
   <si>
-    <t>Updated bat model</t>
-  </si>
-  <si>
-    <t>Changed rabbit model</t>
-  </si>
-  <si>
-    <t>Changed sky orientation</t>
-  </si>
-  <si>
     <t>Release year</t>
-  </si>
-  <si>
-    <t>Added 26.3 content</t>
   </si>
 </sst>
 </file>
@@ -523,6 +493,33 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -530,33 +527,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -766,7 +736,7 @@
       <c r="D1" s="32"/>
       <c r="E1" s="33"/>
       <c r="G1" s="24" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
@@ -812,7 +782,7 @@
         <v>63</v>
       </c>
       <c r="B4" s="26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>11</v>
@@ -825,7 +795,7 @@
       </c>
       <c r="J4" s="10" t="str">
         <f>D8</f>
-        <v>5307-rt5</v>
+        <v>5308-rt5</v>
       </c>
       <c r="K4" s="10">
         <v>26.3</v>
@@ -833,7 +803,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="23" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B5" s="26">
         <v>2026</v>
@@ -855,7 +825,7 @@
       </c>
       <c r="B6" s="27">
         <f>(B2*1000)+(B3*100)+B4+((B5-2026)*1000)</f>
-        <v>5307</v>
+        <v>5308</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>14</v>
@@ -869,11 +839,11 @@
       <c r="K6" s="15"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="45"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="42"/>
       <c r="D7" s="9" t="s">
         <v>3</v>
       </c>
@@ -885,7 +855,7 @@
       </c>
       <c r="H7" s="12" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_3-Classic_Reimagined_11_SE_2.1-build-5307-rt5</v>
+        <v>v10.0.11_3-Classic_Reimagined_11_SE_2.1-build-5308-rt5</v>
       </c>
       <c r="I7" s="13"/>
       <c r="J7" s="14"/>
@@ -893,13 +863,13 @@
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="28" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D8</f>
-        <v>v10.0.11_3-build-5307-rt5</v>
+        <v>v10.0.11_3-build-5308-rt5</v>
       </c>
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="10" t="str">
         <f>B6&amp;"-rt"&amp;B2</f>
-        <v>5307-rt5</v>
+        <v>5308-rt5</v>
       </c>
       <c r="E8" s="19">
         <f>K10</f>
@@ -916,11 +886,11 @@
       <c r="B9" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="38"/>
-      <c r="E9" s="39"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="36"/>
       <c r="G9" s="9" t="s">
         <v>2</v>
       </c>
@@ -938,14 +908,11 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="41"/>
-      <c r="E10" s="42"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="39"/>
       <c r="G10" s="10" t="s">
         <v>11</v>
       </c>
@@ -957,16 +924,13 @@
       </c>
       <c r="J10" s="10" t="str">
         <f>J4</f>
-        <v>5307-rt5</v>
+        <v>5308-rt5</v>
       </c>
       <c r="K10" s="10">
         <v>26.2</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>66</v>
-      </c>
       <c r="G11" s="11" t="s">
         <v>13</v>
       </c>
@@ -979,9 +943,6 @@
       <c r="K11" s="15"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>69</v>
-      </c>
       <c r="G12" s="11" t="s">
         <v>14</v>
       </c>
@@ -994,23 +955,17 @@
       <c r="K12" s="15"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>68</v>
-      </c>
       <c r="G13" s="11" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="12" t="str">
         <f>H12 &amp; "-build-" &amp; J10</f>
-        <v>v10.0.11_2-Classic_Reimagined_11_SE_2.1-build-5307-rt5</v>
+        <v>v10.0.11_2-Classic_Reimagined_11_SE_2.1-build-5308-rt5</v>
       </c>
       <c r="I13" s="13"/>
       <c r="J13" s="14"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>70</v>
-      </c>
       <c r="G14" s="7" t="s">
         <v>1</v>
       </c>
@@ -1020,17 +975,11 @@
       <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>71</v>
-      </c>
       <c r="G15" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>73</v>
-      </c>
       <c r="G16" s="9" t="s">
         <v>2</v>
       </c>
@@ -1047,10 +996,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
-        <v>74</v>
-      </c>
+    <row r="17" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G17" s="10" t="s">
         <v>11</v>
       </c>
@@ -1062,16 +1008,13 @@
       </c>
       <c r="J17" s="10" t="str">
         <f>J10</f>
-        <v>5307-rt5</v>
+        <v>5308-rt5</v>
       </c>
       <c r="K17" s="10">
         <v>26.1</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>75</v>
-      </c>
+    <row r="18" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G18" s="11" t="s">
         <v>13</v>
       </c>
@@ -1083,10 +1026,7 @@
       <c r="J18" s="14"/>
       <c r="K18" s="15"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
-        <v>77</v>
-      </c>
+    <row r="19" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G19" s="11" t="s">
         <v>14</v>
       </c>
@@ -1098,23 +1038,23 @@
       <c r="J19" s="14"/>
       <c r="K19" s="15"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G20" s="11" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="12" t="str">
         <f>H19 &amp; "-build-" &amp; J17</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5307-rt5</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5308-rt5</v>
       </c>
       <c r="I20" s="13"/>
       <c r="J20" s="14"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G21" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G22" s="9" t="s">
         <v>17</v>
       </c>
@@ -1128,7 +1068,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G23" s="10" t="s">
         <v>11</v>
       </c>
@@ -1137,13 +1077,13 @@
       </c>
       <c r="I23" s="10" t="str">
         <f>J17</f>
-        <v>5307-rt5</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G24" s="11" t="s">
         <v>13</v>
       </c>
@@ -1154,7 +1094,7 @@
       <c r="I24" s="17"/>
       <c r="J24" s="15"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G25" s="11" t="s">
         <v>14</v>
       </c>
@@ -1165,17 +1105,17 @@
       <c r="I25" s="17"/>
       <c r="J25" s="15"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G26" s="11" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="16" t="str">
         <f>H25 &amp; "-build-" &amp; I23</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5307-rt5</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5308-rt5</v>
       </c>
       <c r="I26" s="17"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G27" s="9" t="s">
         <v>17</v>
       </c>
@@ -1189,7 +1129,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G28" s="10" t="s">
         <v>11</v>
       </c>
@@ -1198,13 +1138,13 @@
       </c>
       <c r="I28" s="10" t="str">
         <f>I23</f>
-        <v>5307-rt5</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J28" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G29" s="11" t="s">
         <v>13</v>
       </c>
@@ -1215,7 +1155,7 @@
       <c r="I29" s="17"/>
       <c r="J29" s="15"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G30" s="11" t="s">
         <v>14</v>
       </c>
@@ -1226,17 +1166,17 @@
       <c r="I30" s="17"/>
       <c r="J30" s="15"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G31" s="11" t="s">
         <v>15</v>
       </c>
       <c r="H31" s="16" t="str">
         <f>H30 &amp; "-build-" &amp; I28</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5307-rt5</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5308-rt5</v>
       </c>
       <c r="I31" s="17"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G32" s="9" t="s">
         <v>17</v>
       </c>
@@ -1259,7 +1199,7 @@
       </c>
       <c r="I33" s="10" t="str">
         <f>I28</f>
-        <v>5307-rt5</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J33" s="10" t="s">
         <v>20</v>
@@ -1293,7 +1233,7 @@
       </c>
       <c r="H36" s="16" t="str">
         <f>H35 &amp; "-build-" &amp; I33</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5307-rt5</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5308-rt5</v>
       </c>
       <c r="I36" s="17"/>
     </row>
@@ -1320,7 +1260,7 @@
       </c>
       <c r="I38" s="10" t="str">
         <f>I33</f>
-        <v>5307-rt5</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J38" s="10" t="s">
         <v>21</v>
@@ -1354,7 +1294,7 @@
       </c>
       <c r="H41" s="16" t="str">
         <f>H40 &amp; "-build-" &amp; I38</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5307-rt5</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5308-rt5</v>
       </c>
       <c r="I41" s="17"/>
     </row>
@@ -1386,7 +1326,7 @@
       </c>
       <c r="I44" s="10" t="str">
         <f>I38</f>
-        <v>5307-rt5</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J44" s="10" t="s">
         <v>23</v>
@@ -1420,7 +1360,7 @@
       </c>
       <c r="H47" s="16" t="str">
         <f>H46 &amp; "-build-" &amp; I44</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5307-rt5</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5308-rt5</v>
       </c>
       <c r="I47" s="17"/>
     </row>
@@ -1452,7 +1392,7 @@
       </c>
       <c r="I50" s="10" t="str">
         <f>I44</f>
-        <v>5307-rt5</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J50" s="10" t="s">
         <v>25</v>
@@ -1485,7 +1425,7 @@
       </c>
       <c r="H53" s="16" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5307-rt5</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5308-rt5</v>
       </c>
       <c r="I53" s="17"/>
     </row>
@@ -1517,7 +1457,7 @@
       </c>
       <c r="I56" s="10" t="str">
         <f>I50</f>
-        <v>5307-rt5</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J56" s="10" t="s">
         <v>28</v>
@@ -1550,7 +1490,7 @@
       </c>
       <c r="H59" s="16" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5307-rt5</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5308-rt5</v>
       </c>
       <c r="I59" s="17"/>
     </row>
@@ -1590,7 +1530,7 @@
       </c>
       <c r="I63" s="10" t="str">
         <f>I56</f>
-        <v>5307-rt5</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J63" s="10" t="s">
         <v>33</v>
@@ -1623,7 +1563,7 @@
       </c>
       <c r="H66" s="16" t="str">
         <f>H65 &amp; "-build-" &amp; I63</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5307-rt5</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5308-rt5</v>
       </c>
       <c r="I66" s="17"/>
     </row>
@@ -1655,7 +1595,7 @@
       </c>
       <c r="I69" s="10" t="str">
         <f>I63</f>
-        <v>5307-rt5</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J69" s="10" t="s">
         <v>35</v>
@@ -1688,7 +1628,7 @@
       </c>
       <c r="H72" s="16" t="str">
         <f>H71 &amp; "-build-" &amp; I69</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5307-rt5</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5308-rt5</v>
       </c>
       <c r="I72" s="17"/>
     </row>
@@ -1723,7 +1663,7 @@
       </c>
       <c r="I75" s="10" t="str">
         <f>I69</f>
-        <v>5307-rt5</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J75" s="10" t="s">
         <v>38</v>
@@ -1756,7 +1696,7 @@
       </c>
       <c r="H78" s="16" t="str">
         <f>H77 &amp; "-build-" &amp; I75</f>
-        <v>v7.11.3-Better_Default_7-build-5307-rt5</v>
+        <v>v7.11.3-Better_Default_7-build-5308-rt5</v>
       </c>
       <c r="I78" s="17"/>
     </row>
@@ -1784,12 +1724,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1828,21 +1768,21 @@
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="35"/>
+      <c r="C5" s="44"/>
       <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="34" t="str">
+      <c r="B6" s="43" t="str">
         <f>A4 &amp; "." &amp; B4 &amp; "." &amp; C4 &amp; "-" &amp; B5</f>
         <v>v6.0.7-Better_Default_6</v>
       </c>
-      <c r="C6" s="35"/>
+      <c r="C6" s="44"/>
       <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1882,21 +1822,21 @@
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="35"/>
+      <c r="C10" s="44"/>
       <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="34" t="str">
+      <c r="B11" s="43" t="str">
         <f>A9 &amp; "." &amp; B9 &amp; "." &amp; C9 &amp; "-" &amp; B10</f>
         <v>v1.4.0-Better_Default_5</v>
       </c>
-      <c r="C11" s="35"/>
+      <c r="C11" s="44"/>
       <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1936,21 +1876,21 @@
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="34" t="s">
+      <c r="B15" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="35"/>
+      <c r="C15" s="44"/>
       <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="34" t="str">
+      <c r="B16" s="43" t="str">
         <f>A14 &amp; "." &amp; B14 &amp; "." &amp; C14 &amp; "-" &amp; B15</f>
         <v>v1.3.0-Better_Default_4</v>
       </c>
-      <c r="C16" s="35"/>
+      <c r="C16" s="44"/>
       <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1990,21 +1930,21 @@
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="34" t="s">
+      <c r="B20" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="35"/>
+      <c r="C20" s="44"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="34" t="str">
+      <c r="B21" s="43" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
         <v>v1.2.2-Better_Default_3.1</v>
       </c>
-      <c r="C21" s="35"/>
+      <c r="C21" s="44"/>
       <c r="D21" s="5"/>
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2044,21 +1984,21 @@
       <c r="A25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="34" t="s">
+      <c r="B25" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="35"/>
+      <c r="C25" s="44"/>
       <c r="D25" s="5"/>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="34" t="str">
+      <c r="B26" s="43" t="str">
         <f>A24 &amp; "." &amp; B24 &amp; "." &amp; C24 &amp; "-" &amp; B25</f>
         <v>v1.2.1-Better_Default_3</v>
       </c>
-      <c r="C26" s="35"/>
+      <c r="C26" s="44"/>
       <c r="D26" s="5"/>
     </row>
     <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2098,21 +2038,21 @@
       <c r="A30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="34" t="s">
+      <c r="B30" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="35"/>
+      <c r="C30" s="44"/>
       <c r="D30" s="5"/>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="34" t="str">
+      <c r="B31" s="43" t="str">
         <f>A29 &amp; "." &amp; B29 &amp; "." &amp; C29 &amp; "-" &amp; B30</f>
         <v>v1.2.0-Better_Default_2</v>
       </c>
-      <c r="C31" s="35"/>
+      <c r="C31" s="44"/>
       <c r="D31" s="5"/>
     </row>
     <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2152,21 +2092,21 @@
       <c r="A35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="34" t="s">
+      <c r="B35" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="35"/>
+      <c r="C35" s="44"/>
       <c r="D35" s="5"/>
     </row>
     <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="34" t="str">
+      <c r="B36" s="43" t="str">
         <f>A34 &amp; "." &amp; B34 &amp; "." &amp; C34 &amp; "-" &amp; B35</f>
         <v>v1.1.1-Better_Default</v>
       </c>
-      <c r="C36" s="35"/>
+      <c r="C36" s="44"/>
       <c r="D36" s="5"/>
     </row>
     <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2206,30 +2146,25 @@
       <c r="A40" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="34" t="s">
+      <c r="B40" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="35"/>
+      <c r="C40" s="44"/>
       <c r="D40" s="5"/>
     </row>
     <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="34" t="str">
+      <c r="B41" s="43" t="str">
         <f>A39 &amp; "." &amp; B39 &amp; "." &amp; C39 &amp; "-" &amp; B40</f>
         <v>v1.1.0-Better_Default</v>
       </c>
-      <c r="C41" s="35"/>
+      <c r="C41" s="44"/>
       <c r="D41" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2242,6 +2177,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BFB7825-6E3F-42F8-B5DB-2B7950B9E675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ADCB976-D1E5-413F-BBF9-843976E1AED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="70">
   <si>
     <t>Current version in development</t>
   </si>
@@ -238,6 +238,12 @@
   </si>
   <si>
     <t>Release year</t>
+  </si>
+  <si>
+    <t>Added 26.3+ shader support</t>
+  </si>
+  <si>
+    <t>Added leaf textures for Classic Reimagined 11</t>
   </si>
 </sst>
 </file>
@@ -481,9 +487,6 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -527,6 +530,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -728,13 +740,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="33"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="30"/>
       <c r="G1" s="24" t="s">
         <v>66</v>
       </c>
@@ -748,7 +760,7 @@
         <v>62</v>
       </c>
       <c r="B2" s="26">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>5</v>
@@ -795,7 +807,7 @@
       </c>
       <c r="J4" s="10" t="str">
         <f>D8</f>
-        <v>5308-rt5</v>
+        <v>5708-rt5.4</v>
       </c>
       <c r="K4" s="10">
         <v>26.3</v>
@@ -825,7 +837,7 @@
       </c>
       <c r="B6" s="27">
         <f>(B2*1000)+(B3*100)+B4+((B5-2026)*1000)</f>
-        <v>5308</v>
+        <v>5708</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>14</v>
@@ -839,11 +851,11 @@
       <c r="K6" s="15"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="42"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="39"/>
       <c r="D7" s="9" t="s">
         <v>3</v>
       </c>
@@ -855,21 +867,21 @@
       </c>
       <c r="H7" s="12" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_3-Classic_Reimagined_11_SE_2.1-build-5308-rt5</v>
+        <v>v10.0.11_3-Classic_Reimagined_11_SE_2.1-build-5708-rt5.4</v>
       </c>
       <c r="I7" s="13"/>
       <c r="J7" s="14"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="28" t="str">
+      <c r="A8" s="43" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D8</f>
-        <v>v10.0.11_3-build-5308-rt5</v>
-      </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="30"/>
+        <v>v10.0.11_3-build-5708-rt5.4</v>
+      </c>
+      <c r="B8" s="44"/>
+      <c r="C8" s="45"/>
       <c r="D8" s="10" t="str">
         <f>B6&amp;"-rt"&amp;B2</f>
-        <v>5308-rt5</v>
+        <v>5708-rt5.4</v>
       </c>
       <c r="E8" s="19">
         <f>K10</f>
@@ -886,11 +898,11 @@
       <c r="B9" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="35"/>
-      <c r="E9" s="36"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="33"/>
       <c r="G9" s="9" t="s">
         <v>2</v>
       </c>
@@ -908,11 +920,14 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C10" s="37" t="s">
+      <c r="A10" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="38"/>
-      <c r="E10" s="39"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="36"/>
       <c r="G10" s="10" t="s">
         <v>11</v>
       </c>
@@ -924,13 +939,16 @@
       </c>
       <c r="J10" s="10" t="str">
         <f>J4</f>
-        <v>5308-rt5</v>
+        <v>5708-rt5.4</v>
       </c>
       <c r="K10" s="10">
         <v>26.2</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>69</v>
+      </c>
       <c r="G11" s="11" t="s">
         <v>13</v>
       </c>
@@ -960,7 +978,7 @@
       </c>
       <c r="H13" s="12" t="str">
         <f>H12 &amp; "-build-" &amp; J10</f>
-        <v>v10.0.11_2-Classic_Reimagined_11_SE_2.1-build-5308-rt5</v>
+        <v>v10.0.11_2-Classic_Reimagined_11_SE_2.1-build-5708-rt5.4</v>
       </c>
       <c r="I13" s="13"/>
       <c r="J13" s="14"/>
@@ -1008,7 +1026,7 @@
       </c>
       <c r="J17" s="10" t="str">
         <f>J10</f>
-        <v>5308-rt5</v>
+        <v>5708-rt5.4</v>
       </c>
       <c r="K17" s="10">
         <v>26.1</v>
@@ -1044,7 +1062,7 @@
       </c>
       <c r="H20" s="12" t="str">
         <f>H19 &amp; "-build-" &amp; J17</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5308-rt5</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5708-rt5.4</v>
       </c>
       <c r="I20" s="13"/>
       <c r="J20" s="14"/>
@@ -1077,7 +1095,7 @@
       </c>
       <c r="I23" s="10" t="str">
         <f>J17</f>
-        <v>5308-rt5</v>
+        <v>5708-rt5.4</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>18</v>
@@ -1111,7 +1129,7 @@
       </c>
       <c r="H26" s="16" t="str">
         <f>H25 &amp; "-build-" &amp; I23</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5308-rt5</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5708-rt5.4</v>
       </c>
       <c r="I26" s="17"/>
     </row>
@@ -1138,7 +1156,7 @@
       </c>
       <c r="I28" s="10" t="str">
         <f>I23</f>
-        <v>5308-rt5</v>
+        <v>5708-rt5.4</v>
       </c>
       <c r="J28" s="10" t="s">
         <v>19</v>
@@ -1172,7 +1190,7 @@
       </c>
       <c r="H31" s="16" t="str">
         <f>H30 &amp; "-build-" &amp; I28</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5308-rt5</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5708-rt5.4</v>
       </c>
       <c r="I31" s="17"/>
     </row>
@@ -1199,7 +1217,7 @@
       </c>
       <c r="I33" s="10" t="str">
         <f>I28</f>
-        <v>5308-rt5</v>
+        <v>5708-rt5.4</v>
       </c>
       <c r="J33" s="10" t="s">
         <v>20</v>
@@ -1233,7 +1251,7 @@
       </c>
       <c r="H36" s="16" t="str">
         <f>H35 &amp; "-build-" &amp; I33</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5308-rt5</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5708-rt5.4</v>
       </c>
       <c r="I36" s="17"/>
     </row>
@@ -1260,7 +1278,7 @@
       </c>
       <c r="I38" s="10" t="str">
         <f>I33</f>
-        <v>5308-rt5</v>
+        <v>5708-rt5.4</v>
       </c>
       <c r="J38" s="10" t="s">
         <v>21</v>
@@ -1294,7 +1312,7 @@
       </c>
       <c r="H41" s="16" t="str">
         <f>H40 &amp; "-build-" &amp; I38</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5308-rt5</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5708-rt5.4</v>
       </c>
       <c r="I41" s="17"/>
     </row>
@@ -1326,7 +1344,7 @@
       </c>
       <c r="I44" s="10" t="str">
         <f>I38</f>
-        <v>5308-rt5</v>
+        <v>5708-rt5.4</v>
       </c>
       <c r="J44" s="10" t="s">
         <v>23</v>
@@ -1360,7 +1378,7 @@
       </c>
       <c r="H47" s="16" t="str">
         <f>H46 &amp; "-build-" &amp; I44</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5308-rt5</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5708-rt5.4</v>
       </c>
       <c r="I47" s="17"/>
     </row>
@@ -1392,7 +1410,7 @@
       </c>
       <c r="I50" s="10" t="str">
         <f>I44</f>
-        <v>5308-rt5</v>
+        <v>5708-rt5.4</v>
       </c>
       <c r="J50" s="10" t="s">
         <v>25</v>
@@ -1425,7 +1443,7 @@
       </c>
       <c r="H53" s="16" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5308-rt5</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5708-rt5.4</v>
       </c>
       <c r="I53" s="17"/>
     </row>
@@ -1457,7 +1475,7 @@
       </c>
       <c r="I56" s="10" t="str">
         <f>I50</f>
-        <v>5308-rt5</v>
+        <v>5708-rt5.4</v>
       </c>
       <c r="J56" s="10" t="s">
         <v>28</v>
@@ -1490,7 +1508,7 @@
       </c>
       <c r="H59" s="16" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5308-rt5</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5708-rt5.4</v>
       </c>
       <c r="I59" s="17"/>
     </row>
@@ -1530,7 +1548,7 @@
       </c>
       <c r="I63" s="10" t="str">
         <f>I56</f>
-        <v>5308-rt5</v>
+        <v>5708-rt5.4</v>
       </c>
       <c r="J63" s="10" t="s">
         <v>33</v>
@@ -1563,7 +1581,7 @@
       </c>
       <c r="H66" s="16" t="str">
         <f>H65 &amp; "-build-" &amp; I63</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5308-rt5</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5708-rt5.4</v>
       </c>
       <c r="I66" s="17"/>
     </row>
@@ -1595,7 +1613,7 @@
       </c>
       <c r="I69" s="10" t="str">
         <f>I63</f>
-        <v>5308-rt5</v>
+        <v>5708-rt5.4</v>
       </c>
       <c r="J69" s="10" t="s">
         <v>35</v>
@@ -1628,7 +1646,7 @@
       </c>
       <c r="H72" s="16" t="str">
         <f>H71 &amp; "-build-" &amp; I69</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5308-rt5</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5708-rt5.4</v>
       </c>
       <c r="I72" s="17"/>
     </row>
@@ -1663,7 +1681,7 @@
       </c>
       <c r="I75" s="10" t="str">
         <f>I69</f>
-        <v>5308-rt5</v>
+        <v>5708-rt5.4</v>
       </c>
       <c r="J75" s="10" t="s">
         <v>38</v>
@@ -1696,7 +1714,7 @@
       </c>
       <c r="H78" s="16" t="str">
         <f>H77 &amp; "-build-" &amp; I75</f>
-        <v>v7.11.3-Better_Default_7-build-5308-rt5</v>
+        <v>v7.11.3-Better_Default_7-build-5708-rt5.4</v>
       </c>
       <c r="I78" s="17"/>
     </row>
@@ -1704,11 +1722,12 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B4">
     <sortCondition descending="1" ref="A3:A4"/>
   </sortState>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1724,12 +1743,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1768,21 +1787,21 @@
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="44"/>
+      <c r="C5" s="41"/>
       <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="43" t="str">
+      <c r="B6" s="40" t="str">
         <f>A4 &amp; "." &amp; B4 &amp; "." &amp; C4 &amp; "-" &amp; B5</f>
         <v>v6.0.7-Better_Default_6</v>
       </c>
-      <c r="C6" s="44"/>
+      <c r="C6" s="41"/>
       <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1822,21 +1841,21 @@
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="44"/>
+      <c r="C10" s="41"/>
       <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="43" t="str">
+      <c r="B11" s="40" t="str">
         <f>A9 &amp; "." &amp; B9 &amp; "." &amp; C9 &amp; "-" &amp; B10</f>
         <v>v1.4.0-Better_Default_5</v>
       </c>
-      <c r="C11" s="44"/>
+      <c r="C11" s="41"/>
       <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1876,21 +1895,21 @@
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="44"/>
+      <c r="C15" s="41"/>
       <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="43" t="str">
+      <c r="B16" s="40" t="str">
         <f>A14 &amp; "." &amp; B14 &amp; "." &amp; C14 &amp; "-" &amp; B15</f>
         <v>v1.3.0-Better_Default_4</v>
       </c>
-      <c r="C16" s="44"/>
+      <c r="C16" s="41"/>
       <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1930,21 +1949,21 @@
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="44"/>
+      <c r="C20" s="41"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="43" t="str">
+      <c r="B21" s="40" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
         <v>v1.2.2-Better_Default_3.1</v>
       </c>
-      <c r="C21" s="44"/>
+      <c r="C21" s="41"/>
       <c r="D21" s="5"/>
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1984,21 +2003,21 @@
       <c r="A25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="44"/>
+      <c r="C25" s="41"/>
       <c r="D25" s="5"/>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="43" t="str">
+      <c r="B26" s="40" t="str">
         <f>A24 &amp; "." &amp; B24 &amp; "." &amp; C24 &amp; "-" &amp; B25</f>
         <v>v1.2.1-Better_Default_3</v>
       </c>
-      <c r="C26" s="44"/>
+      <c r="C26" s="41"/>
       <c r="D26" s="5"/>
     </row>
     <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2038,21 +2057,21 @@
       <c r="A30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="43" t="s">
+      <c r="B30" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="44"/>
+      <c r="C30" s="41"/>
       <c r="D30" s="5"/>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="43" t="str">
+      <c r="B31" s="40" t="str">
         <f>A29 &amp; "." &amp; B29 &amp; "." &amp; C29 &amp; "-" &amp; B30</f>
         <v>v1.2.0-Better_Default_2</v>
       </c>
-      <c r="C31" s="44"/>
+      <c r="C31" s="41"/>
       <c r="D31" s="5"/>
     </row>
     <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2092,21 +2111,21 @@
       <c r="A35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="43" t="s">
+      <c r="B35" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="44"/>
+      <c r="C35" s="41"/>
       <c r="D35" s="5"/>
     </row>
     <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="43" t="str">
+      <c r="B36" s="40" t="str">
         <f>A34 &amp; "." &amp; B34 &amp; "." &amp; C34 &amp; "-" &amp; B35</f>
         <v>v1.1.1-Better_Default</v>
       </c>
-      <c r="C36" s="44"/>
+      <c r="C36" s="41"/>
       <c r="D36" s="5"/>
     </row>
     <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2146,25 +2165,30 @@
       <c r="A40" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="43" t="s">
+      <c r="B40" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="44"/>
+      <c r="C40" s="41"/>
       <c r="D40" s="5"/>
     </row>
     <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="43" t="str">
+      <c r="B41" s="40" t="str">
         <f>A39 &amp; "." &amp; B39 &amp; "." &amp; C39 &amp; "-" &amp; B40</f>
         <v>v1.1.0-Better_Default</v>
       </c>
-      <c r="C41" s="44"/>
+      <c r="C41" s="41"/>
       <c r="D41" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2177,11 +2201,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ADCB976-D1E5-413F-BBF9-843976E1AED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA13F9E1-7780-4C71-A85F-204CC9B00098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="72">
   <si>
     <t>Current version in development</t>
   </si>
@@ -244,6 +244,12 @@
   </si>
   <si>
     <t>Added leaf textures for Classic Reimagined 11</t>
+  </si>
+  <si>
+    <t>Added shelf mushroom textures</t>
+  </si>
+  <si>
+    <t>Added shelf mushroom models</t>
   </si>
 </sst>
 </file>
@@ -523,6 +529,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -530,15 +545,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -873,12 +879,12 @@
       <c r="J7" s="14"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="43" t="str">
+      <c r="A8" s="40" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D8</f>
         <v>v10.0.11_3-build-5708-rt5.4</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="45"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="42"/>
       <c r="D8" s="10" t="str">
         <f>B6&amp;"-rt"&amp;B2</f>
         <v>5708-rt5.4</v>
@@ -961,6 +967,9 @@
       <c r="K11" s="15"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>71</v>
+      </c>
       <c r="G12" s="11" t="s">
         <v>14</v>
       </c>
@@ -973,6 +982,9 @@
       <c r="K12" s="15"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="G13" s="11" t="s">
         <v>15</v>
       </c>
@@ -1743,12 +1755,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1787,21 +1799,21 @@
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="41"/>
+      <c r="C5" s="44"/>
       <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="40" t="str">
+      <c r="B6" s="43" t="str">
         <f>A4 &amp; "." &amp; B4 &amp; "." &amp; C4 &amp; "-" &amp; B5</f>
         <v>v6.0.7-Better_Default_6</v>
       </c>
-      <c r="C6" s="41"/>
+      <c r="C6" s="44"/>
       <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1841,21 +1853,21 @@
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="41"/>
+      <c r="C10" s="44"/>
       <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="40" t="str">
+      <c r="B11" s="43" t="str">
         <f>A9 &amp; "." &amp; B9 &amp; "." &amp; C9 &amp; "-" &amp; B10</f>
         <v>v1.4.0-Better_Default_5</v>
       </c>
-      <c r="C11" s="41"/>
+      <c r="C11" s="44"/>
       <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1895,21 +1907,21 @@
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="41"/>
+      <c r="C15" s="44"/>
       <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="40" t="str">
+      <c r="B16" s="43" t="str">
         <f>A14 &amp; "." &amp; B14 &amp; "." &amp; C14 &amp; "-" &amp; B15</f>
         <v>v1.3.0-Better_Default_4</v>
       </c>
-      <c r="C16" s="41"/>
+      <c r="C16" s="44"/>
       <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -1949,21 +1961,21 @@
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="41"/>
+      <c r="C20" s="44"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="40" t="str">
+      <c r="B21" s="43" t="str">
         <f>A19 &amp; "." &amp; B19 &amp; "." &amp; C19 &amp; "-" &amp; B20</f>
         <v>v1.2.2-Better_Default_3.1</v>
       </c>
-      <c r="C21" s="41"/>
+      <c r="C21" s="44"/>
       <c r="D21" s="5"/>
     </row>
     <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2003,21 +2015,21 @@
       <c r="A25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="41"/>
+      <c r="C25" s="44"/>
       <c r="D25" s="5"/>
     </row>
     <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="40" t="str">
+      <c r="B26" s="43" t="str">
         <f>A24 &amp; "." &amp; B24 &amp; "." &amp; C24 &amp; "-" &amp; B25</f>
         <v>v1.2.1-Better_Default_3</v>
       </c>
-      <c r="C26" s="41"/>
+      <c r="C26" s="44"/>
       <c r="D26" s="5"/>
     </row>
     <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2057,21 +2069,21 @@
       <c r="A30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="40" t="s">
+      <c r="B30" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="41"/>
+      <c r="C30" s="44"/>
       <c r="D30" s="5"/>
     </row>
     <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="40" t="str">
+      <c r="B31" s="43" t="str">
         <f>A29 &amp; "." &amp; B29 &amp; "." &amp; C29 &amp; "-" &amp; B30</f>
         <v>v1.2.0-Better_Default_2</v>
       </c>
-      <c r="C31" s="41"/>
+      <c r="C31" s="44"/>
       <c r="D31" s="5"/>
     </row>
     <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2111,21 +2123,21 @@
       <c r="A35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="40" t="s">
+      <c r="B35" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="41"/>
+      <c r="C35" s="44"/>
       <c r="D35" s="5"/>
     </row>
     <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="40" t="str">
+      <c r="B36" s="43" t="str">
         <f>A34 &amp; "." &amp; B34 &amp; "." &amp; C34 &amp; "-" &amp; B35</f>
         <v>v1.1.1-Better_Default</v>
       </c>
-      <c r="C36" s="41"/>
+      <c r="C36" s="44"/>
       <c r="D36" s="5"/>
     </row>
     <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
@@ -2165,30 +2177,25 @@
       <c r="A40" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="40" t="s">
+      <c r="B40" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="41"/>
+      <c r="C40" s="44"/>
       <c r="D40" s="5"/>
     </row>
     <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="40" t="str">
+      <c r="B41" s="43" t="str">
         <f>A39 &amp; "." &amp; B39 &amp; "." &amp; C39 &amp; "-" &amp; B40</f>
         <v>v1.1.0-Better_Default</v>
       </c>
-      <c r="C41" s="41"/>
+      <c r="C41" s="44"/>
       <c r="D41" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2201,6 +2208,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA13F9E1-7780-4C71-A85F-204CC9B00098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A7DF4B-1013-4691-B740-55DF6C4C9E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -766,7 +766,7 @@
         <v>62</v>
       </c>
       <c r="B2" s="26">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>5</v>
@@ -813,7 +813,7 @@
       </c>
       <c r="J4" s="10" t="str">
         <f>D8</f>
-        <v>5708-rt5.4</v>
+        <v>5308-rt5</v>
       </c>
       <c r="K4" s="10">
         <v>26.3</v>
@@ -843,7 +843,7 @@
       </c>
       <c r="B6" s="27">
         <f>(B2*1000)+(B3*100)+B4+((B5-2026)*1000)</f>
-        <v>5708</v>
+        <v>5308</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>14</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="H7" s="12" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_3-Classic_Reimagined_11_SE_2.1-build-5708-rt5.4</v>
+        <v>v10.0.11_3-Classic_Reimagined_11_SE_2.1-build-5308-rt5</v>
       </c>
       <c r="I7" s="13"/>
       <c r="J7" s="14"/>
@@ -881,13 +881,13 @@
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="40" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D8</f>
-        <v>v10.0.11_3-build-5708-rt5.4</v>
+        <v>v10.0.11_3-build-5308-rt5</v>
       </c>
       <c r="B8" s="41"/>
       <c r="C8" s="42"/>
       <c r="D8" s="10" t="str">
         <f>B6&amp;"-rt"&amp;B2</f>
-        <v>5708-rt5.4</v>
+        <v>5308-rt5</v>
       </c>
       <c r="E8" s="19">
         <f>K10</f>
@@ -945,7 +945,7 @@
       </c>
       <c r="J10" s="10" t="str">
         <f>J4</f>
-        <v>5708-rt5.4</v>
+        <v>5308-rt5</v>
       </c>
       <c r="K10" s="10">
         <v>26.2</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="H13" s="12" t="str">
         <f>H12 &amp; "-build-" &amp; J10</f>
-        <v>v10.0.11_2-Classic_Reimagined_11_SE_2.1-build-5708-rt5.4</v>
+        <v>v10.0.11_2-Classic_Reimagined_11_SE_2.1-build-5308-rt5</v>
       </c>
       <c r="I13" s="13"/>
       <c r="J13" s="14"/>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="J17" s="10" t="str">
         <f>J10</f>
-        <v>5708-rt5.4</v>
+        <v>5308-rt5</v>
       </c>
       <c r="K17" s="10">
         <v>26.1</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="H20" s="12" t="str">
         <f>H19 &amp; "-build-" &amp; J17</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5708-rt5.4</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5308-rt5</v>
       </c>
       <c r="I20" s="13"/>
       <c r="J20" s="14"/>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I23" s="10" t="str">
         <f>J17</f>
-        <v>5708-rt5.4</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>18</v>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H26" s="16" t="str">
         <f>H25 &amp; "-build-" &amp; I23</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5708-rt5.4</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5308-rt5</v>
       </c>
       <c r="I26" s="17"/>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="I28" s="10" t="str">
         <f>I23</f>
-        <v>5708-rt5.4</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J28" s="10" t="s">
         <v>19</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H31" s="16" t="str">
         <f>H30 &amp; "-build-" &amp; I28</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5708-rt5.4</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5308-rt5</v>
       </c>
       <c r="I31" s="17"/>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I33" s="10" t="str">
         <f>I28</f>
-        <v>5708-rt5.4</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J33" s="10" t="s">
         <v>20</v>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="H36" s="16" t="str">
         <f>H35 &amp; "-build-" &amp; I33</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5708-rt5.4</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5308-rt5</v>
       </c>
       <c r="I36" s="17"/>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="I38" s="10" t="str">
         <f>I33</f>
-        <v>5708-rt5.4</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J38" s="10" t="s">
         <v>21</v>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H41" s="16" t="str">
         <f>H40 &amp; "-build-" &amp; I38</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5708-rt5.4</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5308-rt5</v>
       </c>
       <c r="I41" s="17"/>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="I44" s="10" t="str">
         <f>I38</f>
-        <v>5708-rt5.4</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J44" s="10" t="s">
         <v>23</v>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="H47" s="16" t="str">
         <f>H46 &amp; "-build-" &amp; I44</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5708-rt5.4</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-5308-rt5</v>
       </c>
       <c r="I47" s="17"/>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="I50" s="10" t="str">
         <f>I44</f>
-        <v>5708-rt5.4</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J50" s="10" t="s">
         <v>25</v>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="H53" s="16" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5708-rt5.4</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-5308-rt5</v>
       </c>
       <c r="I53" s="17"/>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="I56" s="10" t="str">
         <f>I50</f>
-        <v>5708-rt5.4</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J56" s="10" t="s">
         <v>28</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="H59" s="16" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5708-rt5.4</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-5308-rt5</v>
       </c>
       <c r="I59" s="17"/>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="I63" s="10" t="str">
         <f>I56</f>
-        <v>5708-rt5.4</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J63" s="10" t="s">
         <v>33</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="H66" s="16" t="str">
         <f>H65 &amp; "-build-" &amp; I63</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5708-rt5.4</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-5308-rt5</v>
       </c>
       <c r="I66" s="17"/>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="I69" s="10" t="str">
         <f>I63</f>
-        <v>5708-rt5.4</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J69" s="10" t="s">
         <v>35</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="H72" s="16" t="str">
         <f>H71 &amp; "-build-" &amp; I69</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5708-rt5.4</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-5308-rt5</v>
       </c>
       <c r="I72" s="17"/>
     </row>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="I75" s="10" t="str">
         <f>I69</f>
-        <v>5708-rt5.4</v>
+        <v>5308-rt5</v>
       </c>
       <c r="J75" s="10" t="s">
         <v>38</v>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="H78" s="16" t="str">
         <f>H77 &amp; "-build-" &amp; I75</f>
-        <v>v7.11.3-Better_Default_7-build-5708-rt5.4</v>
+        <v>v7.11.3-Better_Default_7-build-5308-rt5</v>
       </c>
       <c r="I78" s="17"/>
     </row>
@@ -2196,6 +2196,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2208,11 +2213,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A7DF4B-1013-4691-B740-55DF6C4C9E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D503B18-8514-4A87-98DF-A2E142D27EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="73">
   <si>
     <t>Current version in development</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>Added shelf mushroom models</t>
+  </si>
+  <si>
+    <t>Added cushion textures</t>
   </si>
 </sst>
 </file>
@@ -996,6 +999,9 @@
       <c r="J13" s="14"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="G14" s="7" t="s">
         <v>1</v>
       </c>
@@ -2196,11 +2202,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2213,6 +2214,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D503B18-8514-4A87-98DF-A2E142D27EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE53206-2808-4306-9CDF-C5D9345E964B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="74">
   <si>
     <t>Current version in development</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>Added cushion textures</t>
+  </si>
+  <si>
+    <t>Added straw bed textures</t>
   </si>
 </sst>
 </file>
@@ -956,7 +959,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>13</v>
@@ -971,7 +974,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>14</v>
@@ -986,7 +989,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>15</v>
@@ -1000,7 +1003,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>1</v>
@@ -1011,6 +1014,9 @@
       <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="G15" s="8" t="s">
         <v>5</v>
       </c>
@@ -1737,8 +1743,8 @@
       <c r="I78" s="17"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B4">
-    <sortCondition descending="1" ref="A3:A4"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:A15">
+    <sortCondition ref="A15"/>
   </sortState>
   <mergeCells count="5">
     <mergeCell ref="A1:E1"/>
@@ -2202,6 +2208,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2214,11 +2225,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE53206-2808-4306-9CDF-C5D9345E964B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E11ADD-1A8E-4578-B026-32D5BFE5BA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="75">
   <si>
     <t>Current version in development</t>
   </si>
@@ -256,6 +256,9 @@
   </si>
   <si>
     <t>Added straw bed textures</t>
+  </si>
+  <si>
+    <t>Updated ultrarealistic fog shaders</t>
   </si>
 </sst>
 </file>
@@ -1022,6 +1025,9 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="G16" s="9" t="s">
         <v>2</v>
       </c>
@@ -2208,11 +2214,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2225,6 +2226,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E11ADD-1A8E-4578-B026-32D5BFE5BA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796E6E14-E0E0-46CB-90BB-3E6C11F884FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="78">
   <si>
     <t>Current version in development</t>
   </si>
@@ -243,9 +243,6 @@
     <t>Added 26.3+ shader support</t>
   </si>
   <si>
-    <t>Added leaf textures for Classic Reimagined 11</t>
-  </si>
-  <si>
     <t>Added shelf mushroom textures</t>
   </si>
   <si>
@@ -259,6 +256,18 @@
   </si>
   <si>
     <t>Updated ultrarealistic fog shaders</t>
+  </si>
+  <si>
+    <t>Updated fog model for Classic Reimagined 11</t>
+  </si>
+  <si>
+    <t>Changed leaf textures for Classic Reimagined 11</t>
+  </si>
+  <si>
+    <t>Updated fire textures</t>
+  </si>
+  <si>
+    <t>Updated soul fire textures</t>
   </si>
 </sst>
 </file>
@@ -775,7 +784,7 @@
         <v>62</v>
       </c>
       <c r="B2" s="26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>5</v>
@@ -822,7 +831,7 @@
       </c>
       <c r="J4" s="10" t="str">
         <f>D8</f>
-        <v>5308-rt5</v>
+        <v>6308-rt6</v>
       </c>
       <c r="K4" s="10">
         <v>26.3</v>
@@ -852,7 +861,7 @@
       </c>
       <c r="B6" s="27">
         <f>(B2*1000)+(B3*100)+B4+((B5-2026)*1000)</f>
-        <v>5308</v>
+        <v>6308</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>14</v>
@@ -882,7 +891,7 @@
       </c>
       <c r="H7" s="12" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_3-Classic_Reimagined_11_SE_2.1-build-5308-rt5</v>
+        <v>v10.0.11_3-Classic_Reimagined_11_SE_2.1-build-6308-rt6</v>
       </c>
       <c r="I7" s="13"/>
       <c r="J7" s="14"/>
@@ -890,13 +899,13 @@
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="40" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D8</f>
-        <v>v10.0.11_3-build-5308-rt5</v>
+        <v>v10.0.11_3-build-6308-rt6</v>
       </c>
       <c r="B8" s="41"/>
       <c r="C8" s="42"/>
       <c r="D8" s="10" t="str">
         <f>B6&amp;"-rt"&amp;B2</f>
-        <v>5308-rt5</v>
+        <v>6308-rt6</v>
       </c>
       <c r="E8" s="19">
         <f>K10</f>
@@ -954,7 +963,7 @@
       </c>
       <c r="J10" s="10" t="str">
         <f>J4</f>
-        <v>5308-rt5</v>
+        <v>6308-rt6</v>
       </c>
       <c r="K10" s="10">
         <v>26.2</v>
@@ -962,7 +971,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>13</v>
@@ -977,7 +986,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>14</v>
@@ -992,21 +1001,21 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="12" t="str">
         <f>H12 &amp; "-build-" &amp; J10</f>
-        <v>v10.0.11_2-Classic_Reimagined_11_SE_2.1-build-5308-rt5</v>
+        <v>v10.0.11_2-Classic_Reimagined_11_SE_2.1-build-6308-rt6</v>
       </c>
       <c r="I13" s="13"/>
       <c r="J13" s="14"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>1</v>
@@ -1018,7 +1027,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>5</v>
@@ -1026,7 +1035,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>2</v>
@@ -1044,7 +1053,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="G17" s="10" t="s">
         <v>11</v>
       </c>
@@ -1056,13 +1068,16 @@
       </c>
       <c r="J17" s="10" t="str">
         <f>J10</f>
-        <v>5308-rt5</v>
+        <v>6308-rt6</v>
       </c>
       <c r="K17" s="10">
         <v>26.1</v>
       </c>
     </row>
-    <row r="18" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="G18" s="11" t="s">
         <v>13</v>
       </c>
@@ -1074,7 +1089,10 @@
       <c r="J18" s="14"/>
       <c r="K18" s="15"/>
     </row>
-    <row r="19" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="G19" s="11" t="s">
         <v>14</v>
       </c>
@@ -1086,23 +1104,23 @@
       <c r="J19" s="14"/>
       <c r="K19" s="15"/>
     </row>
-    <row r="20" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G20" s="11" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="12" t="str">
         <f>H19 &amp; "-build-" &amp; J17</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-5308-rt5</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-6308-rt6</v>
       </c>
       <c r="I20" s="13"/>
       <c r="J20" s="14"/>
     </row>
-    <row r="21" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G21" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G22" s="9" t="s">
         <v>17</v>
       </c>
@@ -1116,7 +1134,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G23" s="10" t="s">
         <v>11</v>
       </c>
@@ -1125,13 +1143,13 @@
       </c>
       <c r="I23" s="10" t="str">
         <f>J17</f>
-        <v>5308-rt5</v>
+        <v>6308-rt6</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G24" s="11" t="s">
         <v>13</v>
       </c>
@@ -1142,7 +1160,7 @@
       <c r="I24" s="17"/>
       <c r="J24" s="15"/>
     </row>
-    <row r="25" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G25" s="11" t="s">
         <v>14</v>
       </c>
@@ -1153,17 +1171,17 @@
       <c r="I25" s="17"/>
       <c r="J25" s="15"/>
     </row>
-    <row r="26" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G26" s="11" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="16" t="str">
         <f>H25 &amp; "-build-" &amp; I23</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-5308-rt5</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-6308-rt6</v>
       </c>
       <c r="I26" s="17"/>
     </row>
-    <row r="27" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G27" s="9" t="s">
         <v>17</v>
       </c>
@@ -1177,7 +1195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G28" s="10" t="s">
         <v>11</v>
       </c>
@@ -1186,13 +1204,13 @@
       </c>
       <c r="I28" s="10" t="str">
         <f>I23</f>
-        <v>5308-rt5</v>
+        <v>6308-rt6</v>
       </c>
       <c r="J28" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G29" s="11" t="s">
         <v>13</v>
       </c>
@@ -1203,7 +1221,7 @@
       <c r="I29" s="17"/>
       <c r="J29" s="15"/>
     </row>
-    <row r="30" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G30" s="11" t="s">
         <v>14</v>
       </c>
@@ -1214,17 +1232,17 @@
       <c r="I30" s="17"/>
       <c r="J30" s="15"/>
     </row>
-    <row r="31" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G31" s="11" t="s">
         <v>15</v>
       </c>
       <c r="H31" s="16" t="str">
         <f>H30 &amp; "-build-" &amp; I28</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-5308-rt5</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-6308-rt6</v>
       </c>
       <c r="I31" s="17"/>
     </row>
-    <row r="32" spans="7:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G32" s="9" t="s">
         <v>17</v>
       </c>
@@ -1247,7 +1265,7 @@
       </c>
       <c r="I33" s="10" t="str">
         <f>I28</f>
-        <v>5308-rt5</v>
+        <v>6308-rt6</v>
       </c>
       <c r="J33" s="10" t="s">
         <v>20</v>
@@ -1281,7 +1299,7 @@
       </c>
       <c r="H36" s="16" t="str">
         <f>H35 &amp; "-build-" &amp; I33</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-5308-rt5</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-6308-rt6</v>
       </c>
       <c r="I36" s="17"/>
     </row>
@@ -1308,7 +1326,7 @@
       </c>
       <c r="I38" s="10" t="str">
         <f>I33</f>
-        <v>5308-rt5</v>
+        <v>6308-rt6</v>
       </c>
       <c r="J38" s="10" t="s">
         <v>21</v>
@@ -1342,7 +1360,7 @@
       </c>
       <c r="H41" s="16" t="str">
         <f>H40 &amp; "-build-" &amp; I38</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-5308-rt5</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-6308-rt6</v>
       </c>
       <c r="I41" s="17"/>
     </row>
@@ -1374,7 +1392,7 @@
       </c>
       <c r="I44" s="10" t="str">
         <f>I38</f>
-        <v>5308-rt5</v>
+        <v>6308-rt6</v>
       </c>
       <c r="J44" s="10" t="s">
         <v>23</v>
@@ -1408,7 +1426,7 @@
       </c>
       <c r="H47" s="16" t="str">
         <f>H46 &amp; "-build-" &amp; I44</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-5308-rt5</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-6308-rt6</v>
       </c>
       <c r="I47" s="17"/>
     </row>
@@ -1440,7 +1458,7 @@
       </c>
       <c r="I50" s="10" t="str">
         <f>I44</f>
-        <v>5308-rt5</v>
+        <v>6308-rt6</v>
       </c>
       <c r="J50" s="10" t="s">
         <v>25</v>
@@ -1473,7 +1491,7 @@
       </c>
       <c r="H53" s="16" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-5308-rt5</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-6308-rt6</v>
       </c>
       <c r="I53" s="17"/>
     </row>
@@ -1505,7 +1523,7 @@
       </c>
       <c r="I56" s="10" t="str">
         <f>I50</f>
-        <v>5308-rt5</v>
+        <v>6308-rt6</v>
       </c>
       <c r="J56" s="10" t="s">
         <v>28</v>
@@ -1538,7 +1556,7 @@
       </c>
       <c r="H59" s="16" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-5308-rt5</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-6308-rt6</v>
       </c>
       <c r="I59" s="17"/>
     </row>
@@ -1578,7 +1596,7 @@
       </c>
       <c r="I63" s="10" t="str">
         <f>I56</f>
-        <v>5308-rt5</v>
+        <v>6308-rt6</v>
       </c>
       <c r="J63" s="10" t="s">
         <v>33</v>
@@ -1611,7 +1629,7 @@
       </c>
       <c r="H66" s="16" t="str">
         <f>H65 &amp; "-build-" &amp; I63</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-5308-rt5</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-6308-rt6</v>
       </c>
       <c r="I66" s="17"/>
     </row>
@@ -1643,7 +1661,7 @@
       </c>
       <c r="I69" s="10" t="str">
         <f>I63</f>
-        <v>5308-rt5</v>
+        <v>6308-rt6</v>
       </c>
       <c r="J69" s="10" t="s">
         <v>35</v>
@@ -1676,7 +1694,7 @@
       </c>
       <c r="H72" s="16" t="str">
         <f>H71 &amp; "-build-" &amp; I69</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-5308-rt5</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-6308-rt6</v>
       </c>
       <c r="I72" s="17"/>
     </row>
@@ -1711,7 +1729,7 @@
       </c>
       <c r="I75" s="10" t="str">
         <f>I69</f>
-        <v>5308-rt5</v>
+        <v>6308-rt6</v>
       </c>
       <c r="J75" s="10" t="s">
         <v>38</v>
@@ -1744,13 +1762,13 @@
       </c>
       <c r="H78" s="16" t="str">
         <f>H77 &amp; "-build-" &amp; I75</f>
-        <v>v7.11.3-Better_Default_7-build-5308-rt5</v>
+        <v>v7.11.3-Better_Default_7-build-6308-rt6</v>
       </c>
       <c r="I78" s="17"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:A15">
-    <sortCondition ref="A15"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:A19">
+    <sortCondition ref="A19"/>
   </sortState>
   <mergeCells count="5">
     <mergeCell ref="A1:E1"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796E6E14-E0E0-46CB-90BB-3E6C11F884FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D08716C-A2C0-466D-A2AB-C19899272303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="79">
   <si>
     <t>Current version in development</t>
   </si>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t>Updated soul fire textures</t>
+  </si>
+  <si>
+    <t>Added map items</t>
   </si>
 </sst>
 </file>
@@ -986,7 +989,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>14</v>
@@ -1001,7 +1004,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>15</v>
@@ -1015,7 +1018,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>1</v>
@@ -1027,7 +1030,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>5</v>
@@ -1035,7 +1038,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>2</v>
@@ -1055,7 +1058,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>11</v>
@@ -1076,7 +1079,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>13</v>
@@ -1091,7 +1094,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>14</v>
@@ -1105,6 +1108,9 @@
       <c r="K19" s="15"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="G20" s="11" t="s">
         <v>15</v>
       </c>
@@ -1767,8 +1773,8 @@
       <c r="I78" s="17"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:A19">
-    <sortCondition ref="A19"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:A20">
+    <sortCondition ref="A20"/>
   </sortState>
   <mergeCells count="5">
     <mergeCell ref="A1:E1"/>
@@ -2232,6 +2238,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2244,11 +2255,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/version_guide.xlsx
+++ b/version_guide.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\NeoBeta Remastered\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D08716C-A2C0-466D-A2AB-C19899272303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C798DFE-4E6F-4E7C-A387-2181CEFC12D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="521" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="71">
   <si>
     <t>Current version in development</t>
   </si>
@@ -240,37 +240,13 @@
     <t>Release year</t>
   </si>
   <si>
-    <t>Added 26.3+ shader support</t>
-  </si>
-  <si>
-    <t>Added shelf mushroom textures</t>
-  </si>
-  <si>
-    <t>Added shelf mushroom models</t>
-  </si>
-  <si>
-    <t>Added cushion textures</t>
-  </si>
-  <si>
-    <t>Added straw bed textures</t>
-  </si>
-  <si>
-    <t>Updated ultrarealistic fog shaders</t>
-  </si>
-  <si>
-    <t>Updated fog model for Classic Reimagined 11</t>
-  </si>
-  <si>
-    <t>Changed leaf textures for Classic Reimagined 11</t>
-  </si>
-  <si>
-    <t>Updated fire textures</t>
-  </si>
-  <si>
-    <t>Updated soul fire textures</t>
-  </si>
-  <si>
-    <t>Added map items</t>
+    <t>Added map textures</t>
+  </si>
+  <si>
+    <t>Updated fog shaders</t>
+  </si>
+  <si>
+    <t>Fixed texture sampling (26.3+ only)</t>
   </si>
 </sst>
 </file>
@@ -821,7 +797,7 @@
         <v>63</v>
       </c>
       <c r="B4" s="26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>11</v>
@@ -834,7 +810,7 @@
       </c>
       <c r="J4" s="10" t="str">
         <f>D8</f>
-        <v>6308-rt6</v>
+        <v>6309-rt6</v>
       </c>
       <c r="K4" s="10">
         <v>26.3</v>
@@ -864,7 +840,7 @@
       </c>
       <c r="B6" s="27">
         <f>(B2*1000)+(B3*100)+B4+((B5-2026)*1000)</f>
-        <v>6308</v>
+        <v>6309</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>14</v>
@@ -894,7 +870,7 @@
       </c>
       <c r="H7" s="12" t="str">
         <f>H6 &amp; "-build-" &amp; J4</f>
-        <v>v10.0.11_3-Classic_Reimagined_11_SE_2.1-build-6308-rt6</v>
+        <v>v10.0.11_3-Classic_Reimagined_11_SE_2.1-build-6309-rt6</v>
       </c>
       <c r="I7" s="13"/>
       <c r="J7" s="14"/>
@@ -902,13 +878,13 @@
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="40" t="str">
         <f>G4 &amp; "." &amp; H4 &amp; "_" &amp; I4 &amp; "-build-" &amp; D8</f>
-        <v>v10.0.11_3-build-6308-rt6</v>
+        <v>v10.0.11_3-build-6309-rt6</v>
       </c>
       <c r="B8" s="41"/>
       <c r="C8" s="42"/>
       <c r="D8" s="10" t="str">
         <f>B6&amp;"-rt"&amp;B2</f>
-        <v>6308-rt6</v>
+        <v>6309-rt6</v>
       </c>
       <c r="E8" s="19">
         <f>K10</f>
@@ -966,7 +942,7 @@
       </c>
       <c r="J10" s="10" t="str">
         <f>J4</f>
-        <v>6308-rt6</v>
+        <v>6309-rt6</v>
       </c>
       <c r="K10" s="10">
         <v>26.2</v>
@@ -974,7 +950,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>13</v>
@@ -989,7 +965,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>14</v>
@@ -1003,23 +979,17 @@
       <c r="K12" s="15"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>70</v>
-      </c>
       <c r="G13" s="11" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="12" t="str">
         <f>H12 &amp; "-build-" &amp; J10</f>
-        <v>v10.0.11_2-Classic_Reimagined_11_SE_2.1-build-6308-rt6</v>
+        <v>v10.0.11_2-Classic_Reimagined_11_SE_2.1-build-6309-rt6</v>
       </c>
       <c r="I13" s="13"/>
       <c r="J13" s="14"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>69</v>
-      </c>
       <c r="G14" s="7" t="s">
         <v>1</v>
       </c>
@@ -1029,17 +999,11 @@
       <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>72</v>
-      </c>
       <c r="G15" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>75</v>
-      </c>
       <c r="G16" s="9" t="s">
         <v>2</v>
       </c>
@@ -1056,10 +1020,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
-        <v>76</v>
-      </c>
+    <row r="17" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G17" s="10" t="s">
         <v>11</v>
       </c>
@@ -1071,16 +1032,13 @@
       </c>
       <c r="J17" s="10" t="str">
         <f>J10</f>
-        <v>6308-rt6</v>
+        <v>6309-rt6</v>
       </c>
       <c r="K17" s="10">
         <v>26.1</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>74</v>
-      </c>
+    <row r="18" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G18" s="11" t="s">
         <v>13</v>
       </c>
@@ -1092,10 +1050,7 @@
       <c r="J18" s="14"/>
       <c r="K18" s="15"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
-        <v>77</v>
-      </c>
+    <row r="19" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G19" s="11" t="s">
         <v>14</v>
       </c>
@@ -1107,26 +1062,23 @@
       <c r="J19" s="14"/>
       <c r="K19" s="15"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
-        <v>73</v>
-      </c>
+    <row r="20" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G20" s="11" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="12" t="str">
         <f>H19 &amp; "-build-" &amp; J17</f>
-        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-6308-rt6</v>
+        <v>v10.0.11_1-Classic_Reimagined_10_SE_2.1-build-6309-rt6</v>
       </c>
       <c r="I20" s="13"/>
       <c r="J20" s="14"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G21" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G22" s="9" t="s">
         <v>17</v>
       </c>
@@ -1140,7 +1092,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G23" s="10" t="s">
         <v>11</v>
       </c>
@@ -1149,13 +1101,13 @@
       </c>
       <c r="I23" s="10" t="str">
         <f>J17</f>
-        <v>6308-rt6</v>
+        <v>6309-rt6</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G24" s="11" t="s">
         <v>13</v>
       </c>
@@ -1166,7 +1118,7 @@
       <c r="I24" s="17"/>
       <c r="J24" s="15"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G25" s="11" t="s">
         <v>14</v>
       </c>
@@ -1177,17 +1129,17 @@
       <c r="I25" s="17"/>
       <c r="J25" s="15"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G26" s="11" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="16" t="str">
         <f>H25 &amp; "-build-" &amp; I23</f>
-        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-6308-rt6</v>
+        <v>v10.0.10-Classic_Reimagined_10_SE_2-build-6309-rt6</v>
       </c>
       <c r="I26" s="17"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G27" s="9" t="s">
         <v>17</v>
       </c>
@@ -1201,7 +1153,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G28" s="10" t="s">
         <v>11</v>
       </c>
@@ -1210,13 +1162,13 @@
       </c>
       <c r="I28" s="10" t="str">
         <f>I23</f>
-        <v>6308-rt6</v>
+        <v>6309-rt6</v>
       </c>
       <c r="J28" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G29" s="11" t="s">
         <v>13</v>
       </c>
@@ -1227,7 +1179,7 @@
       <c r="I29" s="17"/>
       <c r="J29" s="15"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G30" s="11" t="s">
         <v>14</v>
       </c>
@@ -1238,17 +1190,17 @@
       <c r="I30" s="17"/>
       <c r="J30" s="15"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G31" s="11" t="s">
         <v>15</v>
       </c>
       <c r="H31" s="16" t="str">
         <f>H30 &amp; "-build-" &amp; I28</f>
-        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-6308-rt6</v>
+        <v>v10.0.9-Classic_Reimagined_10_SE_2-build-6309-rt6</v>
       </c>
       <c r="I31" s="17"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G32" s="9" t="s">
         <v>17</v>
       </c>
@@ -1271,7 +1223,7 @@
       </c>
       <c r="I33" s="10" t="str">
         <f>I28</f>
-        <v>6308-rt6</v>
+        <v>6309-rt6</v>
       </c>
       <c r="J33" s="10" t="s">
         <v>20</v>
@@ -1305,7 +1257,7 @@
       </c>
       <c r="H36" s="16" t="str">
         <f>H35 &amp; "-build-" &amp; I33</f>
-        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-6308-rt6</v>
+        <v>v10.0.7-Classic_Reimagined_10_SE_2-build-6309-rt6</v>
       </c>
       <c r="I36" s="17"/>
     </row>
@@ -1332,7 +1284,7 @@
       </c>
       <c r="I38" s="10" t="str">
         <f>I33</f>
-        <v>6308-rt6</v>
+        <v>6309-rt6</v>
       </c>
       <c r="J38" s="10" t="s">
         <v>21</v>
@@ -1366,7 +1318,7 @@
       </c>
       <c r="H41" s="16" t="str">
         <f>H40 &amp; "-build-" &amp; I38</f>
-        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-6308-rt6</v>
+        <v>v10.0.4-Classic_Reimagined_10_SE_2-build-6309-rt6</v>
       </c>
       <c r="I41" s="17"/>
     </row>
@@ -1398,7 +1350,7 @@
       </c>
       <c r="I44" s="10" t="str">
         <f>I38</f>
-        <v>6308-rt6</v>
+        <v>6309-rt6</v>
       </c>
       <c r="J44" s="10" t="s">
         <v>23</v>
@@ -1432,7 +1384,7 @@
       </c>
       <c r="H47" s="16" t="str">
         <f>H46 &amp; "-build-" &amp; I44</f>
-        <v>v10.0.3-Classic_Reimagined_10_SE-build-6308-rt6</v>
+        <v>v10.0.3-Classic_Reimagined_10_SE-build-6309-rt6</v>
       </c>
       <c r="I47" s="17"/>
     </row>
@@ -1464,7 +1416,7 @@
       </c>
       <c r="I50" s="10" t="str">
         <f>I44</f>
-        <v>6308-rt6</v>
+        <v>6309-rt6</v>
       </c>
       <c r="J50" s="10" t="s">
         <v>25</v>
@@ -1497,7 +1449,7 @@
       </c>
       <c r="H53" s="16" t="str">
         <f>H52 &amp; "-build-" &amp; I50</f>
-        <v>v10.0.2-Classic_Reimagined_10s-build-6308-rt6</v>
+        <v>v10.0.2-Classic_Reimagined_10s-build-6309-rt6</v>
       </c>
       <c r="I53" s="17"/>
     </row>
@@ -1529,7 +1481,7 @@
       </c>
       <c r="I56" s="10" t="str">
         <f>I50</f>
-        <v>6308-rt6</v>
+        <v>6309-rt6</v>
       </c>
       <c r="J56" s="10" t="s">
         <v>28</v>
@@ -1562,7 +1514,7 @@
       </c>
       <c r="H59" s="16" t="str">
         <f>H58 &amp; "-build-" &amp; I56</f>
-        <v>v10.0.1-Classic_Reimagined_10-build-6308-rt6</v>
+        <v>v10.0.1-Classic_Reimagined_10-build-6309-rt6</v>
       </c>
       <c r="I59" s="17"/>
     </row>
@@ -1602,7 +1554,7 @@
       </c>
       <c r="I63" s="10" t="str">
         <f>I56</f>
-        <v>6308-rt6</v>
+        <v>6309-rt6</v>
       </c>
       <c r="J63" s="10" t="s">
         <v>33</v>
@@ -1635,7 +1587,7 @@
       </c>
       <c r="H66" s="16" t="str">
         <f>H65 &amp; "-build-" &amp; I63</f>
-        <v>v8.10.32-Classic_Reimagined_8-build-6308-rt6</v>
+        <v>v8.10.32-Classic_Reimagined_8-build-6309-rt6</v>
       </c>
       <c r="I66" s="17"/>
     </row>
@@ -1667,7 +1619,7 @@
       </c>
       <c r="I69" s="10" t="str">
         <f>I63</f>
-        <v>6308-rt6</v>
+        <v>6309-rt6</v>
       </c>
       <c r="J69" s="10" t="s">
         <v>35</v>
@@ -1700,7 +1652,7 @@
       </c>
       <c r="H72" s="16" t="str">
         <f>H71 &amp; "-build-" &amp; I69</f>
-        <v>v8.10.31-Classic_Reimagined_8-build-6308-rt6</v>
+        <v>v8.10.31-Classic_Reimagined_8-build-6309-rt6</v>
       </c>
       <c r="I72" s="17"/>
     </row>
@@ -1735,7 +1687,7 @@
       </c>
       <c r="I75" s="10" t="str">
         <f>I69</f>
-        <v>6308-rt6</v>
+        <v>6309-rt6</v>
       </c>
       <c r="J75" s="10" t="s">
         <v>38</v>
@@ -1768,7 +1720,7 @@
       </c>
       <c r="H78" s="16" t="str">
         <f>H77 &amp; "-build-" &amp; I75</f>
-        <v>v7.11.3-Better_Default_7-build-6308-rt6</v>
+        <v>v7.11.3-Better_Default_7-build-6309-rt6</v>
       </c>
       <c r="I78" s="17"/>
     </row>
@@ -2238,11 +2190,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
@@ -2255,6 +2202,11 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
